--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -62871,7 +62871,7 @@
         <v>56962</v>
       </c>
       <c r="C2718" t="n">
-        <v>56.75</v>
+        <v>56.7999992370605</v>
       </c>
       <c r="D2718" t="n">
         <v>55.25</v>
@@ -62883,6 +62883,29 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>65823</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>56.0499992370605</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>54.3499984741211</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>56</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>54.7999992370605</v>
+      </c>
+      <c r="G2719" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>29653</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>56.1500015258789</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>56.1500015258789</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>49113</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>54.7000007629395</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>55.0499992370605</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>82466</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>56.9000015258789</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>57</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>57.9000015258789</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>64216</v>
+        <v>70205</v>
       </c>
       <c r="C2715" t="n">
+        <v>59.4500007629395</v>
+      </c>
+      <c r="D2715" t="n">
+        <v>56.9500007629395</v>
+      </c>
+      <c r="E2715" t="n">
+        <v>59.4500007629395</v>
+      </c>
+      <c r="F2715" t="n">
         <v>58</v>
-      </c>
-      <c r="D2715" t="n">
-        <v>56.4500007629395</v>
-      </c>
-      <c r="E2715" t="n">
-        <v>58</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>57.3499984741211</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>57145</v>
+        <v>64216</v>
       </c>
       <c r="C2716" t="n">
-        <v>57.1500015258789</v>
+        <v>58</v>
       </c>
       <c r="D2716" t="n">
-        <v>55.7999992370605</v>
+        <v>56.4500007629395</v>
       </c>
       <c r="E2716" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F2716" t="n">
-        <v>56.7000007629395</v>
+        <v>57.3499984741211</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>51580</v>
+        <v>57145</v>
       </c>
       <c r="C2717" t="n">
-        <v>56.6500015258789</v>
+        <v>57.1500015258789</v>
       </c>
       <c r="D2717" t="n">
-        <v>54.7999992370605</v>
+        <v>55.7999992370605</v>
       </c>
       <c r="E2717" t="n">
-        <v>56.25</v>
+        <v>57</v>
       </c>
       <c r="F2717" t="n">
-        <v>55.3499984741211</v>
+        <v>56.7000007629395</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>56962</v>
+        <v>51580</v>
       </c>
       <c r="C2718" t="n">
-        <v>56.7999992370605</v>
+        <v>56.6500015258789</v>
       </c>
       <c r="D2718" t="n">
-        <v>55.25</v>
+        <v>54.7999992370605</v>
       </c>
       <c r="E2718" t="n">
-        <v>55.25</v>
+        <v>56.25</v>
       </c>
       <c r="F2718" t="n">
-        <v>56.7999992370605</v>
+        <v>55.3499984741211</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>65823</v>
+        <v>56962</v>
       </c>
       <c r="C2719" t="n">
-        <v>56.0499992370605</v>
+        <v>56.7999992370605</v>
       </c>
       <c r="D2719" t="n">
-        <v>54.3499984741211</v>
+        <v>55.25</v>
       </c>
       <c r="E2719" t="n">
-        <v>56</v>
+        <v>55.25</v>
       </c>
       <c r="F2719" t="n">
-        <v>54.7999992370605</v>
+        <v>56.7999992370605</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>29653</v>
+        <v>65823</v>
       </c>
       <c r="C2720" t="n">
-        <v>56.1500015258789</v>
+        <v>56.0499992370605</v>
       </c>
       <c r="D2720" t="n">
-        <v>54.5</v>
+        <v>54.3499984741211</v>
       </c>
       <c r="E2720" t="n">
-        <v>54.5</v>
+        <v>56</v>
       </c>
       <c r="F2720" t="n">
-        <v>56.1500015258789</v>
+        <v>54.7999992370605</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>49113</v>
+        <v>29653</v>
       </c>
       <c r="C2721" t="n">
-        <v>56.5</v>
+        <v>56.1500015258789</v>
       </c>
       <c r="D2721" t="n">
-        <v>54.7000007629395</v>
+        <v>54.5</v>
       </c>
       <c r="E2721" t="n">
-        <v>56.5</v>
+        <v>54.5</v>
       </c>
       <c r="F2721" t="n">
-        <v>55.0499992370605</v>
+        <v>56.1500015258789</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>82466</v>
+        <v>49113</v>
       </c>
       <c r="C2722" t="n">
-        <v>58.5</v>
+        <v>56.5</v>
       </c>
       <c r="D2722" t="n">
-        <v>56.9000015258789</v>
+        <v>54.7000007629395</v>
       </c>
       <c r="E2722" t="n">
-        <v>57</v>
+        <v>56.5</v>
       </c>
       <c r="F2722" t="n">
-        <v>57.9000015258789</v>
+        <v>55.0499992370605</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>87525</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>56.7000007629395</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>57.0499992370605</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -421,7 +421,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>15.5902509689331</v>
+        <v>15.5902538299561</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7186403274536</v>
+        <v>15.7186393737793</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2234210968018</v>
+        <v>15.2234239578247</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>14.5356168746948</v>
+        <v>14.5356187820435</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>13.9395179748535</v>
+        <v>13.9395189285278</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G8" t="n">
-        <v>14.2880058288574</v>
+        <v>14.2880067825317</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="G9" t="n">
-        <v>14.040397644043</v>
+        <v>14.0403985977173</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G10" t="n">
-        <v>13.866153717041</v>
+        <v>13.8661527633667</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G11" t="n">
-        <v>13.1049814224243</v>
+        <v>13.1049823760986</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G12" t="n">
-        <v>12.793176651001</v>
+        <v>12.7931776046753</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G13" t="n">
-        <v>12.8848848342896</v>
+        <v>12.8848838806152</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G14" t="n">
-        <v>12.2887849807739</v>
+        <v>12.2887868881226</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>13.1324939727783</v>
+        <v>13.132493019104</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G19" t="n">
-        <v>16.3239116668701</v>
+        <v>16.3239097595215</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G20" t="n">
-        <v>16.0854721069336</v>
+        <v>16.0854740142822</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G21" t="n">
-        <v>16.3605937957764</v>
+        <v>16.360595703125</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G22" t="n">
-        <v>17.1125946044922</v>
+        <v>17.1125965118408</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>16.5990314483643</v>
+        <v>16.5990295410156</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G24" t="n">
-        <v>15.4710321426392</v>
+        <v>15.4710330963135</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G25" t="n">
-        <v>16.1038150787354</v>
+        <v>16.1038112640381</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G26" t="n">
-        <v>15.3059577941895</v>
+        <v>15.3059587478638</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G27" t="n">
-        <v>14.9391288757324</v>
+        <v>14.9391307830811</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G28" t="n">
-        <v>14.9482975006104</v>
+        <v>14.948299407959</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G30" t="n">
-        <v>15.1042013168335</v>
+        <v>15.1042022705078</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G31" t="n">
-        <v>15.003324508667</v>
+        <v>15.0033254623413</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>15.9112253189087</v>
+        <v>15.9112281799316</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G33" t="n">
-        <v>16.2322025299072</v>
+        <v>16.2322044372559</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G34" t="n">
-        <v>16.7641067504883</v>
+        <v>16.7641048431396</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>17.0575695037842</v>
+        <v>17.0575675964355</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G38" t="n">
-        <v>16.7090816497803</v>
+        <v>16.7090797424316</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G39" t="n">
-        <v>16.3605937957764</v>
+        <v>16.360595703125</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>16.3514232635498</v>
+        <v>16.3514251708984</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G41" t="n">
-        <v>16.1038150787354</v>
+        <v>16.1038112640381</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G42" t="n">
-        <v>16.342248916626</v>
+        <v>16.3422508239746</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>16.8283004760742</v>
+        <v>16.8282985687256</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>16.6357154846191</v>
+        <v>16.6357135772705</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G46" t="n">
-        <v>17.3051815032959</v>
+        <v>17.3051795959473</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G48" t="n">
-        <v>17.4335708618164</v>
+        <v>17.4335670471191</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G50" t="n">
-        <v>16.5348377227783</v>
+        <v>16.534839630127</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>17.5161075592041</v>
+        <v>17.5161056518555</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>16.8741569519043</v>
+        <v>16.8741550445557</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G55" t="n">
-        <v>17.2593269348145</v>
+        <v>17.2593231201172</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G56" t="n">
-        <v>17.4610843658447</v>
+        <v>17.4610805511475</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>17.0575695037842</v>
+        <v>17.0575675964355</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G59" t="n">
-        <v>17.0117168426514</v>
+        <v>17.0117130279541</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G61" t="n">
-        <v>16.5531787872314</v>
+        <v>16.5531768798828</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G63" t="n">
-        <v>16.9383506774902</v>
+        <v>16.9383525848389</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>16.7090816497803</v>
+        <v>16.7090797424316</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G66" t="n">
-        <v>16.5715179443359</v>
+        <v>16.5715198516846</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G67" t="n">
-        <v>16.5256652832031</v>
+        <v>16.5256633758545</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>18.6700000762939</v>
       </c>
       <c r="G68" t="n">
-        <v>17.1217632293701</v>
+        <v>17.1217651367188</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>19.75</v>
       </c>
       <c r="G73" t="n">
-        <v>18.1122035980225</v>
+        <v>18.1122055053711</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>18.0204982757568</v>
+        <v>18.0204944610596</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G76" t="n">
-        <v>17.5986423492432</v>
+        <v>17.5986442565918</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>20</v>
       </c>
       <c r="G77" t="n">
-        <v>18.3414707183838</v>
+        <v>18.3414726257324</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>20.0699996948242</v>
       </c>
       <c r="G78" t="n">
-        <v>18.405668258667</v>
+        <v>18.4056701660156</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G80" t="n">
-        <v>18.093864440918</v>
+        <v>18.0938625335693</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G81" t="n">
-        <v>18.3231296539307</v>
+        <v>18.3231315612793</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G82" t="n">
-        <v>18.0296669006348</v>
+        <v>18.0296688079834</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>17.8921051025391</v>
+        <v>17.8921031951904</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G87" t="n">
-        <v>17.1492767333984</v>
+        <v>17.1492805480957</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G88" t="n">
-        <v>17.4885921478271</v>
+        <v>17.4885940551758</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G90" t="n">
-        <v>17.0759143829346</v>
+        <v>17.0759124755859</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G92" t="n">
-        <v>16.8374729156494</v>
+        <v>16.8374710083008</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G94" t="n">
-        <v>16.3147430419922</v>
+        <v>16.3147411346436</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G96" t="n">
-        <v>16.2505474090576</v>
+        <v>16.2505435943604</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G97" t="n">
-        <v>16.7457675933838</v>
+        <v>16.7457656860352</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G100" t="n">
-        <v>16.1680088043213</v>
+        <v>16.1680068969727</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G101" t="n">
-        <v>16.3514232635498</v>
+        <v>16.3514251708984</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G102" t="n">
-        <v>16.7457675933838</v>
+        <v>16.7457656860352</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G104" t="n">
-        <v>17.3051815032959</v>
+        <v>17.3051795959473</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G105" t="n">
-        <v>17.1492767333984</v>
+        <v>17.1492805480957</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G107" t="n">
-        <v>16.4981536865234</v>
+        <v>16.4981555938721</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>17.2409820556641</v>
+        <v>17.2409858703613</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>17.0117168426514</v>
+        <v>17.0117130279541</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G110" t="n">
-        <v>16.993371963501</v>
+        <v>16.9933738708496</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G112" t="n">
-        <v>16.993371963501</v>
+        <v>16.9933738708496</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G115" t="n">
-        <v>15.8103466033936</v>
+        <v>15.8103513717651</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G116" t="n">
-        <v>15.8470306396484</v>
+        <v>15.8470315933228</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>17</v>
       </c>
       <c r="G117" t="n">
-        <v>15.5902509689331</v>
+        <v>15.5902538299561</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G118" t="n">
-        <v>14.9574718475342</v>
+        <v>14.9574708938599</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G120" t="n">
-        <v>15.0675182342529</v>
+        <v>15.0675201416016</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G121" t="n">
-        <v>15.3334674835205</v>
+        <v>15.3334693908691</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>17</v>
       </c>
       <c r="G122" t="n">
-        <v>15.5902509689331</v>
+        <v>15.5902538299561</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G123" t="n">
-        <v>15.9570827484131</v>
+        <v>15.9570808410645</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G124" t="n">
-        <v>14.9849834442139</v>
+        <v>14.9849843978882</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G126" t="n">
-        <v>14.8841037750244</v>
+        <v>14.8841028213501</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G129" t="n">
-        <v>15.406834602356</v>
+        <v>15.4068374633789</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>16.3899993896484</v>
       </c>
       <c r="G130" t="n">
-        <v>15.0308380126953</v>
+        <v>15.0308351516724</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G132" t="n">
-        <v>14.0037136077881</v>
+        <v>14.0037155151367</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>14.2604970932007</v>
+        <v>14.2604942321777</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G135" t="n">
-        <v>15.397665977478</v>
+        <v>15.3976669311523</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>15.315131187439</v>
+        <v>15.3151292800903</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>15.2234210968018</v>
+        <v>15.2234239578247</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G140" t="n">
-        <v>15.315131187439</v>
+        <v>15.3151292800903</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G141" t="n">
-        <v>15.2509336471558</v>
+        <v>15.2509346008301</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G142" t="n">
-        <v>15.3243007659912</v>
+        <v>15.3242998123169</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G143" t="n">
-        <v>15.2967882156372</v>
+        <v>15.2967863082886</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G144" t="n">
-        <v>15.3793258666992</v>
+        <v>15.3793277740479</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G149" t="n">
-        <v>16.1680088043213</v>
+        <v>16.1680068969727</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G151" t="n">
-        <v>15.6177654266357</v>
+        <v>15.6177663803101</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>15.2234210968018</v>
+        <v>15.2234239578247</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G155" t="n">
-        <v>15.8286914825439</v>
+        <v>15.8286933898926</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G156" t="n">
-        <v>16.0762996673584</v>
+        <v>16.076301574707</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G158" t="n">
-        <v>16.1771793365479</v>
+        <v>16.1771755218506</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G159" t="n">
-        <v>16.1038150787354</v>
+        <v>16.1038112640381</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G160" t="n">
-        <v>15.8470306396484</v>
+        <v>15.8470315933228</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G161" t="n">
-        <v>16.0671291351318</v>
+        <v>16.0671310424805</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G162" t="n">
-        <v>15.9845943450928</v>
+        <v>15.9845933914185</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G164" t="n">
-        <v>17.1401081085205</v>
+        <v>17.1401062011719</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G165" t="n">
-        <v>16.8099613189697</v>
+        <v>16.8099575042725</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G166" t="n">
-        <v>16.8099613189697</v>
+        <v>16.8099575042725</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>16.8741569519043</v>
+        <v>16.8741550445557</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G171" t="n">
-        <v>17.6078128814697</v>
+        <v>17.6078147888184</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>17.1492767333984</v>
+        <v>17.1492805480957</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G173" t="n">
-        <v>17.2409820556641</v>
+        <v>17.2409858703613</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>17.2409820556641</v>
+        <v>17.2409858703613</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G180" t="n">
-        <v>17.0300579071045</v>
+        <v>17.0300598144531</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G182" t="n">
-        <v>17.4610843658447</v>
+        <v>17.4610805511475</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>18.75</v>
       </c>
       <c r="G183" t="n">
-        <v>17.1951293945312</v>
+        <v>17.1951313018799</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>17.3326930999756</v>
+        <v>17.332691192627</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>17.0575695037842</v>
+        <v>17.0575675964355</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G186" t="n">
-        <v>16.7457675933838</v>
+        <v>16.7457656860352</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G188" t="n">
-        <v>17.0300579071045</v>
+        <v>17.0300598144531</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G189" t="n">
-        <v>16.7457675933838</v>
+        <v>16.7457656860352</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G191" t="n">
-        <v>15.7828340530396</v>
+        <v>15.7828369140625</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G192" t="n">
-        <v>15.7828340530396</v>
+        <v>15.7828369140625</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G193" t="n">
-        <v>15.7553243637085</v>
+        <v>15.7553253173828</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>17.25</v>
       </c>
       <c r="G194" t="n">
-        <v>15.8195199966431</v>
+        <v>15.8195209503174</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G195" t="n">
-        <v>15.8286914825439</v>
+        <v>15.8286933898926</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G196" t="n">
-        <v>15.9479093551636</v>
+        <v>15.9479074478149</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G197" t="n">
-        <v>15.8470306396484</v>
+        <v>15.8470315933228</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>15.6361064910889</v>
+        <v>15.6361026763916</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G201" t="n">
-        <v>15.5627403259277</v>
+        <v>15.5627374649048</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G202" t="n">
-        <v>15.4893732070923</v>
+        <v>15.489372253418</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G203" t="n">
-        <v>15.6085958480835</v>
+        <v>15.6085929870605</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>15.6361064910889</v>
+        <v>15.6361026763916</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G205" t="n">
-        <v>15.7553243637085</v>
+        <v>15.7553253173828</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>17.25</v>
       </c>
       <c r="G206" t="n">
-        <v>15.8195199966431</v>
+        <v>15.8195209503174</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G207" t="n">
-        <v>16.0304470062256</v>
+        <v>16.030445098877</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G209" t="n">
-        <v>16.6999073028564</v>
+        <v>16.6999111175537</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G210" t="n">
-        <v>16.0579605102539</v>
+        <v>16.0579566955566</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G212" t="n">
-        <v>15.5443983078003</v>
+        <v>15.5443954467773</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>17</v>
       </c>
       <c r="G214" t="n">
-        <v>15.5902509689331</v>
+        <v>15.5902538299561</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>15.5443983078003</v>
+        <v>15.5443954467773</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>15.406834602356</v>
+        <v>15.4068374633789</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>16.75</v>
       </c>
       <c r="G217" t="n">
-        <v>15.3609828948975</v>
+        <v>15.3609838485718</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G219" t="n">
-        <v>15.2330408096313</v>
+        <v>15.233039855957</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G220" t="n">
-        <v>15.3068504333496</v>
+        <v>15.3068513870239</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>15.5467443466187</v>
+        <v>15.54674243927</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G222" t="n">
-        <v>15.6297807693481</v>
+        <v>15.6297836303711</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G223" t="n">
-        <v>15.7866344451904</v>
+        <v>15.7866325378418</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G224" t="n">
-        <v>15.5190620422363</v>
+        <v>15.5190629959106</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G225" t="n">
-        <v>14.9746952056885</v>
+        <v>14.9746942520142</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G227" t="n">
-        <v>15.4175682067871</v>
+        <v>15.4175701141357</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G228" t="n">
-        <v>15.4083452224731</v>
+        <v>15.4083442687988</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G229" t="n">
-        <v>15.0577354431152</v>
+        <v>15.0577344894409</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G230" t="n">
-        <v>15.7589540481567</v>
+        <v>15.7589530944824</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G232" t="n">
-        <v>15.8235349655151</v>
+        <v>15.8235387802124</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>15.5006074905396</v>
+        <v>15.5006093978882</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G236" t="n">
-        <v>15.7774085998535</v>
+        <v>15.7774066925049</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G237" t="n">
-        <v>15.9434871673584</v>
+        <v>15.9434833526611</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G238" t="n">
-        <v>15.8235349655151</v>
+        <v>15.8235387802124</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>15.7312726974487</v>
+        <v>15.7312717437744</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G241" t="n">
-        <v>16.4693965911865</v>
+        <v>16.4693984985352</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G244" t="n">
-        <v>17.0229930877686</v>
+        <v>17.0229911804199</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G245" t="n">
-        <v>17.106029510498</v>
+        <v>17.1060314178467</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>18.25</v>
       </c>
       <c r="G247" t="n">
-        <v>16.8384590148926</v>
+        <v>16.8384628295898</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>16.9768600463867</v>
+        <v>16.9768581390381</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>16.7923278808594</v>
+        <v>16.7923316955566</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G251" t="n">
-        <v>17.0506706237793</v>
+        <v>17.0506687164307</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>17.6227188110352</v>
+        <v>17.6227149963379</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G253" t="n">
-        <v>17.7795677185059</v>
+        <v>17.7795696258545</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>17.6227188110352</v>
+        <v>17.6227149963379</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>19.25</v>
       </c>
       <c r="G256" t="n">
-        <v>17.7611141204834</v>
+        <v>17.761116027832</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G258" t="n">
-        <v>18.3054847717285</v>
+        <v>18.3054828643799</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>18.7760353088379</v>
+        <v>18.7760372161865</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>18.8221683502197</v>
+        <v>18.822172164917</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G262" t="n">
-        <v>19.4957046508789</v>
+        <v>19.4957084655762</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G264" t="n">
-        <v>18.7852649688721</v>
+        <v>18.7852630615234</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>19.3296318054199</v>
+        <v>19.3296298980713</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>19.0528335571289</v>
+        <v>19.0528316497803</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G270" t="n">
-        <v>18.8867530822754</v>
+        <v>18.8867511749268</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G271" t="n">
-        <v>18.8129405975342</v>
+        <v>18.8129425048828</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G272" t="n">
-        <v>18.8037147521973</v>
+        <v>18.8037166595459</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G273" t="n">
-        <v>18.6284141540527</v>
+        <v>18.6284103393555</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>20</v>
       </c>
       <c r="G275" t="n">
-        <v>18.453104019165</v>
+        <v>18.4531078338623</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>20</v>
       </c>
       <c r="G276" t="n">
-        <v>18.453104019165</v>
+        <v>18.4531078338623</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>20</v>
       </c>
       <c r="G281" t="n">
-        <v>18.453104019165</v>
+        <v>18.4531078338623</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>18.3608436584473</v>
+        <v>18.36083984375</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G286" t="n">
-        <v>18.203987121582</v>
+        <v>18.2039890289307</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>18.3608436584473</v>
+        <v>18.36083984375</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G288" t="n">
-        <v>18.3885231018066</v>
+        <v>18.388521194458</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G290" t="n">
-        <v>18.4992408752441</v>
+        <v>18.4992389678955</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>18.3608436584473</v>
+        <v>18.36083984375</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G292" t="n">
-        <v>18.6007308959961</v>
+        <v>18.6007328033447</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>20</v>
       </c>
       <c r="G294" t="n">
-        <v>18.453104019165</v>
+        <v>18.4531078338623</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>20.5</v>
       </c>
       <c r="G295" t="n">
-        <v>18.9144325256348</v>
+        <v>18.9144344329834</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>18.9974746704102</v>
+        <v>18.9974727630615</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>20.4099998474121</v>
       </c>
       <c r="G302" t="n">
-        <v>18.831392288208</v>
+        <v>18.8313941955566</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G303" t="n">
-        <v>19.1174182891846</v>
+        <v>19.1174201965332</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>21</v>
       </c>
       <c r="G304" t="n">
-        <v>19.3757629394531</v>
+        <v>19.3757610321045</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G305" t="n">
-        <v>18.9697933197021</v>
+        <v>18.9697914123535</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G307" t="n">
-        <v>19.1174182891846</v>
+        <v>19.1174201965332</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>20.8299999237061</v>
       </c>
       <c r="G308" t="n">
-        <v>19.2189121246338</v>
+        <v>19.2189064025879</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>20.4899997711182</v>
       </c>
       <c r="G309" t="n">
-        <v>18.9052066802979</v>
+        <v>18.9052104949951</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.0989646911621</v>
+        <v>19.0989665985107</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G311" t="n">
-        <v>19.2558135986328</v>
+        <v>19.2558174133301</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G312" t="n">
-        <v>19.1543235778809</v>
+        <v>19.1543254852295</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G315" t="n">
-        <v>20.2430591583252</v>
+        <v>20.2430572509766</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>20.7136173248291</v>
+        <v>20.7136135101318</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G318" t="n">
-        <v>20.8243312835693</v>
+        <v>20.8243293762207</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>20.8058776855469</v>
+        <v>20.8058795928955</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G321" t="n">
-        <v>20.473726272583</v>
+        <v>20.4737205505371</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>20.2522869110107</v>
+        <v>20.2522850036621</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>20.1138858795166</v>
+        <v>20.1138896942139</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G328" t="n">
-        <v>20.3630046844482</v>
+        <v>20.3630027770996</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>20.3906841278076</v>
+        <v>20.390682220459</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>22.2399997711182</v>
       </c>
       <c r="G330" t="n">
-        <v>20.5198554992676</v>
+        <v>20.5198516845703</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>20.3906841278076</v>
+        <v>20.390682220459</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G333" t="n">
-        <v>20.6767063140869</v>
+        <v>20.6767024993896</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G335" t="n">
-        <v>20.3168697357178</v>
+        <v>20.3168716430664</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G337" t="n">
-        <v>21.4978675842285</v>
+        <v>21.4978713989258</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G338" t="n">
-        <v>21.3502426147461</v>
+        <v>21.3502445220947</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>23</v>
       </c>
       <c r="G339" t="n">
-        <v>21.2210712432861</v>
+        <v>21.2210750579834</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>23</v>
       </c>
       <c r="G341" t="n">
-        <v>21.2210712432861</v>
+        <v>21.2210750579834</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>22.75</v>
       </c>
       <c r="G342" t="n">
-        <v>20.9904079437256</v>
+        <v>20.9904098510742</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G346" t="n">
-        <v>21.1288089752197</v>
+        <v>21.1288070678711</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>22.7199993133545</v>
       </c>
       <c r="G347" t="n">
-        <v>20.9627265930176</v>
+        <v>20.9627304077148</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G348" t="n">
-        <v>21.1288089752197</v>
+        <v>21.1288070678711</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>21.1288089752197</v>
+        <v>21.1288070678711</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G351" t="n">
-        <v>21.0826778411865</v>
+        <v>21.0826740264893</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G352" t="n">
-        <v>20.5013999938965</v>
+        <v>20.5014019012451</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G354" t="n">
-        <v>21.0273151397705</v>
+        <v>21.0273132324219</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G357" t="n">
-        <v>21.1103515625</v>
+        <v>21.1103534698486</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G358" t="n">
-        <v>21.1011295318604</v>
+        <v>21.1011276245117</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G359" t="n">
-        <v>21.1933898925781</v>
+        <v>21.1933917999268</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>22.9099998474121</v>
       </c>
       <c r="G361" t="n">
-        <v>21.1380348205566</v>
+        <v>21.138032913208</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G362" t="n">
-        <v>20.7136173248291</v>
+        <v>20.7136135101318</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>21.0365447998047</v>
+        <v>21.0365428924561</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G365" t="n">
-        <v>20.5936679840088</v>
+        <v>20.5936660766602</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>21.8700008392334</v>
       </c>
       <c r="G366" t="n">
-        <v>20.1784725189209</v>
+        <v>20.1784706115723</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G367" t="n">
-        <v>20.2615089416504</v>
+        <v>20.261510848999</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G369" t="n">
-        <v>20.5013999938965</v>
+        <v>20.5014019012451</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G370" t="n">
-        <v>20.1876945495605</v>
+        <v>20.1876983642578</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G371" t="n">
-        <v>20.4921741485596</v>
+        <v>20.4921760559082</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G372" t="n">
-        <v>20.5936679840088</v>
+        <v>20.5936660766602</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G373" t="n">
-        <v>20.1415672302246</v>
+        <v>20.141565322876</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G374" t="n">
-        <v>19.9109020233154</v>
+        <v>19.9109001159668</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G375" t="n">
-        <v>20.0769844055176</v>
+        <v>20.0769824981689</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>21.3099994659424</v>
       </c>
       <c r="G376" t="n">
-        <v>19.6617870330811</v>
+        <v>19.6617832183838</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G377" t="n">
-        <v>19.7725048065186</v>
+        <v>19.7725067138672</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G380" t="n">
-        <v>20.4091396331787</v>
+        <v>20.4091377258301</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>21.8700008392334</v>
       </c>
       <c r="G381" t="n">
-        <v>20.1784725189209</v>
+        <v>20.1784706115723</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>22</v>
       </c>
       <c r="G382" t="n">
-        <v>20.2984142303467</v>
+        <v>20.2984199523926</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>19.8186340332031</v>
+        <v>19.8186359405518</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>19.6986904144287</v>
+        <v>19.6986923217773</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G386" t="n">
-        <v>19.5879745483398</v>
+        <v>19.5879764556885</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>19.7909603118896</v>
+        <v>19.790958404541</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>19.9754867553711</v>
+        <v>19.9754848480225</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G391" t="n">
-        <v>19.5418395996094</v>
+        <v>19.541841506958</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>19.9754867553711</v>
+        <v>19.9754848480225</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>22.2399997711182</v>
       </c>
       <c r="G393" t="n">
-        <v>20.5198554992676</v>
+        <v>20.5198516845703</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G394" t="n">
-        <v>20.473726272583</v>
+        <v>20.4737205505371</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>22.25</v>
       </c>
       <c r="G395" t="n">
-        <v>20.5290813446045</v>
+        <v>20.5290832519531</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G396" t="n">
-        <v>20.0769844055176</v>
+        <v>20.0769824981689</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G397" t="n">
-        <v>20.2522869110107</v>
+        <v>20.2522850036621</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G400" t="n">
-        <v>19.7909603118896</v>
+        <v>19.790958404541</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G401" t="n">
-        <v>19.9109020233154</v>
+        <v>19.9109001159668</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G402" t="n">
-        <v>19.6986904144287</v>
+        <v>19.6986923217773</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>19.6986904144287</v>
+        <v>19.6986923217773</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G405" t="n">
-        <v>20.0769844055176</v>
+        <v>20.0769824981689</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G409" t="n">
-        <v>19.9939422607422</v>
+        <v>19.9939441680908</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>20.2522869110107</v>
+        <v>20.2522850036621</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G411" t="n">
-        <v>20.3537769317627</v>
+        <v>20.3537750244141</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G413" t="n">
-        <v>20.7043857574463</v>
+        <v>20.7043876647949</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G415" t="n">
-        <v>20.7043857574463</v>
+        <v>20.7043876647949</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G417" t="n">
-        <v>20.7505168914795</v>
+        <v>20.7505187988281</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G418" t="n">
-        <v>20.8243312835693</v>
+        <v>20.8243293762207</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>22.75</v>
       </c>
       <c r="G419" t="n">
-        <v>20.9904079437256</v>
+        <v>20.9904098510742</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>22.75</v>
       </c>
       <c r="G420" t="n">
-        <v>20.9904079437256</v>
+        <v>20.9904098510742</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G421" t="n">
-        <v>21.0549945831299</v>
+        <v>21.0549926757812</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>22.75</v>
       </c>
       <c r="G422" t="n">
-        <v>20.9904079437256</v>
+        <v>20.9904098510742</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>22.3099994659424</v>
       </c>
       <c r="G423" t="n">
-        <v>20.5844402313232</v>
+        <v>20.5844383239746</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G424" t="n">
-        <v>20.3353252410889</v>
+        <v>20.3353233337402</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>20.3906841278076</v>
+        <v>20.390682220459</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>20.1138858795166</v>
+        <v>20.1138896942139</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G428" t="n">
-        <v>20.1969261169434</v>
+        <v>20.1969299316406</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G429" t="n">
-        <v>20.1969261169434</v>
+        <v>20.1969299316406</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G430" t="n">
-        <v>20.2430591583252</v>
+        <v>20.2430572509766</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G432" t="n">
-        <v>20.2338333129883</v>
+        <v>20.2338352203369</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G433" t="n">
-        <v>19.9109020233154</v>
+        <v>19.9109001159668</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>19.7909603118896</v>
+        <v>19.790958404541</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G436" t="n">
-        <v>19.7079200744629</v>
+        <v>19.7079181671143</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G437" t="n">
-        <v>19.6341075897217</v>
+        <v>19.634105682373</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>19.3296318054199</v>
+        <v>19.3296298980713</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G441" t="n">
-        <v>19.9570350646973</v>
+        <v>19.9570369720459</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G445" t="n">
-        <v>20.3168697357178</v>
+        <v>20.3168716430664</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>20.3906841278076</v>
+        <v>20.390682220459</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>20.3906841278076</v>
+        <v>20.390682220459</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G452" t="n">
-        <v>20.3537769317627</v>
+        <v>20.3537750244141</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G453" t="n">
-        <v>19.4034442901611</v>
+        <v>19.4034423828125</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>19.0528335571289</v>
+        <v>19.0528316497803</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G456" t="n">
-        <v>19.0528335571289</v>
+        <v>19.0528316497803</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>20.5</v>
       </c>
       <c r="G457" t="n">
-        <v>18.9144325256348</v>
+        <v>18.9144344329834</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G458" t="n">
-        <v>18.9974746704102</v>
+        <v>18.9974727630615</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G460" t="n">
-        <v>18.8129405975342</v>
+        <v>18.8129425048828</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G461" t="n">
-        <v>18.7114524841309</v>
+        <v>18.7114486694336</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G462" t="n">
-        <v>18.5084629058838</v>
+        <v>18.5084667205811</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G463" t="n">
-        <v>18.8037147521973</v>
+        <v>18.8037166595459</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G464" t="n">
-        <v>18.8683052062988</v>
+        <v>18.8683013916016</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G465" t="n">
-        <v>18.5546016693115</v>
+        <v>18.5545997619629</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>18.3147106170654</v>
+        <v>18.3147087097168</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>20.25</v>
       </c>
       <c r="G469" t="n">
-        <v>18.6837730407715</v>
+        <v>18.6837692260742</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G471" t="n">
-        <v>19.0067024230957</v>
+        <v>19.0067005157471</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G472" t="n">
-        <v>18.8037147521973</v>
+        <v>18.8037166595459</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G473" t="n">
-        <v>18.8683052062988</v>
+        <v>18.8683013916016</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G474" t="n">
-        <v>18.849760055542</v>
+        <v>18.8497581481934</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G475" t="n">
-        <v>18.8219432830811</v>
+        <v>18.8219413757324</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G478" t="n">
-        <v>17.7834930419922</v>
+        <v>17.7834892272949</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G479" t="n">
-        <v>17.7278594970703</v>
+        <v>17.727855682373</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G480" t="n">
-        <v>17.5238780975342</v>
+        <v>17.5238761901855</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G481" t="n">
-        <v>17.5516929626465</v>
+        <v>17.5516948699951</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G483" t="n">
-        <v>17.7742195129395</v>
+        <v>17.7742176055908</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G486" t="n">
-        <v>18.3398036956787</v>
+        <v>18.3398017883301</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G488" t="n">
-        <v>18.2841720581055</v>
+        <v>18.2841701507568</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G489" t="n">
-        <v>18.2841720581055</v>
+        <v>18.2841701507568</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G490" t="n">
-        <v>18.0431003570557</v>
+        <v>18.0431022644043</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G492" t="n">
-        <v>18.367618560791</v>
+        <v>18.3676166534424</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>20</v>
       </c>
       <c r="G495" t="n">
-        <v>18.5437831878662</v>
+        <v>18.5437850952148</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>20</v>
       </c>
       <c r="G496" t="n">
-        <v>18.5437831878662</v>
+        <v>18.5437850952148</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G497" t="n">
-        <v>18.6457786560059</v>
+        <v>18.6457767486572</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G499" t="n">
-        <v>18.5623302459717</v>
+        <v>18.5623321533203</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G500" t="n">
-        <v>18.4881534576416</v>
+        <v>18.488151550293</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G501" t="n">
-        <v>18.2285404205322</v>
+        <v>18.2285423278809</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G502" t="n">
-        <v>18.2563571929932</v>
+        <v>18.2563591003418</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G503" t="n">
-        <v>18.3212604522705</v>
+        <v>18.3212623596191</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>18.3583469390869</v>
+        <v>18.3583450317383</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G506" t="n">
-        <v>18.5345134735107</v>
+        <v>18.5345115661621</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G507" t="n">
-        <v>18.5808753967285</v>
+        <v>18.5808734893799</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G508" t="n">
-        <v>18.469612121582</v>
+        <v>18.4696102142334</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G509" t="n">
-        <v>18.469612121582</v>
+        <v>18.4696102142334</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>18.2656288146973</v>
+        <v>18.2656307220459</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G511" t="n">
-        <v>18.367618560791</v>
+        <v>18.3676166534424</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>20.25</v>
       </c>
       <c r="G514" t="n">
-        <v>18.7755851745605</v>
+        <v>18.7755813598633</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G516" t="n">
-        <v>19.3318977355957</v>
+        <v>19.3318958282471</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>19.610050201416</v>
+        <v>19.6100540161133</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>22</v>
       </c>
       <c r="G518" t="n">
-        <v>20.3981609344482</v>
+        <v>20.3981647491455</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G520" t="n">
-        <v>21.4180717468262</v>
+        <v>21.4180736541748</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G522" t="n">
-        <v>21.371711730957</v>
+        <v>21.3717155456543</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>21.4644298553467</v>
+        <v>21.4644317626953</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G526" t="n">
-        <v>21.4180717468262</v>
+        <v>21.4180736541748</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>21.371711730957</v>
+        <v>21.3717155456543</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>21.4180717468262</v>
+        <v>21.4180736541748</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G531" t="n">
-        <v>21.6498680114746</v>
+        <v>21.6498699188232</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G533" t="n">
-        <v>21.371711730957</v>
+        <v>21.3717155456543</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>20.3054447174072</v>
+        <v>20.30544090271</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>20.9081172943115</v>
+        <v>20.9081153869629</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G541" t="n">
-        <v>20.3054447174072</v>
+        <v>20.30544090271</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>20.5836029052734</v>
+        <v>20.5836048126221</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G546" t="n">
-        <v>20.9081172943115</v>
+        <v>20.9081153869629</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>21.0471973419189</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G549" t="n">
-        <v>20.7226791381836</v>
+        <v>20.7226810455322</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>22</v>
       </c>
       <c r="G550" t="n">
-        <v>20.3981609344482</v>
+        <v>20.3981647491455</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>20.5372409820557</v>
+        <v>20.537239074707</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>22</v>
       </c>
       <c r="G552" t="n">
-        <v>20.3981609344482</v>
+        <v>20.3981647491455</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>21.4644298553467</v>
+        <v>21.4644317626953</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>22.0671043395996</v>
+        <v>22.0671005249023</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>21.7425880432129</v>
+        <v>21.7425899505615</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G561" t="n">
-        <v>21.371711730957</v>
+        <v>21.3717155456543</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>21.0471973419189</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>21.0471973419189</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>20.5836029052734</v>
+        <v>20.5836048126221</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>20.7226791381836</v>
+        <v>20.7226810455322</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>20.7226791381836</v>
+        <v>20.7226810455322</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>20.7226791381836</v>
+        <v>20.7226810455322</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>20.5372409820557</v>
+        <v>20.537239074707</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.0736465454102</v>
+        <v>20.0736484527588</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>20.0736465454102</v>
+        <v>20.0736484527588</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>20.7690410614014</v>
+        <v>20.7690372467041</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>21.0471973419189</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>21.0471973419189</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>20.7690410614014</v>
+        <v>20.7690372467041</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>20.444522857666</v>
+        <v>20.4445209503174</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G585" t="n">
-        <v>20.8154029846191</v>
+        <v>20.8153991699219</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G586" t="n">
-        <v>21.0471973419189</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G588" t="n">
-        <v>20.5836029052734</v>
+        <v>20.5836048126221</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>20.9081172943115</v>
+        <v>20.9081153869629</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>20.5836029052734</v>
+        <v>20.5836048126221</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>21.1862773895264</v>
+        <v>21.1862754821777</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>20.8154029846191</v>
+        <v>20.8153991699219</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>21.0471973419189</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>20.7226791381836</v>
+        <v>20.7226810455322</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>20.7690410614014</v>
+        <v>20.7690372467041</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G603" t="n">
-        <v>20.444522857666</v>
+        <v>20.4445209503174</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>20.7690410614014</v>
+        <v>20.7690372467041</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>20.5836029052734</v>
+        <v>20.5836048126221</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>22</v>
       </c>
       <c r="G610" t="n">
-        <v>20.3981609344482</v>
+        <v>20.3981647491455</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G611" t="n">
-        <v>20.7226791381836</v>
+        <v>20.7226810455322</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>19.9809284210205</v>
+        <v>19.9809303283691</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>20</v>
       </c>
       <c r="G615" t="n">
-        <v>18.5437831878662</v>
+        <v>18.5437850952148</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G616" t="n">
-        <v>18.4881534576416</v>
+        <v>18.488151550293</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>19.1928176879883</v>
+        <v>19.1928195953369</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G620" t="n">
-        <v>19.6564121246338</v>
+        <v>19.6564140319824</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G621" t="n">
-        <v>19.6564121246338</v>
+        <v>19.6564140319824</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>20.5836029052734</v>
+        <v>20.5836048126221</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G625" t="n">
-        <v>20.2127246856689</v>
+        <v>20.2127265930176</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G626" t="n">
-        <v>20.3054447174072</v>
+        <v>20.30544090271</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>20.5372409820557</v>
+        <v>20.537239074707</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>19.8418502807617</v>
+        <v>19.8418521881104</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G630" t="n">
-        <v>19.8418502807617</v>
+        <v>19.8418521881104</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G631" t="n">
-        <v>20.0736465454102</v>
+        <v>20.0736484527588</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G633" t="n">
-        <v>19.8882122039795</v>
+        <v>19.8882102966309</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G634" t="n">
-        <v>19.8418502807617</v>
+        <v>19.8418521881104</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>19.610050201416</v>
+        <v>19.6100540161133</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G636" t="n">
-        <v>19.6564121246338</v>
+        <v>19.6564140319824</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G637" t="n">
-        <v>19.7491321563721</v>
+        <v>19.7491302490234</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>19.7954902648926</v>
+        <v>19.7954921722412</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>19.610050201416</v>
+        <v>19.6100540161133</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>19.7954902648926</v>
+        <v>19.7954921722412</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>19.7954902648926</v>
+        <v>19.7954921722412</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>20.2127246856689</v>
+        <v>20.2127265930176</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>20.3054447174072</v>
+        <v>20.30544090271</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>20.444522857666</v>
+        <v>20.4445209503174</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>22</v>
       </c>
       <c r="G650" t="n">
-        <v>20.3981609344482</v>
+        <v>20.3981647491455</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>19.8418502807617</v>
+        <v>19.8418521881104</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>19.2855377197266</v>
+        <v>19.2855358123779</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G654" t="n">
-        <v>19.424617767334</v>
+        <v>19.4246158599854</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G655" t="n">
-        <v>19.2855377197266</v>
+        <v>19.2855358123779</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G657" t="n">
-        <v>19.610050201416</v>
+        <v>19.6100540161133</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>19.517333984375</v>
+        <v>19.5173320770264</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>19.610050201416</v>
+        <v>19.6100540161133</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G662" t="n">
-        <v>19.517333984375</v>
+        <v>19.5173320770264</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>19.517333984375</v>
+        <v>19.5173320770264</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G664" t="n">
-        <v>19.610050201416</v>
+        <v>19.6100540161133</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>19.5636920928955</v>
+        <v>19.5636959075928</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G666" t="n">
-        <v>19.610050201416</v>
+        <v>19.6100540161133</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>19.610050201416</v>
+        <v>19.6100540161133</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G668" t="n">
-        <v>19.424617767334</v>
+        <v>19.4246158599854</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>19.5636920928955</v>
+        <v>19.5636959075928</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G670" t="n">
-        <v>19.517333984375</v>
+        <v>19.5173320770264</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>19.3318977355957</v>
+        <v>19.3318958282471</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G672" t="n">
-        <v>19.1464595794678</v>
+        <v>19.1464557647705</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>19.1001014709473</v>
+        <v>19.1000995635986</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G674" t="n">
-        <v>19.1001014709473</v>
+        <v>19.1000995635986</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>19.1001014709473</v>
+        <v>19.1000995635986</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>20.75</v>
       </c>
       <c r="G676" t="n">
-        <v>19.2391777038574</v>
+        <v>19.2391757965088</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>19.424617767334</v>
+        <v>19.4246158599854</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>19.424617767334</v>
+        <v>19.4246158599854</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>21.25</v>
       </c>
       <c r="G680" t="n">
-        <v>19.7027702331543</v>
+        <v>19.7027740478516</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>19.5636920928955</v>
+        <v>19.5636959075928</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>19.7491321563721</v>
+        <v>19.7491302490234</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G685" t="n">
-        <v>20.5372409820557</v>
+        <v>20.537239074707</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>20.3054447174072</v>
+        <v>20.30544090271</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>20.5372409820557</v>
+        <v>20.537239074707</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G689" t="n">
-        <v>20.7226791381836</v>
+        <v>20.7226810455322</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>20.9081172943115</v>
+        <v>20.9081153869629</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G696" t="n">
-        <v>21.1862773895264</v>
+        <v>21.1862754821777</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>21.0471973419189</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>21.4180717468262</v>
+        <v>21.4180736541748</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G701" t="n">
-        <v>21.278995513916</v>
+        <v>21.2789936065674</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G703" t="n">
-        <v>21.1862773895264</v>
+        <v>21.1862754821777</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G710" t="n">
-        <v>19.8882122039795</v>
+        <v>19.8882102966309</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>19.7954902648926</v>
+        <v>19.7954921722412</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>19.5636920928955</v>
+        <v>19.5636959075928</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>19.2855377197266</v>
+        <v>19.2855358123779</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>20.75</v>
       </c>
       <c r="G717" t="n">
-        <v>19.2391777038574</v>
+        <v>19.2391757965088</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G718" t="n">
-        <v>17.5980548858643</v>
+        <v>17.598051071167</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G719" t="n">
-        <v>15.2059049606323</v>
+        <v>15.205904006958</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G720" t="n">
-        <v>15.5953226089478</v>
+        <v>15.5953245162964</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>15.5</v>
       </c>
       <c r="G722" t="n">
-        <v>14.3714323043823</v>
+        <v>14.3714332580566</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G723" t="n">
-        <v>14.7052211761475</v>
+        <v>14.7052202224731</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>16.5</v>
       </c>
       <c r="G724" t="n">
-        <v>15.298623085022</v>
+        <v>15.2986221313477</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G726" t="n">
-        <v>15.8920221328735</v>
+        <v>15.8920240402222</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G727" t="n">
-        <v>15.4284296035767</v>
+        <v>15.428427696228</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G728" t="n">
-        <v>15.2244501113892</v>
+        <v>15.2244462966919</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G729" t="n">
-        <v>15.3542528152466</v>
+        <v>15.3542537689209</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>17</v>
       </c>
       <c r="G730" t="n">
-        <v>15.7622184753418</v>
+        <v>15.7622175216675</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>15.4840621948242</v>
+        <v>15.4840612411499</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G735" t="n">
-        <v>15.2800798416138</v>
+        <v>15.2800769805908</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G737" t="n">
-        <v>14.7599248886108</v>
+        <v>14.7599239349365</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G738" t="n">
-        <v>14.4800281524658</v>
+        <v>14.4800271987915</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G744" t="n">
-        <v>14.5546684265137</v>
+        <v>14.5546674728394</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G745" t="n">
-        <v>14.7599248886108</v>
+        <v>14.7599239349365</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G746" t="n">
-        <v>15.0398225784302</v>
+        <v>15.0398235321045</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G748" t="n">
-        <v>15.1704387664795</v>
+        <v>15.1704397201538</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G749" t="n">
-        <v>14.7599248886108</v>
+        <v>14.7599239349365</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G750" t="n">
-        <v>13.9762105941772</v>
+        <v>13.9762115478516</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G753" t="n">
-        <v>13.6403341293335</v>
+        <v>13.6403360366821</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G755" t="n">
-        <v>14.0695123672485</v>
+        <v>14.0695104598999</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G757" t="n">
-        <v>14.1254911422729</v>
+        <v>14.1254920959473</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G758" t="n">
-        <v>13.8642511367798</v>
+        <v>13.8642520904541</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G759" t="n">
-        <v>13.5470361709595</v>
+        <v>13.5470371246338</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>14.5</v>
       </c>
       <c r="G760" t="n">
-        <v>13.5283765792847</v>
+        <v>13.5283756256104</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G761" t="n">
-        <v>13.6963157653809</v>
+        <v>13.6963148117065</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G764" t="n">
-        <v>14.1068315505981</v>
+        <v>14.1068305969238</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>14.5546684265137</v>
+        <v>14.5546674728394</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G767" t="n">
-        <v>14.7599248886108</v>
+        <v>14.7599239349365</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G768" t="n">
-        <v>14.6479654312134</v>
+        <v>14.6479663848877</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>15.1144618988037</v>
+        <v>15.1144638061523</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>15.1144618988037</v>
+        <v>15.1144638061523</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>15.0211629867554</v>
+        <v>15.0211639404297</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G775" t="n">
-        <v>14.7972440719604</v>
+        <v>14.7972431182861</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G776" t="n">
-        <v>15.0025033950806</v>
+        <v>15.0025024414062</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G777" t="n">
-        <v>15.0211629867554</v>
+        <v>15.0211639404297</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G778" t="n">
-        <v>15.0584812164307</v>
+        <v>15.0584831237793</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G779" t="n">
-        <v>15.0398225784302</v>
+        <v>15.0398235321045</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G780" t="n">
-        <v>15.0958003997803</v>
+        <v>15.0958013534546</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G781" t="n">
-        <v>15.4316806793213</v>
+        <v>15.4316816329956</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>17</v>
       </c>
       <c r="G782" t="n">
-        <v>15.8608551025391</v>
+        <v>15.8608541488647</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>16.7005443572998</v>
+        <v>16.7005462646484</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>18</v>
       </c>
       <c r="G785" t="n">
-        <v>16.7938442230225</v>
+        <v>16.7938499450684</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G787" t="n">
-        <v>16.308687210083</v>
+        <v>16.3086910247803</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G790" t="n">
-        <v>15.8795137405396</v>
+        <v>15.8795156478882</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>15.7675561904907</v>
+        <v>15.7675552368164</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G792" t="n">
-        <v>15.711576461792</v>
+        <v>15.7115774154663</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>17</v>
       </c>
       <c r="G793" t="n">
-        <v>15.8608551025391</v>
+        <v>15.8608541488647</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G794" t="n">
-        <v>16.0287952423096</v>
+        <v>16.0287933349609</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>16.513952255249</v>
+        <v>16.5139503479004</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G798" t="n">
-        <v>16.4019927978516</v>
+        <v>16.4019908905029</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="n">
-        <v>16.3273506164551</v>
+        <v>16.3273487091064</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G801" t="n">
-        <v>16.3460083007812</v>
+        <v>16.3460102081299</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G802" t="n">
-        <v>16.308687210083</v>
+        <v>16.3086910247803</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G803" t="n">
-        <v>16.1220932006836</v>
+        <v>16.122091293335</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G804" t="n">
-        <v>16.1220932006836</v>
+        <v>16.122091293335</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>16.513952255249</v>
+        <v>16.5139503479004</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G806" t="n">
-        <v>16.4952907562256</v>
+        <v>16.495288848877</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>16.7005443572998</v>
+        <v>16.7005462646484</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>16.6072483062744</v>
+        <v>16.6072463989258</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G809" t="n">
-        <v>16.3646717071533</v>
+        <v>16.3646697998047</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>15.7675561904907</v>
+        <v>15.7675552368164</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G812" t="n">
-        <v>15.7488946914673</v>
+        <v>15.7488956451416</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>15.7675561904907</v>
+        <v>15.7675552368164</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G814" t="n">
-        <v>15.8421955108643</v>
+        <v>15.8421964645386</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G815" t="n">
-        <v>15.7488946914673</v>
+        <v>15.7488956451416</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>17</v>
       </c>
       <c r="G816" t="n">
-        <v>15.8608551025391</v>
+        <v>15.8608541488647</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G817" t="n">
-        <v>15.8235359191895</v>
+        <v>15.8235349655151</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G818" t="n">
-        <v>16.0101337432861</v>
+        <v>16.0101318359375</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G819" t="n">
-        <v>15.8795137405396</v>
+        <v>15.8795156478882</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G820" t="n">
-        <v>15.8981761932373</v>
+        <v>15.8981781005859</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G821" t="n">
-        <v>16.0101337432861</v>
+        <v>16.0101318359375</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>16.2340488433838</v>
+        <v>16.2340526580811</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G823" t="n">
-        <v>16.2900295257568</v>
+        <v>16.2900314331055</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>16.4206523895264</v>
+        <v>16.4206466674805</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G826" t="n">
-        <v>16.6632270812988</v>
+        <v>16.6632289886475</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>17.3536396026611</v>
+        <v>17.3536415100098</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G830" t="n">
-        <v>18.1373558044434</v>
+        <v>18.1373538970947</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G831" t="n">
-        <v>18.1186962127686</v>
+        <v>18.1186943054199</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G832" t="n">
-        <v>17.9880771636963</v>
+        <v>17.988073348999</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G833" t="n">
-        <v>17.4096202850342</v>
+        <v>17.4096221923828</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>18</v>
       </c>
       <c r="G837" t="n">
-        <v>16.7938442230225</v>
+        <v>16.7938499450684</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G838" t="n">
-        <v>16.6259059906006</v>
+        <v>16.6259078979492</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>16.6072483062744</v>
+        <v>16.6072463989258</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>16.6072483062744</v>
+        <v>16.6072463989258</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G841" t="n">
-        <v>16.6632270812988</v>
+        <v>16.6632289886475</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G842" t="n">
-        <v>16.5326080322266</v>
+        <v>16.5326061248779</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G843" t="n">
-        <v>16.8498249053955</v>
+        <v>16.8498268127441</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G844" t="n">
-        <v>16.8498249053955</v>
+        <v>16.8498268127441</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G846" t="n">
-        <v>16.9431266784668</v>
+        <v>16.9431228637695</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G847" t="n">
-        <v>17.0364227294922</v>
+        <v>17.0364265441895</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G849" t="n">
-        <v>16.644567489624</v>
+        <v>16.6445713043213</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>17</v>
       </c>
       <c r="G853" t="n">
-        <v>15.8608551025391</v>
+        <v>15.8608541488647</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>16.5</v>
       </c>
       <c r="G854" t="n">
-        <v>15.3943605422974</v>
+        <v>15.394359588623</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G855" t="n">
-        <v>15.4130182266235</v>
+        <v>15.4130201339722</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G856" t="n">
-        <v>15.3570404052734</v>
+        <v>15.3570394515991</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G857" t="n">
-        <v>15.4316806793213</v>
+        <v>15.4316816329956</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G858" t="n">
-        <v>15.0771436691284</v>
+        <v>15.0771417617798</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G859" t="n">
-        <v>14.591986656189</v>
+        <v>14.5919857025146</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G860" t="n">
-        <v>14.7039451599121</v>
+        <v>14.7039470672607</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G863" t="n">
-        <v>14.871883392334</v>
+        <v>14.8718824386597</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G866" t="n">
-        <v>14.4053888320923</v>
+        <v>14.4053859710693</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G868" t="n">
-        <v>14.27476978302</v>
+        <v>14.2747688293457</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G870" t="n">
-        <v>14.7226028442383</v>
+        <v>14.7226047515869</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G871" t="n">
-        <v>14.7972440719604</v>
+        <v>14.7972431182861</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>14.3680667877197</v>
+        <v>14.3680686950684</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G874" t="n">
-        <v>14.5360078811646</v>
+        <v>14.5360069274902</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>14.6479654312134</v>
+        <v>14.6479663848877</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>16.5</v>
       </c>
       <c r="G878" t="n">
-        <v>15.3943605422974</v>
+        <v>15.394359588623</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G879" t="n">
-        <v>15.4316806793213</v>
+        <v>15.4316816329956</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G880" t="n">
-        <v>15.3570404052734</v>
+        <v>15.3570394515991</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>15.3010587692261</v>
+        <v>15.301061630249</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G882" t="n">
-        <v>15.2823991775513</v>
+        <v>15.282398223877</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G883" t="n">
-        <v>15.562294960022</v>
+        <v>15.5622968673706</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G884" t="n">
-        <v>15.0211629867554</v>
+        <v>15.0211639404297</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G888" t="n">
-        <v>15.0398225784302</v>
+        <v>15.0398235321045</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>15.4876594543457</v>
+        <v>15.4876585006714</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G890" t="n">
-        <v>15.4316806793213</v>
+        <v>15.4316816329956</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>16.5</v>
       </c>
       <c r="G891" t="n">
-        <v>15.3943605422974</v>
+        <v>15.394359588623</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G893" t="n">
-        <v>15.3197212219238</v>
+        <v>15.3197193145752</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G894" t="n">
-        <v>15.2264204025269</v>
+        <v>15.2264213562012</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G895" t="n">
-        <v>15.2264204025269</v>
+        <v>15.2264213562012</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G896" t="n">
-        <v>15.0958003997803</v>
+        <v>15.0958013534546</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G897" t="n">
-        <v>15.0025033950806</v>
+        <v>15.0025024414062</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G898" t="n">
-        <v>14.7599248886108</v>
+        <v>14.7599239349365</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G899" t="n">
-        <v>14.871883392334</v>
+        <v>14.8718824386597</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G900" t="n">
-        <v>14.9465227127075</v>
+        <v>14.9465236663818</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G901" t="n">
-        <v>14.77858543396</v>
+        <v>14.7785844802856</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G903" t="n">
-        <v>14.4427061080933</v>
+        <v>14.4427070617676</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G904" t="n">
-        <v>14.591986656189</v>
+        <v>14.5919857025146</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>15.0211629867554</v>
+        <v>15.0211639404297</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>15.0211629867554</v>
+        <v>15.0211639404297</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G909" t="n">
-        <v>14.77858543396</v>
+        <v>14.7785844802856</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G911" t="n">
-        <v>14.7226028442383</v>
+        <v>14.7226047515869</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G912" t="n">
-        <v>14.685284614563</v>
+        <v>14.6852836608887</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G914" t="n">
-        <v>14.7599248886108</v>
+        <v>14.7599239349365</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G917" t="n">
-        <v>14.5546684265137</v>
+        <v>14.5546674728394</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G918" t="n">
-        <v>14.2001304626465</v>
+        <v>14.2001295089722</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G919" t="n">
-        <v>14.1814708709717</v>
+        <v>14.1814699172974</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>15</v>
       </c>
       <c r="G920" t="n">
-        <v>13.9948720932007</v>
+        <v>13.9948711395264</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G921" t="n">
-        <v>13.808274269104</v>
+        <v>13.8082733154297</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G922" t="n">
-        <v>13.6776542663574</v>
+        <v>13.6776561737061</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G923" t="n">
-        <v>14.3307485580444</v>
+        <v>14.3307495117188</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G925" t="n">
-        <v>14.27476978302</v>
+        <v>14.2747688293457</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G926" t="n">
-        <v>14.3307485580444</v>
+        <v>14.3307495117188</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G927" t="n">
-        <v>14.0695123672485</v>
+        <v>14.0695104598999</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>13.7149753570557</v>
+        <v>13.714973449707</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G929" t="n">
-        <v>13.9762105941772</v>
+        <v>13.9762115478516</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G932" t="n">
-        <v>13.8455934524536</v>
+        <v>13.8455944061279</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G933" t="n">
-        <v>14.1441497802734</v>
+        <v>14.1441507339478</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G934" t="n">
-        <v>13.808274269104</v>
+        <v>13.8082733154297</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G935" t="n">
-        <v>13.9202318191528</v>
+        <v>13.9202337265015</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G936" t="n">
-        <v>14.1068315505981</v>
+        <v>14.1068305969238</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>14.3680667877197</v>
+        <v>14.3680686950684</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G940" t="n">
-        <v>14.7226028442383</v>
+        <v>14.7226047515869</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G941" t="n">
-        <v>14.7226028442383</v>
+        <v>14.7226047515869</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G943" t="n">
-        <v>14.7599248886108</v>
+        <v>14.7599239349365</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G944" t="n">
-        <v>14.6479654312134</v>
+        <v>14.6479663848877</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G945" t="n">
-        <v>14.4986867904663</v>
+        <v>14.4986877441406</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G946" t="n">
-        <v>14.7039451599121</v>
+        <v>14.7039470672607</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>14.3680667877197</v>
+        <v>14.3680686950684</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G949" t="n">
-        <v>14.27476978302</v>
+        <v>14.2747688293457</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G950" t="n">
-        <v>13.9015712738037</v>
+        <v>13.901572227478</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G951" t="n">
-        <v>15.2637424468994</v>
+        <v>15.2637414932251</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G952" t="n">
-        <v>14.9465227127075</v>
+        <v>14.9465236663818</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G954" t="n">
-        <v>14.6479654312134</v>
+        <v>14.6479663848877</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G955" t="n">
-        <v>14.088171005249</v>
+        <v>14.0881729125977</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G958" t="n">
-        <v>14.0695123672485</v>
+        <v>14.0695104598999</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G959" t="n">
-        <v>14.0135326385498</v>
+        <v>14.0135316848755</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>14.088171005249</v>
+        <v>14.0881729125977</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>15</v>
       </c>
       <c r="G961" t="n">
-        <v>13.9948720932007</v>
+        <v>13.9948711395264</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G962" t="n">
-        <v>14.3307485580444</v>
+        <v>14.3307495117188</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G963" t="n">
-        <v>14.4053888320923</v>
+        <v>14.4053859710693</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G964" t="n">
-        <v>14.3307485580444</v>
+        <v>14.3307495117188</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G965" t="n">
-        <v>14.3307485580444</v>
+        <v>14.3307495117188</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G966" t="n">
-        <v>14.27476978302</v>
+        <v>14.2747688293457</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G967" t="n">
-        <v>14.3867282867432</v>
+        <v>14.3867273330688</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>14.6479654312134</v>
+        <v>14.6479663848877</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G971" t="n">
-        <v>14.7972440719604</v>
+        <v>14.7972431182861</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G972" t="n">
-        <v>15.0211629867554</v>
+        <v>15.0211639404297</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G974" t="n">
-        <v>14.3867282867432</v>
+        <v>14.3867273330688</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G975" t="n">
-        <v>14.4986867904663</v>
+        <v>14.4986877441406</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G976" t="n">
-        <v>14.4427061080933</v>
+        <v>14.4427070617676</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G977" t="n">
-        <v>14.6479654312134</v>
+        <v>14.6479663848877</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G979" t="n">
-        <v>14.8905439376831</v>
+        <v>14.8905429840088</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G980" t="n">
-        <v>14.8905439376831</v>
+        <v>14.8905429840088</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G981" t="n">
-        <v>15.0958003997803</v>
+        <v>15.0958013534546</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>15.0211629867554</v>
+        <v>15.0211639404297</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G983" t="n">
-        <v>15.1144618988037</v>
+        <v>15.1144638061523</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G984" t="n">
-        <v>15.1891002655029</v>
+        <v>15.1891012191772</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G985" t="n">
-        <v>15.0584812164307</v>
+        <v>15.0584831237793</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G986" t="n">
-        <v>15.0584812164307</v>
+        <v>15.0584831237793</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>15.0211629867554</v>
+        <v>15.0211639404297</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G989" t="n">
-        <v>14.9552392959595</v>
+        <v>14.9552383422852</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G990" t="n">
-        <v>14.8045558929443</v>
+        <v>14.8045568466187</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G995" t="n">
-        <v>15.5768051147461</v>
+        <v>15.5768060684204</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G998" t="n">
-        <v>15.5768051147461</v>
+        <v>15.5768060684204</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1001" t="n">
-        <v>15.5579671859741</v>
+        <v>15.5579700469971</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1002" t="n">
-        <v>15.4261198043823</v>
+        <v>15.4261207580566</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1003" t="n">
-        <v>15.4449558258057</v>
+        <v>15.4449577331543</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1004" t="n">
-        <v>15.3507795333862</v>
+        <v>15.3507785797119</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1005" t="n">
-        <v>15.4449558258057</v>
+        <v>15.4449577331543</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1006" t="n">
-        <v>15.6521463394165</v>
+        <v>15.6521482467651</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1007" t="n">
-        <v>15.6521463394165</v>
+        <v>15.6521482467651</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1008" t="n">
-        <v>15.6898164749146</v>
+        <v>15.6898155212402</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1009" t="n">
-        <v>16.0665225982666</v>
+        <v>16.066520690918</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1011" t="n">
-        <v>15.5014629364014</v>
+        <v>15.5014619827271</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>16.5</v>
       </c>
       <c r="G1012" t="n">
-        <v>15.539134979248</v>
+        <v>15.5391321182251</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1013" t="n">
-        <v>15.5579671859741</v>
+        <v>15.5579700469971</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1014" t="n">
-        <v>15.5768051147461</v>
+        <v>15.5768060684204</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1015" t="n">
-        <v>15.4261198043823</v>
+        <v>15.4261207580566</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1016" t="n">
-        <v>15.9346761703491</v>
+        <v>15.9346742630005</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1017" t="n">
-        <v>15.8781681060791</v>
+        <v>15.8781700134277</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1019" t="n">
-        <v>15.5014629364014</v>
+        <v>15.5014619827271</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1020" t="n">
-        <v>15.3131074905396</v>
+        <v>15.3131084442139</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1021" t="n">
-        <v>15.7274875640869</v>
+        <v>15.7274866104126</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1023" t="n">
-        <v>15.4637937545776</v>
+        <v>15.4637908935547</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1024" t="n">
-        <v>15.3319444656372</v>
+        <v>15.3319454193115</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1025" t="n">
-        <v>15.4637937545776</v>
+        <v>15.4637908935547</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1028" t="n">
-        <v>15.3319444656372</v>
+        <v>15.3319454193115</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1030" t="n">
-        <v>15.0117444992065</v>
+        <v>15.0117454528809</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1033" t="n">
-        <v>14.6538743972778</v>
+        <v>14.6538734436035</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1034" t="n">
-        <v>14.8045558929443</v>
+        <v>14.8045568466187</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.8422260284424</v>
+        <v>14.8422269821167</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1036" t="n">
-        <v>14.4090147018433</v>
+        <v>14.4090137481689</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1038" t="n">
-        <v>13.8439559936523</v>
+        <v>13.843955039978</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>15</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.1264848709106</v>
+        <v>14.1264839172363</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>14.5031900405884</v>
+        <v>14.5031909942627</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.5031900405884</v>
+        <v>14.5031909942627</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1049" t="n">
-        <v>14.2394971847534</v>
+        <v>14.2394962310791</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1053" t="n">
-        <v>13.0528726577759</v>
+        <v>13.0528717041016</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G1054" t="n">
-        <v>12.9210243225098</v>
+        <v>12.9210252761841</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1056" t="n">
-        <v>12.9963665008545</v>
+        <v>12.9963674545288</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>13.5</v>
       </c>
       <c r="G1057" t="n">
-        <v>12.7138366699219</v>
+        <v>12.7138357162476</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1058" t="n">
-        <v>12.3371305465698</v>
+        <v>12.3371295928955</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1059" t="n">
-        <v>12.0922718048096</v>
+        <v>12.0922727584839</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>11.8662481307983</v>
+        <v>11.8662462234497</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G1062" t="n">
-        <v>10.9621534347534</v>
+        <v>10.9621524810791</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1063" t="n">
-        <v>10.0580568313599</v>
+        <v>10.0580577850342</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G1065" t="n">
-        <v>9.53066825866699</v>
+        <v>9.53066730499268</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1070" t="n">
-        <v>9.0409517288208</v>
+        <v>9.04094982147217</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1071" t="n">
-        <v>10.0957269668579</v>
+        <v>10.0957279205322</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1072" t="n">
-        <v>10.6796216964722</v>
+        <v>10.6796236038208</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1073" t="n">
-        <v>11.8474111557007</v>
+        <v>11.8474130630493</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1075" t="n">
-        <v>11.52721118927</v>
+        <v>11.5272121429443</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1077" t="n">
-        <v>10.8491411209106</v>
+        <v>10.8491401672363</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1078" t="n">
-        <v>10.6796216964722</v>
+        <v>10.6796236038208</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1080" t="n">
-        <v>10.0015525817871</v>
+        <v>10.0015506744385</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1083" t="n">
-        <v>10.5477752685547</v>
+        <v>10.5477743148804</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1084" t="n">
-        <v>10.6607866287231</v>
+        <v>10.6607875823975</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1085" t="n">
-        <v>11.0374937057495</v>
+        <v>11.0374927520752</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>11.5</v>
       </c>
       <c r="G1086" t="n">
-        <v>10.8303050994873</v>
+        <v>10.830304145813</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1087" t="n">
-        <v>10.5101051330566</v>
+        <v>10.5101041793823</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1088" t="n">
-        <v>10.1333999633789</v>
+        <v>10.1333980560303</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1091" t="n">
-        <v>10.4347629547119</v>
+        <v>10.4347639083862</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1093" t="n">
-        <v>10.4347629547119</v>
+        <v>10.4347639083862</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1094" t="n">
-        <v>10.6984577178955</v>
+        <v>10.6984567642212</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1096" t="n">
-        <v>10.6231155395508</v>
+        <v>10.6231164932251</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1100" t="n">
-        <v>10.6231155395508</v>
+        <v>10.6231164932251</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1102" t="n">
-        <v>10.6607866287231</v>
+        <v>10.6607875823975</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1103" t="n">
-        <v>10.4724349975586</v>
+        <v>10.4724340438843</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1104" t="n">
-        <v>10.6607866287231</v>
+        <v>10.6607875823975</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1106" t="n">
-        <v>10.6984577178955</v>
+        <v>10.6984567642212</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1107" t="n">
-        <v>10.4724349975586</v>
+        <v>10.4724340438843</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>10.9244813919067</v>
+        <v>10.9244804382324</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>11.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>10.8303050994873</v>
+        <v>10.830304145813</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>10.9244813919067</v>
+        <v>10.9244804382324</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1115" t="n">
-        <v>11.4141998291016</v>
+        <v>11.4141979217529</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1116" t="n">
-        <v>11.4895401000977</v>
+        <v>11.489541053772</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1117" t="n">
-        <v>11.4895401000977</v>
+        <v>11.489541053772</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1118" t="n">
-        <v>11.4895401000977</v>
+        <v>11.489541053772</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G1119" t="n">
-        <v>10.9809856414795</v>
+        <v>10.9809875488281</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1120" t="n">
-        <v>11.3388595581055</v>
+        <v>11.3388576507568</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1123" t="n">
-        <v>11.9227533340454</v>
+        <v>11.9227523803711</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1125" t="n">
-        <v>12.1299409866333</v>
+        <v>12.1299419403076</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1126" t="n">
-        <v>12.0169305801392</v>
+        <v>12.0169296264648</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1128" t="n">
-        <v>11.150505065918</v>
+        <v>11.1505060195923</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1130" t="n">
-        <v>11.1128349304199</v>
+        <v>11.1128358840942</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1131" t="n">
-        <v>11.1128349304199</v>
+        <v>11.1128358840942</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1133" t="n">
-        <v>10.6607866287231</v>
+        <v>10.6607875823975</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1136" t="n">
-        <v>11.0186576843262</v>
+        <v>11.0186586380005</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>10.811469078064</v>
+        <v>10.8114700317383</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>11.5</v>
       </c>
       <c r="G1140" t="n">
-        <v>10.8303050994873</v>
+        <v>10.830304145813</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1141" t="n">
-        <v>10.7172927856445</v>
+        <v>10.7172918319702</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1142" t="n">
-        <v>10.6042823791504</v>
+        <v>10.6042814254761</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1143" t="n">
-        <v>10.7172927856445</v>
+        <v>10.7172918319702</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1144" t="n">
-        <v>10.4724349975586</v>
+        <v>10.4724340438843</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1145" t="n">
-        <v>10.6042823791504</v>
+        <v>10.6042814254761</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.5477752685547</v>
+        <v>10.5477743148804</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1147" t="n">
-        <v>10.4724349975586</v>
+        <v>10.4724340438843</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1150" t="n">
-        <v>10.5854463577271</v>
+        <v>10.5854444503784</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1153" t="n">
-        <v>11.1128349304199</v>
+        <v>11.1128358840942</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.2635173797607</v>
+        <v>11.2635183334351</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1158" t="n">
-        <v>11.150505065918</v>
+        <v>11.1505060195923</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1159" t="n">
-        <v>10.9056453704834</v>
+        <v>10.9056463241577</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1160" t="n">
-        <v>10.8491411209106</v>
+        <v>10.8491401672363</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1164" t="n">
-        <v>10.3970909118652</v>
+        <v>10.3970918655396</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>10.5477752685547</v>
+        <v>10.5477743148804</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1166" t="n">
-        <v>10.7172927856445</v>
+        <v>10.7172918319702</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>11.5</v>
       </c>
       <c r="G1168" t="n">
-        <v>10.8303050994873</v>
+        <v>10.830304145813</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1169" t="n">
-        <v>10.6796216964722</v>
+        <v>10.6796236038208</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1171" t="n">
-        <v>11.4141998291016</v>
+        <v>11.4141979217529</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1174" t="n">
-        <v>11.3388595581055</v>
+        <v>11.3388576507568</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1175" t="n">
-        <v>11.52721118927</v>
+        <v>11.5272121429443</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1176" t="n">
-        <v>11.3576936721802</v>
+        <v>11.3576946258545</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1178" t="n">
-        <v>11.4518709182739</v>
+        <v>11.4518699645996</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1182" t="n">
-        <v>11.4707059860229</v>
+        <v>11.4707069396973</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1183" t="n">
-        <v>11.4707059860229</v>
+        <v>11.4707069396973</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1184" t="n">
-        <v>11.52721118927</v>
+        <v>11.5272121429443</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1186" t="n">
-        <v>11.5837182998657</v>
+        <v>11.5837173461914</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1187" t="n">
-        <v>11.8474111557007</v>
+        <v>11.8474130630493</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1188" t="n">
-        <v>11.6590595245361</v>
+        <v>11.6590585708618</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1189" t="n">
-        <v>11.52721118927</v>
+        <v>11.5272121429443</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1190" t="n">
-        <v>11.8474111557007</v>
+        <v>11.8474130630493</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1191" t="n">
-        <v>12.148777961731</v>
+        <v>12.1487760543823</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1192" t="n">
-        <v>12.0545997619629</v>
+        <v>12.0546007156372</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1193" t="n">
-        <v>12.0357656478882</v>
+        <v>12.0357646942139</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1196" t="n">
-        <v>11.7343988418579</v>
+        <v>11.7343997955322</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1197" t="n">
-        <v>11.6590595245361</v>
+        <v>11.6590585708618</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>11.6778936386108</v>
+        <v>11.6778945922852</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1199" t="n">
-        <v>11.4518709182739</v>
+        <v>11.4518699645996</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1201" t="n">
-        <v>11.169340133667</v>
+        <v>11.1693391799927</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1203" t="n">
-        <v>11.4518709182739</v>
+        <v>11.4518699645996</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1204" t="n">
-        <v>12.5631532669067</v>
+        <v>12.5631542205811</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1209" t="n">
-        <v>13.147047996521</v>
+        <v>13.1470489501953</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1210" t="n">
-        <v>13.3354015350342</v>
+        <v>13.3354005813599</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1213" t="n">
-        <v>13.2412252426147</v>
+        <v>13.2412261962891</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1214" t="n">
-        <v>13.2412252426147</v>
+        <v>13.2412261962891</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1218" t="n">
-        <v>13.147047996521</v>
+        <v>13.1470489501953</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G1219" t="n">
-        <v>12.9210243225098</v>
+        <v>12.9210252761841</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>12.9963665008545</v>
+        <v>12.9963674545288</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1221" t="n">
-        <v>13.147047996521</v>
+        <v>13.1470489501953</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1224" t="n">
-        <v>13.3919067382812</v>
+        <v>13.3919076919556</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1225" t="n">
-        <v>13.0905427932739</v>
+        <v>13.0905418395996</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1228" t="n">
-        <v>11.6778936386108</v>
+        <v>11.6778945922852</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1229" t="n">
-        <v>11.5837182998657</v>
+        <v>11.5837173461914</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>11.8662481307983</v>
+        <v>11.8662462234497</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.8662481307983</v>
+        <v>11.8662462234497</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1234" t="n">
-        <v>12.0545997619629</v>
+        <v>12.0546007156372</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1238" t="n">
-        <v>12.7326736450195</v>
+        <v>12.7326717376709</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1240" t="n">
-        <v>13.2223892211914</v>
+        <v>13.2223901748657</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1243" t="n">
-        <v>13.3354015350342</v>
+        <v>13.3354005813599</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1245" t="n">
-        <v>13.5260171890259</v>
+        <v>13.5260181427002</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1250" t="n">
-        <v>13.2216348648071</v>
+        <v>13.2216339111328</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>14.5</v>
       </c>
       <c r="G1253" t="n">
-        <v>13.7923517227173</v>
+        <v>13.7923526763916</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>14.5</v>
       </c>
       <c r="G1261" t="n">
-        <v>13.7923517227173</v>
+        <v>13.7923526763916</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1265" t="n">
-        <v>13.5260171890259</v>
+        <v>13.5260181427002</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1272" t="n">
-        <v>14.0396633148193</v>
+        <v>14.0396642684937</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1274" t="n">
-        <v>14.6103820800781</v>
+        <v>14.6103830337524</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1275" t="n">
-        <v>14.5342855453491</v>
+        <v>14.5342864990234</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1276" t="n">
-        <v>14.8957405090332</v>
+        <v>14.8957414627075</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1278" t="n">
-        <v>16.3796081542969</v>
+        <v>16.3796062469482</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1279" t="n">
-        <v>16.2274169921875</v>
+        <v>16.2274150848389</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1282" t="n">
-        <v>15.7137699127197</v>
+        <v>15.7137718200684</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1283" t="n">
-        <v>15.8469390869141</v>
+        <v>15.8469381332397</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>16.5</v>
       </c>
       <c r="G1284" t="n">
-        <v>15.6947460174561</v>
+        <v>15.6947450637817</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1285" t="n">
-        <v>15.5045080184937</v>
+        <v>15.504506111145</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1287" t="n">
-        <v>15.6376752853394</v>
+        <v>15.6376762390137</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1288" t="n">
-        <v>15.2381734848022</v>
+        <v>15.2381715774536</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1289" t="n">
-        <v>15.333291053772</v>
+        <v>15.3332920074463</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1290" t="n">
-        <v>15.5045080184937</v>
+        <v>15.504506111145</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1291" t="n">
-        <v>15.61865234375</v>
+        <v>15.6186494827271</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1294" t="n">
-        <v>16.4937515258789</v>
+        <v>16.4937534332275</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1296" t="n">
-        <v>16.5698471069336</v>
+        <v>16.5698490142822</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1297" t="n">
-        <v>16.5317993164062</v>
+        <v>16.5318012237549</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1298" t="n">
-        <v>16.6078968048096</v>
+        <v>16.6078929901123</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1299" t="n">
-        <v>16.5888710021973</v>
+        <v>16.5888690948486</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1300" t="n">
-        <v>17.0454444885254</v>
+        <v>17.0454483032227</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1301" t="n">
-        <v>17.026424407959</v>
+        <v>17.0264225006104</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1305" t="n">
-        <v>16.3225383758545</v>
+        <v>16.3225364685059</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1306" t="n">
-        <v>16.4937515258789</v>
+        <v>16.4937534332275</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1307" t="n">
-        <v>16.4937515258789</v>
+        <v>16.4937534332275</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1309" t="n">
-        <v>16.5508232116699</v>
+        <v>16.5508251190186</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1310" t="n">
-        <v>16.5698471069336</v>
+        <v>16.5698490142822</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1311" t="n">
-        <v>16.5698471069336</v>
+        <v>16.5698490142822</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1313" t="n">
-        <v>16.8171615600586</v>
+        <v>16.81715965271</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1314" t="n">
-        <v>16.5317993164062</v>
+        <v>16.5318012237549</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1315" t="n">
-        <v>16.7410621643066</v>
+        <v>16.7410640716553</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1316" t="n">
-        <v>17.8444519042969</v>
+        <v>17.8444499969482</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1317" t="n">
-        <v>17.9585933685303</v>
+        <v>17.9585952758789</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1318" t="n">
-        <v>17.8444519042969</v>
+        <v>17.8444499969482</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1319" t="n">
-        <v>18.186882019043</v>
+        <v>18.1868801116943</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>20.1653728485107</v>
+        <v>20.1653709411621</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.6422119140625</v>
+        <v>19.6422138214111</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1324" t="n">
-        <v>20.5934085845947</v>
+        <v>20.5934104919434</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1325" t="n">
-        <v>20.3556098937988</v>
+        <v>20.3556118011475</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>21</v>
       </c>
       <c r="G1326" t="n">
-        <v>19.9751300811768</v>
+        <v>19.9751319885254</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>21</v>
       </c>
       <c r="G1330" t="n">
-        <v>19.9751300811768</v>
+        <v>19.9751319885254</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>21</v>
       </c>
       <c r="G1331" t="n">
-        <v>19.9751300811768</v>
+        <v>19.9751319885254</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>20.498291015625</v>
+        <v>20.4982891082764</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1335" t="n">
-        <v>20.8312091827393</v>
+        <v>20.8312072753906</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>21</v>
       </c>
       <c r="G1339" t="n">
-        <v>19.9751300811768</v>
+        <v>19.9751319885254</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>21</v>
       </c>
       <c r="G1342" t="n">
-        <v>19.9751300811768</v>
+        <v>19.9751319885254</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1344" t="n">
-        <v>20.3556098937988</v>
+        <v>20.3556118011475</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1345" t="n">
-        <v>19.5946521759033</v>
+        <v>19.594654083252</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>21</v>
       </c>
       <c r="G1349" t="n">
-        <v>19.9751300811768</v>
+        <v>19.9751319885254</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1350" t="n">
-        <v>19.3568553924561</v>
+        <v>19.3568572998047</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1352" t="n">
-        <v>19.3568553924561</v>
+        <v>19.3568572998047</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1354" t="n">
-        <v>19.6897735595703</v>
+        <v>19.6897754669189</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>20</v>
       </c>
       <c r="G1355" t="n">
-        <v>19.0239334106445</v>
+        <v>19.0239353179932</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1356" t="n">
-        <v>19.5946521759033</v>
+        <v>19.594654083252</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1357" t="n">
-        <v>19.6897735595703</v>
+        <v>19.6897754669189</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1358" t="n">
-        <v>19.6897735595703</v>
+        <v>19.6897754669189</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1360" t="n">
-        <v>20.3556098937988</v>
+        <v>20.3556118011475</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>21</v>
       </c>
       <c r="G1362" t="n">
-        <v>19.9751300811768</v>
+        <v>19.9751319885254</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1363" t="n">
-        <v>20.0702495574951</v>
+        <v>20.0702514648438</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1366" t="n">
-        <v>19.3568553924561</v>
+        <v>19.3568572998047</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1367" t="n">
-        <v>19.6897735595703</v>
+        <v>19.6897754669189</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1371" t="n">
-        <v>20.3556098937988</v>
+        <v>20.3556118011475</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1373" t="n">
-        <v>20.498291015625</v>
+        <v>20.4982891082764</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>22.25</v>
       </c>
       <c r="G1376" t="n">
-        <v>21.1641292572021</v>
+        <v>21.1641273498535</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>22.75</v>
       </c>
       <c r="G1378" t="n">
-        <v>21.6397266387939</v>
+        <v>21.6397247314453</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>22.5</v>
       </c>
       <c r="G1381" t="n">
-        <v>21.401927947998</v>
+        <v>21.4019260406494</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1385" t="n">
-        <v>21.8299655914307</v>
+        <v>21.829963684082</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>22.5</v>
       </c>
       <c r="G1387" t="n">
-        <v>21.401927947998</v>
+        <v>21.4019260406494</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1390" t="n">
-        <v>21.0690097808838</v>
+        <v>21.0690078735352</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>22.75</v>
       </c>
       <c r="G1393" t="n">
-        <v>21.6397266387939</v>
+        <v>21.6397247314453</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>22.25</v>
       </c>
       <c r="G1396" t="n">
-        <v>21.1641292572021</v>
+        <v>21.1641273498535</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>22.1628837585449</v>
+        <v>22.1628818511963</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1400" t="n">
-        <v>22.4958019256592</v>
+        <v>22.4958038330078</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1401" t="n">
-        <v>22.2580032348633</v>
+        <v>22.2580051422119</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>22.5</v>
       </c>
       <c r="G1402" t="n">
-        <v>21.401927947998</v>
+        <v>21.4019260406494</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>23</v>
       </c>
       <c r="G1403" t="n">
-        <v>21.8775253295898</v>
+        <v>21.8775234222412</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1404" t="n">
-        <v>21.8299655914307</v>
+        <v>21.829963684082</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1408" t="n">
-        <v>21.2592468261719</v>
+        <v>21.2592487335205</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1411" t="n">
-        <v>21.2592468261719</v>
+        <v>21.2592487335205</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1412" t="n">
-        <v>21.2592468261719</v>
+        <v>21.2592487335205</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>23.2567596435547</v>
+        <v>23.2567615509033</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1423" t="n">
-        <v>23.0189609527588</v>
+        <v>23.0189628601074</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>23.0189609527588</v>
+        <v>23.0189628601074</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1428" t="n">
-        <v>23.5896778106689</v>
+        <v>23.5896797180176</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>23.4469985961914</v>
+        <v>23.44700050354</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1430" t="n">
-        <v>23.2567596435547</v>
+        <v>23.2567615509033</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1431" t="n">
-        <v>23.5896778106689</v>
+        <v>23.5896797180176</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1433" t="n">
-        <v>22.9238414764404</v>
+        <v>22.9238433837891</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>23.6372413635254</v>
+        <v>23.6372394561768</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>23.5896778106689</v>
+        <v>23.5896797180176</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>23.4945602416992</v>
+        <v>23.4945621490479</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>23.4945602416992</v>
+        <v>23.4945621490479</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1443" t="n">
-        <v>23.2567596435547</v>
+        <v>23.2567615509033</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>23.2567596435547</v>
+        <v>23.2567615509033</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1445" t="n">
-        <v>23.2567596435547</v>
+        <v>23.2567615509033</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G1447" t="n">
-        <v>22.8762798309326</v>
+        <v>22.8762817382812</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G1448" t="n">
-        <v>22.8762798309326</v>
+        <v>22.8762817382812</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1449" t="n">
-        <v>23.3994426727295</v>
+        <v>23.3994407653809</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1450" t="n">
-        <v>23.0189609527588</v>
+        <v>23.0189628601074</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>23.25</v>
       </c>
       <c r="G1453" t="n">
-        <v>22.1153259277344</v>
+        <v>22.1153240203857</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1456" t="n">
-        <v>22.0677661895752</v>
+        <v>22.0677623748779</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>23.25</v>
       </c>
       <c r="G1457" t="n">
-        <v>22.1153259277344</v>
+        <v>22.1153240203857</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>22.1628837585449</v>
+        <v>22.1628818511963</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1462" t="n">
-        <v>23.7323608398438</v>
+        <v>23.7323589324951</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1468" t="n">
-        <v>25.3018360137939</v>
+        <v>25.3018341064453</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>25.9676723480225</v>
+        <v>25.9676704406738</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>27</v>
       </c>
       <c r="G1472" t="n">
-        <v>25.6823120117188</v>
+        <v>25.6823101043701</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>27</v>
       </c>
       <c r="G1474" t="n">
-        <v>25.6823120117188</v>
+        <v>25.6823101043701</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1475" t="n">
-        <v>25.6347560882568</v>
+        <v>25.6347522735596</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1477" t="n">
-        <v>25.492073059082</v>
+        <v>25.4920711517334</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>26.3005886077881</v>
+        <v>26.3005905151367</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>27.75</v>
       </c>
       <c r="G1479" t="n">
-        <v>26.3957099914551</v>
+        <v>26.3957118988037</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1480" t="n">
-        <v>27.2993450164795</v>
+        <v>27.2993469238281</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1483" t="n">
-        <v>27.6798248291016</v>
+        <v>27.6798267364502</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>29.75</v>
       </c>
       <c r="G1484" t="n">
-        <v>28.2981052398682</v>
+        <v>28.2981033325195</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1486" t="n">
-        <v>28.1078643798828</v>
+        <v>28.1078624725342</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>29</v>
       </c>
       <c r="G1487" t="n">
-        <v>27.5847034454346</v>
+        <v>27.5847053527832</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1488" t="n">
-        <v>27.6798248291016</v>
+        <v>27.6798267364502</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>29</v>
       </c>
       <c r="G1489" t="n">
-        <v>27.5847034454346</v>
+        <v>27.5847053527832</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G1490" t="n">
-        <v>27.4420261383057</v>
+        <v>27.4420280456543</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1491" t="n">
-        <v>27.5371494293213</v>
+        <v>27.5371475219727</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G1493" t="n">
-        <v>27.0615482330322</v>
+        <v>27.0615501403809</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>26.7761898040771</v>
+        <v>26.7761878967285</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>58.5999984741211</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>38909</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>59.2000007629395</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>57.5999984741211</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>58.5499992370605</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>57.9000015258789</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>57.9000015258789</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -421,7 +421,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>15.5902538299561</v>
+        <v>15.5902509689331</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7186393737793</v>
+        <v>15.7186422348022</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2234239578247</v>
+        <v>15.2234230041504</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>14.5356187820435</v>
+        <v>14.5356159210205</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>15.5</v>
       </c>
       <c r="G6" t="n">
-        <v>14.2146415710449</v>
+        <v>14.2146406173706</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G8" t="n">
-        <v>14.2880067825317</v>
+        <v>14.2880058288574</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="G9" t="n">
-        <v>14.0403985977173</v>
+        <v>14.0403966903687</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G10" t="n">
-        <v>13.8661527633667</v>
+        <v>13.866153717041</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G12" t="n">
-        <v>12.7931776046753</v>
+        <v>12.793176651001</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G13" t="n">
-        <v>12.8848838806152</v>
+        <v>12.8848848342896</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G14" t="n">
-        <v>12.2887868881226</v>
+        <v>12.2887859344482</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>13.132493019104</v>
+        <v>13.1324949264526</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>17.5</v>
       </c>
       <c r="G18" t="n">
-        <v>16.0487880706787</v>
+        <v>16.048791885376</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G19" t="n">
-        <v>16.3239097595215</v>
+        <v>16.3239078521729</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G20" t="n">
-        <v>16.0854740142822</v>
+        <v>16.0854682922363</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G21" t="n">
-        <v>16.360595703125</v>
+        <v>16.3605937957764</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>16.5990295410156</v>
+        <v>16.5990314483643</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G24" t="n">
-        <v>15.4710330963135</v>
+        <v>15.4710321426392</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G25" t="n">
-        <v>16.1038112640381</v>
+        <v>16.1038150787354</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G26" t="n">
-        <v>15.3059587478638</v>
+        <v>15.3059577941895</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G27" t="n">
-        <v>14.9391307830811</v>
+        <v>14.9391298294067</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G28" t="n">
-        <v>14.948299407959</v>
+        <v>14.9482984542847</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G29" t="n">
-        <v>15.3518142700195</v>
+        <v>15.3518104553223</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G30" t="n">
-        <v>15.1042022705078</v>
+        <v>15.1042032241821</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G31" t="n">
-        <v>15.0033254623413</v>
+        <v>15.0033235549927</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>15.9112281799316</v>
+        <v>15.911229133606</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>17.0575675964355</v>
+        <v>17.0575695037842</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>18.5</v>
       </c>
       <c r="G37" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G38" t="n">
-        <v>16.7090797424316</v>
+        <v>16.7090816497803</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G39" t="n">
-        <v>16.360595703125</v>
+        <v>16.3605937957764</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>16.3514251708984</v>
+        <v>16.3514213562012</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G41" t="n">
-        <v>16.1038112640381</v>
+        <v>16.1038150787354</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>16.8282985687256</v>
+        <v>16.8283004760742</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>16.6357135772705</v>
+        <v>16.6357173919678</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G45" t="n">
-        <v>17.1767883300781</v>
+        <v>17.1767902374268</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G48" t="n">
-        <v>17.4335670471191</v>
+        <v>17.4335708618164</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>18.5</v>
       </c>
       <c r="G49" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G51" t="n">
-        <v>17.2226428985596</v>
+        <v>17.2226409912109</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>18.5</v>
       </c>
       <c r="G53" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>16.8741550445557</v>
+        <v>16.8741569519043</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G55" t="n">
-        <v>17.2593231201172</v>
+        <v>17.2593250274658</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G56" t="n">
-        <v>17.4610805511475</v>
+        <v>17.4610824584961</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>18.5</v>
       </c>
       <c r="G57" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>17.0575675964355</v>
+        <v>17.0575695037842</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G59" t="n">
-        <v>17.0117130279541</v>
+        <v>17.0117149353027</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G60" t="n">
-        <v>16.2138595581055</v>
+        <v>16.2138633728027</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G61" t="n">
-        <v>16.5531768798828</v>
+        <v>16.5531787872314</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>18.5</v>
       </c>
       <c r="G62" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G63" t="n">
-        <v>16.9383525848389</v>
+        <v>16.9383487701416</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>16.7090797424316</v>
+        <v>16.7090816497803</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>17.2868366241455</v>
+        <v>17.2868347167969</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G71" t="n">
-        <v>17.4060573577881</v>
+        <v>17.4060554504395</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>19.75</v>
       </c>
       <c r="G73" t="n">
-        <v>18.1122055053711</v>
+        <v>18.1122035980225</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>18.0204944610596</v>
+        <v>18.0204982757568</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>17.7912273406982</v>
+        <v>17.7912254333496</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G76" t="n">
-        <v>17.5986442565918</v>
+        <v>17.5986423492432</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G79" t="n">
-        <v>18.4331798553467</v>
+        <v>18.4331836700439</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G80" t="n">
-        <v>18.0938625335693</v>
+        <v>18.093864440918</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G81" t="n">
-        <v>18.3231315612793</v>
+        <v>18.3231296539307</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G82" t="n">
-        <v>18.0296688079834</v>
+        <v>18.0296649932861</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>17.8921031951904</v>
+        <v>17.8921051025391</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>18.5</v>
       </c>
       <c r="G86" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G87" t="n">
-        <v>17.1492805480957</v>
+        <v>17.1492767333984</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G90" t="n">
-        <v>17.0759124755859</v>
+        <v>17.0759143829346</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G95" t="n">
-        <v>16.1496658325195</v>
+        <v>16.1496677398682</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G100" t="n">
-        <v>16.1680068969727</v>
+        <v>16.1680107116699</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G101" t="n">
-        <v>16.3514251708984</v>
+        <v>16.3514213562012</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G103" t="n">
-        <v>17.3602027893066</v>
+        <v>17.3602046966553</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G105" t="n">
-        <v>17.1492805480957</v>
+        <v>17.1492767333984</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G106" t="n">
-        <v>16.5164966583252</v>
+        <v>16.5164947509766</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G107" t="n">
-        <v>16.4981555938721</v>
+        <v>16.4981536865234</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G108" t="n">
-        <v>17.2409858703613</v>
+        <v>17.2409820556641</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>17.0117130279541</v>
+        <v>17.0117149353027</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G115" t="n">
-        <v>15.8103513717651</v>
+        <v>15.8103504180908</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G116" t="n">
-        <v>15.8470315933228</v>
+        <v>15.8470363616943</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>17</v>
       </c>
       <c r="G117" t="n">
-        <v>15.5902538299561</v>
+        <v>15.5902509689331</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G120" t="n">
-        <v>15.0675201416016</v>
+        <v>15.0675210952759</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G121" t="n">
-        <v>15.3334693908691</v>
+        <v>15.3334712982178</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>17</v>
       </c>
       <c r="G122" t="n">
-        <v>15.5902538299561</v>
+        <v>15.5902509689331</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G126" t="n">
-        <v>14.8841028213501</v>
+        <v>14.8841047286987</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G128" t="n">
-        <v>14.6823492050171</v>
+        <v>14.6823482513428</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G129" t="n">
-        <v>15.4068374633789</v>
+        <v>15.4068355560303</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>16.3899993896484</v>
       </c>
       <c r="G130" t="n">
-        <v>15.0308351516724</v>
+        <v>15.0308361053467</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>14.6273231506348</v>
+        <v>14.6273241043091</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>14.2604942321777</v>
+        <v>14.2604951858521</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G135" t="n">
-        <v>15.3976669311523</v>
+        <v>15.397665977478</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>15.3151292800903</v>
+        <v>15.3151302337646</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>15.2234239578247</v>
+        <v>15.2234230041504</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G139" t="n">
-        <v>15.3518142700195</v>
+        <v>15.3518104553223</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G140" t="n">
-        <v>15.3151292800903</v>
+        <v>15.3151302337646</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G141" t="n">
-        <v>15.2509346008301</v>
+        <v>15.2509336471558</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G143" t="n">
-        <v>15.2967863082886</v>
+        <v>15.2967882156372</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G144" t="n">
-        <v>15.3793277740479</v>
+        <v>15.3793239593506</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>17.5</v>
       </c>
       <c r="G147" t="n">
-        <v>16.0487880706787</v>
+        <v>16.048791885376</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G148" t="n">
-        <v>16.2138595581055</v>
+        <v>16.2138633728027</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G149" t="n">
-        <v>16.1680068969727</v>
+        <v>16.1680107116699</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>16.140495300293</v>
+        <v>16.1404972076416</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G151" t="n">
-        <v>15.6177663803101</v>
+        <v>15.6177644729614</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G152" t="n">
-        <v>15.3884963989258</v>
+        <v>15.3884954452515</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>15.2234239578247</v>
+        <v>15.2234230041504</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G155" t="n">
-        <v>15.8286933898926</v>
+        <v>15.8286914825439</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G156" t="n">
-        <v>16.076301574707</v>
+        <v>16.0763034820557</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>17.5</v>
       </c>
       <c r="G157" t="n">
-        <v>16.0487880706787</v>
+        <v>16.048791885376</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G158" t="n">
-        <v>16.1771755218506</v>
+        <v>16.1771793365479</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G159" t="n">
-        <v>16.1038112640381</v>
+        <v>16.1038150787354</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G160" t="n">
-        <v>15.8470315933228</v>
+        <v>15.8470363616943</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G162" t="n">
-        <v>15.9845933914185</v>
+        <v>15.9845943450928</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G164" t="n">
-        <v>17.1401062011719</v>
+        <v>17.1401081085205</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G165" t="n">
-        <v>16.8099575042725</v>
+        <v>16.8099594116211</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G166" t="n">
-        <v>16.8099575042725</v>
+        <v>16.8099594116211</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G167" t="n">
-        <v>16.6082038879395</v>
+        <v>16.6082019805908</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>16.8741550445557</v>
+        <v>16.8741569519043</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G169" t="n">
-        <v>16.6448879241943</v>
+        <v>16.6448860168457</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>18.5</v>
       </c>
       <c r="G170" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>17.1492805480957</v>
+        <v>17.1492767333984</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G173" t="n">
-        <v>17.2409858703613</v>
+        <v>17.2409820556641</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>17.2868366241455</v>
+        <v>17.2868347167969</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.2868366241455</v>
+        <v>17.2868347167969</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>17.2868366241455</v>
+        <v>17.2868347167969</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G178" t="n">
-        <v>17.4060573577881</v>
+        <v>17.4060554504395</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>17.2409858703613</v>
+        <v>17.2409820556641</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G180" t="n">
-        <v>17.0300598144531</v>
+        <v>17.0300579071045</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G181" t="n">
-        <v>17.2226428985596</v>
+        <v>17.2226409912109</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G182" t="n">
-        <v>17.4610805511475</v>
+        <v>17.4610824584961</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>17.0575675964355</v>
+        <v>17.0575695037842</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>18.5</v>
       </c>
       <c r="G187" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G188" t="n">
-        <v>17.0300598144531</v>
+        <v>17.0300579071045</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>16.0946407318115</v>
+        <v>16.0946426391602</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G191" t="n">
-        <v>15.7828369140625</v>
+        <v>15.7828359603882</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G192" t="n">
-        <v>15.7828369140625</v>
+        <v>15.7828359603882</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G193" t="n">
-        <v>15.7553253173828</v>
+        <v>15.7553262710571</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>17.25</v>
       </c>
       <c r="G194" t="n">
-        <v>15.8195209503174</v>
+        <v>15.8195199966431</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G195" t="n">
-        <v>15.8286933898926</v>
+        <v>15.8286914825439</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G196" t="n">
-        <v>15.9479074478149</v>
+        <v>15.9479112625122</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G197" t="n">
-        <v>15.8470315933228</v>
+        <v>15.8470363616943</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>15.6361026763916</v>
+        <v>15.6361036300659</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G199" t="n">
-        <v>15.6636171340942</v>
+        <v>15.6636190414429</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G201" t="n">
-        <v>15.5627374649048</v>
+        <v>15.5627384185791</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G202" t="n">
-        <v>15.489372253418</v>
+        <v>15.4893732070923</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G203" t="n">
-        <v>15.6085929870605</v>
+        <v>15.6085948944092</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>15.6361026763916</v>
+        <v>15.6361036300659</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G205" t="n">
-        <v>15.7553253173828</v>
+        <v>15.7553262710571</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>17.25</v>
       </c>
       <c r="G206" t="n">
-        <v>15.8195209503174</v>
+        <v>15.8195199966431</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G207" t="n">
-        <v>16.030445098877</v>
+        <v>16.0304431915283</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G210" t="n">
-        <v>16.0579566955566</v>
+        <v>16.0579605102539</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G211" t="n">
-        <v>15.535228729248</v>
+        <v>15.5352268218994</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G212" t="n">
-        <v>15.5443954467773</v>
+        <v>15.544397354126</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>17</v>
       </c>
       <c r="G214" t="n">
-        <v>15.5902538299561</v>
+        <v>15.5902509689331</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>15.5443954467773</v>
+        <v>15.544397354126</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>15.4068374633789</v>
+        <v>15.4068355560303</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G218" t="n">
-        <v>15.1592264175415</v>
+        <v>15.1592283248901</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G219" t="n">
-        <v>15.233039855957</v>
+        <v>15.2330417633057</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G220" t="n">
-        <v>15.3068513870239</v>
+        <v>15.3068532943726</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>15.54674243927</v>
+        <v>15.5467414855957</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G222" t="n">
-        <v>15.6297836303711</v>
+        <v>15.6297807693481</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G224" t="n">
-        <v>15.5190629959106</v>
+        <v>15.5190620422363</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G225" t="n">
-        <v>14.9746942520142</v>
+        <v>14.9746961593628</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G229" t="n">
-        <v>15.0577344894409</v>
+        <v>15.0577363967896</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G230" t="n">
-        <v>15.7589530944824</v>
+        <v>15.7589540481567</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G231" t="n">
-        <v>16.2202796936035</v>
+        <v>16.2202816009521</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>15.3898906707764</v>
+        <v>15.3898916244507</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>15.5006093978882</v>
+        <v>15.5006084442139</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G237" t="n">
-        <v>15.9434833526611</v>
+        <v>15.943489074707</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>15.7312717437744</v>
+        <v>15.7312726974487</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G240" t="n">
-        <v>16.2202796936035</v>
+        <v>16.2202816009521</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G241" t="n">
-        <v>16.4693984985352</v>
+        <v>16.4693965911865</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>18.5</v>
       </c>
       <c r="G242" t="n">
-        <v>17.0691242218018</v>
+        <v>17.0691204071045</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G244" t="n">
-        <v>17.0229911804199</v>
+        <v>17.0229969024658</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G245" t="n">
-        <v>17.1060314178467</v>
+        <v>17.106029510498</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>18.25</v>
       </c>
       <c r="G247" t="n">
-        <v>16.8384628295898</v>
+        <v>16.8384609222412</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>17.75</v>
       </c>
       <c r="G248" t="n">
-        <v>16.3771324157715</v>
+        <v>16.3771286010742</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>16.9768581390381</v>
+        <v>16.9768619537354</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>16.7923316955566</v>
+        <v>16.7923278808594</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G251" t="n">
-        <v>17.0506687164307</v>
+        <v>17.0506706237793</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>17.6227149963379</v>
+        <v>17.6227169036865</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G253" t="n">
-        <v>17.7795696258545</v>
+        <v>17.7795677185059</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>17.6227149963379</v>
+        <v>17.6227169036865</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>18.7760372161865</v>
+        <v>18.7760334014893</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>18.822172164917</v>
+        <v>18.8221683502197</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G261" t="n">
-        <v>19.4218940734863</v>
+        <v>19.4218921661377</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G262" t="n">
-        <v>19.4957084655762</v>
+        <v>19.4957046508789</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G264" t="n">
-        <v>18.7852630615234</v>
+        <v>18.7852611541748</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>19.3296298980713</v>
+        <v>19.3296279907227</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G266" t="n">
-        <v>19.2004566192627</v>
+        <v>19.2004585266113</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>18.7299041748047</v>
+        <v>18.7299022674561</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G270" t="n">
-        <v>18.8867511749268</v>
+        <v>18.8867530822754</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G271" t="n">
-        <v>18.8129425048828</v>
+        <v>18.8129405975342</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G272" t="n">
-        <v>18.8037166595459</v>
+        <v>18.8037147521973</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G273" t="n">
-        <v>18.6284103393555</v>
+        <v>18.6284122467041</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>18.7299041748047</v>
+        <v>18.7299022674561</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>20</v>
       </c>
       <c r="G275" t="n">
-        <v>18.4531078338623</v>
+        <v>18.4531059265137</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>20</v>
       </c>
       <c r="G276" t="n">
-        <v>18.4531078338623</v>
+        <v>18.4531059265137</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G277" t="n">
-        <v>18.2778015136719</v>
+        <v>18.2778034210205</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>19.5</v>
       </c>
       <c r="G278" t="n">
-        <v>17.9917793273926</v>
+        <v>17.9917812347412</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>19.8700008392334</v>
       </c>
       <c r="G279" t="n">
-        <v>18.3331642150879</v>
+        <v>18.3331604003906</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G280" t="n">
-        <v>18.4069728851318</v>
+        <v>18.4069747924805</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>20</v>
       </c>
       <c r="G281" t="n">
-        <v>18.4531078338623</v>
+        <v>18.4531059265137</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G283" t="n">
-        <v>18.2501220703125</v>
+        <v>18.2501239776611</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G285" t="n">
-        <v>18.1578559875488</v>
+        <v>18.1578598022461</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G286" t="n">
-        <v>18.2039890289307</v>
+        <v>18.2039909362793</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G289" t="n">
-        <v>18.4900150299072</v>
+        <v>18.49001121521</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G292" t="n">
-        <v>18.6007328033447</v>
+        <v>18.6007308959961</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G293" t="n">
-        <v>18.7299041748047</v>
+        <v>18.7299022674561</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>20</v>
       </c>
       <c r="G294" t="n">
-        <v>18.4531078338623</v>
+        <v>18.4531059265137</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>18.9605674743652</v>
+        <v>18.9605693817139</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>18.9974727630615</v>
+        <v>18.9974746704102</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G300" t="n">
-        <v>19.3204021453857</v>
+        <v>19.3204040527344</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G303" t="n">
-        <v>19.1174201965332</v>
+        <v>19.1174182891846</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G305" t="n">
-        <v>18.9697914123535</v>
+        <v>18.9697933197021</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>20.6900005340576</v>
       </c>
       <c r="G306" t="n">
-        <v>19.0897388458252</v>
+        <v>19.0897407531738</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G307" t="n">
-        <v>19.1174201965332</v>
+        <v>19.1174182891846</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>20.8299999237061</v>
       </c>
       <c r="G308" t="n">
-        <v>19.2189064025879</v>
+        <v>19.2189083099365</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>20.4899997711182</v>
       </c>
       <c r="G309" t="n">
-        <v>18.9052104949951</v>
+        <v>18.9052085876465</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G311" t="n">
-        <v>19.2558174133301</v>
+        <v>19.2558193206787</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G313" t="n">
-        <v>19.7817306518555</v>
+        <v>19.7817325592041</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G314" t="n">
-        <v>19.8739986419678</v>
+        <v>19.8740005493164</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G315" t="n">
-        <v>20.2430572509766</v>
+        <v>20.2430610656738</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G321" t="n">
-        <v>20.4737205505371</v>
+        <v>20.4737224578857</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>20.1138896942139</v>
+        <v>20.1138877868652</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G325" t="n">
-        <v>20.5106258392334</v>
+        <v>20.510627746582</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G328" t="n">
-        <v>20.3630027770996</v>
+        <v>20.3630046844482</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>20.390682220459</v>
+        <v>20.3906841278076</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>22.2399997711182</v>
       </c>
       <c r="G330" t="n">
-        <v>20.5198516845703</v>
+        <v>20.5198554992676</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>20.390682220459</v>
+        <v>20.3906841278076</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G333" t="n">
-        <v>20.6767024993896</v>
+        <v>20.6767063140869</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G338" t="n">
-        <v>21.3502445220947</v>
+        <v>21.3502426147461</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>23</v>
       </c>
       <c r="G339" t="n">
-        <v>21.2210750579834</v>
+        <v>21.2210731506348</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>21.1749420166016</v>
+        <v>21.1749439239502</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>23</v>
       </c>
       <c r="G341" t="n">
-        <v>21.2210750579834</v>
+        <v>21.2210731506348</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>22.75</v>
       </c>
       <c r="G342" t="n">
-        <v>20.9904098510742</v>
+        <v>20.990406036377</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>21.1749420166016</v>
+        <v>21.1749439239502</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G344" t="n">
-        <v>20.98118019104</v>
+        <v>20.9811840057373</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>22.7199993133545</v>
       </c>
       <c r="G347" t="n">
-        <v>20.9627304077148</v>
+        <v>20.9627285003662</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G350" t="n">
-        <v>21.2026195526123</v>
+        <v>21.2026233673096</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G351" t="n">
-        <v>21.0826740264893</v>
+        <v>21.0826778411865</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G352" t="n">
-        <v>20.5014019012451</v>
+        <v>20.5013980865479</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G354" t="n">
-        <v>21.0273132324219</v>
+        <v>21.0273170471191</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>22.5599994659424</v>
       </c>
       <c r="G355" t="n">
-        <v>20.8151035308838</v>
+        <v>20.8151073455811</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G358" t="n">
-        <v>21.1011276245117</v>
+        <v>21.1011295318604</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>22.9099998474121</v>
       </c>
       <c r="G361" t="n">
-        <v>21.138032913208</v>
+        <v>21.1380348205566</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G365" t="n">
-        <v>20.5936660766602</v>
+        <v>20.5936679840088</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>21.8700008392334</v>
       </c>
       <c r="G366" t="n">
-        <v>20.1784706115723</v>
+        <v>20.1784744262695</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G368" t="n">
-        <v>20.2707366943359</v>
+        <v>20.2707386016846</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G369" t="n">
-        <v>20.5014019012451</v>
+        <v>20.5013980865479</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G370" t="n">
-        <v>20.1876983642578</v>
+        <v>20.1876964569092</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G371" t="n">
-        <v>20.4921760559082</v>
+        <v>20.4921741485596</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G372" t="n">
-        <v>20.5936660766602</v>
+        <v>20.5936679840088</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G373" t="n">
-        <v>20.141565322876</v>
+        <v>20.1415672302246</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G374" t="n">
-        <v>19.9109001159668</v>
+        <v>19.9109020233154</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G377" t="n">
-        <v>19.7725067138672</v>
+        <v>19.7725048065186</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G378" t="n">
-        <v>20.1323375701904</v>
+        <v>20.1323394775391</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>20.1600189208984</v>
+        <v>20.1600170135498</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>21.8700008392334</v>
       </c>
       <c r="G381" t="n">
-        <v>20.1784706115723</v>
+        <v>20.1784744262695</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>22</v>
       </c>
       <c r="G382" t="n">
-        <v>20.2984199523926</v>
+        <v>20.2984161376953</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G386" t="n">
-        <v>19.5879764556885</v>
+        <v>19.5879726409912</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>21.5300006866455</v>
       </c>
       <c r="G389" t="n">
-        <v>19.8647689819336</v>
+        <v>19.864767074585</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>19.9754848480225</v>
+        <v>19.9754886627197</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G391" t="n">
-        <v>19.541841506958</v>
+        <v>19.5418395996094</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>19.9754848480225</v>
+        <v>19.9754886627197</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>22.2399997711182</v>
       </c>
       <c r="G393" t="n">
-        <v>20.5198516845703</v>
+        <v>20.5198554992676</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G394" t="n">
-        <v>20.4737205505371</v>
+        <v>20.4737224578857</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>22.25</v>
       </c>
       <c r="G395" t="n">
-        <v>20.5290832519531</v>
+        <v>20.5290813446045</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>21.5</v>
       </c>
       <c r="G399" t="n">
-        <v>19.8370895385742</v>
+        <v>19.8370914459229</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G401" t="n">
-        <v>19.9109001159668</v>
+        <v>19.9109020233154</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G406" t="n">
-        <v>20.2707366943359</v>
+        <v>20.2707386016846</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G407" t="n">
-        <v>20.2707366943359</v>
+        <v>20.2707386016846</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>20.2799663543701</v>
+        <v>20.2799644470215</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G409" t="n">
-        <v>19.9939441680908</v>
+        <v>19.9939422607422</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G413" t="n">
-        <v>20.7043876647949</v>
+        <v>20.7043857574463</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G415" t="n">
-        <v>20.7043876647949</v>
+        <v>20.7043857574463</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>22.75</v>
       </c>
       <c r="G419" t="n">
-        <v>20.9904098510742</v>
+        <v>20.990406036377</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>22.75</v>
       </c>
       <c r="G420" t="n">
-        <v>20.9904098510742</v>
+        <v>20.990406036377</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G421" t="n">
-        <v>21.0549926757812</v>
+        <v>21.0549964904785</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>22.75</v>
       </c>
       <c r="G422" t="n">
-        <v>20.9904098510742</v>
+        <v>20.990406036377</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>22.3099994659424</v>
       </c>
       <c r="G423" t="n">
-        <v>20.5844383239746</v>
+        <v>20.5844421386719</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G424" t="n">
-        <v>20.3353233337402</v>
+        <v>20.3353252410889</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G425" t="n">
-        <v>20.2707366943359</v>
+        <v>20.2707386016846</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>20.390682220459</v>
+        <v>20.3906841278076</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>20.1138896942139</v>
+        <v>20.1138877868652</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G428" t="n">
-        <v>20.1969299316406</v>
+        <v>20.1969261169434</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G429" t="n">
-        <v>20.1969299316406</v>
+        <v>20.1969261169434</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G430" t="n">
-        <v>20.2430572509766</v>
+        <v>20.2430610656738</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>20.1600189208984</v>
+        <v>20.1600170135498</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G433" t="n">
-        <v>19.9109001159668</v>
+        <v>19.9109020233154</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>19.7448234558105</v>
+        <v>19.7448253631592</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G436" t="n">
-        <v>19.7079181671143</v>
+        <v>19.7079219818115</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>19.3296298980713</v>
+        <v>19.3296279907227</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G439" t="n">
-        <v>19.7817306518555</v>
+        <v>19.7817325592041</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G441" t="n">
-        <v>19.9570369720459</v>
+        <v>19.9570350646973</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G443" t="n">
-        <v>20.2707366943359</v>
+        <v>20.2707386016846</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G447" t="n">
-        <v>20.2799663543701</v>
+        <v>20.2799644470215</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>20.390682220459</v>
+        <v>20.3906841278076</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>20.390682220459</v>
+        <v>20.3906841278076</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G450" t="n">
-        <v>20.3814582824707</v>
+        <v>20.3814544677734</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G451" t="n">
-        <v>19.8555450439453</v>
+        <v>19.855541229248</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G453" t="n">
-        <v>19.4034423828125</v>
+        <v>19.4034442901611</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G454" t="n">
-        <v>19.1266422271729</v>
+        <v>19.1266441345215</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G458" t="n">
-        <v>18.9974727630615</v>
+        <v>18.9974746704102</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G459" t="n">
-        <v>18.6560916900635</v>
+        <v>18.6560897827148</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G460" t="n">
-        <v>18.8129425048828</v>
+        <v>18.8129405975342</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G461" t="n">
-        <v>18.7114486694336</v>
+        <v>18.7114524841309</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G463" t="n">
-        <v>18.8037166595459</v>
+        <v>18.8037147521973</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G464" t="n">
-        <v>18.8683013916016</v>
+        <v>18.8683052062988</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G466" t="n">
-        <v>18.4346523284912</v>
+        <v>18.4346504211426</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>20.0900001525879</v>
       </c>
       <c r="G467" t="n">
-        <v>18.5361461639404</v>
+        <v>18.5361423492432</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>18.3147087097168</v>
+        <v>18.3147106170654</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>20.25</v>
       </c>
       <c r="G469" t="n">
-        <v>18.6837692260742</v>
+        <v>18.6837711334229</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G470" t="n">
-        <v>18.9605674743652</v>
+        <v>18.9605693817139</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G472" t="n">
-        <v>18.8037166595459</v>
+        <v>18.8037147521973</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G473" t="n">
-        <v>18.8683013916016</v>
+        <v>18.8683052062988</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G474" t="n">
-        <v>18.8497581481934</v>
+        <v>18.8497562408447</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G477" t="n">
-        <v>18.1821823120117</v>
+        <v>18.1821804046631</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G478" t="n">
-        <v>17.7834892272949</v>
+        <v>17.7834911346436</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G479" t="n">
-        <v>17.727855682373</v>
+        <v>17.7278594970703</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G483" t="n">
-        <v>17.7742176055908</v>
+        <v>17.7742195129395</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>19.25</v>
       </c>
       <c r="G484" t="n">
-        <v>17.8483924865723</v>
+        <v>17.8483943939209</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G485" t="n">
-        <v>18.1450939178467</v>
+        <v>18.1450958251953</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G486" t="n">
-        <v>18.3398017883301</v>
+        <v>18.3398056030273</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G487" t="n">
-        <v>18.4603404998779</v>
+        <v>18.4603366851807</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G490" t="n">
-        <v>18.0431022644043</v>
+        <v>18.0431041717529</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G491" t="n">
-        <v>18.1821823120117</v>
+        <v>18.1821804046631</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G492" t="n">
-        <v>18.3676166534424</v>
+        <v>18.3676204681396</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G493" t="n">
-        <v>18.237813949585</v>
+        <v>18.2378120422363</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G494" t="n">
-        <v>18.0987358093262</v>
+        <v>18.0987377166748</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G499" t="n">
-        <v>18.5623321533203</v>
+        <v>18.5623264312744</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G500" t="n">
-        <v>18.488151550293</v>
+        <v>18.4881553649902</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G501" t="n">
-        <v>18.2285423278809</v>
+        <v>18.2285385131836</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G502" t="n">
-        <v>18.2563591003418</v>
+        <v>18.2563571929932</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G503" t="n">
-        <v>18.3212623596191</v>
+        <v>18.3212604522705</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>18.3583450317383</v>
+        <v>18.3583469390869</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G505" t="n">
-        <v>18.3490753173828</v>
+        <v>18.3490772247314</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G507" t="n">
-        <v>18.5808734893799</v>
+        <v>18.5808715820312</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G508" t="n">
-        <v>18.4696102142334</v>
+        <v>18.469612121582</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G509" t="n">
-        <v>18.4696102142334</v>
+        <v>18.469612121582</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G511" t="n">
-        <v>18.3676166534424</v>
+        <v>18.3676204681396</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G512" t="n">
-        <v>18.3490753173828</v>
+        <v>18.3490772247314</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>20.25</v>
       </c>
       <c r="G514" t="n">
-        <v>18.7755813598633</v>
+        <v>18.7755832672119</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>19.0537395477295</v>
+        <v>19.0537414550781</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G516" t="n">
-        <v>19.3318958282471</v>
+        <v>19.3318977355957</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>19.6100540161133</v>
+        <v>19.6100521087646</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>22</v>
       </c>
       <c r="G518" t="n">
-        <v>20.3981647491455</v>
+        <v>20.3981628417969</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G519" t="n">
-        <v>21.1399173736572</v>
+        <v>21.1399154663086</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G520" t="n">
-        <v>21.4180736541748</v>
+        <v>21.4180717468262</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>21.1399173736572</v>
+        <v>21.1399154663086</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>21.2326354980469</v>
+        <v>21.2326335906982</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>21.4644317626953</v>
+        <v>21.4644298553467</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>23</v>
       </c>
       <c r="G525" t="n">
-        <v>21.3253517150879</v>
+        <v>21.3253536224365</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G526" t="n">
-        <v>21.4180736541748</v>
+        <v>21.4180717468262</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>21.6035079956055</v>
+        <v>21.6035118103027</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>23</v>
       </c>
       <c r="G528" t="n">
-        <v>21.3253517150879</v>
+        <v>21.3253536224365</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>21.4180736541748</v>
+        <v>21.4180717468262</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>23</v>
       </c>
       <c r="G532" t="n">
-        <v>21.3253517150879</v>
+        <v>21.3253536224365</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>23</v>
       </c>
       <c r="G534" t="n">
-        <v>21.3253517150879</v>
+        <v>21.3253536224365</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G535" t="n">
-        <v>21.2326354980469</v>
+        <v>21.2326335906982</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>22.5</v>
       </c>
       <c r="G536" t="n">
-        <v>20.861759185791</v>
+        <v>20.8617610931396</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>20.30544090271</v>
+        <v>20.3054447174072</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>20.9081153869629</v>
+        <v>20.9081192016602</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>22.5</v>
       </c>
       <c r="G539" t="n">
-        <v>20.861759185791</v>
+        <v>20.8617610931396</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>22.5</v>
       </c>
       <c r="G540" t="n">
-        <v>20.861759185791</v>
+        <v>20.8617610931396</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G541" t="n">
-        <v>20.30544090271</v>
+        <v>20.3054447174072</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>20.5836048126221</v>
+        <v>20.5836029052734</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G545" t="n">
-        <v>20.9544792175293</v>
+        <v>20.9544773101807</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G546" t="n">
-        <v>20.9081153869629</v>
+        <v>20.9081192016602</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>22</v>
       </c>
       <c r="G550" t="n">
-        <v>20.3981647491455</v>
+        <v>20.3981628417969</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>20.537239074707</v>
+        <v>20.5372409820557</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>22</v>
       </c>
       <c r="G552" t="n">
-        <v>20.3981647491455</v>
+        <v>20.3981628417969</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>21.6035079956055</v>
+        <v>21.6035118103027</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>21.4644317626953</v>
+        <v>21.4644298553467</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>22.0671005249023</v>
+        <v>22.0671043395996</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>21.7425899505615</v>
+        <v>21.7425880432129</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>21.9280242919922</v>
+        <v>21.9280261993408</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>21.8353061676025</v>
+        <v>21.8353080749512</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>23</v>
       </c>
       <c r="G562" t="n">
-        <v>21.3253517150879</v>
+        <v>21.3253536224365</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G565" t="n">
-        <v>20.6763210296631</v>
+        <v>20.6763191223145</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>20.5836048126221</v>
+        <v>20.5836029052734</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>20.9544792175293</v>
+        <v>20.9544773101807</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>22.75</v>
       </c>
       <c r="G569" t="n">
-        <v>21.0935554504395</v>
+        <v>21.0935535430908</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G572" t="n">
-        <v>20.6763210296631</v>
+        <v>20.6763191223145</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>21.75</v>
       </c>
       <c r="G573" t="n">
-        <v>20.1663684844971</v>
+        <v>20.1663703918457</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>20.537239074707</v>
+        <v>20.5372409820557</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>20.7690372467041</v>
+        <v>20.7690391540527</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>22.5</v>
       </c>
       <c r="G580" t="n">
-        <v>20.861759185791</v>
+        <v>20.8617610931396</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>22.5</v>
       </c>
       <c r="G581" t="n">
-        <v>20.861759185791</v>
+        <v>20.8617610931396</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>20.7690372467041</v>
+        <v>20.7690391540527</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>20.4445209503174</v>
+        <v>20.444522857666</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>20.6763210296631</v>
+        <v>20.6763191223145</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G588" t="n">
-        <v>20.5836048126221</v>
+        <v>20.5836029052734</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>20.9544792175293</v>
+        <v>20.9544773101807</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>20.9081153869629</v>
+        <v>20.9081192016602</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>22.5</v>
       </c>
       <c r="G591" t="n">
-        <v>20.861759185791</v>
+        <v>20.8617610931396</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>20.5836048126221</v>
+        <v>20.5836029052734</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>21.1862754821777</v>
+        <v>21.1862773895264</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G595" t="n">
-        <v>21.2326354980469</v>
+        <v>21.2326335906982</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G601" t="n">
-        <v>20.6763210296631</v>
+        <v>20.6763191223145</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>20.7690372467041</v>
+        <v>20.7690391540527</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G603" t="n">
-        <v>20.4445209503174</v>
+        <v>20.444522857666</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G604" t="n">
-        <v>20.2590847015381</v>
+        <v>20.2590827941895</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>20.351806640625</v>
+        <v>20.3518047332764</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>20.6763210296631</v>
+        <v>20.6763191223145</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>20.7690372467041</v>
+        <v>20.7690391540527</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>20.5836048126221</v>
+        <v>20.5836029052734</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>22</v>
       </c>
       <c r="G610" t="n">
-        <v>20.3981647491455</v>
+        <v>20.3981628417969</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>19.9809303283691</v>
+        <v>19.9809284210205</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G614" t="n">
-        <v>18.8683013916016</v>
+        <v>18.8682994842529</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G616" t="n">
-        <v>18.488151550293</v>
+        <v>18.4881553649902</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>20.5</v>
       </c>
       <c r="G618" t="n">
-        <v>19.0073776245117</v>
+        <v>19.0073795318604</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G620" t="n">
-        <v>19.6564140319824</v>
+        <v>19.6564121246338</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G621" t="n">
-        <v>19.6564140319824</v>
+        <v>19.6564121246338</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>21</v>
       </c>
       <c r="G622" t="n">
-        <v>19.4709758758545</v>
+        <v>19.4709739685059</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>20.5836048126221</v>
+        <v>20.5836029052734</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>21.75</v>
       </c>
       <c r="G624" t="n">
-        <v>20.1663684844971</v>
+        <v>20.1663703918457</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G626" t="n">
-        <v>20.30544090271</v>
+        <v>20.3054447174072</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>20.537239074707</v>
+        <v>20.5372409820557</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G632" t="n">
-        <v>20.027286529541</v>
+        <v>20.0272884368896</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>19.6100540161133</v>
+        <v>19.6100521087646</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G636" t="n">
-        <v>19.6564140319824</v>
+        <v>19.6564121246338</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G637" t="n">
-        <v>19.7491302490234</v>
+        <v>19.7491321563721</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>21</v>
       </c>
       <c r="G638" t="n">
-        <v>19.4709758758545</v>
+        <v>19.4709739685059</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>19.6100540161133</v>
+        <v>19.6100521087646</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>21.75</v>
       </c>
       <c r="G643" t="n">
-        <v>20.1663684844971</v>
+        <v>20.1663703918457</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>20.351806640625</v>
+        <v>20.3518047332764</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>20.30544090271</v>
+        <v>20.3054447174072</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>20.4445209503174</v>
+        <v>20.444522857666</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G649" t="n">
-        <v>20.351806640625</v>
+        <v>20.3518047332764</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>22</v>
       </c>
       <c r="G650" t="n">
-        <v>20.3981647491455</v>
+        <v>20.3981628417969</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>21.75</v>
       </c>
       <c r="G651" t="n">
-        <v>20.1663684844971</v>
+        <v>20.1663703918457</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>19.2855358123779</v>
+        <v>19.2855377197266</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G654" t="n">
-        <v>19.4246158599854</v>
+        <v>19.4246139526367</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G655" t="n">
-        <v>19.2855358123779</v>
+        <v>19.2855377197266</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G657" t="n">
-        <v>19.6100540161133</v>
+        <v>19.6100521087646</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>21</v>
       </c>
       <c r="G659" t="n">
-        <v>19.4709758758545</v>
+        <v>19.4709739685059</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>19.6100540161133</v>
+        <v>19.6100521087646</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>21</v>
       </c>
       <c r="G661" t="n">
-        <v>19.4709758758545</v>
+        <v>19.4709739685059</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G664" t="n">
-        <v>19.6100540161133</v>
+        <v>19.6100521087646</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>19.5636959075928</v>
+        <v>19.5636901855469</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G666" t="n">
-        <v>19.6100540161133</v>
+        <v>19.6100521087646</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>19.6100540161133</v>
+        <v>19.6100521087646</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G668" t="n">
-        <v>19.4246158599854</v>
+        <v>19.4246139526367</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>19.5636959075928</v>
+        <v>19.5636901855469</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>19.3318958282471</v>
+        <v>19.3318977355957</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G672" t="n">
-        <v>19.1464557647705</v>
+        <v>19.1464576721191</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>20.75</v>
       </c>
       <c r="G676" t="n">
-        <v>19.2391757965088</v>
+        <v>19.2391777038574</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>19.4246158599854</v>
+        <v>19.4246139526367</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>19.4246158599854</v>
+        <v>19.4246139526367</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>20.027286529541</v>
+        <v>20.0272884368896</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>21.25</v>
       </c>
       <c r="G680" t="n">
-        <v>19.7027740478516</v>
+        <v>19.7027702331543</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>19.5636959075928</v>
+        <v>19.5636901855469</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>19.7491302490234</v>
+        <v>19.7491321563721</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>20.027286529541</v>
+        <v>20.0272884368896</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G685" t="n">
-        <v>20.537239074707</v>
+        <v>20.5372409820557</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>20.30544090271</v>
+        <v>20.3054447174072</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>20.537239074707</v>
+        <v>20.5372409820557</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G688" t="n">
-        <v>20.6763210296631</v>
+        <v>20.6763191223145</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>20.9544792175293</v>
+        <v>20.9544773101807</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>20.9544792175293</v>
+        <v>20.9544773101807</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>20.9081153869629</v>
+        <v>20.9081192016602</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>21.2326354980469</v>
+        <v>21.2326335906982</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>23</v>
       </c>
       <c r="G695" t="n">
-        <v>21.3253517150879</v>
+        <v>21.3253536224365</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G696" t="n">
-        <v>21.1862754821777</v>
+        <v>21.1862773895264</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G697" t="n">
-        <v>21.1399173736572</v>
+        <v>21.1399154663086</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>21.2326354980469</v>
+        <v>21.2326335906982</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>21.4180736541748</v>
+        <v>21.4180717468262</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G701" t="n">
-        <v>21.2789936065674</v>
+        <v>21.2789974212646</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>22.75</v>
       </c>
       <c r="G702" t="n">
-        <v>21.0935554504395</v>
+        <v>21.0935535430908</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G703" t="n">
-        <v>21.1862754821777</v>
+        <v>21.1862773895264</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>22.5</v>
       </c>
       <c r="G706" t="n">
-        <v>20.861759185791</v>
+        <v>20.8617610931396</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>21.5</v>
       </c>
       <c r="G708" t="n">
-        <v>19.9345684051514</v>
+        <v>19.9345703125</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>21.5</v>
       </c>
       <c r="G709" t="n">
-        <v>19.9345684051514</v>
+        <v>19.9345703125</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>21</v>
       </c>
       <c r="G712" t="n">
-        <v>19.4709758758545</v>
+        <v>19.4709739685059</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>19.5636959075928</v>
+        <v>19.5636901855469</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>21</v>
       </c>
       <c r="G715" t="n">
-        <v>19.4709758758545</v>
+        <v>19.4709739685059</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>19.2855358123779</v>
+        <v>19.2855377197266</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>20.75</v>
       </c>
       <c r="G717" t="n">
-        <v>19.2391757965088</v>
+        <v>19.2391777038574</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G719" t="n">
-        <v>15.205904006958</v>
+        <v>15.2059049606323</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G720" t="n">
-        <v>15.5953245162964</v>
+        <v>15.5953226089478</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G721" t="n">
-        <v>14.6681346893311</v>
+        <v>14.6681327819824</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G723" t="n">
-        <v>14.7052202224731</v>
+        <v>14.7052211761475</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>16.5</v>
       </c>
       <c r="G724" t="n">
-        <v>15.2986221313477</v>
+        <v>15.298623085022</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G725" t="n">
-        <v>15.521146774292</v>
+        <v>15.5211458206177</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G727" t="n">
-        <v>15.428427696228</v>
+        <v>15.428430557251</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G728" t="n">
-        <v>15.2244462966919</v>
+        <v>15.2244472503662</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G729" t="n">
-        <v>15.3542537689209</v>
+        <v>15.3542547225952</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>17</v>
       </c>
       <c r="G730" t="n">
-        <v>15.7622175216675</v>
+        <v>15.7622165679932</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G731" t="n">
-        <v>15.6880416870117</v>
+        <v>15.6880407333374</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G732" t="n">
-        <v>15.6880416870117</v>
+        <v>15.6880407333374</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G733" t="n">
-        <v>15.5582370758057</v>
+        <v>15.558235168457</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G735" t="n">
-        <v>15.2800769805908</v>
+        <v>15.2800798416138</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G736" t="n">
-        <v>14.9092044830322</v>
+        <v>14.9092035293579</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G738" t="n">
-        <v>14.4800271987915</v>
+        <v>14.4800281524658</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G739" t="n">
-        <v>14.3120889663696</v>
+        <v>14.3120880126953</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G741" t="n">
-        <v>14.3120889663696</v>
+        <v>14.3120880126953</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G747" t="n">
-        <v>15.3383808135986</v>
+        <v>15.3383798599243</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G751" t="n">
-        <v>13.8269338607788</v>
+        <v>13.8269329071045</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G753" t="n">
-        <v>13.6403360366821</v>
+        <v>13.6403341293335</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G754" t="n">
-        <v>14.2374505996704</v>
+        <v>14.2374496459961</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G755" t="n">
-        <v>14.0695104598999</v>
+        <v>14.0695114135742</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G756" t="n">
-        <v>14.0508527755737</v>
+        <v>14.0508518218994</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G757" t="n">
-        <v>14.1254920959473</v>
+        <v>14.1254911422729</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G758" t="n">
-        <v>13.8642520904541</v>
+        <v>13.8642511367798</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G761" t="n">
-        <v>13.6963148117065</v>
+        <v>13.6963157653809</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G762" t="n">
-        <v>13.9575519561768</v>
+        <v>13.9575529098511</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G763" t="n">
-        <v>14.2374505996704</v>
+        <v>14.2374496459961</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G764" t="n">
-        <v>14.1068305969238</v>
+        <v>14.1068315505981</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G768" t="n">
-        <v>14.6479663848877</v>
+        <v>14.6479654312134</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>15.1144638061523</v>
+        <v>15.1144618988037</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>15.1144638061523</v>
+        <v>15.1144618988037</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>16</v>
       </c>
       <c r="G772" t="n">
-        <v>14.927864074707</v>
+        <v>14.9278631210327</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>16</v>
       </c>
       <c r="G773" t="n">
-        <v>14.927864074707</v>
+        <v>14.9278631210327</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G776" t="n">
-        <v>15.0025024414062</v>
+        <v>15.0025033950806</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G777" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G778" t="n">
-        <v>15.0584831237793</v>
+        <v>15.058482170105</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G780" t="n">
-        <v>15.0958013534546</v>
+        <v>15.0958023071289</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G781" t="n">
-        <v>15.4316816329956</v>
+        <v>15.4316825866699</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>17</v>
       </c>
       <c r="G782" t="n">
-        <v>15.8608541488647</v>
+        <v>15.8608551025391</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>16.7005462646484</v>
+        <v>16.7005443572998</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>18</v>
       </c>
       <c r="G785" t="n">
-        <v>16.7938499450684</v>
+        <v>16.7938480377197</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G786" t="n">
-        <v>16.3833312988281</v>
+        <v>16.3833293914795</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>15.7675552368164</v>
+        <v>15.7675561904907</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>17</v>
       </c>
       <c r="G793" t="n">
-        <v>15.8608541488647</v>
+        <v>15.8608551025391</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G795" t="n">
-        <v>16.0474548339844</v>
+        <v>16.047456741333</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G796" t="n">
-        <v>16.1407527923584</v>
+        <v>16.1407489776611</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G799" t="n">
-        <v>16.178071975708</v>
+        <v>16.1780738830566</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="n">
-        <v>16.3273487091064</v>
+        <v>16.3273525238037</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G803" t="n">
-        <v>16.122091293335</v>
+        <v>16.1220932006836</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G804" t="n">
-        <v>16.122091293335</v>
+        <v>16.1220932006836</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>16.7005462646484</v>
+        <v>16.7005443572998</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>16.6072463989258</v>
+        <v>16.6072483062744</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>15.7675552368164</v>
+        <v>15.7675561904907</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G812" t="n">
-        <v>15.7488956451416</v>
+        <v>15.7488965988159</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>15.7675552368164</v>
+        <v>15.7675561904907</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G814" t="n">
-        <v>15.8421964645386</v>
+        <v>15.8421936035156</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G815" t="n">
-        <v>15.7488956451416</v>
+        <v>15.7488965988159</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>17</v>
       </c>
       <c r="G816" t="n">
-        <v>15.8608541488647</v>
+        <v>15.8608551025391</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G817" t="n">
-        <v>15.8235349655151</v>
+        <v>15.8235340118408</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G818" t="n">
-        <v>16.0101318359375</v>
+        <v>16.0101356506348</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G820" t="n">
-        <v>15.8981781005859</v>
+        <v>15.8981761932373</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G821" t="n">
-        <v>16.0101318359375</v>
+        <v>16.0101356506348</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>16.2340526580811</v>
+        <v>16.2340507507324</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G823" t="n">
-        <v>16.2900314331055</v>
+        <v>16.2900295257568</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>16.4206466674805</v>
+        <v>16.4206504821777</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G826" t="n">
-        <v>16.6632289886475</v>
+        <v>16.6632251739502</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>17.3536415100098</v>
+        <v>17.3536396026611</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G829" t="n">
-        <v>18.1560134887695</v>
+        <v>18.1560115814209</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G830" t="n">
-        <v>18.1373538970947</v>
+        <v>18.1373558044434</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G832" t="n">
-        <v>17.988073348999</v>
+        <v>17.9880771636963</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>18</v>
       </c>
       <c r="G837" t="n">
-        <v>16.7938499450684</v>
+        <v>16.7938480377197</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G838" t="n">
-        <v>16.6259078979492</v>
+        <v>16.6259059906006</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>16.6072463989258</v>
+        <v>16.6072483062744</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>16.6072463989258</v>
+        <v>16.6072483062744</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G841" t="n">
-        <v>16.6632289886475</v>
+        <v>16.6632251739502</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G842" t="n">
-        <v>16.5326061248779</v>
+        <v>16.5326099395752</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G843" t="n">
-        <v>16.8498268127441</v>
+        <v>16.8498249053955</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G844" t="n">
-        <v>16.8498268127441</v>
+        <v>16.8498249053955</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G845" t="n">
-        <v>16.7192096710205</v>
+        <v>16.7192077636719</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G846" t="n">
-        <v>16.9431228637695</v>
+        <v>16.9431247711182</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G847" t="n">
-        <v>17.0364265441895</v>
+        <v>17.0364246368408</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G849" t="n">
-        <v>16.6445713043213</v>
+        <v>16.644567489624</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>17</v>
       </c>
       <c r="G853" t="n">
-        <v>15.8608541488647</v>
+        <v>15.8608551025391</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>16.5</v>
       </c>
       <c r="G854" t="n">
-        <v>15.394359588623</v>
+        <v>15.3943586349487</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G855" t="n">
-        <v>15.4130201339722</v>
+        <v>15.4130210876465</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G856" t="n">
-        <v>15.3570394515991</v>
+        <v>15.3570404052734</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G857" t="n">
-        <v>15.4316816329956</v>
+        <v>15.4316825866699</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G858" t="n">
-        <v>15.0771417617798</v>
+        <v>15.0771427154541</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G860" t="n">
-        <v>14.7039470672607</v>
+        <v>14.7039461135864</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G861" t="n">
-        <v>14.9838428497314</v>
+        <v>14.9838438034058</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G863" t="n">
-        <v>14.8718824386597</v>
+        <v>14.8718814849854</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G866" t="n">
-        <v>14.4053859710693</v>
+        <v>14.405387878418</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G868" t="n">
-        <v>14.2747688293457</v>
+        <v>14.27476978302</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>15.5</v>
       </c>
       <c r="G872" t="n">
-        <v>14.4613676071167</v>
+        <v>14.4613666534424</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>14.3680686950684</v>
+        <v>14.368067741394</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G874" t="n">
-        <v>14.5360069274902</v>
+        <v>14.5360059738159</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>14.6479663848877</v>
+        <v>14.6479654312134</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>16.5</v>
       </c>
       <c r="G878" t="n">
-        <v>15.394359588623</v>
+        <v>15.3943586349487</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G879" t="n">
-        <v>15.4316816329956</v>
+        <v>15.4316825866699</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G880" t="n">
-        <v>15.3570394515991</v>
+        <v>15.3570404052734</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>15.301061630249</v>
+        <v>15.3010606765747</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G882" t="n">
-        <v>15.282398223877</v>
+        <v>15.2824010848999</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G884" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G887" t="n">
-        <v>14.9092044830322</v>
+        <v>14.9092035293579</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>15.4876585006714</v>
+        <v>15.4876613616943</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G890" t="n">
-        <v>15.4316816329956</v>
+        <v>15.4316825866699</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>16.5</v>
       </c>
       <c r="G891" t="n">
-        <v>15.394359588623</v>
+        <v>15.3943586349487</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G893" t="n">
-        <v>15.3197193145752</v>
+        <v>15.3197183609009</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G894" t="n">
-        <v>15.2264213562012</v>
+        <v>15.2264204025269</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G895" t="n">
-        <v>15.2264213562012</v>
+        <v>15.2264204025269</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G896" t="n">
-        <v>15.0958013534546</v>
+        <v>15.0958023071289</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G897" t="n">
-        <v>15.0025024414062</v>
+        <v>15.0025033950806</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G899" t="n">
-        <v>14.8718824386597</v>
+        <v>14.8718814849854</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G901" t="n">
-        <v>14.7785844802856</v>
+        <v>14.77858543396</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G906" t="n">
-        <v>14.9092044830322</v>
+        <v>14.9092035293579</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G907" t="n">
-        <v>14.9092044830322</v>
+        <v>14.9092035293579</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G909" t="n">
-        <v>14.7785844802856</v>
+        <v>14.77858543396</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G912" t="n">
-        <v>14.6852836608887</v>
+        <v>14.6852855682373</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G915" t="n">
-        <v>14.5173482894897</v>
+        <v>14.5173473358154</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>15.5</v>
       </c>
       <c r="G916" t="n">
-        <v>14.4613676071167</v>
+        <v>14.4613666534424</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G918" t="n">
-        <v>14.2001295089722</v>
+        <v>14.2001304626465</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>15</v>
       </c>
       <c r="G920" t="n">
-        <v>13.9948711395264</v>
+        <v>13.994873046875</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G921" t="n">
-        <v>13.8082733154297</v>
+        <v>13.808274269104</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G922" t="n">
-        <v>13.6776561737061</v>
+        <v>13.6776552200317</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G923" t="n">
-        <v>14.3307495117188</v>
+        <v>14.3307476043701</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G925" t="n">
-        <v>14.2747688293457</v>
+        <v>14.27476978302</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G926" t="n">
-        <v>14.3307495117188</v>
+        <v>14.3307476043701</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G927" t="n">
-        <v>14.0695104598999</v>
+        <v>14.0695114135742</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G933" t="n">
-        <v>14.1441507339478</v>
+        <v>14.1441516876221</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G934" t="n">
-        <v>13.8082733154297</v>
+        <v>13.808274269104</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G935" t="n">
-        <v>13.9202337265015</v>
+        <v>13.9202318191528</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G936" t="n">
-        <v>14.1068305969238</v>
+        <v>14.1068315505981</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>14.3680686950684</v>
+        <v>14.368067741394</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G944" t="n">
-        <v>14.6479663848877</v>
+        <v>14.6479654312134</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G945" t="n">
-        <v>14.4986877441406</v>
+        <v>14.4986867904663</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G946" t="n">
-        <v>14.7039470672607</v>
+        <v>14.7039461135864</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>14.3680686950684</v>
+        <v>14.368067741394</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G949" t="n">
-        <v>14.2747688293457</v>
+        <v>14.27476978302</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G950" t="n">
-        <v>13.901572227478</v>
+        <v>13.9015712738037</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G951" t="n">
-        <v>15.2637414932251</v>
+        <v>15.2637405395508</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G954" t="n">
-        <v>14.6479663848877</v>
+        <v>14.6479654312134</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G955" t="n">
-        <v>14.0881729125977</v>
+        <v>14.088171005249</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G958" t="n">
-        <v>14.0695104598999</v>
+        <v>14.0695114135742</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G959" t="n">
-        <v>14.0135316848755</v>
+        <v>14.0135326385498</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>14.0881729125977</v>
+        <v>14.088171005249</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>15</v>
       </c>
       <c r="G961" t="n">
-        <v>13.9948711395264</v>
+        <v>13.994873046875</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G962" t="n">
-        <v>14.3307495117188</v>
+        <v>14.3307476043701</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G963" t="n">
-        <v>14.4053859710693</v>
+        <v>14.405387878418</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G964" t="n">
-        <v>14.3307495117188</v>
+        <v>14.3307476043701</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G965" t="n">
-        <v>14.3307495117188</v>
+        <v>14.3307476043701</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G966" t="n">
-        <v>14.2747688293457</v>
+        <v>14.27476978302</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>14.6479663848877</v>
+        <v>14.6479654312134</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G972" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>16</v>
       </c>
       <c r="G973" t="n">
-        <v>14.927864074707</v>
+        <v>14.9278631210327</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G975" t="n">
-        <v>14.4986877441406</v>
+        <v>14.4986867904663</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G977" t="n">
-        <v>14.6479663848877</v>
+        <v>14.6479654312134</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G979" t="n">
-        <v>14.8905429840088</v>
+        <v>14.8905439376831</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G980" t="n">
-        <v>14.8905429840088</v>
+        <v>14.8905439376831</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G981" t="n">
-        <v>15.0958013534546</v>
+        <v>15.0958023071289</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G983" t="n">
-        <v>15.1144638061523</v>
+        <v>15.1144618988037</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G984" t="n">
-        <v>15.1891012191772</v>
+        <v>15.1891002655029</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G985" t="n">
-        <v>15.0584831237793</v>
+        <v>15.058482170105</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G986" t="n">
-        <v>15.0584831237793</v>
+        <v>15.058482170105</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G989" t="n">
-        <v>14.9552383422852</v>
+        <v>14.9552392959595</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G990" t="n">
-        <v>14.8045568466187</v>
+        <v>14.8045558929443</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G995" t="n">
-        <v>15.5768060684204</v>
+        <v>15.5768070220947</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G998" t="n">
-        <v>15.5768060684204</v>
+        <v>15.5768070220947</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G999" t="n">
-        <v>15.5956382751465</v>
+        <v>15.5956401824951</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1000" t="n">
-        <v>15.5956382751465</v>
+        <v>15.5956401824951</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1002" t="n">
-        <v>15.4261207580566</v>
+        <v>15.426121711731</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1006" t="n">
-        <v>15.6521482467651</v>
+        <v>15.6521453857422</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1007" t="n">
-        <v>15.6521482467651</v>
+        <v>15.6521453857422</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1009" t="n">
-        <v>16.066520690918</v>
+        <v>16.0665225982666</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1011" t="n">
-        <v>15.5014619827271</v>
+        <v>15.5014629364014</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>16.5</v>
       </c>
       <c r="G1012" t="n">
-        <v>15.5391321182251</v>
+        <v>15.5391330718994</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1014" t="n">
-        <v>15.5768060684204</v>
+        <v>15.5768070220947</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1015" t="n">
-        <v>15.4261207580566</v>
+        <v>15.426121711731</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1016" t="n">
-        <v>15.9346742630005</v>
+        <v>15.9346723556519</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1019" t="n">
-        <v>15.5014619827271</v>
+        <v>15.5014629364014</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1022" t="n">
-        <v>15.5956382751465</v>
+        <v>15.5956401824951</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1024" t="n">
-        <v>15.3319454193115</v>
+        <v>15.3319444656372</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.5956382751465</v>
+        <v>15.5956401824951</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.4826278686523</v>
+        <v>15.482626914978</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1028" t="n">
-        <v>15.3319454193115</v>
+        <v>15.3319444656372</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1030" t="n">
-        <v>15.0117454528809</v>
+        <v>15.0117425918579</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1034" t="n">
-        <v>14.8045568466187</v>
+        <v>14.8045558929443</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1036" t="n">
-        <v>14.4090137481689</v>
+        <v>14.4090147018433</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1038" t="n">
-        <v>13.843955039978</v>
+        <v>13.8439540863037</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>15</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.1264839172363</v>
+        <v>14.126485824585</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1041" t="n">
-        <v>14.6915454864502</v>
+        <v>14.6915445327759</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1048" t="n">
-        <v>14.522027015686</v>
+        <v>14.5220260620117</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1049" t="n">
-        <v>14.2394962310791</v>
+        <v>14.2394971847534</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1050" t="n">
-        <v>14.1829919815063</v>
+        <v>14.182991027832</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1051" t="n">
-        <v>13.9569664001465</v>
+        <v>13.9569654464722</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1053" t="n">
-        <v>13.0528717041016</v>
+        <v>13.0528707504272</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1058" t="n">
-        <v>12.3371295928955</v>
+        <v>12.3371305465698</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1059" t="n">
-        <v>12.0922727584839</v>
+        <v>12.0922698974609</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>11.8662462234497</v>
+        <v>11.866247177124</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1061" t="n">
-        <v>11.3953657150269</v>
+        <v>11.3953647613525</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G1065" t="n">
-        <v>9.53066730499268</v>
+        <v>9.53066825866699</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G1067" t="n">
-        <v>9.35173320770264</v>
+        <v>9.35173416137695</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.04267883300781</v>
+        <v>8.0426778793335</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1070" t="n">
-        <v>9.04094982147217</v>
+        <v>9.0409517288208</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1072" t="n">
-        <v>10.6796236038208</v>
+        <v>10.6796226501465</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1074" t="n">
-        <v>12.8080129623413</v>
+        <v>12.8080139160156</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1077" t="n">
-        <v>10.8491401672363</v>
+        <v>10.8491411209106</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1078" t="n">
-        <v>10.6796236038208</v>
+        <v>10.6796226501465</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1082" t="n">
-        <v>10.2652444839478</v>
+        <v>10.2652454376221</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1084" t="n">
-        <v>10.6607875823975</v>
+        <v>10.6607856750488</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1085" t="n">
-        <v>11.0374927520752</v>
+        <v>11.0374937057495</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>11.5</v>
       </c>
       <c r="G1086" t="n">
-        <v>10.830304145813</v>
+        <v>10.8303060531616</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1089" t="n">
-        <v>9.81319808959961</v>
+        <v>9.81319713592529</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1094" t="n">
-        <v>10.6984567642212</v>
+        <v>10.6984577178955</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1102" t="n">
-        <v>10.6607875823975</v>
+        <v>10.6607856750488</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1104" t="n">
-        <v>10.6607875823975</v>
+        <v>10.6607856750488</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1106" t="n">
-        <v>10.6984567642212</v>
+        <v>10.6984577178955</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>10.9244804382324</v>
+        <v>10.9244813919067</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>11.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>10.830304145813</v>
+        <v>10.8303060531616</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>10.9244804382324</v>
+        <v>10.9244813919067</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1114" t="n">
-        <v>10.8679752349854</v>
+        <v>10.8679761886597</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1116" t="n">
-        <v>11.489541053772</v>
+        <v>11.4895401000977</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1117" t="n">
-        <v>11.489541053772</v>
+        <v>11.4895401000977</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1118" t="n">
-        <v>11.489541053772</v>
+        <v>11.4895401000977</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1120" t="n">
-        <v>11.3388576507568</v>
+        <v>11.3388586044312</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1124" t="n">
-        <v>12.205283164978</v>
+        <v>12.2052822113037</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>12.5</v>
       </c>
       <c r="G1127" t="n">
-        <v>11.7720708847046</v>
+        <v>11.7720699310303</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1128" t="n">
-        <v>11.1505060195923</v>
+        <v>11.150505065918</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1130" t="n">
-        <v>11.1128358840942</v>
+        <v>11.1128349304199</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1131" t="n">
-        <v>11.1128358840942</v>
+        <v>11.1128349304199</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1133" t="n">
-        <v>10.6607875823975</v>
+        <v>10.6607856750488</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>10.8114700317383</v>
+        <v>10.811469078064</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>11.5</v>
       </c>
       <c r="G1140" t="n">
-        <v>10.830304145813</v>
+        <v>10.8303060531616</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1141" t="n">
-        <v>10.7172918319702</v>
+        <v>10.7172927856445</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1143" t="n">
-        <v>10.7172918319702</v>
+        <v>10.7172927856445</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1148" t="n">
-        <v>10.3405857086182</v>
+        <v>10.3405866622925</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.3782577514648</v>
+        <v>10.3782587051392</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1150" t="n">
-        <v>10.5854444503784</v>
+        <v>10.5854454040527</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1153" t="n">
-        <v>11.1128358840942</v>
+        <v>11.1128349304199</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1154" t="n">
-        <v>11.1316690444946</v>
+        <v>11.1316699981689</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.2635183334351</v>
+        <v>11.2635173797607</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1157" t="n">
-        <v>10.9998226165771</v>
+        <v>10.9998235702515</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1158" t="n">
-        <v>11.1505060195923</v>
+        <v>11.150505065918</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1159" t="n">
-        <v>10.9056463241577</v>
+        <v>10.905647277832</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1160" t="n">
-        <v>10.8491401672363</v>
+        <v>10.8491411209106</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1162" t="n">
-        <v>10.52894115448</v>
+        <v>10.5289402008057</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1166" t="n">
-        <v>10.7172918319702</v>
+        <v>10.7172927856445</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>11.5</v>
       </c>
       <c r="G1168" t="n">
-        <v>10.830304145813</v>
+        <v>10.8303060531616</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1169" t="n">
-        <v>10.6796236038208</v>
+        <v>10.6796226501465</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1170" t="n">
-        <v>10.9998226165771</v>
+        <v>10.9998235702515</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>11.3953657150269</v>
+        <v>11.3953647613525</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1174" t="n">
-        <v>11.3388576507568</v>
+        <v>11.3388586044312</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1176" t="n">
-        <v>11.3576946258545</v>
+        <v>11.3576927185059</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>12.5</v>
       </c>
       <c r="G1179" t="n">
-        <v>11.7720708847046</v>
+        <v>11.7720699310303</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>12.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>11.7720708847046</v>
+        <v>11.7720699310303</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1181" t="n">
-        <v>11.546046257019</v>
+        <v>11.5460472106934</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>12.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>11.7720708847046</v>
+        <v>11.7720699310303</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1186" t="n">
-        <v>11.5837173461914</v>
+        <v>11.58371925354</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1188" t="n">
-        <v>11.6590585708618</v>
+        <v>11.6590595245361</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1191" t="n">
-        <v>12.1487760543823</v>
+        <v>12.1487770080566</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1192" t="n">
-        <v>12.0546007156372</v>
+        <v>12.0545997619629</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1196" t="n">
-        <v>11.7343997955322</v>
+        <v>11.7344007492065</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1197" t="n">
-        <v>11.6590585708618</v>
+        <v>11.6590595245361</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>11.6778945922852</v>
+        <v>11.6778926849365</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1200" t="n">
-        <v>11.1316690444946</v>
+        <v>11.1316699981689</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1201" t="n">
-        <v>11.1693391799927</v>
+        <v>11.1693410873413</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1202" t="n">
-        <v>11.546046257019</v>
+        <v>11.5460472106934</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1204" t="n">
-        <v>12.5631542205811</v>
+        <v>12.5631532669067</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1206" t="n">
-        <v>13.2977304458618</v>
+        <v>13.2977313995361</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1210" t="n">
-        <v>13.3354005813599</v>
+        <v>13.3354015350342</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1211" t="n">
-        <v>13.3730726242065</v>
+        <v>13.3730716705322</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1212" t="n">
-        <v>13.0152006149292</v>
+        <v>13.0152015686035</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1213" t="n">
-        <v>13.2412261962891</v>
+        <v>13.2412252426147</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1214" t="n">
-        <v>13.2412261962891</v>
+        <v>13.2412252426147</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1217" t="n">
-        <v>13.3165664672852</v>
+        <v>13.3165655136108</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1223" t="n">
-        <v>13.0340366363525</v>
+        <v>13.0340375900269</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1224" t="n">
-        <v>13.3919076919556</v>
+        <v>13.3919067382812</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1227" t="n">
-        <v>11.9415893554688</v>
+        <v>11.9415874481201</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1228" t="n">
-        <v>11.6778945922852</v>
+        <v>11.6778926849365</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1229" t="n">
-        <v>11.5837173461914</v>
+        <v>11.58371925354</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>11.8662462234497</v>
+        <v>11.866247177124</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1231" t="n">
-        <v>11.9792604446411</v>
+        <v>11.9792594909668</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.8662462234497</v>
+        <v>11.866247177124</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1234" t="n">
-        <v>12.0546007156372</v>
+        <v>12.0545997619629</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1235" t="n">
-        <v>12.3559656143188</v>
+        <v>12.3559646606445</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1236" t="n">
-        <v>12.7703428268433</v>
+        <v>12.7703418731689</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1237" t="n">
-        <v>12.8080129623413</v>
+        <v>12.8080139160156</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1238" t="n">
-        <v>12.7326717376709</v>
+        <v>12.7326726913452</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1239" t="n">
-        <v>12.9586954116821</v>
+        <v>12.9586963653564</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1241" t="n">
-        <v>13.3542375564575</v>
+        <v>13.3542366027832</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1243" t="n">
-        <v>13.3354005813599</v>
+        <v>13.3354015350342</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1244" t="n">
-        <v>13.2977304458618</v>
+        <v>13.2977313995361</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>14</v>
       </c>
       <c r="G1247" t="n">
-        <v>13.3167543411255</v>
+        <v>13.3167552947998</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>14</v>
       </c>
       <c r="G1249" t="n">
-        <v>13.3167543411255</v>
+        <v>13.3167552947998</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>13.4118747711182</v>
+        <v>13.4118757247925</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>14.5</v>
       </c>
       <c r="G1253" t="n">
-        <v>13.7923526763916</v>
+        <v>13.7923536300659</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1257" t="n">
-        <v>14.1157608032227</v>
+        <v>14.1157598495483</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1258" t="n">
-        <v>13.8874731063843</v>
+        <v>13.8874740600586</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>14.5</v>
       </c>
       <c r="G1261" t="n">
-        <v>13.7923526763916</v>
+        <v>13.7923536300659</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1264" t="n">
-        <v>13.4499235153198</v>
+        <v>13.4499216079712</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G1269" t="n">
-        <v>13.6211376190186</v>
+        <v>13.6211385726929</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1272" t="n">
-        <v>14.0396642684937</v>
+        <v>14.039665222168</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1276" t="n">
-        <v>14.8957414627075</v>
+        <v>14.8957405090332</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1277" t="n">
-        <v>14.9337892532349</v>
+        <v>14.9337882995605</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1279" t="n">
-        <v>16.2274150848389</v>
+        <v>16.2274169921875</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1280" t="n">
-        <v>16.0752277374268</v>
+        <v>16.0752258300781</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1281" t="n">
-        <v>16.0752277374268</v>
+        <v>16.0752258300781</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1282" t="n">
-        <v>15.7137718200684</v>
+        <v>15.7137699127197</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1283" t="n">
-        <v>15.8469381332397</v>
+        <v>15.8469390869141</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>16.5</v>
       </c>
       <c r="G1284" t="n">
-        <v>15.6947450637817</v>
+        <v>15.6947460174561</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1285" t="n">
-        <v>15.504506111145</v>
+        <v>15.5045051574707</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1287" t="n">
-        <v>15.6376762390137</v>
+        <v>15.6376752853394</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1288" t="n">
-        <v>15.2381715774536</v>
+        <v>15.2381725311279</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1289" t="n">
-        <v>15.3332920074463</v>
+        <v>15.3332929611206</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1290" t="n">
-        <v>15.504506111145</v>
+        <v>15.5045051574707</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1291" t="n">
-        <v>15.6186494827271</v>
+        <v>15.6186504364014</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1292" t="n">
-        <v>15.7518167495728</v>
+        <v>15.7518186569214</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1295" t="n">
-        <v>16.664966583252</v>
+        <v>16.6649684906006</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1296" t="n">
-        <v>16.5698490142822</v>
+        <v>16.5698471069336</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1297" t="n">
-        <v>16.5318012237549</v>
+        <v>16.5317993164062</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1298" t="n">
-        <v>16.6078929901123</v>
+        <v>16.6078968048096</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1299" t="n">
-        <v>16.5888690948486</v>
+        <v>16.5888710021973</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1300" t="n">
-        <v>17.0454483032227</v>
+        <v>17.045446395874</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1301" t="n">
-        <v>17.0264225006104</v>
+        <v>17.026424407959</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1305" t="n">
-        <v>16.3225364685059</v>
+        <v>16.3225383758545</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1309" t="n">
-        <v>16.5508251190186</v>
+        <v>16.5508232116699</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1310" t="n">
-        <v>16.5698490142822</v>
+        <v>16.5698471069336</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1311" t="n">
-        <v>16.5698490142822</v>
+        <v>16.5698471069336</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1313" t="n">
-        <v>16.81715965271</v>
+        <v>16.8171615600586</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1314" t="n">
-        <v>16.5318012237549</v>
+        <v>16.5317993164062</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1319" t="n">
-        <v>18.1868801116943</v>
+        <v>18.186882019043</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>20.5</v>
       </c>
       <c r="G1320" t="n">
-        <v>19.499532699585</v>
+        <v>19.4995365142822</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>20.1653709411621</v>
+        <v>20.1653728485107</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.6422138214111</v>
+        <v>19.6422119140625</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1324" t="n">
-        <v>20.5934104919434</v>
+        <v>20.5934085845947</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1325" t="n">
-        <v>20.3556118011475</v>
+        <v>20.3556098937988</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1327" t="n">
-        <v>19.8324527740479</v>
+        <v>19.8324546813965</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>20.75</v>
       </c>
       <c r="G1328" t="n">
-        <v>19.7373313903809</v>
+        <v>19.7373332977295</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>20.403169631958</v>
+        <v>20.4031677246094</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>20.4982891082764</v>
+        <v>20.4982872009277</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1335" t="n">
-        <v>20.8312072753906</v>
+        <v>20.831205368042</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>19.9275722503662</v>
+        <v>19.9275741577148</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>20.75</v>
       </c>
       <c r="G1340" t="n">
-        <v>19.7373313903809</v>
+        <v>19.7373332977295</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1341" t="n">
-        <v>19.8324527740479</v>
+        <v>19.8324546813965</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1343" t="n">
-        <v>20.7836494445801</v>
+        <v>20.7836475372314</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1344" t="n">
-        <v>20.3556118011475</v>
+        <v>20.3556098937988</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1346" t="n">
-        <v>19.8324527740479</v>
+        <v>19.8324546813965</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1350" t="n">
-        <v>19.3568572998047</v>
+        <v>19.3568553924561</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1352" t="n">
-        <v>19.3568572998047</v>
+        <v>19.3568553924561</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>19.4044151306152</v>
+        <v>19.4044132232666</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1354" t="n">
-        <v>19.6897754669189</v>
+        <v>19.6897735595703</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1357" t="n">
-        <v>19.6897754669189</v>
+        <v>19.6897735595703</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1358" t="n">
-        <v>19.6897754669189</v>
+        <v>19.6897735595703</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1359" t="n">
-        <v>20.1178131103516</v>
+        <v>20.1178112030029</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1360" t="n">
-        <v>20.3556118011475</v>
+        <v>20.3556098937988</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1364" t="n">
-        <v>20.1178131103516</v>
+        <v>20.1178112030029</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1365" t="n">
-        <v>20.1178131103516</v>
+        <v>20.1178112030029</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1366" t="n">
-        <v>19.3568572998047</v>
+        <v>19.3568553924561</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1367" t="n">
-        <v>19.6897754669189</v>
+        <v>19.6897735595703</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1371" t="n">
-        <v>20.3556118011475</v>
+        <v>20.3556098937988</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1373" t="n">
-        <v>20.4982891082764</v>
+        <v>20.4982872009277</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1385" t="n">
-        <v>21.829963684082</v>
+        <v>21.8299655914307</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1388" t="n">
-        <v>20.7836494445801</v>
+        <v>20.7836475372314</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1389" t="n">
-        <v>20.7836494445801</v>
+        <v>20.7836475372314</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>22.1628818511963</v>
+        <v>22.1628837585449</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1398" t="n">
-        <v>22.6384811401367</v>
+        <v>22.6384830474854</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>23.161642074585</v>
+        <v>23.1616401672363</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1400" t="n">
-        <v>22.4958038330078</v>
+        <v>22.4958019256592</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1404" t="n">
-        <v>21.829963684082</v>
+        <v>21.8299655914307</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1408" t="n">
-        <v>21.2592487335205</v>
+        <v>21.2592468261719</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1411" t="n">
-        <v>21.2592487335205</v>
+        <v>21.2592468261719</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1412" t="n">
-        <v>21.2592487335205</v>
+        <v>21.2592468261719</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1414" t="n">
-        <v>21.7824058532715</v>
+        <v>21.7824039459229</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1415" t="n">
-        <v>21.7824058532715</v>
+        <v>21.7824039459229</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1416" t="n">
-        <v>22.6384811401367</v>
+        <v>22.6384830474854</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1417" t="n">
-        <v>24.3506393432617</v>
+        <v>24.3506374359131</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>24.5</v>
       </c>
       <c r="G1419" t="n">
-        <v>23.3043212890625</v>
+        <v>23.3043193817139</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>24.5</v>
       </c>
       <c r="G1420" t="n">
-        <v>23.3043212890625</v>
+        <v>23.3043193817139</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>23.2567615509033</v>
+        <v>23.2567596435547</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G1422" t="n">
-        <v>23.161642074585</v>
+        <v>23.1616401672363</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1428" t="n">
-        <v>23.5896797180176</v>
+        <v>23.5896759033203</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1430" t="n">
-        <v>23.2567615509033</v>
+        <v>23.2567596435547</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1431" t="n">
-        <v>23.5896797180176</v>
+        <v>23.5896759033203</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1433" t="n">
-        <v>22.9238433837891</v>
+        <v>22.9238414764404</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>23.161642074585</v>
+        <v>23.1616401672363</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G1436" t="n">
-        <v>23.161642074585</v>
+        <v>23.1616401672363</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>23.5896797180176</v>
+        <v>23.5896759033203</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>24.75</v>
       </c>
       <c r="G1439" t="n">
-        <v>23.5421199798584</v>
+        <v>23.5421180725098</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1443" t="n">
-        <v>23.2567615509033</v>
+        <v>23.2567596435547</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>23.2567615509033</v>
+        <v>23.2567596435547</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1445" t="n">
-        <v>23.2567615509033</v>
+        <v>23.2567596435547</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1446" t="n">
-        <v>22.6384811401367</v>
+        <v>22.6384830474854</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1449" t="n">
-        <v>23.3994407653809</v>
+        <v>23.3994426727295</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>22.4482460021973</v>
+        <v>22.4482440948486</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1456" t="n">
-        <v>22.0677623748779</v>
+        <v>22.0677642822266</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1458" t="n">
-        <v>22.020206451416</v>
+        <v>22.0202045440674</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>22.1628818511963</v>
+        <v>22.1628837585449</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>24.3506393432617</v>
+        <v>24.3506374359131</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1462" t="n">
-        <v>23.7323589324951</v>
+        <v>23.7323608398438</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1464" t="n">
-        <v>23.8750381469727</v>
+        <v>23.8750400543213</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1465" t="n">
-        <v>24.3506393432617</v>
+        <v>24.3506374359131</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>27</v>
       </c>
       <c r="G1472" t="n">
-        <v>25.6823101043701</v>
+        <v>25.6823120117188</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>27</v>
       </c>
       <c r="G1474" t="n">
-        <v>25.6823101043701</v>
+        <v>25.6823120117188</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1475" t="n">
-        <v>25.6347522735596</v>
+        <v>25.6347541809082</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1476" t="n">
-        <v>25.7774314880371</v>
+        <v>25.7774333953857</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1477" t="n">
-        <v>25.4920711517334</v>
+        <v>25.492073059082</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>27.75</v>
       </c>
       <c r="G1479" t="n">
-        <v>26.3957118988037</v>
+        <v>26.3957099914551</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1480" t="n">
-        <v>27.2993469238281</v>
+        <v>27.2993488311768</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>27.1566677093506</v>
+        <v>27.156665802002</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1485" t="n">
-        <v>27.7749462127686</v>
+        <v>27.7749481201172</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1486" t="n">
-        <v>28.1078624725342</v>
+        <v>28.1078643798828</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>29</v>
       </c>
       <c r="G1487" t="n">
-        <v>27.5847053527832</v>
+        <v>27.5847072601318</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>29</v>
       </c>
       <c r="G1489" t="n">
-        <v>27.5847053527832</v>
+        <v>27.5847072601318</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1491" t="n">
-        <v>27.5371475219727</v>
+        <v>27.5371494293213</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>28.75</v>
       </c>
       <c r="G1492" t="n">
-        <v>27.3469066619873</v>
+        <v>27.3469085693359</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>26.7761878967285</v>
+        <v>26.7761859893799</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1495" t="n">
-        <v>26.9664268493652</v>
+        <v>26.9664287567139</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>28.25</v>
       </c>
       <c r="G1496" t="n">
-        <v>26.8713073730469</v>
+        <v>26.8713092803955</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>28.25</v>
       </c>
       <c r="G1498" t="n">
-        <v>26.8713073730469</v>
+        <v>26.8713092803955</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>27.25</v>
       </c>
       <c r="G1500" t="n">
-        <v>26.0770359039307</v>
+        <v>26.077033996582</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1502" t="n">
-        <v>25.2636241912842</v>
+        <v>25.2636222839355</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G1505" t="n">
-        <v>23.9717330932617</v>
+        <v>23.9717311859131</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1506" t="n">
-        <v>24.5937538146973</v>
+        <v>24.5937557220459</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1507" t="n">
-        <v>24.4980602264404</v>
+        <v>24.4980583190918</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1509" t="n">
-        <v>26.2205791473389</v>
+        <v>26.2205772399902</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1512" t="n">
-        <v>25.7421016693115</v>
+        <v>25.7420997619629</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>26.8500003814697</v>
       </c>
       <c r="G1513" t="n">
-        <v>25.6942539215088</v>
+        <v>25.6942520141602</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G1514" t="n">
-        <v>25.3114700317383</v>
+        <v>25.3114719390869</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1515" t="n">
-        <v>25.7421016693115</v>
+        <v>25.7420997619629</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1516" t="n">
-        <v>25.7421016693115</v>
+        <v>25.7420997619629</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1517" t="n">
-        <v>25.550708770752</v>
+        <v>25.5507106781006</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1518" t="n">
-        <v>25.2636241912842</v>
+        <v>25.2636222839355</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1519" t="n">
-        <v>24.9765377044678</v>
+        <v>24.9765357971191</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G1522" t="n">
-        <v>25.3114700317383</v>
+        <v>25.3114719390869</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1524" t="n">
-        <v>25.7421016693115</v>
+        <v>25.7420997619629</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1528" t="n">
-        <v>25.9813404083252</v>
+        <v>25.9813385009766</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G1529" t="n">
-        <v>25.9813404083252</v>
+        <v>25.9813385009766</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1530" t="n">
-        <v>25.4550132751465</v>
+        <v>25.4550151824951</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1532" t="n">
-        <v>24.5937538146973</v>
+        <v>24.5937557220459</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1534" t="n">
-        <v>25.4550132751465</v>
+        <v>25.4550151824951</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1535" t="n">
-        <v>25.4550132751465</v>
+        <v>25.4550151824951</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>26.5</v>
       </c>
       <c r="G1539" t="n">
-        <v>25.359317779541</v>
+        <v>25.3593196868896</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>26</v>
       </c>
       <c r="G1540" t="n">
-        <v>24.880838394165</v>
+        <v>24.8808403015137</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1543" t="n">
-        <v>22.6319961547852</v>
+        <v>22.6319942474365</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1545" t="n">
-        <v>22.8712348937988</v>
+        <v>22.8712329864502</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1547" t="n">
-        <v>23.0626258850098</v>
+        <v>23.0626239776611</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1548" t="n">
-        <v>23.2540149688721</v>
+        <v>23.2540168762207</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1549" t="n">
-        <v>23.0626258850098</v>
+        <v>23.0626239776611</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1550" t="n">
-        <v>22.2970600128174</v>
+        <v>22.297061920166</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>21.6750392913818</v>
+        <v>21.6750411987305</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1557" t="n">
-        <v>21.9621257781982</v>
+        <v>21.9621295928955</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>23</v>
       </c>
       <c r="G1560" t="n">
-        <v>22.009973526001</v>
+        <v>22.0099754333496</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1561" t="n">
-        <v>21.9142799377441</v>
+        <v>21.9142780303955</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1562" t="n">
-        <v>21.2444095611572</v>
+        <v>21.2444114685059</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>20.25</v>
       </c>
       <c r="G1565" t="n">
-        <v>19.378345489502</v>
+        <v>19.3783473968506</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1566" t="n">
-        <v>20.0482158660889</v>
+        <v>20.0482177734375</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1567" t="n">
-        <v>19.8089790344238</v>
+        <v>19.8089771270752</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1569" t="n">
-        <v>19.0242729187012</v>
+        <v>19.0242710113525</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1575" t="n">
-        <v>17.4357261657715</v>
+        <v>17.4357280731201</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1577" t="n">
-        <v>17.7228164672852</v>
+        <v>17.7228145599365</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1580" t="n">
-        <v>18.1438732147217</v>
+        <v>18.1438751220703</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1588" t="n">
-        <v>19.8089790344238</v>
+        <v>19.8089771270752</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G1601" t="n">
-        <v>18.6032123565674</v>
+        <v>18.603214263916</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1602" t="n">
-        <v>19.2826519012451</v>
+        <v>19.2826538085938</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>20.5</v>
       </c>
       <c r="G1603" t="n">
-        <v>19.6175842285156</v>
+        <v>19.6175861358643</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1605" t="n">
-        <v>18.622350692749</v>
+        <v>18.6223526000977</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>20</v>
       </c>
       <c r="G1610" t="n">
-        <v>19.1391086578369</v>
+        <v>19.1391105651855</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1617" t="n">
-        <v>17.7228164672852</v>
+        <v>17.7228145599365</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>21.5</v>
       </c>
       <c r="G1624" t="n">
-        <v>20.5745410919189</v>
+        <v>20.5745391845703</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>23.25</v>
       </c>
       <c r="G1630" t="n">
-        <v>22.2492122650146</v>
+        <v>22.2492141723633</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>23.25</v>
       </c>
       <c r="G1632" t="n">
-        <v>22.2492122650146</v>
+        <v>22.2492141723633</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1636" t="n">
-        <v>22.8712348937988</v>
+        <v>22.8712329864502</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1643" t="n">
-        <v>19.7611293792725</v>
+        <v>19.7611274719238</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>21</v>
       </c>
       <c r="G1644" t="n">
-        <v>20.0960636138916</v>
+        <v>20.096061706543</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1650" t="n">
-        <v>19.7132816314697</v>
+        <v>19.7132797241211</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>20.25</v>
       </c>
       <c r="G1651" t="n">
-        <v>19.378345489502</v>
+        <v>19.3783473968506</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G1656" t="n">
-        <v>17.4548645019531</v>
+        <v>17.4548664093018</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1657" t="n">
-        <v>17.4357261657715</v>
+        <v>17.4357280731201</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>20</v>
       </c>
       <c r="G1659" t="n">
-        <v>19.1391086578369</v>
+        <v>19.1391105651855</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1661" t="n">
-        <v>18.3735427856445</v>
+        <v>18.3735446929932</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1662" t="n">
-        <v>18.1055965423584</v>
+        <v>18.1055946350098</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G1664" t="n">
-        <v>18.4309597015381</v>
+        <v>18.4309616088867</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1667" t="n">
-        <v>18.8137454986572</v>
+        <v>18.8137435913086</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1670" t="n">
-        <v>18.163013458252</v>
+        <v>18.1630153656006</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1674" t="n">
-        <v>19.186954498291</v>
+        <v>19.1869564056396</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1675" t="n">
-        <v>19.0242729187012</v>
+        <v>19.0242710113525</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G1676" t="n">
-        <v>18.7180480957031</v>
+        <v>18.7180461883545</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1678" t="n">
-        <v>18.8520202636719</v>
+        <v>18.8520240783691</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1680" t="n">
-        <v>19.2826519012451</v>
+        <v>19.2826538085938</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1681" t="n">
-        <v>19.2826519012451</v>
+        <v>19.2826538085938</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>20</v>
       </c>
       <c r="G1683" t="n">
-        <v>19.1391086578369</v>
+        <v>19.1391105651855</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1684" t="n">
-        <v>19.186954498291</v>
+        <v>19.1869564056396</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1692" t="n">
-        <v>17.7993717193604</v>
+        <v>17.7993698120117</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1693" t="n">
-        <v>17.5122833251953</v>
+        <v>17.5122814178467</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1702" t="n">
-        <v>18.12473487854</v>
+        <v>18.1247367858887</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1703" t="n">
-        <v>18.1438732147217</v>
+        <v>18.1438751220703</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1705" t="n">
-        <v>17.5505638122559</v>
+        <v>17.5505619049072</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>18</v>
       </c>
       <c r="G1706" t="n">
-        <v>17.2251987457275</v>
+        <v>17.2251968383789</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1708" t="n">
-        <v>15.885461807251</v>
+        <v>15.8854608535767</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1710" t="n">
-        <v>16.0959911346436</v>
+        <v>16.0959892272949</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1712" t="n">
-        <v>16.1151294708252</v>
+        <v>16.1151275634766</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>16</v>
       </c>
       <c r="G1713" t="n">
-        <v>15.3112859725952</v>
+        <v>15.3112869262695</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1715" t="n">
-        <v>15.2538690567017</v>
+        <v>15.253867149353</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1716" t="n">
-        <v>16.6127452850342</v>
+        <v>16.6127471923828</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1717" t="n">
-        <v>16.0194320678711</v>
+        <v>16.0194301605225</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1718" t="n">
-        <v>16.6510257720947</v>
+        <v>16.6510238647461</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1719" t="n">
-        <v>16.7658576965332</v>
+        <v>16.7658596038818</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1720" t="n">
-        <v>17.5122833251953</v>
+        <v>17.5122814178467</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1721" t="n">
-        <v>16.9955291748047</v>
+        <v>16.9955310821533</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1722" t="n">
-        <v>17.320894241333</v>
+        <v>17.3208923339844</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1725" t="n">
-        <v>17.0146675109863</v>
+        <v>17.0146656036377</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1726" t="n">
-        <v>16.6127452850342</v>
+        <v>16.6127471923828</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1731" t="n">
-        <v>18.6989097595215</v>
+        <v>18.6989116668701</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1737" t="n">
-        <v>20.0003681182861</v>
+        <v>20.0003662109375</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1738" t="n">
-        <v>19.7611293792725</v>
+        <v>19.7611274719238</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1739" t="n">
-        <v>19.7611293792725</v>
+        <v>19.7611274719238</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1740" t="n">
-        <v>19.7611293792725</v>
+        <v>19.7611274719238</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G1741" t="n">
-        <v>19.5697402954102</v>
+        <v>19.5697383880615</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1743" t="n">
-        <v>19.8089790344238</v>
+        <v>19.8089771270752</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>21.5</v>
       </c>
       <c r="G1751" t="n">
-        <v>20.5745410919189</v>
+        <v>20.5745391845703</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1753" t="n">
-        <v>20.7180862426758</v>
+        <v>20.7180843353271</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>21.25</v>
       </c>
       <c r="G1757" t="n">
-        <v>20.6010704040527</v>
+        <v>20.6010723114014</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1759" t="n">
-        <v>20.3102321624756</v>
+        <v>20.3102340698242</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>21.25</v>
       </c>
       <c r="G1761" t="n">
-        <v>20.6010704040527</v>
+        <v>20.6010723114014</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1765" t="n">
-        <v>20.4071788787842</v>
+        <v>20.4071769714355</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>21.25</v>
       </c>
       <c r="G1768" t="n">
-        <v>20.6010704040527</v>
+        <v>20.6010723114014</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>21.25</v>
       </c>
       <c r="G1769" t="n">
-        <v>20.6010704040527</v>
+        <v>20.6010723114014</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1770" t="n">
-        <v>21.1827487945557</v>
+        <v>21.182746887207</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>21.25</v>
       </c>
       <c r="G1771" t="n">
-        <v>20.6010704040527</v>
+        <v>20.6010723114014</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1774" t="n">
-        <v>19.9709205627441</v>
+        <v>19.9709186553955</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>21.25</v>
       </c>
       <c r="G1785" t="n">
-        <v>20.6010704040527</v>
+        <v>20.6010723114014</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1788" t="n">
-        <v>21.6190071105957</v>
+        <v>21.6190052032471</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1790" t="n">
-        <v>21.6190071105957</v>
+        <v>21.6190052032471</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>23.5</v>
       </c>
       <c r="G1797" t="n">
-        <v>22.7823619842529</v>
+        <v>22.7823600769043</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>23.5</v>
       </c>
       <c r="G1798" t="n">
-        <v>22.7823619842529</v>
+        <v>22.7823600769043</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1804" t="n">
-        <v>23.0731983184814</v>
+        <v>23.0732002258301</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1806" t="n">
-        <v>23.5579299926758</v>
+        <v>23.5579319000244</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1807" t="n">
-        <v>23.5579299926758</v>
+        <v>23.5579319000244</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G1810" t="n">
-        <v>23.6064052581787</v>
+        <v>23.6064033508301</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1815" t="n">
-        <v>23.1701469421387</v>
+        <v>23.17014503479</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1818" t="n">
-        <v>23.1701469421387</v>
+        <v>23.17014503479</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G1821" t="n">
-        <v>23.8002948760986</v>
+        <v>23.8002967834473</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G1823" t="n">
-        <v>25.157543182373</v>
+        <v>25.1575450897217</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1824" t="n">
-        <v>24.8182334899902</v>
+        <v>24.8182315826416</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1825" t="n">
-        <v>24.6243381500244</v>
+        <v>24.624340057373</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1827" t="n">
-        <v>24.6243381500244</v>
+        <v>24.624340057373</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G1829" t="n">
-        <v>24.285026550293</v>
+        <v>24.2850284576416</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1830" t="n">
-        <v>24.1396064758301</v>
+        <v>24.1396083831787</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1833" t="n">
-        <v>22.5884666442871</v>
+        <v>22.5884685516357</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1834" t="n">
-        <v>23.5579299926758</v>
+        <v>23.5579319000244</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>23.75</v>
       </c>
       <c r="G1836" t="n">
-        <v>23.0247287750244</v>
+        <v>23.0247268676758</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G1837" t="n">
-        <v>22.73388671875</v>
+        <v>22.7338886260986</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G1843" t="n">
-        <v>22.73388671875</v>
+        <v>22.7338886260986</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1844" t="n">
-        <v>23.0731983184814</v>
+        <v>23.0732002258301</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G1846" t="n">
-        <v>23.8002948760986</v>
+        <v>23.8002967834473</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G1848" t="n">
-        <v>23.8972415924072</v>
+        <v>23.8972434997559</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G1849" t="n">
-        <v>23.6064052581787</v>
+        <v>23.6064033508301</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>23.75</v>
       </c>
       <c r="G1851" t="n">
-        <v>23.0247287750244</v>
+        <v>23.0247268676758</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G1852" t="n">
-        <v>23.6064052581787</v>
+        <v>23.6064033508301</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1854" t="n">
-        <v>24.091136932373</v>
+        <v>24.0911350250244</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1858" t="n">
-        <v>24.6243381500244</v>
+        <v>24.624340057373</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G1861" t="n">
-        <v>23.8002948760986</v>
+        <v>23.8002967834473</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>23.75</v>
       </c>
       <c r="G1866" t="n">
-        <v>23.0247287750244</v>
+        <v>23.0247268676758</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>23.5</v>
       </c>
       <c r="G1869" t="n">
-        <v>22.7823619842529</v>
+        <v>22.7823600769043</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1870" t="n">
-        <v>23.1701469421387</v>
+        <v>23.17014503479</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1875" t="n">
-        <v>22.5884666442871</v>
+        <v>22.5884685516357</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>23.75</v>
       </c>
       <c r="G1877" t="n">
-        <v>23.0247287750244</v>
+        <v>23.0247268676758</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>23.75</v>
       </c>
       <c r="G1879" t="n">
-        <v>23.0247287750244</v>
+        <v>23.0247268676758</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>23.5</v>
       </c>
       <c r="G1881" t="n">
-        <v>22.7823619842529</v>
+        <v>22.7823600769043</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>22.5</v>
       </c>
       <c r="G1885" t="n">
-        <v>21.8128986358643</v>
+        <v>21.8129005432129</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1889" t="n">
-        <v>22.3945770263672</v>
+        <v>22.3945751190186</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1891" t="n">
-        <v>22.3945770263672</v>
+        <v>22.3945751190186</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1893" t="n">
-        <v>22.5884666442871</v>
+        <v>22.5884685516357</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G1896" t="n">
-        <v>22.3461017608643</v>
+        <v>22.3461036682129</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>23.25</v>
       </c>
       <c r="G1897" t="n">
-        <v>22.5399971008301</v>
+        <v>22.5399951934814</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1898" t="n">
-        <v>22.3945770263672</v>
+        <v>22.3945751190186</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1903" t="n">
-        <v>21.5220603942871</v>
+        <v>21.5220623016357</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1904" t="n">
-        <v>21.5220603942871</v>
+        <v>21.5220623016357</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>22.5</v>
       </c>
       <c r="G1928" t="n">
-        <v>21.8128986358643</v>
+        <v>21.8129005432129</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1929" t="n">
-        <v>21.6190071105957</v>
+        <v>21.6190052032471</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>22.5</v>
       </c>
       <c r="G1930" t="n">
-        <v>21.8128986358643</v>
+        <v>21.8129005432129</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1931" t="n">
-        <v>21.5220603942871</v>
+        <v>21.5220623016357</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1933" t="n">
-        <v>21.1827487945557</v>
+        <v>21.182746887207</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>21.75</v>
       </c>
       <c r="G1934" t="n">
-        <v>21.0858020782471</v>
+        <v>21.0858039855957</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1936" t="n">
-        <v>20.8919105529785</v>
+        <v>20.8919086456299</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1937" t="n">
-        <v>20.8919105529785</v>
+        <v>20.8919086456299</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1946" t="n">
-        <v>21.1827487945557</v>
+        <v>21.182746887207</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1949" t="n">
-        <v>21.8613700866699</v>
+        <v>21.8613719940186</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1951" t="n">
-        <v>21.6190071105957</v>
+        <v>21.6190052032471</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>22.5</v>
       </c>
       <c r="G1953" t="n">
-        <v>21.8128986358643</v>
+        <v>21.8129005432129</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1958" t="n">
-        <v>21.8613700866699</v>
+        <v>21.8613719940186</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1959" t="n">
-        <v>22.5884666442871</v>
+        <v>22.5884685516357</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G1962" t="n">
-        <v>22.73388671875</v>
+        <v>22.7338886260986</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1965" t="n">
-        <v>22.5884666442871</v>
+        <v>22.5884685516357</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1967" t="n">
-        <v>22.5884666442871</v>
+        <v>22.5884685516357</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1972" t="n">
-        <v>25.0121212005615</v>
+        <v>25.0121231079102</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51719,7 +51719,7 @@
         <v>26.5</v>
       </c>
       <c r="G1975" t="n">
-        <v>25.6907482147217</v>
+        <v>25.690746307373</v>
       </c>
       <c r="H1975" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>26.5</v>
       </c>
       <c r="G1977" t="n">
-        <v>25.6907482147217</v>
+        <v>25.690746307373</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G1984" t="n">
-        <v>26.223949432373</v>
+        <v>26.2239513397217</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1986" t="n">
-        <v>25.3029651641846</v>
+        <v>25.3029632568359</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52031,7 +52031,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1987" t="n">
-        <v>24.8182334899902</v>
+        <v>24.8182315826416</v>
       </c>
       <c r="H1987" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>24.75</v>
       </c>
       <c r="G1991" t="n">
-        <v>23.9941883087158</v>
+        <v>23.9941864013672</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G1993" t="n">
-        <v>23.8002948760986</v>
+        <v>23.8002967834473</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>25</v>
       </c>
       <c r="G1995" t="n">
-        <v>24.2365550994873</v>
+        <v>24.2365531921387</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1999" t="n">
-        <v>25.4968528747559</v>
+        <v>25.4968547821045</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>26.5</v>
       </c>
       <c r="G2002" t="n">
-        <v>25.6907482147217</v>
+        <v>25.690746307373</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G2003" t="n">
-        <v>25.4968528747559</v>
+        <v>25.4968547821045</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>26.5</v>
       </c>
       <c r="G2005" t="n">
-        <v>25.6907482147217</v>
+        <v>25.690746307373</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>57.9000015258789</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>79972</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>59.4000015258789</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>58.5499992370605</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>58.7000007629395</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>59.0999984741211</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>59.0999984741211</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>48.5999984741211</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>49.6599998474121</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>93250</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>51.1500015258789</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>49.7599983215332</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>50</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>50.7000007629395</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>87321</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>50.7000007629395</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>49.0999984741211</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>50.5</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>49.4000015258789</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>168532</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>49</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>47.2999992370605</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>49</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>49</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>47.6599998474121</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>103294</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>49.4199981689453</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>47.9000015258789</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>48</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>219072</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>49.5999984741211</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>49.560001373291</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -456,7 +456,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7186393737793</v>
+        <v>15.7186403274536</v>
       </c>
       <c r="H3" t="n">
         <v>35642</v>
@@ -485,7 +485,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2234210968018</v>
+        <v>15.2234239578247</v>
       </c>
       <c r="H4" t="n">
         <v>65319</v>
@@ -514,7 +514,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>14.5356168746948</v>
+        <v>14.5356178283691</v>
       </c>
       <c r="H5" t="n">
         <v>96087</v>
@@ -543,7 +543,7 @@
         <v>15.5</v>
       </c>
       <c r="G6" t="n">
-        <v>14.2146415710449</v>
+        <v>14.2146406173706</v>
       </c>
       <c r="H6" t="n">
         <v>81338</v>
@@ -601,7 +601,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G8" t="n">
-        <v>14.2880067825317</v>
+        <v>14.2880058288574</v>
       </c>
       <c r="H8" t="n">
         <v>64629</v>
@@ -659,7 +659,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G10" t="n">
-        <v>13.8661527633667</v>
+        <v>13.866153717041</v>
       </c>
       <c r="H10" t="n">
         <v>49474</v>
@@ -717,7 +717,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G12" t="n">
-        <v>12.7931776046753</v>
+        <v>12.793176651001</v>
       </c>
       <c r="H12" t="n">
         <v>70420</v>
@@ -746,7 +746,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G13" t="n">
-        <v>12.8848857879639</v>
+        <v>12.8848848342896</v>
       </c>
       <c r="H13" t="n">
         <v>51845</v>
@@ -775,7 +775,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G14" t="n">
-        <v>12.2887859344482</v>
+        <v>12.2887878417969</v>
       </c>
       <c r="H14" t="n">
         <v>71385</v>
@@ -804,7 +804,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G15" t="n">
-        <v>12.9490785598755</v>
+        <v>12.9490795135498</v>
       </c>
       <c r="H15" t="n">
         <v>79009</v>
@@ -833,7 +833,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>13.132495880127</v>
+        <v>13.132493019104</v>
       </c>
       <c r="H16" t="n">
         <v>85369</v>
@@ -920,7 +920,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G19" t="n">
-        <v>16.3239059448242</v>
+        <v>16.3239078521729</v>
       </c>
       <c r="H19" t="n">
         <v>253918</v>
@@ -949,7 +949,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G20" t="n">
-        <v>16.085470199585</v>
+        <v>16.0854721069336</v>
       </c>
       <c r="H20" t="n">
         <v>156267</v>
@@ -978,7 +978,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G21" t="n">
-        <v>16.3605937957764</v>
+        <v>16.360595703125</v>
       </c>
       <c r="H21" t="n">
         <v>116126</v>
@@ -1036,7 +1036,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>16.5990314483643</v>
+        <v>16.5990295410156</v>
       </c>
       <c r="H23" t="n">
         <v>490894</v>
@@ -1065,7 +1065,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G24" t="n">
-        <v>15.4710311889648</v>
+        <v>15.4710330963135</v>
       </c>
       <c r="H24" t="n">
         <v>293009</v>
@@ -1123,7 +1123,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G26" t="n">
-        <v>15.3059606552124</v>
+        <v>15.3059587478638</v>
       </c>
       <c r="H26" t="n">
         <v>118150</v>
@@ -1152,7 +1152,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G27" t="n">
-        <v>14.9391298294067</v>
+        <v>14.9391307830811</v>
       </c>
       <c r="H27" t="n">
         <v>147822</v>
@@ -1181,7 +1181,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G28" t="n">
-        <v>14.9483013153076</v>
+        <v>14.948299407959</v>
       </c>
       <c r="H28" t="n">
         <v>97617</v>
@@ -1210,7 +1210,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G29" t="n">
-        <v>15.3518114089966</v>
+        <v>15.3518123626709</v>
       </c>
       <c r="H29" t="n">
         <v>133443</v>
@@ -1239,7 +1239,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G30" t="n">
-        <v>15.1042013168335</v>
+        <v>15.1042032241821</v>
       </c>
       <c r="H30" t="n">
         <v>42426</v>
@@ -1268,7 +1268,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G31" t="n">
-        <v>15.003324508667</v>
+        <v>15.0033264160156</v>
       </c>
       <c r="H31" t="n">
         <v>50728</v>
@@ -1297,7 +1297,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>15.9112281799316</v>
+        <v>15.911226272583</v>
       </c>
       <c r="H32" t="n">
         <v>139615</v>
@@ -1326,7 +1326,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G33" t="n">
-        <v>16.2322044372559</v>
+        <v>16.2322025299072</v>
       </c>
       <c r="H33" t="n">
         <v>61554</v>
@@ -1355,7 +1355,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G34" t="n">
-        <v>16.7641067504883</v>
+        <v>16.7641086578369</v>
       </c>
       <c r="H34" t="n">
         <v>132571</v>
@@ -1442,7 +1442,7 @@
         <v>18.5</v>
       </c>
       <c r="G37" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H37" t="n">
         <v>111528</v>
@@ -1500,7 +1500,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G39" t="n">
-        <v>16.3605937957764</v>
+        <v>16.360595703125</v>
       </c>
       <c r="H39" t="n">
         <v>65595</v>
@@ -1529,7 +1529,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>16.3514232635498</v>
+        <v>16.3514194488525</v>
       </c>
       <c r="H40" t="n">
         <v>40812</v>
@@ -1587,7 +1587,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G42" t="n">
-        <v>16.342248916626</v>
+        <v>16.3422546386719</v>
       </c>
       <c r="H42" t="n">
         <v>43527</v>
@@ -1703,7 +1703,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G46" t="n">
-        <v>17.3051776885986</v>
+        <v>17.3051815032959</v>
       </c>
       <c r="H46" t="n">
         <v>69241</v>
@@ -1732,7 +1732,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G47" t="n">
-        <v>17.3693771362305</v>
+        <v>17.3693733215332</v>
       </c>
       <c r="H47" t="n">
         <v>111422</v>
@@ -1761,7 +1761,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G48" t="n">
-        <v>17.4335689544678</v>
+        <v>17.4335670471191</v>
       </c>
       <c r="H48" t="n">
         <v>322204</v>
@@ -1790,7 +1790,7 @@
         <v>18.5</v>
       </c>
       <c r="G49" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H49" t="n">
         <v>55559</v>
@@ -1848,7 +1848,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G51" t="n">
-        <v>17.2226409912109</v>
+        <v>17.2226428985596</v>
       </c>
       <c r="H51" t="n">
         <v>34164</v>
@@ -1877,7 +1877,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>17.5161056518555</v>
+        <v>17.5161094665527</v>
       </c>
       <c r="H52" t="n">
         <v>55267</v>
@@ -1906,7 +1906,7 @@
         <v>18.5</v>
       </c>
       <c r="G53" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H53" t="n">
         <v>23006</v>
@@ -1964,7 +1964,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G55" t="n">
-        <v>17.2593231201172</v>
+        <v>17.2593250274658</v>
       </c>
       <c r="H55" t="n">
         <v>37241</v>
@@ -1993,7 +1993,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G56" t="n">
-        <v>17.4610824584961</v>
+        <v>17.4610805511475</v>
       </c>
       <c r="H56" t="n">
         <v>30163</v>
@@ -2022,7 +2022,7 @@
         <v>18.5</v>
       </c>
       <c r="G57" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H57" t="n">
         <v>40462</v>
@@ -2109,7 +2109,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G60" t="n">
-        <v>16.2138633728027</v>
+        <v>16.2138595581055</v>
       </c>
       <c r="H60" t="n">
         <v>98478</v>
@@ -2138,7 +2138,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G61" t="n">
-        <v>16.5531749725342</v>
+        <v>16.5531787872314</v>
       </c>
       <c r="H61" t="n">
         <v>50561</v>
@@ -2167,7 +2167,7 @@
         <v>18.5</v>
       </c>
       <c r="G62" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H62" t="n">
         <v>31403</v>
@@ -2196,7 +2196,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G63" t="n">
-        <v>16.9383487701416</v>
+        <v>16.9383506774902</v>
       </c>
       <c r="H63" t="n">
         <v>19939</v>
@@ -2283,7 +2283,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G66" t="n">
-        <v>16.5715217590332</v>
+        <v>16.5715179443359</v>
       </c>
       <c r="H66" t="n">
         <v>32129</v>
@@ -2341,7 +2341,7 @@
         <v>18.6700000762939</v>
       </c>
       <c r="G68" t="n">
-        <v>17.1217651367188</v>
+        <v>17.1217632293701</v>
       </c>
       <c r="H68" t="n">
         <v>54494</v>
@@ -2370,7 +2370,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>17.5619621276855</v>
+        <v>17.5619583129883</v>
       </c>
       <c r="H69" t="n">
         <v>83128</v>
@@ -2399,7 +2399,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>17.6353244781494</v>
+        <v>17.6353225708008</v>
       </c>
       <c r="H70" t="n">
         <v>42644</v>
@@ -2428,7 +2428,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G71" t="n">
-        <v>17.4060573577881</v>
+        <v>17.4060554504395</v>
       </c>
       <c r="H71" t="n">
         <v>20298</v>
@@ -2457,7 +2457,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G72" t="n">
-        <v>17.8645935058594</v>
+        <v>17.8645915985107</v>
       </c>
       <c r="H72" t="n">
         <v>69176</v>
@@ -2515,7 +2515,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>18.0204963684082</v>
+        <v>18.0204944610596</v>
       </c>
       <c r="H74" t="n">
         <v>17233</v>
@@ -2573,7 +2573,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G76" t="n">
-        <v>17.5986461639404</v>
+        <v>17.5986442565918</v>
       </c>
       <c r="H76" t="n">
         <v>117794</v>
@@ -2631,7 +2631,7 @@
         <v>20.0699996948242</v>
       </c>
       <c r="G78" t="n">
-        <v>18.4056663513184</v>
+        <v>18.405668258667</v>
       </c>
       <c r="H78" t="n">
         <v>99094</v>
@@ -2660,7 +2660,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G79" t="n">
-        <v>18.433177947998</v>
+        <v>18.4331798553467</v>
       </c>
       <c r="H79" t="n">
         <v>36927</v>
@@ -2689,7 +2689,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G80" t="n">
-        <v>18.0938625335693</v>
+        <v>18.0938606262207</v>
       </c>
       <c r="H80" t="n">
         <v>19099</v>
@@ -2718,7 +2718,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G81" t="n">
-        <v>18.3231296539307</v>
+        <v>18.3231315612793</v>
       </c>
       <c r="H81" t="n">
         <v>26322</v>
@@ -2747,7 +2747,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G82" t="n">
-        <v>18.0296688079834</v>
+        <v>18.0296649932861</v>
       </c>
       <c r="H82" t="n">
         <v>13198</v>
@@ -2805,7 +2805,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>17.5619621276855</v>
+        <v>17.5619583129883</v>
       </c>
       <c r="H84" t="n">
         <v>37467</v>
@@ -2863,7 +2863,7 @@
         <v>18.5</v>
       </c>
       <c r="G86" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H86" t="n">
         <v>48847</v>
@@ -2892,7 +2892,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G87" t="n">
-        <v>17.1492767333984</v>
+        <v>17.1492786407471</v>
       </c>
       <c r="H87" t="n">
         <v>16818</v>
@@ -2921,7 +2921,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G88" t="n">
-        <v>17.4885959625244</v>
+        <v>17.4885921478271</v>
       </c>
       <c r="H88" t="n">
         <v>28099</v>
@@ -2950,7 +2950,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G89" t="n">
-        <v>17.1676158905029</v>
+        <v>17.1676177978516</v>
       </c>
       <c r="H89" t="n">
         <v>29034</v>
@@ -3008,7 +3008,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G91" t="n">
-        <v>16.7732810974121</v>
+        <v>16.7732772827148</v>
       </c>
       <c r="H91" t="n">
         <v>20209</v>
@@ -3037,7 +3037,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G92" t="n">
-        <v>16.8374710083008</v>
+        <v>16.8374729156494</v>
       </c>
       <c r="H92" t="n">
         <v>18052</v>
@@ -3095,7 +3095,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G94" t="n">
-        <v>16.3147430419922</v>
+        <v>16.3147411346436</v>
       </c>
       <c r="H94" t="n">
         <v>55875</v>
@@ -3124,7 +3124,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G95" t="n">
-        <v>16.1496677398682</v>
+        <v>16.1496658325195</v>
       </c>
       <c r="H95" t="n">
         <v>14197</v>
@@ -3153,7 +3153,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G96" t="n">
-        <v>16.250545501709</v>
+        <v>16.2505435943604</v>
       </c>
       <c r="H96" t="n">
         <v>36784</v>
@@ -3182,7 +3182,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G97" t="n">
-        <v>16.7457675933838</v>
+        <v>16.7457656860352</v>
       </c>
       <c r="H97" t="n">
         <v>37611</v>
@@ -3240,7 +3240,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G99" t="n">
-        <v>16.4156169891357</v>
+        <v>16.4156188964844</v>
       </c>
       <c r="H99" t="n">
         <v>11742</v>
@@ -3298,7 +3298,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G101" t="n">
-        <v>16.3514232635498</v>
+        <v>16.3514194488525</v>
       </c>
       <c r="H101" t="n">
         <v>40913</v>
@@ -3327,7 +3327,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G102" t="n">
-        <v>16.7457675933838</v>
+        <v>16.7457656860352</v>
       </c>
       <c r="H102" t="n">
         <v>88393</v>
@@ -3385,7 +3385,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G104" t="n">
-        <v>17.3051776885986</v>
+        <v>17.3051815032959</v>
       </c>
       <c r="H104" t="n">
         <v>65612</v>
@@ -3414,7 +3414,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G105" t="n">
-        <v>17.1492767333984</v>
+        <v>17.1492786407471</v>
       </c>
       <c r="H105" t="n">
         <v>9668</v>
@@ -3443,7 +3443,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G106" t="n">
-        <v>16.5164947509766</v>
+        <v>16.5164966583252</v>
       </c>
       <c r="H106" t="n">
         <v>55198</v>
@@ -3559,7 +3559,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G110" t="n">
-        <v>16.9933738708496</v>
+        <v>16.9933776855469</v>
       </c>
       <c r="H110" t="n">
         <v>12079</v>
@@ -3617,7 +3617,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G112" t="n">
-        <v>16.9933738708496</v>
+        <v>16.9933776855469</v>
       </c>
       <c r="H112" t="n">
         <v>25750</v>
@@ -3646,7 +3646,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G113" t="n">
-        <v>16.7732810974121</v>
+        <v>16.7732772827148</v>
       </c>
       <c r="H113" t="n">
         <v>25389</v>
@@ -3675,7 +3675,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>16.4156169891357</v>
+        <v>16.4156188964844</v>
       </c>
       <c r="H114" t="n">
         <v>28373</v>
@@ -3733,7 +3733,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G116" t="n">
-        <v>15.8470344543457</v>
+        <v>15.84703540802</v>
       </c>
       <c r="H116" t="n">
         <v>50453</v>
@@ -3820,7 +3820,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G119" t="n">
-        <v>14.7648849487305</v>
+        <v>14.7648868560791</v>
       </c>
       <c r="H119" t="n">
         <v>97119</v>
@@ -3849,7 +3849,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G120" t="n">
-        <v>15.0675182342529</v>
+        <v>15.0675191879272</v>
       </c>
       <c r="H120" t="n">
         <v>58276</v>
@@ -3878,7 +3878,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G121" t="n">
-        <v>15.3334703445435</v>
+        <v>15.3334684371948</v>
       </c>
       <c r="H121" t="n">
         <v>77133</v>
@@ -3965,7 +3965,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G124" t="n">
-        <v>14.9849824905396</v>
+        <v>14.9849843978882</v>
       </c>
       <c r="H124" t="n">
         <v>97441</v>
@@ -3994,7 +3994,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G125" t="n">
-        <v>14.4530792236328</v>
+        <v>14.4530801773071</v>
       </c>
       <c r="H125" t="n">
         <v>58086</v>
@@ -4023,7 +4023,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G126" t="n">
-        <v>14.8841037750244</v>
+        <v>14.8841047286987</v>
       </c>
       <c r="H126" t="n">
         <v>70918</v>
@@ -4052,7 +4052,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G127" t="n">
-        <v>14.5264463424683</v>
+        <v>14.5264453887939</v>
       </c>
       <c r="H127" t="n">
         <v>39264</v>
@@ -4081,7 +4081,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G128" t="n">
-        <v>14.6823501586914</v>
+        <v>14.6823472976685</v>
       </c>
       <c r="H128" t="n">
         <v>26403</v>
@@ -4110,7 +4110,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G129" t="n">
-        <v>15.4068355560303</v>
+        <v>15.4068365097046</v>
       </c>
       <c r="H129" t="n">
         <v>31770</v>
@@ -4139,7 +4139,7 @@
         <v>16.3899993896484</v>
       </c>
       <c r="G130" t="n">
-        <v>15.0308380126953</v>
+        <v>15.030837059021</v>
       </c>
       <c r="H130" t="n">
         <v>43988</v>
@@ -4168,7 +4168,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>14.6273231506348</v>
+        <v>14.6273241043091</v>
       </c>
       <c r="H131" t="n">
         <v>41521</v>
@@ -4197,7 +4197,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G132" t="n">
-        <v>14.0037155151367</v>
+        <v>14.0037136077881</v>
       </c>
       <c r="H132" t="n">
         <v>106495</v>
@@ -4255,7 +4255,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G134" t="n">
-        <v>14.6548347473145</v>
+        <v>14.6548376083374</v>
       </c>
       <c r="H134" t="n">
         <v>19776</v>
@@ -4313,7 +4313,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>15.3151292800903</v>
+        <v>15.315128326416</v>
       </c>
       <c r="H136" t="n">
         <v>66703</v>
@@ -4342,7 +4342,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>15.2234210968018</v>
+        <v>15.2234239578247</v>
       </c>
       <c r="H137" t="n">
         <v>26494</v>
@@ -4371,7 +4371,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>15.4985446929932</v>
+        <v>15.4985456466675</v>
       </c>
       <c r="H138" t="n">
         <v>25530</v>
@@ -4400,7 +4400,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G139" t="n">
-        <v>15.3518114089966</v>
+        <v>15.3518123626709</v>
       </c>
       <c r="H139" t="n">
         <v>35750</v>
@@ -4429,7 +4429,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G140" t="n">
-        <v>15.3151292800903</v>
+        <v>15.315128326416</v>
       </c>
       <c r="H140" t="n">
         <v>16474</v>
@@ -4458,7 +4458,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G141" t="n">
-        <v>15.2509346008301</v>
+        <v>15.2509317398071</v>
       </c>
       <c r="H141" t="n">
         <v>13555</v>
@@ -4487,7 +4487,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G142" t="n">
-        <v>15.3242988586426</v>
+        <v>15.3242998123169</v>
       </c>
       <c r="H142" t="n">
         <v>24507</v>
@@ -4545,7 +4545,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G144" t="n">
-        <v>15.3793258666992</v>
+        <v>15.3793239593506</v>
       </c>
       <c r="H144" t="n">
         <v>13919</v>
@@ -4574,7 +4574,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>15.4985446929932</v>
+        <v>15.4985456466675</v>
       </c>
       <c r="H145" t="n">
         <v>30704</v>
@@ -4603,7 +4603,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>15.4985446929932</v>
+        <v>15.4985456466675</v>
       </c>
       <c r="H146" t="n">
         <v>31317</v>
@@ -4661,7 +4661,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G148" t="n">
-        <v>16.2138633728027</v>
+        <v>16.2138595581055</v>
       </c>
       <c r="H148" t="n">
         <v>47178</v>
@@ -4748,7 +4748,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G151" t="n">
-        <v>15.6177644729614</v>
+        <v>15.6177654266357</v>
       </c>
       <c r="H151" t="n">
         <v>37397</v>
@@ -4777,7 +4777,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G152" t="n">
-        <v>15.3884963989258</v>
+        <v>15.3884944915771</v>
       </c>
       <c r="H152" t="n">
         <v>39472</v>
@@ -4806,7 +4806,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>15.2234210968018</v>
+        <v>15.2234239578247</v>
       </c>
       <c r="H153" t="n">
         <v>23169</v>
@@ -4835,7 +4835,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G154" t="n">
-        <v>16.1221523284912</v>
+        <v>16.1221542358398</v>
       </c>
       <c r="H154" t="n">
         <v>34140</v>
@@ -4864,7 +4864,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G155" t="n">
-        <v>15.8286895751953</v>
+        <v>15.8286914825439</v>
       </c>
       <c r="H155" t="n">
         <v>9705</v>
@@ -4893,7 +4893,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G156" t="n">
-        <v>16.0763034820557</v>
+        <v>16.076301574707</v>
       </c>
       <c r="H156" t="n">
         <v>10800</v>
@@ -5009,7 +5009,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G160" t="n">
-        <v>15.8470344543457</v>
+        <v>15.84703540802</v>
       </c>
       <c r="H160" t="n">
         <v>34139</v>
@@ -5067,7 +5067,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G162" t="n">
-        <v>15.9845933914185</v>
+        <v>15.9845914840698</v>
       </c>
       <c r="H162" t="n">
         <v>27116</v>
@@ -5096,7 +5096,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>16.4156169891357</v>
+        <v>16.4156188964844</v>
       </c>
       <c r="H163" t="n">
         <v>33297</v>
@@ -5125,7 +5125,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G164" t="n">
-        <v>17.1401042938232</v>
+        <v>17.1401062011719</v>
       </c>
       <c r="H164" t="n">
         <v>61398</v>
@@ -5154,7 +5154,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G165" t="n">
-        <v>16.8099594116211</v>
+        <v>16.8099613189697</v>
       </c>
       <c r="H165" t="n">
         <v>28597</v>
@@ -5183,7 +5183,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G166" t="n">
-        <v>16.8099594116211</v>
+        <v>16.8099613189697</v>
       </c>
       <c r="H166" t="n">
         <v>21263</v>
@@ -5270,7 +5270,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G169" t="n">
-        <v>16.6448860168457</v>
+        <v>16.6448841094971</v>
       </c>
       <c r="H169" t="n">
         <v>11997</v>
@@ -5299,7 +5299,7 @@
         <v>18.5</v>
       </c>
       <c r="G170" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H170" t="n">
         <v>28535</v>
@@ -5328,7 +5328,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G171" t="n">
-        <v>17.6078147888184</v>
+        <v>17.6078128814697</v>
       </c>
       <c r="H171" t="n">
         <v>76322</v>
@@ -5357,7 +5357,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>17.1492767333984</v>
+        <v>17.1492786407471</v>
       </c>
       <c r="H172" t="n">
         <v>36526</v>
@@ -5415,7 +5415,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G174" t="n">
-        <v>17.158447265625</v>
+        <v>17.1584415435791</v>
       </c>
       <c r="H174" t="n">
         <v>31232</v>
@@ -5531,7 +5531,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G178" t="n">
-        <v>17.4060573577881</v>
+        <v>17.4060554504395</v>
       </c>
       <c r="H178" t="n">
         <v>13916</v>
@@ -5589,7 +5589,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G180" t="n">
-        <v>17.0300559997559</v>
+        <v>17.0300579071045</v>
       </c>
       <c r="H180" t="n">
         <v>9227</v>
@@ -5618,7 +5618,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G181" t="n">
-        <v>17.2226409912109</v>
+        <v>17.2226428985596</v>
       </c>
       <c r="H181" t="n">
         <v>23636</v>
@@ -5647,7 +5647,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G182" t="n">
-        <v>17.4610824584961</v>
+        <v>17.4610805511475</v>
       </c>
       <c r="H182" t="n">
         <v>15383</v>
@@ -5676,7 +5676,7 @@
         <v>18.75</v>
       </c>
       <c r="G183" t="n">
-        <v>17.1951313018799</v>
+        <v>17.1951293945312</v>
       </c>
       <c r="H183" t="n">
         <v>26910</v>
@@ -5705,7 +5705,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>17.3326950073242</v>
+        <v>17.332691192627</v>
       </c>
       <c r="H184" t="n">
         <v>5983</v>
@@ -5763,7 +5763,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G186" t="n">
-        <v>16.7457675933838</v>
+        <v>16.7457656860352</v>
       </c>
       <c r="H186" t="n">
         <v>11319</v>
@@ -5792,7 +5792,7 @@
         <v>18.5</v>
       </c>
       <c r="G187" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H187" t="n">
         <v>39369</v>
@@ -5821,7 +5821,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G188" t="n">
-        <v>17.0300559997559</v>
+        <v>17.0300579071045</v>
       </c>
       <c r="H188" t="n">
         <v>3253</v>
@@ -5850,7 +5850,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G189" t="n">
-        <v>16.7457675933838</v>
+        <v>16.7457656860352</v>
       </c>
       <c r="H189" t="n">
         <v>7874</v>
@@ -5879,7 +5879,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>16.0946426391602</v>
+        <v>16.0946407318115</v>
       </c>
       <c r="H190" t="n">
         <v>57476</v>
@@ -5908,7 +5908,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G191" t="n">
-        <v>15.7828340530396</v>
+        <v>15.7828369140625</v>
       </c>
       <c r="H191" t="n">
         <v>119969</v>
@@ -5937,7 +5937,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G192" t="n">
-        <v>15.7828340530396</v>
+        <v>15.7828369140625</v>
       </c>
       <c r="H192" t="n">
         <v>32497</v>
@@ -5966,7 +5966,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G193" t="n">
-        <v>15.7553272247314</v>
+        <v>15.7553253173828</v>
       </c>
       <c r="H193" t="n">
         <v>20971</v>
@@ -5995,7 +5995,7 @@
         <v>17.25</v>
       </c>
       <c r="G194" t="n">
-        <v>15.8195171356201</v>
+        <v>15.8195209503174</v>
       </c>
       <c r="H194" t="n">
         <v>39194</v>
@@ -6024,7 +6024,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G195" t="n">
-        <v>15.8286895751953</v>
+        <v>15.8286914825439</v>
       </c>
       <c r="H195" t="n">
         <v>23145</v>
@@ -6053,7 +6053,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G196" t="n">
-        <v>15.9479093551636</v>
+        <v>15.9479074478149</v>
       </c>
       <c r="H196" t="n">
         <v>26230</v>
@@ -6082,7 +6082,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G197" t="n">
-        <v>15.8470344543457</v>
+        <v>15.84703540802</v>
       </c>
       <c r="H197" t="n">
         <v>27826</v>
@@ -6140,7 +6140,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G199" t="n">
-        <v>15.6636161804199</v>
+        <v>15.6636171340942</v>
       </c>
       <c r="H199" t="n">
         <v>15286</v>
@@ -6169,7 +6169,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>15.4985446929932</v>
+        <v>15.4985456466675</v>
       </c>
       <c r="H200" t="n">
         <v>26596</v>
@@ -6198,7 +6198,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G201" t="n">
-        <v>15.5627412796021</v>
+        <v>15.5627365112305</v>
       </c>
       <c r="H201" t="n">
         <v>28742</v>
@@ -6227,7 +6227,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G202" t="n">
-        <v>15.4893712997437</v>
+        <v>15.489372253418</v>
       </c>
       <c r="H202" t="n">
         <v>13901</v>
@@ -6256,7 +6256,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G203" t="n">
-        <v>15.6085968017578</v>
+        <v>15.6085948944092</v>
       </c>
       <c r="H203" t="n">
         <v>14432</v>
@@ -6314,7 +6314,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G205" t="n">
-        <v>15.7553272247314</v>
+        <v>15.7553253173828</v>
       </c>
       <c r="H205" t="n">
         <v>20290</v>
@@ -6343,7 +6343,7 @@
         <v>17.25</v>
       </c>
       <c r="G206" t="n">
-        <v>15.8195171356201</v>
+        <v>15.8195209503174</v>
       </c>
       <c r="H206" t="n">
         <v>15108</v>
@@ -6401,7 +6401,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G208" t="n">
-        <v>16.1221523284912</v>
+        <v>16.1221542358398</v>
       </c>
       <c r="H208" t="n">
         <v>32129</v>
@@ -6459,7 +6459,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G210" t="n">
-        <v>16.0579605102539</v>
+        <v>16.0579586029053</v>
       </c>
       <c r="H210" t="n">
         <v>31814</v>
@@ -6517,7 +6517,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G212" t="n">
-        <v>15.5443992614746</v>
+        <v>15.5443964004517</v>
       </c>
       <c r="H212" t="n">
         <v>15697</v>
@@ -6546,7 +6546,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G213" t="n">
-        <v>15.7002973556519</v>
+        <v>15.7003011703491</v>
       </c>
       <c r="H213" t="n">
         <v>29571</v>
@@ -6604,7 +6604,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>15.5443992614746</v>
+        <v>15.5443964004517</v>
       </c>
       <c r="H215" t="n">
         <v>10667</v>
@@ -6633,7 +6633,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>15.4068355560303</v>
+        <v>15.4068365097046</v>
       </c>
       <c r="H216" t="n">
         <v>23788</v>
@@ -6662,7 +6662,7 @@
         <v>16.75</v>
       </c>
       <c r="G217" t="n">
-        <v>15.3609828948975</v>
+        <v>15.3609838485718</v>
       </c>
       <c r="H217" t="n">
         <v>17451</v>
@@ -6691,7 +6691,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G218" t="n">
-        <v>15.1592273712158</v>
+        <v>15.1592264175415</v>
       </c>
       <c r="H218" t="n">
         <v>13732</v>
@@ -6720,7 +6720,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G219" t="n">
-        <v>15.2330408096313</v>
+        <v>15.2330417633057</v>
       </c>
       <c r="H219" t="n">
         <v>15710</v>
@@ -6778,7 +6778,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>15.5467433929443</v>
+        <v>15.5467414855957</v>
       </c>
       <c r="H221" t="n">
         <v>22485</v>
@@ -6836,7 +6836,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G223" t="n">
-        <v>15.7866334915161</v>
+        <v>15.7866306304932</v>
       </c>
       <c r="H223" t="n">
         <v>18529</v>
@@ -6865,7 +6865,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G224" t="n">
-        <v>15.5190629959106</v>
+        <v>15.5190649032593</v>
       </c>
       <c r="H224" t="n">
         <v>12930</v>
@@ -6923,7 +6923,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G226" t="n">
-        <v>15.3253049850464</v>
+        <v>15.3253059387207</v>
       </c>
       <c r="H226" t="n">
         <v>16757</v>
@@ -6952,7 +6952,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G227" t="n">
-        <v>15.4175701141357</v>
+        <v>15.4175710678101</v>
       </c>
       <c r="H227" t="n">
         <v>23714</v>
@@ -7010,7 +7010,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G229" t="n">
-        <v>15.0577344894409</v>
+        <v>15.0577363967896</v>
       </c>
       <c r="H229" t="n">
         <v>21791</v>
@@ -7039,7 +7039,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G230" t="n">
-        <v>15.7589521408081</v>
+        <v>15.7589530944824</v>
       </c>
       <c r="H230" t="n">
         <v>26262</v>
@@ -7068,7 +7068,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G231" t="n">
-        <v>16.2202796936035</v>
+        <v>16.2202777862549</v>
       </c>
       <c r="H231" t="n">
         <v>47333</v>
@@ -7097,7 +7097,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G232" t="n">
-        <v>15.8235397338867</v>
+        <v>15.8235387802124</v>
       </c>
       <c r="H232" t="n">
         <v>10075</v>
@@ -7126,7 +7126,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>15.3898916244507</v>
+        <v>15.3898944854736</v>
       </c>
       <c r="H233" t="n">
         <v>13313</v>
@@ -7155,7 +7155,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>15.5006093978882</v>
+        <v>15.5006084442139</v>
       </c>
       <c r="H234" t="n">
         <v>38423</v>
@@ -7184,7 +7184,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G235" t="n">
-        <v>15.2145853042603</v>
+        <v>15.2145862579346</v>
       </c>
       <c r="H235" t="n">
         <v>15151</v>
@@ -7242,7 +7242,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G237" t="n">
-        <v>15.9434871673584</v>
+        <v>15.9434852600098</v>
       </c>
       <c r="H237" t="n">
         <v>20608</v>
@@ -7271,7 +7271,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G238" t="n">
-        <v>15.8235397338867</v>
+        <v>15.8235387802124</v>
       </c>
       <c r="H238" t="n">
         <v>32816</v>
@@ -7300,7 +7300,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>15.7312746047974</v>
+        <v>15.7312726974487</v>
       </c>
       <c r="H239" t="n">
         <v>13860</v>
@@ -7329,7 +7329,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G240" t="n">
-        <v>16.2202796936035</v>
+        <v>16.2202777862549</v>
       </c>
       <c r="H240" t="n">
         <v>17938</v>
@@ -7387,7 +7387,7 @@
         <v>18.5</v>
       </c>
       <c r="G242" t="n">
-        <v>17.0691242218018</v>
+        <v>17.0691223144531</v>
       </c>
       <c r="H242" t="n">
         <v>48602</v>
@@ -7416,7 +7416,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G243" t="n">
-        <v>17.142936706543</v>
+        <v>17.1429347991943</v>
       </c>
       <c r="H243" t="n">
         <v>41612</v>
@@ -7503,7 +7503,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G246" t="n">
-        <v>16.9122714996338</v>
+        <v>16.9122734069824</v>
       </c>
       <c r="H246" t="n">
         <v>16838</v>
@@ -7532,7 +7532,7 @@
         <v>18.25</v>
       </c>
       <c r="G247" t="n">
-        <v>16.8384590148926</v>
+        <v>16.8384628295898</v>
       </c>
       <c r="H247" t="n">
         <v>14036</v>
@@ -7590,7 +7590,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>16.9768581390381</v>
+        <v>16.9768562316895</v>
       </c>
       <c r="H249" t="n">
         <v>27486</v>
@@ -7648,7 +7648,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G251" t="n">
-        <v>17.0506725311279</v>
+        <v>17.0506706237793</v>
       </c>
       <c r="H251" t="n">
         <v>30246</v>
@@ -7677,7 +7677,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>17.6227188110352</v>
+        <v>17.6227207183838</v>
       </c>
       <c r="H252" t="n">
         <v>152617</v>
@@ -7706,7 +7706,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G253" t="n">
-        <v>17.7795696258545</v>
+        <v>17.7795715332031</v>
       </c>
       <c r="H253" t="n">
         <v>63110</v>
@@ -7735,7 +7735,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>17.6227188110352</v>
+        <v>17.6227207183838</v>
       </c>
       <c r="H254" t="n">
         <v>33338</v>
@@ -7851,7 +7851,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G258" t="n">
-        <v>18.3054847717285</v>
+        <v>18.3054809570312</v>
       </c>
       <c r="H258" t="n">
         <v>77282</v>
@@ -7880,7 +7880,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>18.7760372161865</v>
+        <v>18.7760391235352</v>
       </c>
       <c r="H259" t="n">
         <v>73997</v>
@@ -7909,7 +7909,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>18.8221683502197</v>
+        <v>18.8221702575684</v>
       </c>
       <c r="H260" t="n">
         <v>29111</v>
@@ -7967,7 +7967,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G262" t="n">
-        <v>19.4957084655762</v>
+        <v>19.4957065582275</v>
       </c>
       <c r="H262" t="n">
         <v>36901</v>
@@ -8112,7 +8112,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>19.0528335571289</v>
+        <v>19.0528316497803</v>
       </c>
       <c r="H267" t="n">
         <v>21370</v>
@@ -8141,7 +8141,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G268" t="n">
-        <v>18.951343536377</v>
+        <v>18.9513416290283</v>
       </c>
       <c r="H268" t="n">
         <v>24551</v>
@@ -8170,7 +8170,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>18.7299041748047</v>
+        <v>18.7299022674561</v>
       </c>
       <c r="H269" t="n">
         <v>28479</v>
@@ -8199,7 +8199,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G270" t="n">
-        <v>18.8867530822754</v>
+        <v>18.8867492675781</v>
       </c>
       <c r="H270" t="n">
         <v>22743</v>
@@ -8228,7 +8228,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G271" t="n">
-        <v>18.8129425048828</v>
+        <v>18.8129386901855</v>
       </c>
       <c r="H271" t="n">
         <v>18271</v>
@@ -8257,7 +8257,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G272" t="n">
-        <v>18.8037185668945</v>
+        <v>18.8037128448486</v>
       </c>
       <c r="H272" t="n">
         <v>21264</v>
@@ -8286,7 +8286,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G273" t="n">
-        <v>18.6284122467041</v>
+        <v>18.6284103393555</v>
       </c>
       <c r="H273" t="n">
         <v>23196</v>
@@ -8315,7 +8315,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>18.7299041748047</v>
+        <v>18.7299022674561</v>
       </c>
       <c r="H274" t="n">
         <v>12986</v>
@@ -8402,7 +8402,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G277" t="n">
-        <v>18.2778034210205</v>
+        <v>18.2778015136719</v>
       </c>
       <c r="H277" t="n">
         <v>19746</v>
@@ -8431,7 +8431,7 @@
         <v>19.5</v>
       </c>
       <c r="G278" t="n">
-        <v>17.9917793273926</v>
+        <v>17.9917755126953</v>
       </c>
       <c r="H278" t="n">
         <v>16008</v>
@@ -8460,7 +8460,7 @@
         <v>19.8700008392334</v>
       </c>
       <c r="G279" t="n">
-        <v>18.3331623077393</v>
+        <v>18.3331642150879</v>
       </c>
       <c r="H279" t="n">
         <v>20550</v>
@@ -8489,7 +8489,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G280" t="n">
-        <v>18.4069786071777</v>
+        <v>18.4069728851318</v>
       </c>
       <c r="H280" t="n">
         <v>20999</v>
@@ -8547,7 +8547,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G282" t="n">
-        <v>18.3423900604248</v>
+        <v>18.3423881530762</v>
       </c>
       <c r="H282" t="n">
         <v>18898</v>
@@ -8721,7 +8721,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G288" t="n">
-        <v>18.3885231018066</v>
+        <v>18.388521194458</v>
       </c>
       <c r="H288" t="n">
         <v>13551</v>
@@ -8750,7 +8750,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G289" t="n">
-        <v>18.4900131225586</v>
+        <v>18.49001121521</v>
       </c>
       <c r="H289" t="n">
         <v>58575</v>
@@ -8866,7 +8866,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G293" t="n">
-        <v>18.7299041748047</v>
+        <v>18.7299022674561</v>
       </c>
       <c r="H293" t="n">
         <v>11363</v>
@@ -8953,7 +8953,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>19.2834968566895</v>
+        <v>19.2834949493408</v>
       </c>
       <c r="H296" t="n">
         <v>49075</v>
@@ -8982,7 +8982,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>18.9605693817139</v>
+        <v>18.9605674743652</v>
       </c>
       <c r="H297" t="n">
         <v>135669</v>
@@ -9040,7 +9040,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G299" t="n">
-        <v>19.237361907959</v>
+        <v>19.2373638153076</v>
       </c>
       <c r="H299" t="n">
         <v>19856</v>
@@ -9127,7 +9127,7 @@
         <v>20.4099998474121</v>
       </c>
       <c r="G302" t="n">
-        <v>18.8313941955566</v>
+        <v>18.8313961029053</v>
       </c>
       <c r="H302" t="n">
         <v>18297</v>
@@ -9156,7 +9156,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G303" t="n">
-        <v>19.1174182891846</v>
+        <v>19.1174163818359</v>
       </c>
       <c r="H303" t="n">
         <v>14235</v>
@@ -9185,7 +9185,7 @@
         <v>21</v>
       </c>
       <c r="G304" t="n">
-        <v>19.3757610321045</v>
+        <v>19.3757629394531</v>
       </c>
       <c r="H304" t="n">
         <v>41845</v>
@@ -9272,7 +9272,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G307" t="n">
-        <v>19.1174182891846</v>
+        <v>19.1174163818359</v>
       </c>
       <c r="H307" t="n">
         <v>19679</v>
@@ -9359,7 +9359,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.0989646911621</v>
+        <v>19.0989685058594</v>
       </c>
       <c r="H310" t="n">
         <v>29568</v>
@@ -9388,7 +9388,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G311" t="n">
-        <v>19.2558174133301</v>
+        <v>19.2558212280273</v>
       </c>
       <c r="H311" t="n">
         <v>45882</v>
@@ -9446,7 +9446,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G313" t="n">
-        <v>19.7817306518555</v>
+        <v>19.7817325592041</v>
       </c>
       <c r="H313" t="n">
         <v>66148</v>
@@ -9649,7 +9649,7 @@
         <v>21.6900005340576</v>
       </c>
       <c r="G320" t="n">
-        <v>20.0123920440674</v>
+        <v>20.0123958587646</v>
       </c>
       <c r="H320" t="n">
         <v>63283</v>
@@ -9707,7 +9707,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>20.2522869110107</v>
+        <v>20.2522850036621</v>
       </c>
       <c r="H322" t="n">
         <v>33960</v>
@@ -9736,7 +9736,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>20.1138858795166</v>
+        <v>20.1138877868652</v>
       </c>
       <c r="H323" t="n">
         <v>28637</v>
@@ -9765,7 +9765,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>20.4368133544922</v>
+        <v>20.4368152618408</v>
       </c>
       <c r="H324" t="n">
         <v>22191</v>
@@ -9794,7 +9794,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G325" t="n">
-        <v>20.5106239318848</v>
+        <v>20.5106258392334</v>
       </c>
       <c r="H325" t="n">
         <v>50029</v>
@@ -10229,7 +10229,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>21.1749382019043</v>
+        <v>21.1749401092529</v>
       </c>
       <c r="H340" t="n">
         <v>31821</v>
@@ -10316,7 +10316,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>21.1749382019043</v>
+        <v>21.1749401092529</v>
       </c>
       <c r="H343" t="n">
         <v>64135</v>
@@ -10345,7 +10345,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G344" t="n">
-        <v>20.9811820983887</v>
+        <v>20.9811840057373</v>
       </c>
       <c r="H344" t="n">
         <v>90206</v>
@@ -10548,7 +10548,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G351" t="n">
-        <v>21.0826759338379</v>
+        <v>21.0826740264893</v>
       </c>
       <c r="H351" t="n">
         <v>85673</v>
@@ -10577,7 +10577,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G352" t="n">
-        <v>20.5014019012451</v>
+        <v>20.5013999938965</v>
       </c>
       <c r="H352" t="n">
         <v>36212</v>
@@ -10693,7 +10693,7 @@
         <v>22.7299995422363</v>
       </c>
       <c r="G356" t="n">
-        <v>20.9719581604004</v>
+        <v>20.9719562530518</v>
       </c>
       <c r="H356" t="n">
         <v>37552</v>
@@ -10722,7 +10722,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G357" t="n">
-        <v>21.1103515625</v>
+        <v>21.1103534698486</v>
       </c>
       <c r="H357" t="n">
         <v>28638</v>
@@ -10751,7 +10751,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G358" t="n">
-        <v>21.1011276245117</v>
+        <v>21.1011257171631</v>
       </c>
       <c r="H358" t="n">
         <v>30676</v>
@@ -10809,7 +10809,7 @@
         <v>22.7299995422363</v>
       </c>
       <c r="G360" t="n">
-        <v>20.9719581604004</v>
+        <v>20.9719562530518</v>
       </c>
       <c r="H360" t="n">
         <v>11283</v>
@@ -10896,7 +10896,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G363" t="n">
-        <v>20.79665184021</v>
+        <v>20.7966537475586</v>
       </c>
       <c r="H363" t="n">
         <v>57934</v>
@@ -11041,7 +11041,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G368" t="n">
-        <v>20.2707366943359</v>
+        <v>20.2707386016846</v>
       </c>
       <c r="H368" t="n">
         <v>69910</v>
@@ -11070,7 +11070,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G369" t="n">
-        <v>20.5014019012451</v>
+        <v>20.5013999938965</v>
       </c>
       <c r="H369" t="n">
         <v>57155</v>
@@ -11099,7 +11099,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G370" t="n">
-        <v>20.1877002716064</v>
+        <v>20.1876983642578</v>
       </c>
       <c r="H370" t="n">
         <v>20027</v>
@@ -11128,7 +11128,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G371" t="n">
-        <v>20.4921722412109</v>
+        <v>20.4921760559082</v>
       </c>
       <c r="H371" t="n">
         <v>62846</v>
@@ -11215,7 +11215,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G374" t="n">
-        <v>19.9109001159668</v>
+        <v>19.9109020233154</v>
       </c>
       <c r="H374" t="n">
         <v>58932</v>
@@ -11244,7 +11244,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G375" t="n">
-        <v>20.0769805908203</v>
+        <v>20.0769786834717</v>
       </c>
       <c r="H375" t="n">
         <v>8785</v>
@@ -11273,7 +11273,7 @@
         <v>21.3099994659424</v>
       </c>
       <c r="G376" t="n">
-        <v>19.6617870330811</v>
+        <v>19.6617832183838</v>
       </c>
       <c r="H376" t="n">
         <v>17186</v>
@@ -11302,7 +11302,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G377" t="n">
-        <v>19.7725028991699</v>
+        <v>19.7725048065186</v>
       </c>
       <c r="H377" t="n">
         <v>24885</v>
@@ -11360,7 +11360,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>20.1600189208984</v>
+        <v>20.1600208282471</v>
       </c>
       <c r="H379" t="n">
         <v>12751</v>
@@ -11447,7 +11447,7 @@
         <v>22</v>
       </c>
       <c r="G382" t="n">
-        <v>20.2984199523926</v>
+        <v>20.2984180450439</v>
       </c>
       <c r="H382" t="n">
         <v>12653</v>
@@ -11505,7 +11505,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>19.698694229126</v>
+        <v>19.6986923217773</v>
       </c>
       <c r="H384" t="n">
         <v>15447</v>
@@ -11534,7 +11534,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G385" t="n">
-        <v>19.7540550231934</v>
+        <v>19.7540531158447</v>
       </c>
       <c r="H385" t="n">
         <v>8476</v>
@@ -11592,7 +11592,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>19.7909564971924</v>
+        <v>19.790958404541</v>
       </c>
       <c r="H387" t="n">
         <v>13573</v>
@@ -11621,7 +11621,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G388" t="n">
-        <v>19.9385814666748</v>
+        <v>19.9385833740234</v>
       </c>
       <c r="H388" t="n">
         <v>15173</v>
@@ -11679,7 +11679,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>19.9754867553711</v>
+        <v>19.9754848480225</v>
       </c>
       <c r="H390" t="n">
         <v>31020</v>
@@ -11737,7 +11737,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>19.9754867553711</v>
+        <v>19.9754848480225</v>
       </c>
       <c r="H392" t="n">
         <v>34425</v>
@@ -11824,7 +11824,7 @@
         <v>22.25</v>
       </c>
       <c r="G395" t="n">
-        <v>20.5290813446045</v>
+        <v>20.5290851593018</v>
       </c>
       <c r="H395" t="n">
         <v>32303</v>
@@ -11853,7 +11853,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G396" t="n">
-        <v>20.0769805908203</v>
+        <v>20.0769786834717</v>
       </c>
       <c r="H396" t="n">
         <v>38946</v>
@@ -11882,7 +11882,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G397" t="n">
-        <v>20.2522869110107</v>
+        <v>20.2522850036621</v>
       </c>
       <c r="H397" t="n">
         <v>42378</v>
@@ -11911,7 +11911,7 @@
         <v>21.7900009155273</v>
       </c>
       <c r="G398" t="n">
-        <v>20.1046619415283</v>
+        <v>20.1046600341797</v>
       </c>
       <c r="H398" t="n">
         <v>30566</v>
@@ -11940,7 +11940,7 @@
         <v>21.5</v>
       </c>
       <c r="G399" t="n">
-        <v>19.8370895385742</v>
+        <v>19.8370914459229</v>
       </c>
       <c r="H399" t="n">
         <v>36331</v>
@@ -11969,7 +11969,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G400" t="n">
-        <v>19.7909564971924</v>
+        <v>19.790958404541</v>
       </c>
       <c r="H400" t="n">
         <v>14656</v>
@@ -11998,7 +11998,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G401" t="n">
-        <v>19.9109001159668</v>
+        <v>19.9109020233154</v>
       </c>
       <c r="H401" t="n">
         <v>23442</v>
@@ -12027,7 +12027,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G402" t="n">
-        <v>19.698694229126</v>
+        <v>19.6986923217773</v>
       </c>
       <c r="H402" t="n">
         <v>18860</v>
@@ -12056,7 +12056,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>19.698694229126</v>
+        <v>19.6986923217773</v>
       </c>
       <c r="H403" t="n">
         <v>21085</v>
@@ -12085,7 +12085,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G404" t="n">
-        <v>19.5972023010254</v>
+        <v>19.5971984863281</v>
       </c>
       <c r="H404" t="n">
         <v>7170</v>
@@ -12114,7 +12114,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G405" t="n">
-        <v>20.0769805908203</v>
+        <v>20.0769786834717</v>
       </c>
       <c r="H405" t="n">
         <v>39480</v>
@@ -12143,7 +12143,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G406" t="n">
-        <v>20.2707366943359</v>
+        <v>20.2707386016846</v>
       </c>
       <c r="H406" t="n">
         <v>19645</v>
@@ -12172,7 +12172,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G407" t="n">
-        <v>20.2707366943359</v>
+        <v>20.2707386016846</v>
       </c>
       <c r="H407" t="n">
         <v>12205</v>
@@ -12201,7 +12201,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>20.2799663543701</v>
+        <v>20.2799682617188</v>
       </c>
       <c r="H408" t="n">
         <v>18657</v>
@@ -12230,7 +12230,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G409" t="n">
-        <v>19.9939422607422</v>
+        <v>19.9939403533936</v>
       </c>
       <c r="H409" t="n">
         <v>12488</v>
@@ -12259,7 +12259,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>20.2522869110107</v>
+        <v>20.2522850036621</v>
       </c>
       <c r="H410" t="n">
         <v>36549</v>
@@ -12288,7 +12288,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G411" t="n">
-        <v>20.3537769317627</v>
+        <v>20.3537750244141</v>
       </c>
       <c r="H411" t="n">
         <v>25491</v>
@@ -12346,7 +12346,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G413" t="n">
-        <v>20.7043857574463</v>
+        <v>20.7043876647949</v>
       </c>
       <c r="H413" t="n">
         <v>28346</v>
@@ -12375,7 +12375,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G414" t="n">
-        <v>20.2061557769775</v>
+        <v>20.2061538696289</v>
       </c>
       <c r="H414" t="n">
         <v>22878</v>
@@ -12404,7 +12404,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G415" t="n">
-        <v>20.7043857574463</v>
+        <v>20.7043876647949</v>
       </c>
       <c r="H415" t="n">
         <v>7332</v>
@@ -12433,7 +12433,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G416" t="n">
-        <v>20.4275894165039</v>
+        <v>20.4275875091553</v>
       </c>
       <c r="H416" t="n">
         <v>26649</v>
@@ -12462,7 +12462,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G417" t="n">
-        <v>20.7505207061768</v>
+        <v>20.7505168914795</v>
       </c>
       <c r="H417" t="n">
         <v>77812</v>
@@ -12578,7 +12578,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G421" t="n">
-        <v>21.0549945831299</v>
+        <v>21.0549964904785</v>
       </c>
       <c r="H421" t="n">
         <v>29792</v>
@@ -12636,7 +12636,7 @@
         <v>22.3099994659424</v>
       </c>
       <c r="G423" t="n">
-        <v>20.5844402313232</v>
+        <v>20.5844383239746</v>
       </c>
       <c r="H423" t="n">
         <v>22154</v>
@@ -12665,7 +12665,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G424" t="n">
-        <v>20.3353252410889</v>
+        <v>20.3353233337402</v>
       </c>
       <c r="H424" t="n">
         <v>6450</v>
@@ -12694,7 +12694,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G425" t="n">
-        <v>20.2707366943359</v>
+        <v>20.2707386016846</v>
       </c>
       <c r="H425" t="n">
         <v>20559</v>
@@ -12752,7 +12752,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G427" t="n">
-        <v>20.1138858795166</v>
+        <v>20.1138877868652</v>
       </c>
       <c r="H427" t="n">
         <v>80031</v>
@@ -12781,7 +12781,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G428" t="n">
-        <v>20.1969242095947</v>
+        <v>20.196928024292</v>
       </c>
       <c r="H428" t="n">
         <v>15886</v>
@@ -12810,7 +12810,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G429" t="n">
-        <v>20.1969242095947</v>
+        <v>20.196928024292</v>
       </c>
       <c r="H429" t="n">
         <v>22061</v>
@@ -12868,7 +12868,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>20.1600189208984</v>
+        <v>20.1600208282471</v>
       </c>
       <c r="H431" t="n">
         <v>11427</v>
@@ -12926,7 +12926,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G433" t="n">
-        <v>19.9109001159668</v>
+        <v>19.9109020233154</v>
       </c>
       <c r="H433" t="n">
         <v>48281</v>
@@ -12955,7 +12955,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>19.7448234558105</v>
+        <v>19.7448215484619</v>
       </c>
       <c r="H434" t="n">
         <v>11290</v>
@@ -12984,7 +12984,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>19.7909564971924</v>
+        <v>19.790958404541</v>
       </c>
       <c r="H435" t="n">
         <v>27283</v>
@@ -13013,7 +13013,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G436" t="n">
-        <v>19.7079181671143</v>
+        <v>19.7079219818115</v>
       </c>
       <c r="H436" t="n">
         <v>23244</v>
@@ -13100,7 +13100,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G439" t="n">
-        <v>19.7817306518555</v>
+        <v>19.7817325592041</v>
       </c>
       <c r="H439" t="n">
         <v>24594</v>
@@ -13158,7 +13158,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G441" t="n">
-        <v>19.9570331573486</v>
+        <v>19.9570369720459</v>
       </c>
       <c r="H441" t="n">
         <v>33947</v>
@@ -13187,7 +13187,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G442" t="n">
-        <v>20.2061557769775</v>
+        <v>20.2061538696289</v>
       </c>
       <c r="H442" t="n">
         <v>26218</v>
@@ -13216,7 +13216,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G443" t="n">
-        <v>20.2707366943359</v>
+        <v>20.2707386016846</v>
       </c>
       <c r="H443" t="n">
         <v>7095</v>
@@ -13332,7 +13332,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G447" t="n">
-        <v>20.2799663543701</v>
+        <v>20.2799682617188</v>
       </c>
       <c r="H447" t="n">
         <v>25474</v>
@@ -13419,7 +13419,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G450" t="n">
-        <v>20.3814563751221</v>
+        <v>20.3814582824707</v>
       </c>
       <c r="H450" t="n">
         <v>7845</v>
@@ -13448,7 +13448,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G451" t="n">
-        <v>19.855541229248</v>
+        <v>19.8555431365967</v>
       </c>
       <c r="H451" t="n">
         <v>36507</v>
@@ -13477,7 +13477,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G452" t="n">
-        <v>20.3537769317627</v>
+        <v>20.3537750244141</v>
       </c>
       <c r="H452" t="n">
         <v>104609</v>
@@ -13506,7 +13506,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G453" t="n">
-        <v>19.4034461975098</v>
+        <v>19.4034404754639</v>
       </c>
       <c r="H453" t="n">
         <v>67115</v>
@@ -13564,7 +13564,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>19.0528335571289</v>
+        <v>19.0528316497803</v>
       </c>
       <c r="H455" t="n">
         <v>33727</v>
@@ -13593,7 +13593,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G456" t="n">
-        <v>19.0528335571289</v>
+        <v>19.0528316497803</v>
       </c>
       <c r="H456" t="n">
         <v>35171</v>
@@ -13680,7 +13680,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G459" t="n">
-        <v>18.6560897827148</v>
+        <v>18.6560916900635</v>
       </c>
       <c r="H459" t="n">
         <v>29725</v>
@@ -13709,7 +13709,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G460" t="n">
-        <v>18.8129425048828</v>
+        <v>18.8129386901855</v>
       </c>
       <c r="H460" t="n">
         <v>29832</v>
@@ -13738,7 +13738,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G461" t="n">
-        <v>18.7114505767822</v>
+        <v>18.7114524841309</v>
       </c>
       <c r="H461" t="n">
         <v>16803</v>
@@ -13767,7 +13767,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G462" t="n">
-        <v>18.5084648132324</v>
+        <v>18.5084667205811</v>
       </c>
       <c r="H462" t="n">
         <v>27962</v>
@@ -13796,7 +13796,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G463" t="n">
-        <v>18.8037185668945</v>
+        <v>18.8037128448486</v>
       </c>
       <c r="H463" t="n">
         <v>15728</v>
@@ -13854,7 +13854,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G465" t="n">
-        <v>18.5546016693115</v>
+        <v>18.5545978546143</v>
       </c>
       <c r="H465" t="n">
         <v>13390</v>
@@ -13883,7 +13883,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G466" t="n">
-        <v>18.4346523284912</v>
+        <v>18.4346542358398</v>
       </c>
       <c r="H466" t="n">
         <v>25305</v>
@@ -13912,7 +13912,7 @@
         <v>20.0900001525879</v>
       </c>
       <c r="G467" t="n">
-        <v>18.5361442565918</v>
+        <v>18.5361480712891</v>
       </c>
       <c r="H467" t="n">
         <v>19752</v>
@@ -13941,7 +13941,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>18.3147106170654</v>
+        <v>18.3147087097168</v>
       </c>
       <c r="H468" t="n">
         <v>8584</v>
@@ -13970,7 +13970,7 @@
         <v>20.25</v>
       </c>
       <c r="G469" t="n">
-        <v>18.6837711334229</v>
+        <v>18.6837692260742</v>
       </c>
       <c r="H469" t="n">
         <v>15211</v>
@@ -13999,7 +13999,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G470" t="n">
-        <v>18.9605693817139</v>
+        <v>18.9605674743652</v>
       </c>
       <c r="H470" t="n">
         <v>21082</v>
@@ -14057,7 +14057,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G472" t="n">
-        <v>18.8037185668945</v>
+        <v>18.8037128448486</v>
       </c>
       <c r="H472" t="n">
         <v>20881</v>
@@ -14115,7 +14115,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G474" t="n">
-        <v>18.849760055542</v>
+        <v>18.8497562408447</v>
       </c>
       <c r="H474" t="n">
         <v>18471</v>
@@ -14144,7 +14144,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G475" t="n">
-        <v>18.8219432830811</v>
+        <v>18.8219413757324</v>
       </c>
       <c r="H475" t="n">
         <v>22915</v>
@@ -14173,7 +14173,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G476" t="n">
-        <v>18.4047088623047</v>
+        <v>18.4047069549561</v>
       </c>
       <c r="H476" t="n">
         <v>17548</v>
@@ -14202,7 +14202,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G477" t="n">
-        <v>18.1821804046631</v>
+        <v>18.1821823120117</v>
       </c>
       <c r="H477" t="n">
         <v>27017</v>
@@ -14260,7 +14260,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G479" t="n">
-        <v>17.7278614044189</v>
+        <v>17.7278594970703</v>
       </c>
       <c r="H479" t="n">
         <v>19845</v>
@@ -14289,7 +14289,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G480" t="n">
-        <v>17.5238800048828</v>
+        <v>17.5238780975342</v>
       </c>
       <c r="H480" t="n">
         <v>28888</v>
@@ -14318,7 +14318,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G481" t="n">
-        <v>17.5516929626465</v>
+        <v>17.5516948699951</v>
       </c>
       <c r="H481" t="n">
         <v>20865</v>
@@ -14347,7 +14347,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G482" t="n">
-        <v>17.8205757141113</v>
+        <v>17.82057762146</v>
       </c>
       <c r="H482" t="n">
         <v>32245</v>
@@ -14434,7 +14434,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G485" t="n">
-        <v>18.1450958251953</v>
+        <v>18.1450939178467</v>
       </c>
       <c r="H485" t="n">
         <v>22132</v>
@@ -14463,7 +14463,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G486" t="n">
-        <v>18.3398056030273</v>
+        <v>18.3398017883301</v>
       </c>
       <c r="H486" t="n">
         <v>15740</v>
@@ -14492,7 +14492,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G487" t="n">
-        <v>18.4603404998779</v>
+        <v>18.4603385925293</v>
       </c>
       <c r="H487" t="n">
         <v>25717</v>
@@ -14579,7 +14579,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G490" t="n">
-        <v>18.0431041717529</v>
+        <v>18.0431022644043</v>
       </c>
       <c r="H490" t="n">
         <v>16630</v>
@@ -14608,7 +14608,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G491" t="n">
-        <v>18.1821804046631</v>
+        <v>18.1821823120117</v>
       </c>
       <c r="H491" t="n">
         <v>44994</v>
@@ -14637,7 +14637,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G492" t="n">
-        <v>18.3676204681396</v>
+        <v>18.367618560791</v>
       </c>
       <c r="H492" t="n">
         <v>26139</v>
@@ -14666,7 +14666,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G493" t="n">
-        <v>18.2378120422363</v>
+        <v>18.237813949585</v>
       </c>
       <c r="H493" t="n">
         <v>42972</v>
@@ -14695,7 +14695,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G494" t="n">
-        <v>18.0987339019775</v>
+        <v>18.0987377166748</v>
       </c>
       <c r="H494" t="n">
         <v>9160</v>
@@ -14782,7 +14782,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G497" t="n">
-        <v>18.6457786560059</v>
+        <v>18.6457767486572</v>
       </c>
       <c r="H497" t="n">
         <v>12181</v>
@@ -14840,7 +14840,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G499" t="n">
-        <v>18.562328338623</v>
+        <v>18.5623302459717</v>
       </c>
       <c r="H499" t="n">
         <v>11716</v>
@@ -14869,7 +14869,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G500" t="n">
-        <v>18.4881534576416</v>
+        <v>18.488151550293</v>
       </c>
       <c r="H500" t="n">
         <v>22877</v>
@@ -14898,7 +14898,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G501" t="n">
-        <v>18.2285404205322</v>
+        <v>18.2285423278809</v>
       </c>
       <c r="H501" t="n">
         <v>22558</v>
@@ -14927,7 +14927,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G502" t="n">
-        <v>18.2563571929932</v>
+        <v>18.2563591003418</v>
       </c>
       <c r="H502" t="n">
         <v>30706</v>
@@ -14956,7 +14956,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G503" t="n">
-        <v>18.3212623596191</v>
+        <v>18.3212604522705</v>
       </c>
       <c r="H503" t="n">
         <v>35093</v>
@@ -15014,7 +15014,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G505" t="n">
-        <v>18.3490791320801</v>
+        <v>18.3490772247314</v>
       </c>
       <c r="H505" t="n">
         <v>18477</v>
@@ -15043,7 +15043,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G506" t="n">
-        <v>18.5345134735107</v>
+        <v>18.5345115661621</v>
       </c>
       <c r="H506" t="n">
         <v>14488</v>
@@ -15072,7 +15072,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G507" t="n">
-        <v>18.5808715820312</v>
+        <v>18.5808734893799</v>
       </c>
       <c r="H507" t="n">
         <v>24263</v>
@@ -15101,7 +15101,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G508" t="n">
-        <v>18.469612121582</v>
+        <v>18.4696083068848</v>
       </c>
       <c r="H508" t="n">
         <v>19500</v>
@@ -15130,7 +15130,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G509" t="n">
-        <v>18.469612121582</v>
+        <v>18.4696083068848</v>
       </c>
       <c r="H509" t="n">
         <v>9688</v>
@@ -15188,7 +15188,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G511" t="n">
-        <v>18.3676204681396</v>
+        <v>18.367618560791</v>
       </c>
       <c r="H511" t="n">
         <v>20759</v>
@@ -15217,7 +15217,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G512" t="n">
-        <v>18.3490791320801</v>
+        <v>18.3490772247314</v>
       </c>
       <c r="H512" t="n">
         <v>6062</v>
@@ -15304,7 +15304,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>19.0537414550781</v>
+        <v>19.0537395477295</v>
       </c>
       <c r="H515" t="n">
         <v>24155</v>
@@ -15333,7 +15333,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G516" t="n">
-        <v>19.3318939208984</v>
+        <v>19.3318958282471</v>
       </c>
       <c r="H516" t="n">
         <v>70849</v>
@@ -15391,7 +15391,7 @@
         <v>22</v>
       </c>
       <c r="G518" t="n">
-        <v>20.3981647491455</v>
+        <v>20.3981628417969</v>
       </c>
       <c r="H518" t="n">
         <v>70505</v>
@@ -15420,7 +15420,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G519" t="n">
-        <v>21.1399154663086</v>
+        <v>21.13991355896</v>
       </c>
       <c r="H519" t="n">
         <v>163517</v>
@@ -15478,7 +15478,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>21.1399154663086</v>
+        <v>21.13991355896</v>
       </c>
       <c r="H521" t="n">
         <v>76402</v>
@@ -15507,7 +15507,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G522" t="n">
-        <v>21.3717098236084</v>
+        <v>21.371711730957</v>
       </c>
       <c r="H522" t="n">
         <v>76179</v>
@@ -15536,7 +15536,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>21.2326354980469</v>
+        <v>21.2326335906982</v>
       </c>
       <c r="H523" t="n">
         <v>49536</v>
@@ -15565,7 +15565,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>21.4644317626953</v>
+        <v>21.4644298553467</v>
       </c>
       <c r="H524" t="n">
         <v>47137</v>
@@ -15652,7 +15652,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>21.6035099029541</v>
+        <v>21.6035079956055</v>
       </c>
       <c r="H527" t="n">
         <v>69528</v>
@@ -15710,7 +15710,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>21.3717098236084</v>
+        <v>21.371711730957</v>
       </c>
       <c r="H529" t="n">
         <v>26143</v>
@@ -15768,7 +15768,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G531" t="n">
-        <v>21.6498699188232</v>
+        <v>21.6498680114746</v>
       </c>
       <c r="H531" t="n">
         <v>48363</v>
@@ -15826,7 +15826,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G533" t="n">
-        <v>21.3717098236084</v>
+        <v>21.371711730957</v>
       </c>
       <c r="H533" t="n">
         <v>42345</v>
@@ -15884,7 +15884,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G535" t="n">
-        <v>21.2326354980469</v>
+        <v>21.2326335906982</v>
       </c>
       <c r="H535" t="n">
         <v>38209</v>
@@ -15971,7 +15971,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>20.9081192016602</v>
+        <v>20.9081153869629</v>
       </c>
       <c r="H538" t="n">
         <v>23371</v>
@@ -16116,7 +16116,7 @@
         <v>22.25</v>
       </c>
       <c r="G543" t="n">
-        <v>20.6299610137939</v>
+        <v>20.6299629211426</v>
       </c>
       <c r="H543" t="n">
         <v>20428</v>
@@ -16174,7 +16174,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G545" t="n">
-        <v>20.9544792175293</v>
+        <v>20.9544773101807</v>
       </c>
       <c r="H545" t="n">
         <v>16417</v>
@@ -16203,7 +16203,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G546" t="n">
-        <v>20.9081192016602</v>
+        <v>20.9081153869629</v>
       </c>
       <c r="H546" t="n">
         <v>11923</v>
@@ -16232,7 +16232,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471935272217</v>
       </c>
       <c r="H547" t="n">
         <v>8341</v>
@@ -16261,7 +16261,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>21.0008354187012</v>
+        <v>21.0008335113525</v>
       </c>
       <c r="H548" t="n">
         <v>10821</v>
@@ -16290,7 +16290,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G549" t="n">
-        <v>20.7226791381836</v>
+        <v>20.722677230835</v>
       </c>
       <c r="H549" t="n">
         <v>9616</v>
@@ -16319,7 +16319,7 @@
         <v>22</v>
       </c>
       <c r="G550" t="n">
-        <v>20.3981647491455</v>
+        <v>20.3981628417969</v>
       </c>
       <c r="H550" t="n">
         <v>10608</v>
@@ -16377,7 +16377,7 @@
         <v>22</v>
       </c>
       <c r="G552" t="n">
-        <v>20.3981647491455</v>
+        <v>20.3981628417969</v>
       </c>
       <c r="H552" t="n">
         <v>63901</v>
@@ -16406,7 +16406,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>21.6035099029541</v>
+        <v>21.6035079956055</v>
       </c>
       <c r="H553" t="n">
         <v>106785</v>
@@ -16435,7 +16435,7 @@
         <v>23.25</v>
       </c>
       <c r="G554" t="n">
-        <v>21.5571517944336</v>
+        <v>21.5571479797363</v>
       </c>
       <c r="H554" t="n">
         <v>156886</v>
@@ -16464,7 +16464,7 @@
         <v>23.25</v>
       </c>
       <c r="G555" t="n">
-        <v>21.5571517944336</v>
+        <v>21.5571479797363</v>
       </c>
       <c r="H555" t="n">
         <v>237507</v>
@@ -16493,7 +16493,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>21.4644317626953</v>
+        <v>21.4644298553467</v>
       </c>
       <c r="H556" t="n">
         <v>33185</v>
@@ -16551,7 +16551,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>21.7425899505615</v>
+        <v>21.7425880432129</v>
       </c>
       <c r="H558" t="n">
         <v>63622</v>
@@ -16580,7 +16580,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>21.9280242919922</v>
+        <v>21.9280281066895</v>
       </c>
       <c r="H559" t="n">
         <v>54096</v>
@@ -16609,7 +16609,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>21.8353099822998</v>
+        <v>21.8353061676025</v>
       </c>
       <c r="H560" t="n">
         <v>38449</v>
@@ -16638,7 +16638,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G561" t="n">
-        <v>21.3717098236084</v>
+        <v>21.371711730957</v>
       </c>
       <c r="H561" t="n">
         <v>32122</v>
@@ -16696,7 +16696,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471935272217</v>
       </c>
       <c r="H563" t="n">
         <v>43117</v>
@@ -16725,7 +16725,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471935272217</v>
       </c>
       <c r="H564" t="n">
         <v>21687</v>
@@ -16812,7 +16812,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>20.9544792175293</v>
+        <v>20.9544773101807</v>
       </c>
       <c r="H567" t="n">
         <v>15271</v>
@@ -16841,7 +16841,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>20.7226791381836</v>
+        <v>20.722677230835</v>
       </c>
       <c r="H568" t="n">
         <v>27519</v>
@@ -16870,7 +16870,7 @@
         <v>22.75</v>
       </c>
       <c r="G569" t="n">
-        <v>21.0935573577881</v>
+        <v>21.0935535430908</v>
       </c>
       <c r="H569" t="n">
         <v>41089</v>
@@ -16899,7 +16899,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>20.7226791381836</v>
+        <v>20.722677230835</v>
       </c>
       <c r="H570" t="n">
         <v>21232</v>
@@ -16928,7 +16928,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>20.7226791381836</v>
+        <v>20.722677230835</v>
       </c>
       <c r="H571" t="n">
         <v>12000</v>
@@ -16986,7 +16986,7 @@
         <v>21.75</v>
       </c>
       <c r="G573" t="n">
-        <v>20.1663665771484</v>
+        <v>20.1663684844971</v>
       </c>
       <c r="H573" t="n">
         <v>19943</v>
@@ -17160,7 +17160,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471935272217</v>
       </c>
       <c r="H579" t="n">
         <v>36379</v>
@@ -17247,7 +17247,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471935272217</v>
       </c>
       <c r="H582" t="n">
         <v>19364</v>
@@ -17305,7 +17305,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G584" t="n">
-        <v>20.444522857666</v>
+        <v>20.4445247650146</v>
       </c>
       <c r="H584" t="n">
         <v>16581</v>
@@ -17334,7 +17334,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G585" t="n">
-        <v>20.8153991699219</v>
+        <v>20.8153972625732</v>
       </c>
       <c r="H585" t="n">
         <v>34337</v>
@@ -17363,7 +17363,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G586" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471935272217</v>
       </c>
       <c r="H586" t="n">
         <v>31766</v>
@@ -17450,7 +17450,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>20.9544792175293</v>
+        <v>20.9544773101807</v>
       </c>
       <c r="H589" t="n">
         <v>42855</v>
@@ -17479,7 +17479,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>20.9081192016602</v>
+        <v>20.9081153869629</v>
       </c>
       <c r="H590" t="n">
         <v>5669</v>
@@ -17537,7 +17537,7 @@
         <v>22.25</v>
       </c>
       <c r="G592" t="n">
-        <v>20.6299610137939</v>
+        <v>20.6299629211426</v>
       </c>
       <c r="H592" t="n">
         <v>27279</v>
@@ -17624,7 +17624,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G595" t="n">
-        <v>21.2326354980469</v>
+        <v>21.2326335906982</v>
       </c>
       <c r="H595" t="n">
         <v>33837</v>
@@ -17653,7 +17653,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>21.0008354187012</v>
+        <v>21.0008335113525</v>
       </c>
       <c r="H596" t="n">
         <v>7652</v>
@@ -17682,7 +17682,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>20.8153991699219</v>
+        <v>20.8153972625732</v>
       </c>
       <c r="H597" t="n">
         <v>13297</v>
@@ -17711,7 +17711,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471935272217</v>
       </c>
       <c r="H598" t="n">
         <v>23626</v>
@@ -17769,7 +17769,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>20.7226791381836</v>
+        <v>20.722677230835</v>
       </c>
       <c r="H600" t="n">
         <v>48289</v>
@@ -17856,7 +17856,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G603" t="n">
-        <v>20.444522857666</v>
+        <v>20.4445247650146</v>
       </c>
       <c r="H603" t="n">
         <v>29035</v>
@@ -17914,7 +17914,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>20.3518085479736</v>
+        <v>20.3518047332764</v>
       </c>
       <c r="H605" t="n">
         <v>31385</v>
@@ -17943,7 +17943,7 @@
         <v>22.25</v>
       </c>
       <c r="G606" t="n">
-        <v>20.6299610137939</v>
+        <v>20.6299629211426</v>
       </c>
       <c r="H606" t="n">
         <v>88362</v>
@@ -18059,7 +18059,7 @@
         <v>22</v>
       </c>
       <c r="G610" t="n">
-        <v>20.3981647491455</v>
+        <v>20.3981628417969</v>
       </c>
       <c r="H610" t="n">
         <v>17228</v>
@@ -18088,7 +18088,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G611" t="n">
-        <v>20.7226791381836</v>
+        <v>20.722677230835</v>
       </c>
       <c r="H611" t="n">
         <v>20399</v>
@@ -18117,7 +18117,7 @@
         <v>22.25</v>
       </c>
       <c r="G612" t="n">
-        <v>20.6299610137939</v>
+        <v>20.6299629211426</v>
       </c>
       <c r="H612" t="n">
         <v>25403</v>
@@ -18146,7 +18146,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>19.9809265136719</v>
+        <v>19.9809303283691</v>
       </c>
       <c r="H613" t="n">
         <v>53004</v>
@@ -18175,7 +18175,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G614" t="n">
-        <v>18.8683032989502</v>
+        <v>18.8683013916016</v>
       </c>
       <c r="H614" t="n">
         <v>68212</v>
@@ -18233,7 +18233,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G616" t="n">
-        <v>18.4881534576416</v>
+        <v>18.488151550293</v>
       </c>
       <c r="H616" t="n">
         <v>41726</v>
@@ -18349,7 +18349,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G620" t="n">
-        <v>19.6564121246338</v>
+        <v>19.6564159393311</v>
       </c>
       <c r="H620" t="n">
         <v>35604</v>
@@ -18378,7 +18378,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G621" t="n">
-        <v>19.6564121246338</v>
+        <v>19.6564159393311</v>
       </c>
       <c r="H621" t="n">
         <v>30321</v>
@@ -18407,7 +18407,7 @@
         <v>21</v>
       </c>
       <c r="G622" t="n">
-        <v>19.4709758758545</v>
+        <v>19.4709777832031</v>
       </c>
       <c r="H622" t="n">
         <v>12684</v>
@@ -18465,7 +18465,7 @@
         <v>21.75</v>
       </c>
       <c r="G624" t="n">
-        <v>20.1663665771484</v>
+        <v>20.1663684844971</v>
       </c>
       <c r="H624" t="n">
         <v>26565</v>
@@ -18494,7 +18494,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G625" t="n">
-        <v>20.2127246856689</v>
+        <v>20.2127265930176</v>
       </c>
       <c r="H625" t="n">
         <v>41019</v>
@@ -18552,7 +18552,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>20.1200065612793</v>
+        <v>20.1200103759766</v>
       </c>
       <c r="H627" t="n">
         <v>16136</v>
@@ -18610,7 +18610,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>19.8418502807617</v>
+        <v>19.8418521881104</v>
       </c>
       <c r="H629" t="n">
         <v>14368</v>
@@ -18639,7 +18639,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G630" t="n">
-        <v>19.8418502807617</v>
+        <v>19.8418521881104</v>
       </c>
       <c r="H630" t="n">
         <v>7158</v>
@@ -18697,7 +18697,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G632" t="n">
-        <v>20.0272903442383</v>
+        <v>20.0272884368896</v>
       </c>
       <c r="H632" t="n">
         <v>11595</v>
@@ -18726,7 +18726,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G633" t="n">
-        <v>19.8882083892822</v>
+        <v>19.8882122039795</v>
       </c>
       <c r="H633" t="n">
         <v>14444</v>
@@ -18755,7 +18755,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G634" t="n">
-        <v>19.8418502807617</v>
+        <v>19.8418521881104</v>
       </c>
       <c r="H634" t="n">
         <v>15839</v>
@@ -18813,7 +18813,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G636" t="n">
-        <v>19.6564121246338</v>
+        <v>19.6564159393311</v>
       </c>
       <c r="H636" t="n">
         <v>16915</v>
@@ -18842,7 +18842,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G637" t="n">
-        <v>19.7491321563721</v>
+        <v>19.7491302490234</v>
       </c>
       <c r="H637" t="n">
         <v>101033</v>
@@ -18871,7 +18871,7 @@
         <v>21</v>
       </c>
       <c r="G638" t="n">
-        <v>19.4709758758545</v>
+        <v>19.4709777832031</v>
       </c>
       <c r="H638" t="n">
         <v>31002</v>
@@ -18900,7 +18900,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>19.7954921722412</v>
+        <v>19.7954940795898</v>
       </c>
       <c r="H639" t="n">
         <v>51440</v>
@@ -18958,7 +18958,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>19.7954921722412</v>
+        <v>19.7954940795898</v>
       </c>
       <c r="H641" t="n">
         <v>20014</v>
@@ -18987,7 +18987,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>19.7954921722412</v>
+        <v>19.7954940795898</v>
       </c>
       <c r="H642" t="n">
         <v>19845</v>
@@ -19016,7 +19016,7 @@
         <v>21.75</v>
       </c>
       <c r="G643" t="n">
-        <v>20.1663665771484</v>
+        <v>20.1663684844971</v>
       </c>
       <c r="H643" t="n">
         <v>20181</v>
@@ -19045,7 +19045,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>20.2127246856689</v>
+        <v>20.2127265930176</v>
       </c>
       <c r="H644" t="n">
         <v>46061</v>
@@ -19074,7 +19074,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G645" t="n">
-        <v>20.1200065612793</v>
+        <v>20.1200103759766</v>
       </c>
       <c r="H645" t="n">
         <v>34095</v>
@@ -19103,7 +19103,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G646" t="n">
-        <v>20.3518085479736</v>
+        <v>20.3518047332764</v>
       </c>
       <c r="H646" t="n">
         <v>16901</v>
@@ -19161,7 +19161,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G648" t="n">
-        <v>20.444522857666</v>
+        <v>20.4445247650146</v>
       </c>
       <c r="H648" t="n">
         <v>29204</v>
@@ -19190,7 +19190,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G649" t="n">
-        <v>20.3518085479736</v>
+        <v>20.3518047332764</v>
       </c>
       <c r="H649" t="n">
         <v>67074</v>
@@ -19219,7 +19219,7 @@
         <v>22</v>
       </c>
       <c r="G650" t="n">
-        <v>20.3981647491455</v>
+        <v>20.3981628417969</v>
       </c>
       <c r="H650" t="n">
         <v>5748</v>
@@ -19248,7 +19248,7 @@
         <v>21.75</v>
       </c>
       <c r="G651" t="n">
-        <v>20.1663665771484</v>
+        <v>20.1663684844971</v>
       </c>
       <c r="H651" t="n">
         <v>14885</v>
@@ -19277,7 +19277,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>19.8418502807617</v>
+        <v>19.8418521881104</v>
       </c>
       <c r="H652" t="n">
         <v>14698</v>
@@ -19306,7 +19306,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>19.2855358123779</v>
+        <v>19.2855377197266</v>
       </c>
       <c r="H653" t="n">
         <v>25929</v>
@@ -19335,7 +19335,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G654" t="n">
-        <v>19.4246139526367</v>
+        <v>19.4246158599854</v>
       </c>
       <c r="H654" t="n">
         <v>27208</v>
@@ -19364,7 +19364,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G655" t="n">
-        <v>19.2855358123779</v>
+        <v>19.2855377197266</v>
       </c>
       <c r="H655" t="n">
         <v>22236</v>
@@ -19480,7 +19480,7 @@
         <v>21</v>
       </c>
       <c r="G659" t="n">
-        <v>19.4709758758545</v>
+        <v>19.4709777832031</v>
       </c>
       <c r="H659" t="n">
         <v>10511</v>
@@ -19538,7 +19538,7 @@
         <v>21</v>
       </c>
       <c r="G661" t="n">
-        <v>19.4709758758545</v>
+        <v>19.4709777832031</v>
       </c>
       <c r="H661" t="n">
         <v>26576</v>
@@ -19654,7 +19654,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>19.5636901855469</v>
+        <v>19.5636940002441</v>
       </c>
       <c r="H665" t="n">
         <v>7572</v>
@@ -19741,7 +19741,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G668" t="n">
-        <v>19.4246139526367</v>
+        <v>19.4246158599854</v>
       </c>
       <c r="H668" t="n">
         <v>9967</v>
@@ -19770,7 +19770,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>19.5636901855469</v>
+        <v>19.5636940002441</v>
       </c>
       <c r="H669" t="n">
         <v>10384</v>
@@ -19828,7 +19828,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>19.3318939208984</v>
+        <v>19.3318958282471</v>
       </c>
       <c r="H671" t="n">
         <v>9635</v>
@@ -19857,7 +19857,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G672" t="n">
-        <v>19.1464614868164</v>
+        <v>19.1464595794678</v>
       </c>
       <c r="H672" t="n">
         <v>4451</v>
@@ -19973,7 +19973,7 @@
         <v>20.75</v>
       </c>
       <c r="G676" t="n">
-        <v>19.2391757965088</v>
+        <v>19.2391777038574</v>
       </c>
       <c r="H676" t="n">
         <v>7292</v>
@@ -20002,7 +20002,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>19.4246139526367</v>
+        <v>19.4246158599854</v>
       </c>
       <c r="H677" t="n">
         <v>4723</v>
@@ -20031,7 +20031,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>19.4246139526367</v>
+        <v>19.4246158599854</v>
       </c>
       <c r="H678" t="n">
         <v>3805</v>
@@ -20060,7 +20060,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>20.0272903442383</v>
+        <v>20.0272884368896</v>
       </c>
       <c r="H679" t="n">
         <v>11621</v>
@@ -20118,7 +20118,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>19.5636901855469</v>
+        <v>19.5636940002441</v>
       </c>
       <c r="H681" t="n">
         <v>14113</v>
@@ -20147,7 +20147,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>19.7491321563721</v>
+        <v>19.7491302490234</v>
       </c>
       <c r="H682" t="n">
         <v>16185</v>
@@ -20176,7 +20176,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>20.0272903442383</v>
+        <v>20.0272884368896</v>
       </c>
       <c r="H683" t="n">
         <v>13405</v>
@@ -20205,7 +20205,7 @@
         <v>22.25</v>
       </c>
       <c r="G684" t="n">
-        <v>20.6299610137939</v>
+        <v>20.6299629211426</v>
       </c>
       <c r="H684" t="n">
         <v>27903</v>
@@ -20350,7 +20350,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G689" t="n">
-        <v>20.7226791381836</v>
+        <v>20.722677230835</v>
       </c>
       <c r="H689" t="n">
         <v>13795</v>
@@ -20379,7 +20379,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G690" t="n">
-        <v>21.0008354187012</v>
+        <v>21.0008335113525</v>
       </c>
       <c r="H690" t="n">
         <v>14529</v>
@@ -20408,7 +20408,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>20.9544792175293</v>
+        <v>20.9544773101807</v>
       </c>
       <c r="H691" t="n">
         <v>21175</v>
@@ -20437,7 +20437,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>20.9544792175293</v>
+        <v>20.9544773101807</v>
       </c>
       <c r="H692" t="n">
         <v>4369</v>
@@ -20466,7 +20466,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>20.9081192016602</v>
+        <v>20.9081153869629</v>
       </c>
       <c r="H693" t="n">
         <v>7284</v>
@@ -20495,7 +20495,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>21.2326354980469</v>
+        <v>21.2326335906982</v>
       </c>
       <c r="H694" t="n">
         <v>44066</v>
@@ -20582,7 +20582,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G697" t="n">
-        <v>21.1399154663086</v>
+        <v>21.13991355896</v>
       </c>
       <c r="H697" t="n">
         <v>14041</v>
@@ -20611,7 +20611,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471935272217</v>
       </c>
       <c r="H698" t="n">
         <v>23800</v>
@@ -20640,7 +20640,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>21.2326354980469</v>
+        <v>21.2326335906982</v>
       </c>
       <c r="H699" t="n">
         <v>45041</v>
@@ -20727,7 +20727,7 @@
         <v>22.75</v>
       </c>
       <c r="G702" t="n">
-        <v>21.0935573577881</v>
+        <v>21.0935535430908</v>
       </c>
       <c r="H702" t="n">
         <v>9042</v>
@@ -20785,7 +20785,7 @@
         <v>23.25</v>
       </c>
       <c r="G704" t="n">
-        <v>21.5571517944336</v>
+        <v>21.5571479797363</v>
       </c>
       <c r="H704" t="n">
         <v>12269</v>
@@ -20814,7 +20814,7 @@
         <v>23.25</v>
       </c>
       <c r="G705" t="n">
-        <v>21.5571517944336</v>
+        <v>21.5571479797363</v>
       </c>
       <c r="H705" t="n">
         <v>12214</v>
@@ -20872,7 +20872,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>20.1200065612793</v>
+        <v>20.1200103759766</v>
       </c>
       <c r="H707" t="n">
         <v>26134</v>
@@ -20959,7 +20959,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G710" t="n">
-        <v>19.8882083892822</v>
+        <v>19.8882122039795</v>
       </c>
       <c r="H710" t="n">
         <v>25401</v>
@@ -20988,7 +20988,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>19.7954921722412</v>
+        <v>19.7954940795898</v>
       </c>
       <c r="H711" t="n">
         <v>11915</v>
@@ -21017,7 +21017,7 @@
         <v>21</v>
       </c>
       <c r="G712" t="n">
-        <v>19.4709758758545</v>
+        <v>19.4709777832031</v>
       </c>
       <c r="H712" t="n">
         <v>14023</v>
@@ -21046,7 +21046,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G713" t="n">
-        <v>20.1200065612793</v>
+        <v>20.1200103759766</v>
       </c>
       <c r="H713" t="n">
         <v>20192</v>
@@ -21075,7 +21075,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>19.5636901855469</v>
+        <v>19.5636940002441</v>
       </c>
       <c r="H714" t="n">
         <v>60696</v>
@@ -21104,7 +21104,7 @@
         <v>21</v>
       </c>
       <c r="G715" t="n">
-        <v>19.4709758758545</v>
+        <v>19.4709777832031</v>
       </c>
       <c r="H715" t="n">
         <v>31944</v>
@@ -21133,7 +21133,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>19.2855358123779</v>
+        <v>19.2855377197266</v>
       </c>
       <c r="H716" t="n">
         <v>53397</v>
@@ -21162,7 +21162,7 @@
         <v>20.75</v>
       </c>
       <c r="G717" t="n">
-        <v>19.2391757965088</v>
+        <v>19.2391777038574</v>
       </c>
       <c r="H717" t="n">
         <v>8400</v>
@@ -21220,7 +21220,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G719" t="n">
-        <v>15.205904006958</v>
+        <v>15.2059049606323</v>
       </c>
       <c r="H719" t="n">
         <v>293766</v>
@@ -21249,7 +21249,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G720" t="n">
-        <v>15.5953226089478</v>
+        <v>15.5953235626221</v>
       </c>
       <c r="H720" t="n">
         <v>193084</v>
@@ -21307,7 +21307,7 @@
         <v>15.5</v>
       </c>
       <c r="G722" t="n">
-        <v>14.371434211731</v>
+        <v>14.3714332580566</v>
       </c>
       <c r="H722" t="n">
         <v>192645</v>
@@ -21394,7 +21394,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G725" t="n">
-        <v>15.5211477279663</v>
+        <v>15.5211505889893</v>
       </c>
       <c r="H725" t="n">
         <v>84445</v>
@@ -21423,7 +21423,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G726" t="n">
-        <v>15.8920211791992</v>
+        <v>15.8920221328735</v>
       </c>
       <c r="H726" t="n">
         <v>89330</v>
@@ -21452,7 +21452,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G727" t="n">
-        <v>15.4284286499023</v>
+        <v>15.4284296035767</v>
       </c>
       <c r="H727" t="n">
         <v>105540</v>
@@ -21481,7 +21481,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G728" t="n">
-        <v>15.2244501113892</v>
+        <v>15.2244472503662</v>
       </c>
       <c r="H728" t="n">
         <v>58119</v>
@@ -21510,7 +21510,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G729" t="n">
-        <v>15.3542528152466</v>
+        <v>15.3542537689209</v>
       </c>
       <c r="H729" t="n">
         <v>20474</v>
@@ -21568,7 +21568,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G731" t="n">
-        <v>15.6880407333374</v>
+        <v>15.6880416870117</v>
       </c>
       <c r="H731" t="n">
         <v>46259</v>
@@ -21597,7 +21597,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G732" t="n">
-        <v>15.6880407333374</v>
+        <v>15.6880416870117</v>
       </c>
       <c r="H732" t="n">
         <v>40182</v>
@@ -21626,7 +21626,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G733" t="n">
-        <v>15.5582361221313</v>
+        <v>15.558235168457</v>
       </c>
       <c r="H733" t="n">
         <v>68590</v>
@@ -21655,7 +21655,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>15.4840612411499</v>
+        <v>15.4840593338013</v>
       </c>
       <c r="H734" t="n">
         <v>42010</v>
@@ -21684,7 +21684,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G735" t="n">
-        <v>15.2800788879395</v>
+        <v>15.2800779342651</v>
       </c>
       <c r="H735" t="n">
         <v>38419</v>
@@ -21742,7 +21742,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G737" t="n">
-        <v>14.7599258422852</v>
+        <v>14.7599248886108</v>
       </c>
       <c r="H737" t="n">
         <v>32514</v>
@@ -21771,7 +21771,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G738" t="n">
-        <v>14.4800281524658</v>
+        <v>14.4800271987915</v>
       </c>
       <c r="H738" t="n">
         <v>35416</v>
@@ -21800,7 +21800,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G739" t="n">
-        <v>14.3120899200439</v>
+        <v>14.3120889663696</v>
       </c>
       <c r="H739" t="n">
         <v>29995</v>
@@ -21858,7 +21858,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G741" t="n">
-        <v>14.3120899200439</v>
+        <v>14.3120889663696</v>
       </c>
       <c r="H741" t="n">
         <v>99873</v>
@@ -21887,7 +21887,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G742" t="n">
-        <v>14.8159055709839</v>
+        <v>14.8159036636353</v>
       </c>
       <c r="H742" t="n">
         <v>23327</v>
@@ -21945,7 +21945,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G744" t="n">
-        <v>14.5546674728394</v>
+        <v>14.5546684265137</v>
       </c>
       <c r="H744" t="n">
         <v>33338</v>
@@ -21974,7 +21974,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G745" t="n">
-        <v>14.7599258422852</v>
+        <v>14.7599248886108</v>
       </c>
       <c r="H745" t="n">
         <v>79480</v>
@@ -22003,7 +22003,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G746" t="n">
-        <v>15.0398225784302</v>
+        <v>15.0398235321045</v>
       </c>
       <c r="H746" t="n">
         <v>39162</v>
@@ -22090,7 +22090,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G749" t="n">
-        <v>14.7599258422852</v>
+        <v>14.7599248886108</v>
       </c>
       <c r="H749" t="n">
         <v>27881</v>
@@ -22119,7 +22119,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G750" t="n">
-        <v>13.9762105941772</v>
+        <v>13.9762125015259</v>
       </c>
       <c r="H750" t="n">
         <v>59346</v>
@@ -22148,7 +22148,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G751" t="n">
-        <v>13.8269338607788</v>
+        <v>13.8269329071045</v>
       </c>
       <c r="H751" t="n">
         <v>21193</v>
@@ -22206,7 +22206,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G753" t="n">
-        <v>13.6403350830078</v>
+        <v>13.6403341293335</v>
       </c>
       <c r="H753" t="n">
         <v>38754</v>
@@ -22235,7 +22235,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G754" t="n">
-        <v>14.2374486923218</v>
+        <v>14.2374505996704</v>
       </c>
       <c r="H754" t="n">
         <v>47839</v>
@@ -22351,7 +22351,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G758" t="n">
-        <v>13.8642530441284</v>
+        <v>13.8642520904541</v>
       </c>
       <c r="H758" t="n">
         <v>16527</v>
@@ -22380,7 +22380,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G759" t="n">
-        <v>13.5470361709595</v>
+        <v>13.5470380783081</v>
       </c>
       <c r="H759" t="n">
         <v>27400</v>
@@ -22409,7 +22409,7 @@
         <v>14.5</v>
       </c>
       <c r="G760" t="n">
-        <v>13.528374671936</v>
+        <v>13.5283756256104</v>
       </c>
       <c r="H760" t="n">
         <v>24670</v>
@@ -22438,7 +22438,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G761" t="n">
-        <v>13.6963148117065</v>
+        <v>13.6963157653809</v>
       </c>
       <c r="H761" t="n">
         <v>32342</v>
@@ -22496,7 +22496,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G763" t="n">
-        <v>14.2374486923218</v>
+        <v>14.2374505996704</v>
       </c>
       <c r="H763" t="n">
         <v>22749</v>
@@ -22583,7 +22583,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>14.5546674728394</v>
+        <v>14.5546684265137</v>
       </c>
       <c r="H766" t="n">
         <v>29260</v>
@@ -22612,7 +22612,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G767" t="n">
-        <v>14.7599258422852</v>
+        <v>14.7599248886108</v>
       </c>
       <c r="H767" t="n">
         <v>15092</v>
@@ -22670,7 +22670,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>15.1144618988037</v>
+        <v>15.114462852478</v>
       </c>
       <c r="H769" t="n">
         <v>32371</v>
@@ -22699,7 +22699,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>15.1144618988037</v>
+        <v>15.114462852478</v>
       </c>
       <c r="H770" t="n">
         <v>29082</v>
@@ -22728,7 +22728,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>15.0211620330811</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H771" t="n">
         <v>18295</v>
@@ -22815,7 +22815,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G774" t="n">
-        <v>14.9651861190796</v>
+        <v>14.965184211731</v>
       </c>
       <c r="H774" t="n">
         <v>7959</v>
@@ -22844,7 +22844,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G775" t="n">
-        <v>14.7972450256348</v>
+        <v>14.7972431182861</v>
       </c>
       <c r="H775" t="n">
         <v>22626</v>
@@ -22873,7 +22873,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G776" t="n">
-        <v>15.0025033950806</v>
+        <v>15.0025024414062</v>
       </c>
       <c r="H776" t="n">
         <v>28368</v>
@@ -22902,7 +22902,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G777" t="n">
-        <v>15.0211620330811</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H777" t="n">
         <v>12161</v>
@@ -22931,7 +22931,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G778" t="n">
-        <v>15.0584812164307</v>
+        <v>15.058482170105</v>
       </c>
       <c r="H778" t="n">
         <v>11898</v>
@@ -22960,7 +22960,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G779" t="n">
-        <v>15.0398225784302</v>
+        <v>15.0398235321045</v>
       </c>
       <c r="H779" t="n">
         <v>23254</v>
@@ -23018,7 +23018,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G781" t="n">
-        <v>15.431679725647</v>
+        <v>15.4316816329956</v>
       </c>
       <c r="H781" t="n">
         <v>75352</v>
@@ -23134,7 +23134,7 @@
         <v>18</v>
       </c>
       <c r="G785" t="n">
-        <v>16.7938461303711</v>
+        <v>16.7938480377197</v>
       </c>
       <c r="H785" t="n">
         <v>36242</v>
@@ -23163,7 +23163,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G786" t="n">
-        <v>16.3833293914795</v>
+        <v>16.3833312988281</v>
       </c>
       <c r="H786" t="n">
         <v>21191</v>
@@ -23221,7 +23221,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G788" t="n">
-        <v>16.1594123840332</v>
+        <v>16.1594085693359</v>
       </c>
       <c r="H788" t="n">
         <v>18002</v>
@@ -23250,7 +23250,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G789" t="n">
-        <v>16.2527122497559</v>
+        <v>16.2527141571045</v>
       </c>
       <c r="H789" t="n">
         <v>20511</v>
@@ -23279,7 +23279,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G790" t="n">
-        <v>15.8795175552368</v>
+        <v>15.8795166015625</v>
       </c>
       <c r="H790" t="n">
         <v>17031</v>
@@ -23308,7 +23308,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>15.7675561904907</v>
+        <v>15.7675552368164</v>
       </c>
       <c r="H791" t="n">
         <v>21984</v>
@@ -23337,7 +23337,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G792" t="n">
-        <v>15.7115745544434</v>
+        <v>15.7115774154663</v>
       </c>
       <c r="H792" t="n">
         <v>9190</v>
@@ -23395,7 +23395,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G794" t="n">
-        <v>16.0287952423096</v>
+        <v>16.0287933349609</v>
       </c>
       <c r="H794" t="n">
         <v>16281</v>
@@ -23482,7 +23482,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>16.5139484405518</v>
+        <v>16.5139503479004</v>
       </c>
       <c r="H797" t="n">
         <v>17894</v>
@@ -23540,7 +23540,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G799" t="n">
-        <v>16.178071975708</v>
+        <v>16.1780738830566</v>
       </c>
       <c r="H799" t="n">
         <v>35647</v>
@@ -23569,7 +23569,7 @@
         <v>17.5</v>
       </c>
       <c r="G800" t="n">
-        <v>16.3273506164551</v>
+        <v>16.3273487091064</v>
       </c>
       <c r="H800" t="n">
         <v>9871</v>
@@ -23598,7 +23598,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G801" t="n">
-        <v>16.3460083007812</v>
+        <v>16.3460102081299</v>
       </c>
       <c r="H801" t="n">
         <v>15026</v>
@@ -23656,7 +23656,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G803" t="n">
-        <v>16.1220951080322</v>
+        <v>16.1220932006836</v>
       </c>
       <c r="H803" t="n">
         <v>16875</v>
@@ -23685,7 +23685,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G804" t="n">
-        <v>16.1220951080322</v>
+        <v>16.1220932006836</v>
       </c>
       <c r="H804" t="n">
         <v>14233</v>
@@ -23714,7 +23714,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>16.5139484405518</v>
+        <v>16.5139503479004</v>
       </c>
       <c r="H805" t="n">
         <v>28460</v>
@@ -23801,7 +23801,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>16.6072463989258</v>
+        <v>16.6072444915771</v>
       </c>
       <c r="H808" t="n">
         <v>7788</v>
@@ -23830,7 +23830,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G809" t="n">
-        <v>16.3646678924561</v>
+        <v>16.3646697998047</v>
       </c>
       <c r="H809" t="n">
         <v>46188</v>
@@ -23888,7 +23888,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>15.7675561904907</v>
+        <v>15.7675552368164</v>
       </c>
       <c r="H811" t="n">
         <v>26100</v>
@@ -23917,7 +23917,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G812" t="n">
-        <v>15.7488965988159</v>
+        <v>15.7488956451416</v>
       </c>
       <c r="H812" t="n">
         <v>18087</v>
@@ -23946,7 +23946,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>15.7675561904907</v>
+        <v>15.7675552368164</v>
       </c>
       <c r="H813" t="n">
         <v>17451</v>
@@ -23975,7 +23975,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G814" t="n">
-        <v>15.8421955108643</v>
+        <v>15.8421964645386</v>
       </c>
       <c r="H814" t="n">
         <v>31398</v>
@@ -24004,7 +24004,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G815" t="n">
-        <v>15.7488965988159</v>
+        <v>15.7488956451416</v>
       </c>
       <c r="H815" t="n">
         <v>8805</v>
@@ -24062,7 +24062,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G817" t="n">
-        <v>15.8235340118408</v>
+        <v>15.8235349655151</v>
       </c>
       <c r="H817" t="n">
         <v>19265</v>
@@ -24120,7 +24120,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G819" t="n">
-        <v>15.8795175552368</v>
+        <v>15.8795166015625</v>
       </c>
       <c r="H819" t="n">
         <v>10457</v>
@@ -24149,7 +24149,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G820" t="n">
-        <v>15.898175239563</v>
+        <v>15.8981742858887</v>
       </c>
       <c r="H820" t="n">
         <v>9126</v>
@@ -24207,7 +24207,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>16.2340526580811</v>
+        <v>16.2340507507324</v>
       </c>
       <c r="H822" t="n">
         <v>61264</v>
@@ -24236,7 +24236,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G823" t="n">
-        <v>16.2900295257568</v>
+        <v>16.2900314331055</v>
       </c>
       <c r="H823" t="n">
         <v>15799</v>
@@ -24265,7 +24265,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>16.4206485748291</v>
+        <v>16.4206504821777</v>
       </c>
       <c r="H824" t="n">
         <v>21788</v>
@@ -24323,7 +24323,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G826" t="n">
-        <v>16.6632270812988</v>
+        <v>16.6632289886475</v>
       </c>
       <c r="H826" t="n">
         <v>36590</v>
@@ -24468,7 +24468,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G831" t="n">
-        <v>18.1186962127686</v>
+        <v>18.1186943054199</v>
       </c>
       <c r="H831" t="n">
         <v>21478</v>
@@ -24497,7 +24497,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G832" t="n">
-        <v>17.9880771636963</v>
+        <v>17.9880752563477</v>
       </c>
       <c r="H832" t="n">
         <v>18627</v>
@@ -24526,7 +24526,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G833" t="n">
-        <v>17.4096183776855</v>
+        <v>17.4096202850342</v>
       </c>
       <c r="H833" t="n">
         <v>47242</v>
@@ -24555,7 +24555,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G834" t="n">
-        <v>17.017765045166</v>
+        <v>17.0177631378174</v>
       </c>
       <c r="H834" t="n">
         <v>30697</v>
@@ -24613,7 +24613,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G836" t="n">
-        <v>16.8684844970703</v>
+        <v>16.8684864044189</v>
       </c>
       <c r="H836" t="n">
         <v>31843</v>
@@ -24642,7 +24642,7 @@
         <v>18</v>
       </c>
       <c r="G837" t="n">
-        <v>16.7938461303711</v>
+        <v>16.7938480377197</v>
       </c>
       <c r="H837" t="n">
         <v>33449</v>
@@ -24700,7 +24700,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>16.6072463989258</v>
+        <v>16.6072444915771</v>
       </c>
       <c r="H839" t="n">
         <v>21116</v>
@@ -24729,7 +24729,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>16.6072463989258</v>
+        <v>16.6072444915771</v>
       </c>
       <c r="H840" t="n">
         <v>26446</v>
@@ -24758,7 +24758,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G841" t="n">
-        <v>16.6632270812988</v>
+        <v>16.6632289886475</v>
       </c>
       <c r="H841" t="n">
         <v>47781</v>
@@ -24787,7 +24787,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G842" t="n">
-        <v>16.5326080322266</v>
+        <v>16.5326061248779</v>
       </c>
       <c r="H842" t="n">
         <v>6625</v>
@@ -24816,7 +24816,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G843" t="n">
-        <v>16.8498249053955</v>
+        <v>16.8498268127441</v>
       </c>
       <c r="H843" t="n">
         <v>30729</v>
@@ -24845,7 +24845,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G844" t="n">
-        <v>16.8498249053955</v>
+        <v>16.8498268127441</v>
       </c>
       <c r="H844" t="n">
         <v>8387</v>
@@ -24874,7 +24874,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G845" t="n">
-        <v>16.7192039489746</v>
+        <v>16.7192096710205</v>
       </c>
       <c r="H845" t="n">
         <v>8828</v>
@@ -24903,7 +24903,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G846" t="n">
-        <v>16.9431266784668</v>
+        <v>16.9431228637695</v>
       </c>
       <c r="H846" t="n">
         <v>7484</v>
@@ -24961,7 +24961,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G848" t="n">
-        <v>17.1110610961914</v>
+        <v>17.1110649108887</v>
       </c>
       <c r="H848" t="n">
         <v>14480</v>
@@ -24990,7 +24990,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G849" t="n">
-        <v>16.644567489624</v>
+        <v>16.6445693969727</v>
       </c>
       <c r="H849" t="n">
         <v>27230</v>
@@ -25048,7 +25048,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G851" t="n">
-        <v>16.1034336090088</v>
+        <v>16.1034317016602</v>
       </c>
       <c r="H851" t="n">
         <v>27584</v>
@@ -25077,7 +25077,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G852" t="n">
-        <v>16.1034336090088</v>
+        <v>16.1034317016602</v>
       </c>
       <c r="H852" t="n">
         <v>40911</v>
@@ -25135,7 +25135,7 @@
         <v>16.5</v>
       </c>
       <c r="G854" t="n">
-        <v>15.394359588623</v>
+        <v>15.3943605422974</v>
       </c>
       <c r="H854" t="n">
         <v>40064</v>
@@ -25164,7 +25164,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G855" t="n">
-        <v>15.4130172729492</v>
+        <v>15.4130182266235</v>
       </c>
       <c r="H855" t="n">
         <v>101404</v>
@@ -25193,7 +25193,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G856" t="n">
-        <v>15.3570394515991</v>
+        <v>15.3570404052734</v>
       </c>
       <c r="H856" t="n">
         <v>76066</v>
@@ -25222,7 +25222,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G857" t="n">
-        <v>15.431679725647</v>
+        <v>15.4316816329956</v>
       </c>
       <c r="H857" t="n">
         <v>42973</v>
@@ -25251,7 +25251,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G858" t="n">
-        <v>15.0771408081055</v>
+        <v>15.0771417617798</v>
       </c>
       <c r="H858" t="n">
         <v>25946</v>
@@ -25280,7 +25280,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G859" t="n">
-        <v>14.591986656189</v>
+        <v>14.5919857025146</v>
       </c>
       <c r="H859" t="n">
         <v>22488</v>
@@ -25309,7 +25309,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G860" t="n">
-        <v>14.7039451599121</v>
+        <v>14.7039461135864</v>
       </c>
       <c r="H860" t="n">
         <v>23693</v>
@@ -25338,7 +25338,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G861" t="n">
-        <v>14.9838418960571</v>
+        <v>14.9838428497314</v>
       </c>
       <c r="H861" t="n">
         <v>15878</v>
@@ -25396,7 +25396,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G863" t="n">
-        <v>14.8718843460083</v>
+        <v>14.871883392334</v>
       </c>
       <c r="H863" t="n">
         <v>11696</v>
@@ -25454,7 +25454,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G865" t="n">
-        <v>14.741265296936</v>
+        <v>14.7412643432617</v>
       </c>
       <c r="H865" t="n">
         <v>13099</v>
@@ -25483,7 +25483,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G866" t="n">
-        <v>14.405387878418</v>
+        <v>14.4053869247437</v>
       </c>
       <c r="H866" t="n">
         <v>28040</v>
@@ -25541,7 +25541,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G868" t="n">
-        <v>14.27476978302</v>
+        <v>14.2747678756714</v>
       </c>
       <c r="H868" t="n">
         <v>39174</v>
@@ -25628,7 +25628,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G871" t="n">
-        <v>14.7972450256348</v>
+        <v>14.7972431182861</v>
       </c>
       <c r="H871" t="n">
         <v>49735</v>
@@ -25657,7 +25657,7 @@
         <v>15.5</v>
       </c>
       <c r="G872" t="n">
-        <v>14.461368560791</v>
+        <v>14.4613676071167</v>
       </c>
       <c r="H872" t="n">
         <v>27300</v>
@@ -25715,7 +25715,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G874" t="n">
-        <v>14.5360078811646</v>
+        <v>14.5360059738159</v>
       </c>
       <c r="H874" t="n">
         <v>20430</v>
@@ -25802,7 +25802,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G877" t="n">
-        <v>15.4689979553223</v>
+        <v>15.4689989089966</v>
       </c>
       <c r="H877" t="n">
         <v>48759</v>
@@ -25831,7 +25831,7 @@
         <v>16.5</v>
       </c>
       <c r="G878" t="n">
-        <v>15.394359588623</v>
+        <v>15.3943605422974</v>
       </c>
       <c r="H878" t="n">
         <v>37103</v>
@@ -25860,7 +25860,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G879" t="n">
-        <v>15.431679725647</v>
+        <v>15.4316816329956</v>
       </c>
       <c r="H879" t="n">
         <v>22992</v>
@@ -25889,7 +25889,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G880" t="n">
-        <v>15.3570394515991</v>
+        <v>15.3570404052734</v>
       </c>
       <c r="H880" t="n">
         <v>39729</v>
@@ -25918,7 +25918,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>15.3010597229004</v>
+        <v>15.301061630249</v>
       </c>
       <c r="H881" t="n">
         <v>18408</v>
@@ -26005,7 +26005,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G884" t="n">
-        <v>15.0211620330811</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H884" t="n">
         <v>14419</v>
@@ -26034,7 +26034,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G885" t="n">
-        <v>15.1331195831299</v>
+        <v>15.1331205368042</v>
       </c>
       <c r="H885" t="n">
         <v>9715</v>
@@ -26063,7 +26063,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G886" t="n">
-        <v>14.9651861190796</v>
+        <v>14.965184211731</v>
       </c>
       <c r="H886" t="n">
         <v>6520</v>
@@ -26092,7 +26092,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G887" t="n">
-        <v>14.9092025756836</v>
+        <v>14.9092044830322</v>
       </c>
       <c r="H887" t="n">
         <v>21487</v>
@@ -26121,7 +26121,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G888" t="n">
-        <v>15.0398225784302</v>
+        <v>15.0398235321045</v>
       </c>
       <c r="H888" t="n">
         <v>11864</v>
@@ -26150,7 +26150,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G889" t="n">
-        <v>15.4876575469971</v>
+        <v>15.4876594543457</v>
       </c>
       <c r="H889" t="n">
         <v>20824</v>
@@ -26179,7 +26179,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G890" t="n">
-        <v>15.431679725647</v>
+        <v>15.4316816329956</v>
       </c>
       <c r="H890" t="n">
         <v>18050</v>
@@ -26208,7 +26208,7 @@
         <v>16.5</v>
       </c>
       <c r="G891" t="n">
-        <v>15.394359588623</v>
+        <v>15.3943605422974</v>
       </c>
       <c r="H891" t="n">
         <v>18797</v>
@@ -26237,7 +26237,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G892" t="n">
-        <v>15.4689979553223</v>
+        <v>15.4689989089966</v>
       </c>
       <c r="H892" t="n">
         <v>22331</v>
@@ -26266,7 +26266,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G893" t="n">
-        <v>15.3197212219238</v>
+        <v>15.3197193145752</v>
       </c>
       <c r="H893" t="n">
         <v>22421</v>
@@ -26295,7 +26295,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G894" t="n">
-        <v>15.2264194488525</v>
+        <v>15.2264213562012</v>
       </c>
       <c r="H894" t="n">
         <v>6135</v>
@@ -26324,7 +26324,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G895" t="n">
-        <v>15.2264194488525</v>
+        <v>15.2264213562012</v>
       </c>
       <c r="H895" t="n">
         <v>5603</v>
@@ -26382,7 +26382,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G897" t="n">
-        <v>15.0025033950806</v>
+        <v>15.0025024414062</v>
       </c>
       <c r="H897" t="n">
         <v>15701</v>
@@ -26411,7 +26411,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G898" t="n">
-        <v>14.7599258422852</v>
+        <v>14.7599248886108</v>
       </c>
       <c r="H898" t="n">
         <v>42893</v>
@@ -26440,7 +26440,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G899" t="n">
-        <v>14.8718843460083</v>
+        <v>14.871883392334</v>
       </c>
       <c r="H899" t="n">
         <v>42950</v>
@@ -26469,7 +26469,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G900" t="n">
-        <v>14.9465246200562</v>
+        <v>14.9465236663818</v>
       </c>
       <c r="H900" t="n">
         <v>23925</v>
@@ -26498,7 +26498,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G901" t="n">
-        <v>14.77858543396</v>
+        <v>14.7785844802856</v>
       </c>
       <c r="H901" t="n">
         <v>22369</v>
@@ -26556,7 +26556,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G903" t="n">
-        <v>14.4427080154419</v>
+        <v>14.4427070617676</v>
       </c>
       <c r="H903" t="n">
         <v>41043</v>
@@ -26585,7 +26585,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G904" t="n">
-        <v>14.591986656189</v>
+        <v>14.5919857025146</v>
       </c>
       <c r="H904" t="n">
         <v>41338</v>
@@ -26614,7 +26614,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>15.0211620330811</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H905" t="n">
         <v>56292</v>
@@ -26643,7 +26643,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G906" t="n">
-        <v>14.9092025756836</v>
+        <v>14.9092044830322</v>
       </c>
       <c r="H906" t="n">
         <v>35494</v>
@@ -26672,7 +26672,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G907" t="n">
-        <v>14.9092025756836</v>
+        <v>14.9092044830322</v>
       </c>
       <c r="H907" t="n">
         <v>21951</v>
@@ -26701,7 +26701,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>15.0211620330811</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H908" t="n">
         <v>12911</v>
@@ -26730,7 +26730,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G909" t="n">
-        <v>14.77858543396</v>
+        <v>14.7785844802856</v>
       </c>
       <c r="H909" t="n">
         <v>13798</v>
@@ -26759,7 +26759,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G910" t="n">
-        <v>14.8159055709839</v>
+        <v>14.8159036636353</v>
       </c>
       <c r="H910" t="n">
         <v>17570</v>
@@ -26817,7 +26817,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G912" t="n">
-        <v>14.6852855682373</v>
+        <v>14.685284614563</v>
       </c>
       <c r="H912" t="n">
         <v>12131</v>
@@ -26875,7 +26875,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G914" t="n">
-        <v>14.7599258422852</v>
+        <v>14.7599248886108</v>
       </c>
       <c r="H914" t="n">
         <v>16508</v>
@@ -26904,7 +26904,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G915" t="n">
-        <v>14.5173473358154</v>
+        <v>14.5173482894897</v>
       </c>
       <c r="H915" t="n">
         <v>13161</v>
@@ -26933,7 +26933,7 @@
         <v>15.5</v>
       </c>
       <c r="G916" t="n">
-        <v>14.461368560791</v>
+        <v>14.4613676071167</v>
       </c>
       <c r="H916" t="n">
         <v>30625</v>
@@ -26962,7 +26962,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G917" t="n">
-        <v>14.5546674728394</v>
+        <v>14.5546684265137</v>
       </c>
       <c r="H917" t="n">
         <v>9480</v>
@@ -27107,7 +27107,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G922" t="n">
-        <v>13.6776542663574</v>
+        <v>13.6776552200317</v>
       </c>
       <c r="H922" t="n">
         <v>25261</v>
@@ -27136,7 +27136,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G923" t="n">
-        <v>14.3307476043701</v>
+        <v>14.3307485580444</v>
       </c>
       <c r="H923" t="n">
         <v>13369</v>
@@ -27165,7 +27165,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G924" t="n">
-        <v>14.1628103256226</v>
+        <v>14.1628112792969</v>
       </c>
       <c r="H924" t="n">
         <v>23143</v>
@@ -27194,7 +27194,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G925" t="n">
-        <v>14.27476978302</v>
+        <v>14.2747678756714</v>
       </c>
       <c r="H925" t="n">
         <v>36761</v>
@@ -27223,7 +27223,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G926" t="n">
-        <v>14.3307476043701</v>
+        <v>14.3307485580444</v>
       </c>
       <c r="H926" t="n">
         <v>13857</v>
@@ -27281,7 +27281,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>13.7149744033813</v>
+        <v>13.7149753570557</v>
       </c>
       <c r="H928" t="n">
         <v>50442</v>
@@ -27310,7 +27310,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G929" t="n">
-        <v>13.9762105941772</v>
+        <v>13.9762125015259</v>
       </c>
       <c r="H929" t="n">
         <v>36481</v>
@@ -27368,7 +27368,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G931" t="n">
-        <v>13.938892364502</v>
+        <v>13.9388914108276</v>
       </c>
       <c r="H931" t="n">
         <v>39887</v>
@@ -27716,7 +27716,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G943" t="n">
-        <v>14.7599258422852</v>
+        <v>14.7599248886108</v>
       </c>
       <c r="H943" t="n">
         <v>29056</v>
@@ -27803,7 +27803,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G946" t="n">
-        <v>14.7039451599121</v>
+        <v>14.7039461135864</v>
       </c>
       <c r="H946" t="n">
         <v>16079</v>
@@ -27832,7 +27832,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G947" t="n">
-        <v>14.741265296936</v>
+        <v>14.7412643432617</v>
       </c>
       <c r="H947" t="n">
         <v>32039</v>
@@ -27890,7 +27890,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G949" t="n">
-        <v>14.27476978302</v>
+        <v>14.2747678756714</v>
       </c>
       <c r="H949" t="n">
         <v>31043</v>
@@ -27919,7 +27919,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G950" t="n">
-        <v>13.901572227478</v>
+        <v>13.9015731811523</v>
       </c>
       <c r="H950" t="n">
         <v>31947</v>
@@ -27977,7 +27977,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G952" t="n">
-        <v>14.9465246200562</v>
+        <v>14.9465236663818</v>
       </c>
       <c r="H952" t="n">
         <v>82129</v>
@@ -28006,7 +28006,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G953" t="n">
-        <v>15.1331195831299</v>
+        <v>15.1331205368042</v>
       </c>
       <c r="H953" t="n">
         <v>42848</v>
@@ -28093,7 +28093,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G956" t="n">
-        <v>13.938892364502</v>
+        <v>13.9388914108276</v>
       </c>
       <c r="H956" t="n">
         <v>38593</v>
@@ -28122,7 +28122,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G957" t="n">
-        <v>14.1628103256226</v>
+        <v>14.1628112792969</v>
       </c>
       <c r="H957" t="n">
         <v>23706</v>
@@ -28180,7 +28180,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G959" t="n">
-        <v>14.0135326385498</v>
+        <v>14.0135316848755</v>
       </c>
       <c r="H959" t="n">
         <v>32572</v>
@@ -28267,7 +28267,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G962" t="n">
-        <v>14.3307476043701</v>
+        <v>14.3307485580444</v>
       </c>
       <c r="H962" t="n">
         <v>62002</v>
@@ -28296,7 +28296,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G963" t="n">
-        <v>14.405387878418</v>
+        <v>14.4053869247437</v>
       </c>
       <c r="H963" t="n">
         <v>39229</v>
@@ -28325,7 +28325,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G964" t="n">
-        <v>14.3307476043701</v>
+        <v>14.3307485580444</v>
       </c>
       <c r="H964" t="n">
         <v>33011</v>
@@ -28354,7 +28354,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G965" t="n">
-        <v>14.3307476043701</v>
+        <v>14.3307485580444</v>
       </c>
       <c r="H965" t="n">
         <v>63095</v>
@@ -28383,7 +28383,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G966" t="n">
-        <v>14.27476978302</v>
+        <v>14.2747678756714</v>
       </c>
       <c r="H966" t="n">
         <v>54032</v>
@@ -28412,7 +28412,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G967" t="n">
-        <v>14.3867282867432</v>
+        <v>14.3867273330688</v>
       </c>
       <c r="H967" t="n">
         <v>52484</v>
@@ -28499,7 +28499,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G970" t="n">
-        <v>14.741265296936</v>
+        <v>14.7412643432617</v>
       </c>
       <c r="H970" t="n">
         <v>93949</v>
@@ -28528,7 +28528,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G971" t="n">
-        <v>14.7972450256348</v>
+        <v>14.7972431182861</v>
       </c>
       <c r="H971" t="n">
         <v>56451</v>
@@ -28557,7 +28557,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G972" t="n">
-        <v>15.0211620330811</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H972" t="n">
         <v>45023</v>
@@ -28615,7 +28615,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G974" t="n">
-        <v>14.3867282867432</v>
+        <v>14.3867273330688</v>
       </c>
       <c r="H974" t="n">
         <v>140755</v>
@@ -28673,7 +28673,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G976" t="n">
-        <v>14.4427080154419</v>
+        <v>14.4427070617676</v>
       </c>
       <c r="H976" t="n">
         <v>46413</v>
@@ -28847,7 +28847,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>15.0211620330811</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H982" t="n">
         <v>43914</v>
@@ -28876,7 +28876,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G983" t="n">
-        <v>15.1144618988037</v>
+        <v>15.114462852478</v>
       </c>
       <c r="H983" t="n">
         <v>20830</v>
@@ -28905,7 +28905,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G984" t="n">
-        <v>15.1891021728516</v>
+        <v>15.1891012191772</v>
       </c>
       <c r="H984" t="n">
         <v>65074</v>
@@ -28934,7 +28934,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G985" t="n">
-        <v>15.0584812164307</v>
+        <v>15.058482170105</v>
       </c>
       <c r="H985" t="n">
         <v>22328</v>
@@ -28963,7 +28963,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G986" t="n">
-        <v>15.0584812164307</v>
+        <v>15.058482170105</v>
       </c>
       <c r="H986" t="n">
         <v>14789</v>
@@ -28992,7 +28992,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>15.0211620330811</v>
+        <v>15.0211629867554</v>
       </c>
       <c r="H987" t="n">
         <v>38085</v>
@@ -29050,7 +29050,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G989" t="n">
-        <v>14.9552392959595</v>
+        <v>14.9552383422852</v>
       </c>
       <c r="H989" t="n">
         <v>18527</v>
@@ -29137,7 +29137,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>14.7857208251953</v>
+        <v>14.785719871521</v>
       </c>
       <c r="H992" t="n">
         <v>41280</v>
@@ -29195,7 +29195,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G994" t="n">
-        <v>15.2754373550415</v>
+        <v>15.2754383087158</v>
       </c>
       <c r="H994" t="n">
         <v>96495</v>
@@ -29224,7 +29224,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G995" t="n">
-        <v>15.5768051147461</v>
+        <v>15.5768070220947</v>
       </c>
       <c r="H995" t="n">
         <v>234762</v>
@@ -29311,7 +29311,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G998" t="n">
-        <v>15.5768051147461</v>
+        <v>15.5768070220947</v>
       </c>
       <c r="H998" t="n">
         <v>155080</v>
@@ -29340,7 +29340,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G999" t="n">
-        <v>15.5956373214722</v>
+        <v>15.5956382751465</v>
       </c>
       <c r="H999" t="n">
         <v>133198</v>
@@ -29369,7 +29369,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1000" t="n">
-        <v>15.5956373214722</v>
+        <v>15.5956382751465</v>
       </c>
       <c r="H1000" t="n">
         <v>38462</v>
@@ -29398,7 +29398,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1001" t="n">
-        <v>15.5579671859741</v>
+        <v>15.5579681396484</v>
       </c>
       <c r="H1001" t="n">
         <v>29662</v>
@@ -29456,7 +29456,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1003" t="n">
-        <v>15.44495677948</v>
+        <v>15.4449586868286</v>
       </c>
       <c r="H1003" t="n">
         <v>28443</v>
@@ -29485,7 +29485,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1004" t="n">
-        <v>15.3507804870605</v>
+        <v>15.3507785797119</v>
       </c>
       <c r="H1004" t="n">
         <v>50387</v>
@@ -29514,7 +29514,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1005" t="n">
-        <v>15.44495677948</v>
+        <v>15.4449586868286</v>
       </c>
       <c r="H1005" t="n">
         <v>27302</v>
@@ -29746,7 +29746,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1013" t="n">
-        <v>15.5579671859741</v>
+        <v>15.5579681396484</v>
       </c>
       <c r="H1013" t="n">
         <v>19229</v>
@@ -29775,7 +29775,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1014" t="n">
-        <v>15.5768051147461</v>
+        <v>15.5768070220947</v>
       </c>
       <c r="H1014" t="n">
         <v>15642</v>
@@ -29833,7 +29833,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1016" t="n">
-        <v>15.9346733093262</v>
+        <v>15.9346723556519</v>
       </c>
       <c r="H1016" t="n">
         <v>53402</v>
@@ -29862,7 +29862,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1017" t="n">
-        <v>15.8781709671021</v>
+        <v>15.8781700134277</v>
       </c>
       <c r="H1017" t="n">
         <v>42179</v>
@@ -30007,7 +30007,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1022" t="n">
-        <v>15.5956373214722</v>
+        <v>15.5956382751465</v>
       </c>
       <c r="H1022" t="n">
         <v>32083</v>
@@ -30036,7 +30036,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1023" t="n">
-        <v>15.4637937545776</v>
+        <v>15.463791847229</v>
       </c>
       <c r="H1023" t="n">
         <v>23994</v>
@@ -30065,7 +30065,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1024" t="n">
-        <v>15.3319463729858</v>
+        <v>15.3319454193115</v>
       </c>
       <c r="H1024" t="n">
         <v>35910</v>
@@ -30094,7 +30094,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1025" t="n">
-        <v>15.4637937545776</v>
+        <v>15.463791847229</v>
       </c>
       <c r="H1025" t="n">
         <v>37112</v>
@@ -30123,7 +30123,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.5956373214722</v>
+        <v>15.5956382751465</v>
       </c>
       <c r="H1026" t="n">
         <v>30480</v>
@@ -30152,7 +30152,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.4826278686523</v>
+        <v>15.482626914978</v>
       </c>
       <c r="H1027" t="n">
         <v>19815</v>
@@ -30181,7 +30181,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1028" t="n">
-        <v>15.3319463729858</v>
+        <v>15.3319454193115</v>
       </c>
       <c r="H1028" t="n">
         <v>30374</v>
@@ -30297,7 +30297,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G1032" t="n">
-        <v>15.1059236526489</v>
+        <v>15.1059217453003</v>
       </c>
       <c r="H1032" t="n">
         <v>17428</v>
@@ -30384,7 +30384,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.8422260284424</v>
+        <v>14.8422269821167</v>
       </c>
       <c r="H1035" t="n">
         <v>19012</v>
@@ -30413,7 +30413,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1036" t="n">
-        <v>14.4090147018433</v>
+        <v>14.4090137481689</v>
       </c>
       <c r="H1036" t="n">
         <v>46547</v>
@@ -30471,7 +30471,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1038" t="n">
-        <v>13.843955039978</v>
+        <v>13.8439559936523</v>
       </c>
       <c r="H1038" t="n">
         <v>55688</v>
@@ -30500,7 +30500,7 @@
         <v>15</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.1264839172363</v>
+        <v>14.1264848709106</v>
       </c>
       <c r="H1039" t="n">
         <v>28204</v>
@@ -30558,7 +30558,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1041" t="n">
-        <v>14.6915445327759</v>
+        <v>14.6915454864502</v>
       </c>
       <c r="H1041" t="n">
         <v>30895</v>
@@ -30616,7 +30616,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.2960023880005</v>
+        <v>14.2960033416748</v>
       </c>
       <c r="H1043" t="n">
         <v>74475</v>
@@ -30674,7 +30674,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1045" t="n">
-        <v>14.2960023880005</v>
+        <v>14.2960033416748</v>
       </c>
       <c r="H1045" t="n">
         <v>45324</v>
@@ -30703,7 +30703,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.2960023880005</v>
+        <v>14.2960033416748</v>
       </c>
       <c r="H1046" t="n">
         <v>43642</v>
@@ -30732,7 +30732,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1047" t="n">
-        <v>14.3336734771729</v>
+        <v>14.3336725234985</v>
       </c>
       <c r="H1047" t="n">
         <v>22716</v>
@@ -30848,7 +30848,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1051" t="n">
-        <v>13.9569673538208</v>
+        <v>13.9569654464722</v>
       </c>
       <c r="H1051" t="n">
         <v>46619</v>
@@ -30906,7 +30906,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1053" t="n">
-        <v>13.0528717041016</v>
+        <v>13.0528726577759</v>
       </c>
       <c r="H1053" t="n">
         <v>93637</v>
@@ -31022,7 +31022,7 @@
         <v>13.5</v>
       </c>
       <c r="G1057" t="n">
-        <v>12.7138347625732</v>
+        <v>12.7138357162476</v>
       </c>
       <c r="H1057" t="n">
         <v>138574</v>
@@ -31051,7 +31051,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1058" t="n">
-        <v>12.3371305465698</v>
+        <v>12.3371295928955</v>
       </c>
       <c r="H1058" t="n">
         <v>74518</v>
@@ -31109,7 +31109,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1060" t="n">
-        <v>11.8662490844727</v>
+        <v>11.866247177124</v>
       </c>
       <c r="H1060" t="n">
         <v>63834</v>
@@ -31138,7 +31138,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1061" t="n">
-        <v>11.3953647613525</v>
+        <v>11.3953657150269</v>
       </c>
       <c r="H1061" t="n">
         <v>61208</v>
@@ -31196,7 +31196,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1063" t="n">
-        <v>10.0580568313599</v>
+        <v>10.0580587387085</v>
       </c>
       <c r="H1063" t="n">
         <v>141497</v>
@@ -31544,7 +31544,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1075" t="n">
-        <v>11.52721118927</v>
+        <v>11.5272121429443</v>
       </c>
       <c r="H1075" t="n">
         <v>81745</v>
@@ -31573,7 +31573,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1076" t="n">
-        <v>10.8868103027344</v>
+        <v>10.8868112564087</v>
       </c>
       <c r="H1076" t="n">
         <v>92029</v>
@@ -31689,7 +31689,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1080" t="n">
-        <v>10.0015516281128</v>
+        <v>10.0015506744385</v>
       </c>
       <c r="H1080" t="n">
         <v>31361</v>
@@ -31776,7 +31776,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1083" t="n">
-        <v>10.5477752685547</v>
+        <v>10.5477743148804</v>
       </c>
       <c r="H1083" t="n">
         <v>11260</v>
@@ -31805,7 +31805,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1084" t="n">
-        <v>10.6607875823975</v>
+        <v>10.6607866287231</v>
       </c>
       <c r="H1084" t="n">
         <v>39954</v>
@@ -31834,7 +31834,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1085" t="n">
-        <v>11.0374937057495</v>
+        <v>11.0374927520752</v>
       </c>
       <c r="H1085" t="n">
         <v>29423</v>
@@ -31863,7 +31863,7 @@
         <v>11.5</v>
       </c>
       <c r="G1086" t="n">
-        <v>10.8303050994873</v>
+        <v>10.830304145813</v>
       </c>
       <c r="H1086" t="n">
         <v>29924</v>
@@ -31892,7 +31892,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1087" t="n">
-        <v>10.5101041793823</v>
+        <v>10.5101051330566</v>
       </c>
       <c r="H1087" t="n">
         <v>44963</v>
@@ -31950,7 +31950,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1089" t="n">
-        <v>9.81319904327393</v>
+        <v>9.81319808959961</v>
       </c>
       <c r="H1089" t="n">
         <v>44587</v>
@@ -31979,7 +31979,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1090" t="n">
-        <v>10.1522331237793</v>
+        <v>10.1522340774536</v>
       </c>
       <c r="H1090" t="n">
         <v>40026</v>
@@ -32037,7 +32037,7 @@
         <v>11</v>
       </c>
       <c r="G1092" t="n">
-        <v>10.3594217300415</v>
+        <v>10.3594226837158</v>
       </c>
       <c r="H1092" t="n">
         <v>15970</v>
@@ -32211,7 +32211,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1098" t="n">
-        <v>10.8868103027344</v>
+        <v>10.8868112564087</v>
       </c>
       <c r="H1098" t="n">
         <v>21458</v>
@@ -32240,7 +32240,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1099" t="n">
-        <v>10.8868103027344</v>
+        <v>10.8868112564087</v>
       </c>
       <c r="H1099" t="n">
         <v>13705</v>
@@ -32298,7 +32298,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1101" t="n">
-        <v>10.7549648284912</v>
+        <v>10.7549638748169</v>
       </c>
       <c r="H1101" t="n">
         <v>17490</v>
@@ -32327,7 +32327,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1102" t="n">
-        <v>10.6607875823975</v>
+        <v>10.6607866287231</v>
       </c>
       <c r="H1102" t="n">
         <v>22423</v>
@@ -32356,7 +32356,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1103" t="n">
-        <v>10.4724349975586</v>
+        <v>10.4724340438843</v>
       </c>
       <c r="H1103" t="n">
         <v>16823</v>
@@ -32385,7 +32385,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1104" t="n">
-        <v>10.6607875823975</v>
+        <v>10.6607866287231</v>
       </c>
       <c r="H1104" t="n">
         <v>2137</v>
@@ -32414,7 +32414,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1105" t="n">
-        <v>10.7549648284912</v>
+        <v>10.7549638748169</v>
       </c>
       <c r="H1105" t="n">
         <v>18877</v>
@@ -32472,7 +32472,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1107" t="n">
-        <v>10.4724349975586</v>
+        <v>10.4724340438843</v>
       </c>
       <c r="H1107" t="n">
         <v>9680</v>
@@ -32501,7 +32501,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1108" t="n">
-        <v>10.1522331237793</v>
+        <v>10.1522340774536</v>
       </c>
       <c r="H1108" t="n">
         <v>24692</v>
@@ -32559,7 +32559,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1110" t="n">
-        <v>10.8868103027344</v>
+        <v>10.8868112564087</v>
       </c>
       <c r="H1110" t="n">
         <v>59827</v>
@@ -32588,7 +32588,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>10.9244832992554</v>
+        <v>10.9244813919067</v>
       </c>
       <c r="H1111" t="n">
         <v>28876</v>
@@ -32617,7 +32617,7 @@
         <v>11.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>10.8303050994873</v>
+        <v>10.830304145813</v>
       </c>
       <c r="H1112" t="n">
         <v>25770</v>
@@ -32646,7 +32646,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>10.9244832992554</v>
+        <v>10.9244813919067</v>
       </c>
       <c r="H1113" t="n">
         <v>40746</v>
@@ -32704,7 +32704,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1115" t="n">
-        <v>11.4141998291016</v>
+        <v>11.4141988754272</v>
       </c>
       <c r="H1115" t="n">
         <v>101849</v>
@@ -32878,7 +32878,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1121" t="n">
-        <v>11.4330368041992</v>
+        <v>11.4330348968506</v>
       </c>
       <c r="H1121" t="n">
         <v>47351</v>
@@ -32907,7 +32907,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1122" t="n">
-        <v>11.7155656814575</v>
+        <v>11.7155637741089</v>
       </c>
       <c r="H1122" t="n">
         <v>73584</v>
@@ -33023,7 +33023,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1126" t="n">
-        <v>12.0169296264648</v>
+        <v>12.0169305801392</v>
       </c>
       <c r="H1126" t="n">
         <v>70083</v>
@@ -33052,7 +33052,7 @@
         <v>12.5</v>
       </c>
       <c r="G1127" t="n">
-        <v>11.7720708847046</v>
+        <v>11.7720718383789</v>
       </c>
       <c r="H1127" t="n">
         <v>39780</v>
@@ -33110,7 +33110,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1129" t="n">
-        <v>10.9433164596558</v>
+        <v>10.9433174133301</v>
       </c>
       <c r="H1129" t="n">
         <v>38358</v>
@@ -33197,7 +33197,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1132" t="n">
-        <v>10.9433164596558</v>
+        <v>10.9433174133301</v>
       </c>
       <c r="H1132" t="n">
         <v>114207</v>
@@ -33226,7 +33226,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1133" t="n">
-        <v>10.6607875823975</v>
+        <v>10.6607866287231</v>
       </c>
       <c r="H1133" t="n">
         <v>82825</v>
@@ -33284,7 +33284,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1135" t="n">
-        <v>10.9433164596558</v>
+        <v>10.9433174133301</v>
       </c>
       <c r="H1135" t="n">
         <v>57098</v>
@@ -33313,7 +33313,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1136" t="n">
-        <v>11.0186576843262</v>
+        <v>11.0186586380005</v>
       </c>
       <c r="H1136" t="n">
         <v>36151</v>
@@ -33371,7 +33371,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>10.811469078064</v>
+        <v>10.8114709854126</v>
       </c>
       <c r="H1138" t="n">
         <v>27528</v>
@@ -33400,7 +33400,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1139" t="n">
-        <v>10.7549648284912</v>
+        <v>10.7549638748169</v>
       </c>
       <c r="H1139" t="n">
         <v>15905</v>
@@ -33429,7 +33429,7 @@
         <v>11.5</v>
       </c>
       <c r="G1140" t="n">
-        <v>10.8303050994873</v>
+        <v>10.830304145813</v>
       </c>
       <c r="H1140" t="n">
         <v>16197</v>
@@ -33487,7 +33487,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1142" t="n">
-        <v>10.6042814254761</v>
+        <v>10.6042823791504</v>
       </c>
       <c r="H1142" t="n">
         <v>29971</v>
@@ -33545,7 +33545,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1144" t="n">
-        <v>10.4724349975586</v>
+        <v>10.4724340438843</v>
       </c>
       <c r="H1144" t="n">
         <v>19008</v>
@@ -33574,7 +33574,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1145" t="n">
-        <v>10.6042814254761</v>
+        <v>10.6042823791504</v>
       </c>
       <c r="H1145" t="n">
         <v>16370</v>
@@ -33603,7 +33603,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.5477752685547</v>
+        <v>10.5477743148804</v>
       </c>
       <c r="H1146" t="n">
         <v>20019</v>
@@ -33632,7 +33632,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1147" t="n">
-        <v>10.4724349975586</v>
+        <v>10.4724340438843</v>
       </c>
       <c r="H1147" t="n">
         <v>14881</v>
@@ -33661,7 +33661,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1148" t="n">
-        <v>10.3405847549438</v>
+        <v>10.3405857086182</v>
       </c>
       <c r="H1148" t="n">
         <v>19361</v>
@@ -33690,7 +33690,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.3782577514648</v>
+        <v>10.3782587051392</v>
       </c>
       <c r="H1149" t="n">
         <v>23719</v>
@@ -33748,7 +33748,7 @@
         <v>11</v>
       </c>
       <c r="G1151" t="n">
-        <v>10.3594217300415</v>
+        <v>10.3594226837158</v>
       </c>
       <c r="H1151" t="n">
         <v>46138</v>
@@ -33777,7 +33777,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1152" t="n">
-        <v>10.8868103027344</v>
+        <v>10.8868112564087</v>
       </c>
       <c r="H1152" t="n">
         <v>30370</v>
@@ -33835,7 +33835,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1154" t="n">
-        <v>11.1316699981689</v>
+        <v>11.1316690444946</v>
       </c>
       <c r="H1154" t="n">
         <v>22117</v>
@@ -33893,7 +33893,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1156" t="n">
-        <v>11.2070112228394</v>
+        <v>11.2070121765137</v>
       </c>
       <c r="H1156" t="n">
         <v>26448</v>
@@ -33980,7 +33980,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1159" t="n">
-        <v>10.905647277832</v>
+        <v>10.9056463241577</v>
       </c>
       <c r="H1159" t="n">
         <v>13158</v>
@@ -34038,7 +34038,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1161" t="n">
-        <v>10.7549648284912</v>
+        <v>10.7549638748169</v>
       </c>
       <c r="H1161" t="n">
         <v>4082</v>
@@ -34125,7 +34125,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1164" t="n">
-        <v>10.3970928192139</v>
+        <v>10.3970918655396</v>
       </c>
       <c r="H1164" t="n">
         <v>28392</v>
@@ -34154,7 +34154,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>10.5477752685547</v>
+        <v>10.5477743148804</v>
       </c>
       <c r="H1165" t="n">
         <v>20206</v>
@@ -34212,7 +34212,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1167" t="n">
-        <v>10.8868103027344</v>
+        <v>10.8868112564087</v>
       </c>
       <c r="H1167" t="n">
         <v>15874</v>
@@ -34241,7 +34241,7 @@
         <v>11.5</v>
       </c>
       <c r="G1168" t="n">
-        <v>10.8303050994873</v>
+        <v>10.830304145813</v>
       </c>
       <c r="H1168" t="n">
         <v>22483</v>
@@ -34328,7 +34328,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1171" t="n">
-        <v>11.4141998291016</v>
+        <v>11.4141988754272</v>
       </c>
       <c r="H1171" t="n">
         <v>44185</v>
@@ -34357,7 +34357,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1172" t="n">
-        <v>11.5648813247681</v>
+        <v>11.5648822784424</v>
       </c>
       <c r="H1172" t="n">
         <v>18291</v>
@@ -34386,7 +34386,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>11.3953647613525</v>
+        <v>11.3953657150269</v>
       </c>
       <c r="H1173" t="n">
         <v>20817</v>
@@ -34444,7 +34444,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1175" t="n">
-        <v>11.52721118927</v>
+        <v>11.5272121429443</v>
       </c>
       <c r="H1175" t="n">
         <v>28816</v>
@@ -34473,7 +34473,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1176" t="n">
-        <v>11.3576955795288</v>
+        <v>11.3576946258545</v>
       </c>
       <c r="H1176" t="n">
         <v>33595</v>
@@ -34560,7 +34560,7 @@
         <v>12.5</v>
       </c>
       <c r="G1179" t="n">
-        <v>11.7720708847046</v>
+        <v>11.7720718383789</v>
       </c>
       <c r="H1179" t="n">
         <v>25777</v>
@@ -34589,7 +34589,7 @@
         <v>12.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>11.7720708847046</v>
+        <v>11.7720718383789</v>
       </c>
       <c r="H1180" t="n">
         <v>36341</v>
@@ -34647,7 +34647,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1182" t="n">
-        <v>11.4707059860229</v>
+        <v>11.4707069396973</v>
       </c>
       <c r="H1182" t="n">
         <v>10686</v>
@@ -34676,7 +34676,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1183" t="n">
-        <v>11.4707059860229</v>
+        <v>11.4707069396973</v>
       </c>
       <c r="H1183" t="n">
         <v>11553</v>
@@ -34705,7 +34705,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1184" t="n">
-        <v>11.52721118927</v>
+        <v>11.5272121429443</v>
       </c>
       <c r="H1184" t="n">
         <v>18255</v>
@@ -34734,7 +34734,7 @@
         <v>12.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>11.7720708847046</v>
+        <v>11.7720718383789</v>
       </c>
       <c r="H1185" t="n">
         <v>17102</v>
@@ -34763,7 +34763,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1186" t="n">
-        <v>11.5837182998657</v>
+        <v>11.5837173461914</v>
       </c>
       <c r="H1186" t="n">
         <v>59441</v>
@@ -34850,7 +34850,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1189" t="n">
-        <v>11.52721118927</v>
+        <v>11.5272121429443</v>
       </c>
       <c r="H1189" t="n">
         <v>7469</v>
@@ -34908,7 +34908,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1191" t="n">
-        <v>12.1487770080566</v>
+        <v>12.1487760543823</v>
       </c>
       <c r="H1191" t="n">
         <v>66738</v>
@@ -34937,7 +34937,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1192" t="n">
-        <v>12.0546007156372</v>
+        <v>12.0545997619629</v>
       </c>
       <c r="H1192" t="n">
         <v>37163</v>
@@ -34966,7 +34966,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1193" t="n">
-        <v>12.0357637405396</v>
+        <v>12.0357656478882</v>
       </c>
       <c r="H1193" t="n">
         <v>8487</v>
@@ -35111,7 +35111,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>11.6778926849365</v>
+        <v>11.6778936386108</v>
       </c>
       <c r="H1198" t="n">
         <v>17452</v>
@@ -35169,7 +35169,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1200" t="n">
-        <v>11.1316699981689</v>
+        <v>11.1316690444946</v>
       </c>
       <c r="H1200" t="n">
         <v>13334</v>
@@ -35372,7 +35372,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G1207" t="n">
-        <v>13.7686138153076</v>
+        <v>13.7686128616333</v>
       </c>
       <c r="H1207" t="n">
         <v>124694</v>
@@ -35430,7 +35430,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1209" t="n">
-        <v>13.1470470428467</v>
+        <v>13.1470489501953</v>
       </c>
       <c r="H1209" t="n">
         <v>158525</v>
@@ -35459,7 +35459,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1210" t="n">
-        <v>13.3354015350342</v>
+        <v>13.3354005813599</v>
       </c>
       <c r="H1210" t="n">
         <v>72649</v>
@@ -35517,7 +35517,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1212" t="n">
-        <v>13.0152015686035</v>
+        <v>13.0152006149292</v>
       </c>
       <c r="H1212" t="n">
         <v>79712</v>
@@ -35546,7 +35546,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1213" t="n">
-        <v>13.2412252426147</v>
+        <v>13.2412261962891</v>
       </c>
       <c r="H1213" t="n">
         <v>127327</v>
@@ -35575,7 +35575,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1214" t="n">
-        <v>13.2412252426147</v>
+        <v>13.2412261962891</v>
       </c>
       <c r="H1214" t="n">
         <v>120947</v>
@@ -35662,7 +35662,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1217" t="n">
-        <v>13.3165664672852</v>
+        <v>13.3165655136108</v>
       </c>
       <c r="H1217" t="n">
         <v>212459</v>
@@ -35691,7 +35691,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1218" t="n">
-        <v>13.1470470428467</v>
+        <v>13.1470489501953</v>
       </c>
       <c r="H1218" t="n">
         <v>203717</v>
@@ -35778,7 +35778,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1221" t="n">
-        <v>13.1470470428467</v>
+        <v>13.1470489501953</v>
       </c>
       <c r="H1221" t="n">
         <v>113818</v>
@@ -35836,7 +35836,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1223" t="n">
-        <v>13.0340375900269</v>
+        <v>13.0340366363525</v>
       </c>
       <c r="H1223" t="n">
         <v>64149</v>
@@ -35894,7 +35894,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1225" t="n">
-        <v>13.0905427932739</v>
+        <v>13.0905418395996</v>
       </c>
       <c r="H1225" t="n">
         <v>89591</v>
@@ -35981,7 +35981,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1228" t="n">
-        <v>11.6778926849365</v>
+        <v>11.6778936386108</v>
       </c>
       <c r="H1228" t="n">
         <v>327627</v>
@@ -36010,7 +36010,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1229" t="n">
-        <v>11.5837182998657</v>
+        <v>11.5837173461914</v>
       </c>
       <c r="H1229" t="n">
         <v>57369</v>
@@ -36039,7 +36039,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>11.8662490844727</v>
+        <v>11.866247177124</v>
       </c>
       <c r="H1230" t="n">
         <v>56969</v>
@@ -36068,7 +36068,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1231" t="n">
-        <v>11.9792594909668</v>
+        <v>11.9792604446411</v>
       </c>
       <c r="H1231" t="n">
         <v>93930</v>
@@ -36097,7 +36097,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.8662490844727</v>
+        <v>11.866247177124</v>
       </c>
       <c r="H1232" t="n">
         <v>39318</v>
@@ -36155,7 +36155,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1234" t="n">
-        <v>12.0546007156372</v>
+        <v>12.0545997619629</v>
       </c>
       <c r="H1234" t="n">
         <v>51769</v>
@@ -36184,7 +36184,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1235" t="n">
-        <v>12.3559646606445</v>
+        <v>12.3559656143188</v>
       </c>
       <c r="H1235" t="n">
         <v>78204</v>
@@ -36271,7 +36271,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1238" t="n">
-        <v>12.7326726913452</v>
+        <v>12.7326717376709</v>
       </c>
       <c r="H1238" t="n">
         <v>59041</v>
@@ -36300,7 +36300,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1239" t="n">
-        <v>12.9586944580078</v>
+        <v>12.9586954116821</v>
       </c>
       <c r="H1239" t="n">
         <v>51120</v>
@@ -36329,7 +36329,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1240" t="n">
-        <v>13.2223901748657</v>
+        <v>13.22239112854</v>
       </c>
       <c r="H1240" t="n">
         <v>81081</v>
@@ -36416,7 +36416,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1243" t="n">
-        <v>13.3354015350342</v>
+        <v>13.3354005813599</v>
       </c>
       <c r="H1243" t="n">
         <v>72531</v>
@@ -36503,7 +36503,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1246" t="n">
-        <v>13.5450420379639</v>
+        <v>13.5450410842896</v>
       </c>
       <c r="H1246" t="n">
         <v>58153</v>
@@ -36532,7 +36532,7 @@
         <v>14</v>
       </c>
       <c r="G1247" t="n">
-        <v>13.3167543411255</v>
+        <v>13.3167552947998</v>
       </c>
       <c r="H1247" t="n">
         <v>136688</v>
@@ -36561,7 +36561,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1248" t="n">
-        <v>13.3548030853271</v>
+        <v>13.3548040390015</v>
       </c>
       <c r="H1248" t="n">
         <v>54674</v>
@@ -36590,7 +36590,7 @@
         <v>14</v>
       </c>
       <c r="G1249" t="n">
-        <v>13.3167543411255</v>
+        <v>13.3167552947998</v>
       </c>
       <c r="H1249" t="n">
         <v>29135</v>
@@ -36619,7 +36619,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1250" t="n">
-        <v>13.2216348648071</v>
+        <v>13.2216339111328</v>
       </c>
       <c r="H1250" t="n">
         <v>39597</v>
@@ -36706,7 +36706,7 @@
         <v>14.5</v>
       </c>
       <c r="G1253" t="n">
-        <v>13.7923517227173</v>
+        <v>13.7923526763916</v>
       </c>
       <c r="H1253" t="n">
         <v>42188</v>
@@ -36764,7 +36764,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1255" t="n">
-        <v>14.0777130126953</v>
+        <v>14.077712059021</v>
       </c>
       <c r="H1255" t="n">
         <v>52106</v>
@@ -36793,7 +36793,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1256" t="n">
-        <v>14.0586881637573</v>
+        <v>14.0586862564087</v>
       </c>
       <c r="H1256" t="n">
         <v>46069</v>
@@ -36851,7 +36851,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1258" t="n">
-        <v>13.8874731063843</v>
+        <v>13.88747215271</v>
       </c>
       <c r="H1258" t="n">
         <v>40359</v>
@@ -36880,7 +36880,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1259" t="n">
-        <v>13.6021137237549</v>
+        <v>13.6021146774292</v>
       </c>
       <c r="H1259" t="n">
         <v>39144</v>
@@ -36938,7 +36938,7 @@
         <v>14.5</v>
       </c>
       <c r="G1261" t="n">
-        <v>13.7923517227173</v>
+        <v>13.7923526763916</v>
       </c>
       <c r="H1261" t="n">
         <v>33194</v>
@@ -37112,7 +37112,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1267" t="n">
-        <v>13.6021137237549</v>
+        <v>13.6021146774292</v>
       </c>
       <c r="H1267" t="n">
         <v>48312</v>
@@ -37141,7 +37141,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1268" t="n">
-        <v>13.6972332000732</v>
+        <v>13.6972322463989</v>
       </c>
       <c r="H1268" t="n">
         <v>31000</v>
@@ -37170,7 +37170,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G1269" t="n">
-        <v>13.6211385726929</v>
+        <v>13.6211376190186</v>
       </c>
       <c r="H1269" t="n">
         <v>34160</v>
@@ -37228,7 +37228,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1271" t="n">
-        <v>13.7733287811279</v>
+        <v>13.7733297348022</v>
       </c>
       <c r="H1271" t="n">
         <v>69076</v>
@@ -37257,7 +37257,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1272" t="n">
-        <v>14.0396633148193</v>
+        <v>14.039665222168</v>
       </c>
       <c r="H1272" t="n">
         <v>37089</v>
@@ -37286,7 +37286,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1273" t="n">
-        <v>14.2489261627197</v>
+        <v>14.2489280700684</v>
       </c>
       <c r="H1273" t="n">
         <v>56336</v>
@@ -37315,7 +37315,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1274" t="n">
-        <v>14.6103811264038</v>
+        <v>14.6103830337524</v>
       </c>
       <c r="H1274" t="n">
         <v>54321</v>
@@ -37373,7 +37373,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1276" t="n">
-        <v>14.8957414627075</v>
+        <v>14.8957405090332</v>
       </c>
       <c r="H1276" t="n">
         <v>85533</v>
@@ -37547,7 +37547,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1282" t="n">
-        <v>15.7137689590454</v>
+        <v>15.7137699127197</v>
       </c>
       <c r="H1282" t="n">
         <v>43067</v>
@@ -37634,7 +37634,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1285" t="n">
-        <v>15.5045080184937</v>
+        <v>15.504506111145</v>
       </c>
       <c r="H1285" t="n">
         <v>29435</v>
@@ -37721,7 +37721,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1288" t="n">
-        <v>15.2381734848022</v>
+        <v>15.2381725311279</v>
       </c>
       <c r="H1288" t="n">
         <v>26089</v>
@@ -37779,7 +37779,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1290" t="n">
-        <v>15.5045080184937</v>
+        <v>15.504506111145</v>
       </c>
       <c r="H1290" t="n">
         <v>45621</v>
@@ -37808,7 +37808,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1291" t="n">
-        <v>15.61865234375</v>
+        <v>15.6186504364014</v>
       </c>
       <c r="H1291" t="n">
         <v>40152</v>
@@ -37895,7 +37895,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1294" t="n">
-        <v>16.4937515258789</v>
+        <v>16.4937534332275</v>
       </c>
       <c r="H1294" t="n">
         <v>84980</v>
@@ -38069,7 +38069,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1300" t="n">
-        <v>17.0454444885254</v>
+        <v>17.0454483032227</v>
       </c>
       <c r="H1300" t="n">
         <v>58160</v>
@@ -38185,7 +38185,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1304" t="n">
-        <v>16.3415622711182</v>
+        <v>16.3415603637695</v>
       </c>
       <c r="H1304" t="n">
         <v>47971</v>
@@ -38243,7 +38243,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1306" t="n">
-        <v>16.4937515258789</v>
+        <v>16.4937534332275</v>
       </c>
       <c r="H1306" t="n">
         <v>47420</v>
@@ -38272,7 +38272,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1307" t="n">
-        <v>16.4937515258789</v>
+        <v>16.4937534332275</v>
       </c>
       <c r="H1307" t="n">
         <v>55219</v>
@@ -38301,7 +38301,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1308" t="n">
-        <v>16.7981338500977</v>
+        <v>16.798131942749</v>
       </c>
       <c r="H1308" t="n">
         <v>75807</v>
@@ -38330,7 +38330,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1309" t="n">
-        <v>16.5508251190186</v>
+        <v>16.5508232116699</v>
       </c>
       <c r="H1309" t="n">
         <v>49669</v>
@@ -38504,7 +38504,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1315" t="n">
-        <v>16.7410621643066</v>
+        <v>16.7410640716553</v>
       </c>
       <c r="H1315" t="n">
         <v>102800</v>
@@ -38620,7 +38620,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1319" t="n">
-        <v>18.1868839263916</v>
+        <v>18.186882019043</v>
       </c>
       <c r="H1319" t="n">
         <v>78904</v>
@@ -38649,7 +38649,7 @@
         <v>20.5</v>
       </c>
       <c r="G1320" t="n">
-        <v>19.499532699585</v>
+        <v>19.4995346069336</v>
       </c>
       <c r="H1320" t="n">
         <v>472190</v>
@@ -38707,7 +38707,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>20.1653709411621</v>
+        <v>20.1653728485107</v>
       </c>
       <c r="H1322" t="n">
         <v>187102</v>
@@ -38852,7 +38852,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1327" t="n">
-        <v>19.8324508666992</v>
+        <v>19.8324527740479</v>
       </c>
       <c r="H1327" t="n">
         <v>67445</v>
@@ -38881,7 +38881,7 @@
         <v>20.75</v>
       </c>
       <c r="G1328" t="n">
-        <v>19.7373332977295</v>
+        <v>19.7373313903809</v>
       </c>
       <c r="H1328" t="n">
         <v>37827</v>
@@ -38910,7 +38910,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1329" t="n">
-        <v>19.880012512207</v>
+        <v>19.8800106048584</v>
       </c>
       <c r="H1329" t="n">
         <v>37861</v>
@@ -38997,7 +38997,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1332" t="n">
-        <v>20.2604904174805</v>
+        <v>20.2604885101318</v>
       </c>
       <c r="H1332" t="n">
         <v>45869</v>
@@ -39084,7 +39084,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1335" t="n">
-        <v>20.8312110900879</v>
+        <v>20.8312072753906</v>
       </c>
       <c r="H1335" t="n">
         <v>75131</v>
@@ -39113,7 +39113,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>20.7360877990723</v>
+        <v>20.7360897064209</v>
       </c>
       <c r="H1336" t="n">
         <v>74275</v>
@@ -39229,7 +39229,7 @@
         <v>20.75</v>
       </c>
       <c r="G1340" t="n">
-        <v>19.7373332977295</v>
+        <v>19.7373313903809</v>
       </c>
       <c r="H1340" t="n">
         <v>39655</v>
@@ -39258,7 +39258,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1341" t="n">
-        <v>19.8324508666992</v>
+        <v>19.8324527740479</v>
       </c>
       <c r="H1341" t="n">
         <v>38357</v>
@@ -39403,7 +39403,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1346" t="n">
-        <v>19.8324508666992</v>
+        <v>19.8324527740479</v>
       </c>
       <c r="H1346" t="n">
         <v>47741</v>
@@ -39432,7 +39432,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1347" t="n">
-        <v>19.880012512207</v>
+        <v>19.8800106048584</v>
       </c>
       <c r="H1347" t="n">
         <v>37284</v>
@@ -39635,7 +39635,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1354" t="n">
-        <v>19.6897735595703</v>
+        <v>19.6897754669189</v>
       </c>
       <c r="H1354" t="n">
         <v>62104</v>
@@ -39664,7 +39664,7 @@
         <v>20</v>
       </c>
       <c r="G1355" t="n">
-        <v>19.0239353179932</v>
+        <v>19.0239334106445</v>
       </c>
       <c r="H1355" t="n">
         <v>78898</v>
@@ -39722,7 +39722,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1357" t="n">
-        <v>19.6897735595703</v>
+        <v>19.6897754669189</v>
       </c>
       <c r="H1357" t="n">
         <v>51491</v>
@@ -39751,7 +39751,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1358" t="n">
-        <v>19.6897735595703</v>
+        <v>19.6897754669189</v>
       </c>
       <c r="H1358" t="n">
         <v>32149</v>
@@ -39838,7 +39838,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G1361" t="n">
-        <v>20.3080520629883</v>
+        <v>20.3080501556396</v>
       </c>
       <c r="H1361" t="n">
         <v>51337</v>
@@ -40012,7 +40012,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1367" t="n">
-        <v>19.6897735595703</v>
+        <v>19.6897754669189</v>
       </c>
       <c r="H1367" t="n">
         <v>26808</v>
@@ -40041,7 +40041,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G1368" t="n">
-        <v>20.3080520629883</v>
+        <v>20.3080501556396</v>
       </c>
       <c r="H1368" t="n">
         <v>62948</v>
@@ -40070,7 +40070,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G1369" t="n">
-        <v>20.3080520629883</v>
+        <v>20.3080501556396</v>
       </c>
       <c r="H1369" t="n">
         <v>22283</v>
@@ -40099,7 +40099,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G1370" t="n">
-        <v>20.3080520629883</v>
+        <v>20.3080501556396</v>
       </c>
       <c r="H1370" t="n">
         <v>91807</v>
@@ -40157,7 +40157,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1372" t="n">
-        <v>20.7360877990723</v>
+        <v>20.7360897064209</v>
       </c>
       <c r="H1372" t="n">
         <v>119560</v>
@@ -40215,7 +40215,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1374" t="n">
-        <v>20.9738883972168</v>
+        <v>20.9738903045654</v>
       </c>
       <c r="H1374" t="n">
         <v>46334</v>
@@ -40244,7 +40244,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1375" t="n">
-        <v>21.544605255127</v>
+        <v>21.5446033477783</v>
       </c>
       <c r="H1375" t="n">
         <v>68470</v>
@@ -40302,7 +40302,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1377" t="n">
-        <v>21.544605255127</v>
+        <v>21.5446033477783</v>
       </c>
       <c r="H1377" t="n">
         <v>80182</v>
@@ -40360,7 +40360,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1379" t="n">
-        <v>21.5921649932861</v>
+        <v>21.5921669006348</v>
       </c>
       <c r="H1379" t="n">
         <v>26702</v>
@@ -40389,7 +40389,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1380" t="n">
-        <v>21.6872844696045</v>
+        <v>21.6872863769531</v>
       </c>
       <c r="H1380" t="n">
         <v>51826</v>
@@ -40447,7 +40447,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1382" t="n">
-        <v>21.544605255127</v>
+        <v>21.5446033477783</v>
       </c>
       <c r="H1382" t="n">
         <v>74252</v>
@@ -40563,7 +40563,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>21.544605255127</v>
+        <v>21.5446033477783</v>
       </c>
       <c r="H1386" t="n">
         <v>37330</v>
@@ -40708,7 +40708,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1391" t="n">
-        <v>20.9738883972168</v>
+        <v>20.9738903045654</v>
       </c>
       <c r="H1391" t="n">
         <v>41158</v>
@@ -40969,7 +40969,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G1400" t="n">
-        <v>22.4958019256592</v>
+        <v>22.4958038330078</v>
       </c>
       <c r="H1400" t="n">
         <v>47832</v>
@@ -40998,7 +40998,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1401" t="n">
-        <v>22.2580032348633</v>
+        <v>22.2580051422119</v>
       </c>
       <c r="H1401" t="n">
         <v>47339</v>
@@ -41056,7 +41056,7 @@
         <v>23</v>
       </c>
       <c r="G1403" t="n">
-        <v>21.8775253295898</v>
+        <v>21.8775234222412</v>
       </c>
       <c r="H1403" t="n">
         <v>38196</v>
@@ -41259,7 +41259,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1410" t="n">
-        <v>20.6409702301025</v>
+        <v>20.6409721374512</v>
       </c>
       <c r="H1410" t="n">
         <v>41453</v>
@@ -41346,7 +41346,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1413" t="n">
-        <v>21.544605255127</v>
+        <v>21.5446033477783</v>
       </c>
       <c r="H1413" t="n">
         <v>28728</v>
@@ -41375,7 +41375,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1414" t="n">
-        <v>21.7824077606201</v>
+        <v>21.7824058532715</v>
       </c>
       <c r="H1414" t="n">
         <v>31750</v>
@@ -41404,7 +41404,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1415" t="n">
-        <v>21.7824077606201</v>
+        <v>21.7824058532715</v>
       </c>
       <c r="H1415" t="n">
         <v>15907</v>
@@ -41491,7 +41491,7 @@
         <v>25</v>
       </c>
       <c r="G1418" t="n">
-        <v>23.7799186706543</v>
+        <v>23.7799205780029</v>
       </c>
       <c r="H1418" t="n">
         <v>94597</v>
@@ -41723,7 +41723,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G1426" t="n">
-        <v>23.3518810272217</v>
+        <v>23.351879119873</v>
       </c>
       <c r="H1426" t="n">
         <v>34114</v>
@@ -41810,7 +41810,7 @@
         <v>24.6499996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>23.4469985961914</v>
+        <v>23.44700050354</v>
       </c>
       <c r="H1429" t="n">
         <v>17885</v>
@@ -41897,7 +41897,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G1432" t="n">
-        <v>23.3518810272217</v>
+        <v>23.351879119873</v>
       </c>
       <c r="H1432" t="n">
         <v>60051</v>
@@ -42042,7 +42042,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>23.6372413635254</v>
+        <v>23.6372394561768</v>
       </c>
       <c r="H1437" t="n">
         <v>45021</v>
@@ -42129,7 +42129,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>23.4945583343506</v>
+        <v>23.4945621490479</v>
       </c>
       <c r="H1440" t="n">
         <v>14918</v>
@@ -42158,7 +42158,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G1441" t="n">
-        <v>23.3518810272217</v>
+        <v>23.351879119873</v>
       </c>
       <c r="H1441" t="n">
         <v>19867</v>
@@ -42187,7 +42187,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>23.4945583343506</v>
+        <v>23.4945621490479</v>
       </c>
       <c r="H1442" t="n">
         <v>10407</v>
@@ -42390,7 +42390,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1449" t="n">
-        <v>23.3994426727295</v>
+        <v>23.3994407653809</v>
       </c>
       <c r="H1449" t="n">
         <v>45794</v>
@@ -42535,7 +42535,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>21.5921649932861</v>
+        <v>21.5921669006348</v>
       </c>
       <c r="H1454" t="n">
         <v>22726</v>
@@ -42564,7 +42564,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G1455" t="n">
-        <v>21.4494876861572</v>
+        <v>21.4494857788086</v>
       </c>
       <c r="H1455" t="n">
         <v>25107</v>
@@ -42593,7 +42593,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1456" t="n">
-        <v>22.0677680969238</v>
+        <v>22.0677642822266</v>
       </c>
       <c r="H1456" t="n">
         <v>22236</v>
@@ -42651,7 +42651,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1458" t="n">
-        <v>22.0202045440674</v>
+        <v>22.020206451416</v>
       </c>
       <c r="H1458" t="n">
         <v>20644</v>
@@ -42796,7 +42796,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G1463" t="n">
-        <v>24.3030776977539</v>
+        <v>24.3030757904053</v>
       </c>
       <c r="H1463" t="n">
         <v>46885</v>
@@ -42883,7 +42883,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1466" t="n">
-        <v>23.6848011016846</v>
+        <v>23.6847991943359</v>
       </c>
       <c r="H1466" t="n">
         <v>30449</v>
@@ -42912,7 +42912,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1467" t="n">
-        <v>23.6848011016846</v>
+        <v>23.6847991943359</v>
       </c>
       <c r="H1467" t="n">
         <v>16035</v>
@@ -42970,7 +42970,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1469" t="n">
-        <v>25.587194442749</v>
+        <v>25.5871925354004</v>
       </c>
       <c r="H1469" t="n">
         <v>59036</v>
@@ -42999,7 +42999,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1470" t="n">
-        <v>25.587194442749</v>
+        <v>25.5871925354004</v>
       </c>
       <c r="H1470" t="n">
         <v>32590</v>
@@ -43086,7 +43086,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1473" t="n">
-        <v>25.587194442749</v>
+        <v>25.5871925354004</v>
       </c>
       <c r="H1473" t="n">
         <v>69207</v>
@@ -43173,7 +43173,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1476" t="n">
-        <v>25.7774314880371</v>
+        <v>25.7774333953857</v>
       </c>
       <c r="H1476" t="n">
         <v>56380</v>
@@ -43231,7 +43231,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>26.3005886077881</v>
+        <v>26.3005905151367</v>
       </c>
       <c r="H1478" t="n">
         <v>120375</v>
@@ -43260,7 +43260,7 @@
         <v>27.75</v>
       </c>
       <c r="G1479" t="n">
-        <v>26.3957118988037</v>
+        <v>26.3957099914551</v>
       </c>
       <c r="H1479" t="n">
         <v>73035</v>
@@ -43289,7 +43289,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1480" t="n">
-        <v>27.2993450164795</v>
+        <v>27.2993469238281</v>
       </c>
       <c r="H1480" t="n">
         <v>76138</v>
@@ -43318,7 +43318,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1481" t="n">
-        <v>27.2042274475098</v>
+        <v>27.2042293548584</v>
       </c>
       <c r="H1481" t="n">
         <v>60662</v>
@@ -43347,7 +43347,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>27.1566677093506</v>
+        <v>27.156665802002</v>
       </c>
       <c r="H1482" t="n">
         <v>48644</v>
@@ -43376,7 +43376,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1483" t="n">
-        <v>27.6798248291016</v>
+        <v>27.6798267364502</v>
       </c>
       <c r="H1483" t="n">
         <v>47611</v>
@@ -43434,7 +43434,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1485" t="n">
-        <v>27.7749462127686</v>
+        <v>27.7749443054199</v>
       </c>
       <c r="H1485" t="n">
         <v>107361</v>
@@ -43463,7 +43463,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1486" t="n">
-        <v>28.1078643798828</v>
+        <v>28.1078624725342</v>
       </c>
       <c r="H1486" t="n">
         <v>49683</v>
@@ -43492,7 +43492,7 @@
         <v>29</v>
       </c>
       <c r="G1487" t="n">
-        <v>27.5847034454346</v>
+        <v>27.5847053527832</v>
       </c>
       <c r="H1487" t="n">
         <v>116229</v>
@@ -43521,7 +43521,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1488" t="n">
-        <v>27.6798248291016</v>
+        <v>27.6798267364502</v>
       </c>
       <c r="H1488" t="n">
         <v>73233</v>
@@ -43550,7 +43550,7 @@
         <v>29</v>
       </c>
       <c r="G1489" t="n">
-        <v>27.5847034454346</v>
+        <v>27.5847053527832</v>
       </c>
       <c r="H1489" t="n">
         <v>110948</v>
@@ -43666,7 +43666,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G1493" t="n">
-        <v>27.0615501403809</v>
+        <v>27.0615482330322</v>
       </c>
       <c r="H1493" t="n">
         <v>27966</v>
@@ -43695,7 +43695,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>26.7761898040771</v>
+        <v>26.7761878967285</v>
       </c>
       <c r="H1494" t="n">
         <v>34445</v>
@@ -43782,7 +43782,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1497" t="n">
-        <v>26.5383911132812</v>
+        <v>26.5383892059326</v>
       </c>
       <c r="H1497" t="n">
         <v>48672</v>
@@ -43840,7 +43840,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G1499" t="n">
-        <v>26.7469062805176</v>
+        <v>26.7469043731689</v>
       </c>
       <c r="H1499" t="n">
         <v>26321</v>
@@ -43927,7 +43927,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1502" t="n">
-        <v>25.2636241912842</v>
+        <v>25.2636222839355</v>
       </c>
       <c r="H1502" t="n">
         <v>22913</v>
@@ -43956,7 +43956,7 @@
         <v>25.5</v>
       </c>
       <c r="G1503" t="n">
-        <v>24.402364730835</v>
+        <v>24.4023628234863</v>
       </c>
       <c r="H1503" t="n">
         <v>67767</v>
@@ -43985,7 +43985,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G1504" t="n">
-        <v>24.5459060668945</v>
+        <v>24.5459041595459</v>
       </c>
       <c r="H1504" t="n">
         <v>33849</v>
@@ -44014,7 +44014,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G1505" t="n">
-        <v>23.9717330932617</v>
+        <v>23.9717311859131</v>
       </c>
       <c r="H1505" t="n">
         <v>51717</v>
@@ -44362,7 +44362,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1517" t="n">
-        <v>25.5507125854492</v>
+        <v>25.5507106781006</v>
       </c>
       <c r="H1517" t="n">
         <v>57102</v>
@@ -44391,7 +44391,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1518" t="n">
-        <v>25.2636241912842</v>
+        <v>25.2636222839355</v>
       </c>
       <c r="H1518" t="n">
         <v>47608</v>
@@ -44478,7 +44478,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G1521" t="n">
-        <v>25.4071674346924</v>
+        <v>25.4071655273438</v>
       </c>
       <c r="H1521" t="n">
         <v>31449</v>
@@ -44768,7 +44768,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G1531" t="n">
-        <v>25.4071674346924</v>
+        <v>25.4071655273438</v>
       </c>
       <c r="H1531" t="n">
         <v>29927</v>
@@ -45000,7 +45000,7 @@
         <v>26.5</v>
       </c>
       <c r="G1539" t="n">
-        <v>25.359317779541</v>
+        <v>25.3593196868896</v>
       </c>
       <c r="H1539" t="n">
         <v>102304</v>
@@ -45232,7 +45232,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1547" t="n">
-        <v>23.0626258850098</v>
+        <v>23.0626239776611</v>
       </c>
       <c r="H1547" t="n">
         <v>51127</v>
@@ -45290,7 +45290,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1549" t="n">
-        <v>23.0626258850098</v>
+        <v>23.0626239776611</v>
       </c>
       <c r="H1549" t="n">
         <v>37351</v>
@@ -45319,7 +45319,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1550" t="n">
-        <v>22.2970581054688</v>
+        <v>22.2970600128174</v>
       </c>
       <c r="H1550" t="n">
         <v>53650</v>
@@ -45435,7 +45435,7 @@
         <v>23.5</v>
       </c>
       <c r="G1554" t="n">
-        <v>22.488452911377</v>
+        <v>22.4884510040283</v>
       </c>
       <c r="H1554" t="n">
         <v>64375</v>
@@ -45464,7 +45464,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1555" t="n">
-        <v>22.6798439025879</v>
+        <v>22.6798458099365</v>
       </c>
       <c r="H1555" t="n">
         <v>38570</v>
@@ -45493,7 +45493,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1556" t="n">
-        <v>22.3449096679688</v>
+        <v>22.3449077606201</v>
       </c>
       <c r="H1556" t="n">
         <v>16276</v>
@@ -45551,7 +45551,7 @@
         <v>23.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>22.488452911377</v>
+        <v>22.4884510040283</v>
       </c>
       <c r="H1558" t="n">
         <v>80091</v>
@@ -45638,7 +45638,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1561" t="n">
-        <v>21.9142799377441</v>
+        <v>21.9142780303955</v>
       </c>
       <c r="H1561" t="n">
         <v>39704</v>
@@ -45667,7 +45667,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1562" t="n">
-        <v>21.2444114685059</v>
+        <v>21.2444095611572</v>
       </c>
       <c r="H1562" t="n">
         <v>56633</v>
@@ -45696,7 +45696,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1563" t="n">
-        <v>21.0051727294922</v>
+        <v>21.0051708221436</v>
       </c>
       <c r="H1563" t="n">
         <v>58911</v>
@@ -45870,7 +45870,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1569" t="n">
-        <v>19.0242748260498</v>
+        <v>19.0242729187012</v>
       </c>
       <c r="H1569" t="n">
         <v>75410</v>
@@ -45899,7 +45899,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1570" t="n">
-        <v>18.0099010467529</v>
+        <v>18.0098991394043</v>
       </c>
       <c r="H1570" t="n">
         <v>66847</v>
@@ -46073,7 +46073,7 @@
         <v>19</v>
       </c>
       <c r="G1576" t="n">
-        <v>18.1821537017822</v>
+        <v>18.1821517944336</v>
       </c>
       <c r="H1576" t="n">
         <v>151380</v>
@@ -46102,7 +46102,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1577" t="n">
-        <v>17.7228164672852</v>
+        <v>17.7228145599365</v>
       </c>
       <c r="H1577" t="n">
         <v>56315</v>
@@ -46131,7 +46131,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1578" t="n">
-        <v>17.3783111572266</v>
+        <v>17.3783092498779</v>
       </c>
       <c r="H1578" t="n">
         <v>61174</v>
@@ -46305,7 +46305,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1584" t="n">
-        <v>18.2587108612061</v>
+        <v>18.2587089538574</v>
       </c>
       <c r="H1584" t="n">
         <v>32872</v>
@@ -46450,7 +46450,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1589" t="n">
-        <v>19.4740428924561</v>
+        <v>19.4740447998047</v>
       </c>
       <c r="H1589" t="n">
         <v>63334</v>
@@ -46479,7 +46479,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1590" t="n">
-        <v>18.9859943389893</v>
+        <v>18.9859962463379</v>
       </c>
       <c r="H1590" t="n">
         <v>63475</v>
@@ -46508,7 +46508,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1591" t="n">
-        <v>19.0816917419434</v>
+        <v>19.0816898345947</v>
       </c>
       <c r="H1591" t="n">
         <v>56316</v>
@@ -46566,7 +46566,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1593" t="n">
-        <v>18.5075168609619</v>
+        <v>18.5075149536133</v>
       </c>
       <c r="H1593" t="n">
         <v>64560</v>
@@ -46624,7 +46624,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1595" t="n">
-        <v>17.6462593078613</v>
+        <v>17.64626121521</v>
       </c>
       <c r="H1595" t="n">
         <v>36779</v>
@@ -46653,7 +46653,7 @@
         <v>19</v>
       </c>
       <c r="G1596" t="n">
-        <v>18.1821537017822</v>
+        <v>18.1821517944336</v>
       </c>
       <c r="H1596" t="n">
         <v>34936</v>
@@ -46711,7 +46711,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1598" t="n">
-        <v>18.2778472900391</v>
+        <v>18.2778491973877</v>
       </c>
       <c r="H1598" t="n">
         <v>30288</v>
@@ -46798,7 +46798,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G1601" t="n">
-        <v>18.6032161712646</v>
+        <v>18.603214263916</v>
       </c>
       <c r="H1601" t="n">
         <v>62995</v>
@@ -46856,7 +46856,7 @@
         <v>20.5</v>
       </c>
       <c r="G1603" t="n">
-        <v>19.6175842285156</v>
+        <v>19.6175861358643</v>
       </c>
       <c r="H1603" t="n">
         <v>50284</v>
@@ -46885,7 +46885,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1604" t="n">
-        <v>19.0051345825195</v>
+        <v>19.0051326751709</v>
       </c>
       <c r="H1604" t="n">
         <v>60703</v>
@@ -47030,7 +47030,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1609" t="n">
-        <v>19.4740428924561</v>
+        <v>19.4740447998047</v>
       </c>
       <c r="H1609" t="n">
         <v>43479</v>
@@ -47088,7 +47088,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1611" t="n">
-        <v>19.4740428924561</v>
+        <v>19.4740447998047</v>
       </c>
       <c r="H1611" t="n">
         <v>36819</v>
@@ -47117,7 +47117,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G1612" t="n">
-        <v>18.9859943389893</v>
+        <v>18.9859962463379</v>
       </c>
       <c r="H1612" t="n">
         <v>67720</v>
@@ -47204,7 +47204,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1615" t="n">
-        <v>17.4165897369385</v>
+        <v>17.4165916442871</v>
       </c>
       <c r="H1615" t="n">
         <v>46857</v>
@@ -47262,7 +47262,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1617" t="n">
-        <v>17.7228164672852</v>
+        <v>17.7228145599365</v>
       </c>
       <c r="H1617" t="n">
         <v>39618</v>
@@ -47320,7 +47320,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1619" t="n">
-        <v>18.5075168609619</v>
+        <v>18.5075149536133</v>
       </c>
       <c r="H1619" t="n">
         <v>42906</v>
@@ -47378,7 +47378,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1621" t="n">
-        <v>19.665433883667</v>
+        <v>19.6654319763184</v>
       </c>
       <c r="H1621" t="n">
         <v>140303</v>
@@ -47436,7 +47436,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1623" t="n">
-        <v>20.861629486084</v>
+        <v>20.8616275787354</v>
       </c>
       <c r="H1623" t="n">
         <v>164207</v>
@@ -47465,7 +47465,7 @@
         <v>21.5</v>
       </c>
       <c r="G1624" t="n">
-        <v>20.5745429992676</v>
+        <v>20.5745410919189</v>
       </c>
       <c r="H1624" t="n">
         <v>68979</v>
@@ -47726,7 +47726,7 @@
         <v>24</v>
       </c>
       <c r="G1633" t="n">
-        <v>22.9669303894043</v>
+        <v>22.9669322967529</v>
       </c>
       <c r="H1633" t="n">
         <v>66009</v>
@@ -47755,7 +47755,7 @@
         <v>24</v>
       </c>
       <c r="G1634" t="n">
-        <v>22.9669303894043</v>
+        <v>22.9669322967529</v>
       </c>
       <c r="H1634" t="n">
         <v>90059</v>
@@ -48132,7 +48132,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1647" t="n">
-        <v>19.665433883667</v>
+        <v>19.6654319763184</v>
       </c>
       <c r="H1647" t="n">
         <v>33689</v>
@@ -48190,7 +48190,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1649" t="n">
-        <v>19.4740428924561</v>
+        <v>19.4740447998047</v>
       </c>
       <c r="H1649" t="n">
         <v>23664</v>
@@ -48509,7 +48509,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1660" t="n">
-        <v>18.6797714233398</v>
+        <v>18.6797695159912</v>
       </c>
       <c r="H1660" t="n">
         <v>40834</v>
@@ -48741,7 +48741,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G1668" t="n">
-        <v>18.4118213653564</v>
+        <v>18.4118232727051</v>
       </c>
       <c r="H1668" t="n">
         <v>22304</v>
@@ -48770,7 +48770,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1669" t="n">
-        <v>18.3161239624023</v>
+        <v>18.316125869751</v>
       </c>
       <c r="H1669" t="n">
         <v>14369</v>
@@ -48828,7 +48828,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1671" t="n">
-        <v>17.8567867279053</v>
+        <v>17.8567886352539</v>
       </c>
       <c r="H1671" t="n">
         <v>39483</v>
@@ -48944,7 +48944,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1675" t="n">
-        <v>19.0242748260498</v>
+        <v>19.0242729187012</v>
       </c>
       <c r="H1675" t="n">
         <v>14819</v>
@@ -49292,7 +49292,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1687" t="n">
-        <v>18.5075168609619</v>
+        <v>18.5075149536133</v>
       </c>
       <c r="H1687" t="n">
         <v>19430</v>
@@ -49437,7 +49437,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1692" t="n">
-        <v>17.7993717193604</v>
+        <v>17.7993698120117</v>
       </c>
       <c r="H1692" t="n">
         <v>32076</v>
@@ -49466,7 +49466,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1693" t="n">
-        <v>17.5122852325439</v>
+        <v>17.5122833251953</v>
       </c>
       <c r="H1693" t="n">
         <v>19578</v>
@@ -49495,7 +49495,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1694" t="n">
-        <v>17.6462593078613</v>
+        <v>17.64626121521</v>
       </c>
       <c r="H1694" t="n">
         <v>28734</v>
@@ -49611,7 +49611,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1698" t="n">
-        <v>18.5075168609619</v>
+        <v>18.5075149536133</v>
       </c>
       <c r="H1698" t="n">
         <v>48664</v>
@@ -49843,7 +49843,7 @@
         <v>18</v>
       </c>
       <c r="G1706" t="n">
-        <v>17.2251987457275</v>
+        <v>17.2251968383789</v>
       </c>
       <c r="H1706" t="n">
         <v>42500</v>
@@ -49988,7 +49988,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1711" t="n">
-        <v>15.9428768157959</v>
+        <v>15.9428777694702</v>
       </c>
       <c r="H1711" t="n">
         <v>9691</v>
@@ -50046,7 +50046,7 @@
         <v>16</v>
       </c>
       <c r="G1713" t="n">
-        <v>15.3112859725952</v>
+        <v>15.3112869262695</v>
       </c>
       <c r="H1713" t="n">
         <v>41395</v>
@@ -50104,7 +50104,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1715" t="n">
-        <v>15.2538690567017</v>
+        <v>15.2538681030273</v>
       </c>
       <c r="H1715" t="n">
         <v>21742</v>
@@ -50162,7 +50162,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1717" t="n">
-        <v>16.0194339752197</v>
+        <v>16.0194320678711</v>
       </c>
       <c r="H1717" t="n">
         <v>52825</v>
@@ -50191,7 +50191,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1718" t="n">
-        <v>16.6510238647461</v>
+        <v>16.6510257720947</v>
       </c>
       <c r="H1718" t="n">
         <v>97817</v>
@@ -50220,7 +50220,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1719" t="n">
-        <v>16.7658596038818</v>
+        <v>16.7658576965332</v>
       </c>
       <c r="H1719" t="n">
         <v>48640</v>
@@ -50249,7 +50249,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1720" t="n">
-        <v>17.5122852325439</v>
+        <v>17.5122833251953</v>
       </c>
       <c r="H1720" t="n">
         <v>67009</v>
@@ -50278,7 +50278,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1721" t="n">
-        <v>16.9955272674561</v>
+        <v>16.9955291748047</v>
       </c>
       <c r="H1721" t="n">
         <v>50526</v>
@@ -50394,7 +50394,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1725" t="n">
-        <v>17.014669418335</v>
+        <v>17.0146675109863</v>
       </c>
       <c r="H1725" t="n">
         <v>31677</v>
@@ -50481,7 +50481,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1728" t="n">
-        <v>17.8376483917236</v>
+        <v>17.8376502990723</v>
       </c>
       <c r="H1728" t="n">
         <v>141822</v>
@@ -50626,7 +50626,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1733" t="n">
-        <v>19.4261951446533</v>
+        <v>19.4261932373047</v>
       </c>
       <c r="H1733" t="n">
         <v>52128</v>
@@ -50742,7 +50742,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1737" t="n">
-        <v>20.0003681182861</v>
+        <v>20.0003662109375</v>
       </c>
       <c r="H1737" t="n">
         <v>19921</v>
@@ -50887,7 +50887,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1742" t="n">
-        <v>19.4261951446533</v>
+        <v>19.4261932373047</v>
       </c>
       <c r="H1742" t="n">
         <v>32434</v>
@@ -51090,7 +51090,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1749" t="n">
-        <v>20.861629486084</v>
+        <v>20.8616275787354</v>
       </c>
       <c r="H1749" t="n">
         <v>181023</v>
@@ -51148,7 +51148,7 @@
         <v>21.5</v>
       </c>
       <c r="G1751" t="n">
-        <v>20.5745429992676</v>
+        <v>20.5745410919189</v>
       </c>
       <c r="H1751" t="n">
         <v>83866</v>
@@ -51409,7 +51409,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1760" t="n">
-        <v>20.5525970458984</v>
+        <v>20.5525989532471</v>
       </c>
       <c r="H1760" t="n">
         <v>30643</v>
@@ -51467,7 +51467,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1762" t="n">
-        <v>20.4556522369385</v>
+        <v>20.4556503295898</v>
       </c>
       <c r="H1762" t="n">
         <v>51852</v>
@@ -51496,7 +51496,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1763" t="n">
-        <v>20.4556522369385</v>
+        <v>20.4556503295898</v>
       </c>
       <c r="H1763" t="n">
         <v>42594</v>
@@ -51525,7 +51525,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1764" t="n">
-        <v>20.5525970458984</v>
+        <v>20.5525989532471</v>
       </c>
       <c r="H1764" t="n">
         <v>10955</v>
@@ -51786,7 +51786,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G1773" t="n">
-        <v>20.0193920135498</v>
+        <v>20.0193939208984</v>
       </c>
       <c r="H1773" t="n">
         <v>145243</v>
@@ -51815,7 +51815,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1774" t="n">
-        <v>19.9709205627441</v>
+        <v>19.9709186553955</v>
       </c>
       <c r="H1774" t="n">
         <v>27625</v>
@@ -51844,7 +51844,7 @@
         <v>20.75</v>
       </c>
       <c r="G1775" t="n">
-        <v>20.1163387298584</v>
+        <v>20.116340637207</v>
       </c>
       <c r="H1775" t="n">
         <v>30004</v>
@@ -51931,7 +51931,7 @@
         <v>21.5</v>
       </c>
       <c r="G1778" t="n">
-        <v>20.8434352874756</v>
+        <v>20.8434371948242</v>
       </c>
       <c r="H1778" t="n">
         <v>20079</v>
@@ -52018,7 +52018,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G1781" t="n">
-        <v>20.69801902771</v>
+        <v>20.6980171203613</v>
       </c>
       <c r="H1781" t="n">
         <v>14990</v>
@@ -52105,7 +52105,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G1784" t="n">
-        <v>20.69801902771</v>
+        <v>20.6980171203613</v>
       </c>
       <c r="H1784" t="n">
         <v>30204</v>
@@ -52163,7 +52163,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1786" t="n">
-        <v>20.5525970458984</v>
+        <v>20.5525989532471</v>
       </c>
       <c r="H1786" t="n">
         <v>13526</v>
@@ -52221,7 +52221,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1788" t="n">
-        <v>21.6190032958984</v>
+        <v>21.6190052032471</v>
       </c>
       <c r="H1788" t="n">
         <v>61630</v>
@@ -52279,7 +52279,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1790" t="n">
-        <v>21.6190032958984</v>
+        <v>21.6190052032471</v>
       </c>
       <c r="H1790" t="n">
         <v>41879</v>
@@ -52598,7 +52598,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G1801" t="n">
-        <v>23.4125099182129</v>
+        <v>23.4125118255615</v>
       </c>
       <c r="H1801" t="n">
         <v>61697</v>
@@ -52656,7 +52656,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G1803" t="n">
-        <v>23.3155632019043</v>
+        <v>23.3155651092529</v>
       </c>
       <c r="H1803" t="n">
         <v>31982</v>
@@ -52685,7 +52685,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1804" t="n">
-        <v>23.0731983184814</v>
+        <v>23.0732002258301</v>
       </c>
       <c r="H1804" t="n">
         <v>57307</v>
@@ -52801,7 +52801,7 @@
         <v>24.25</v>
       </c>
       <c r="G1808" t="n">
-        <v>23.5094585418701</v>
+        <v>23.5094566345215</v>
       </c>
       <c r="H1808" t="n">
         <v>26547</v>
@@ -52830,7 +52830,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1809" t="n">
-        <v>23.4609870910645</v>
+        <v>23.4609851837158</v>
       </c>
       <c r="H1809" t="n">
         <v>17397</v>
@@ -52946,7 +52946,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1813" t="n">
-        <v>23.121675491333</v>
+        <v>23.1216735839844</v>
       </c>
       <c r="H1813" t="n">
         <v>21578</v>
@@ -53033,7 +53033,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1816" t="n">
-        <v>23.121675491333</v>
+        <v>23.1216735839844</v>
       </c>
       <c r="H1816" t="n">
         <v>26874</v>
@@ -53120,7 +53120,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1819" t="n">
-        <v>23.121675491333</v>
+        <v>23.1216735839844</v>
       </c>
       <c r="H1819" t="n">
         <v>23947</v>
@@ -53178,7 +53178,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G1821" t="n">
-        <v>23.8002948760986</v>
+        <v>23.8002967834473</v>
       </c>
       <c r="H1821" t="n">
         <v>37990</v>
@@ -53207,7 +53207,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1822" t="n">
-        <v>24.5273933410645</v>
+        <v>24.5273914337158</v>
       </c>
       <c r="H1822" t="n">
         <v>61190</v>
@@ -53265,7 +53265,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1824" t="n">
-        <v>24.818229675293</v>
+        <v>24.8182315826416</v>
       </c>
       <c r="H1824" t="n">
         <v>110628</v>
@@ -53410,7 +53410,7 @@
         <v>25.0499992370605</v>
       </c>
       <c r="G1829" t="n">
-        <v>24.285026550293</v>
+        <v>24.2850284576416</v>
       </c>
       <c r="H1829" t="n">
         <v>29649</v>
@@ -53439,7 +53439,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1830" t="n">
-        <v>24.1396064758301</v>
+        <v>24.1396083831787</v>
       </c>
       <c r="H1830" t="n">
         <v>29105</v>
@@ -53584,7 +53584,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1835" t="n">
-        <v>22.4915237426758</v>
+        <v>22.4915218353271</v>
       </c>
       <c r="H1835" t="n">
         <v>55727</v>
@@ -53642,7 +53642,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G1837" t="n">
-        <v>22.7338905334473</v>
+        <v>22.7338886260986</v>
       </c>
       <c r="H1837" t="n">
         <v>47921</v>
@@ -53700,7 +53700,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G1839" t="n">
-        <v>23.4125099182129</v>
+        <v>23.4125118255615</v>
       </c>
       <c r="H1839" t="n">
         <v>35433</v>
@@ -53787,7 +53787,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1842" t="n">
-        <v>22.4915237426758</v>
+        <v>22.4915218353271</v>
       </c>
       <c r="H1842" t="n">
         <v>32516</v>
@@ -53816,7 +53816,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G1843" t="n">
-        <v>22.7338905334473</v>
+        <v>22.7338886260986</v>
       </c>
       <c r="H1843" t="n">
         <v>42459</v>
@@ -53845,7 +53845,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1844" t="n">
-        <v>23.0731983184814</v>
+        <v>23.0732002258301</v>
       </c>
       <c r="H1844" t="n">
         <v>30609</v>
@@ -53903,7 +53903,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G1846" t="n">
-        <v>23.8002948760986</v>
+        <v>23.8002967834473</v>
       </c>
       <c r="H1846" t="n">
         <v>44142</v>
@@ -54164,7 +54164,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1855" t="n">
-        <v>24.1880836486816</v>
+        <v>24.188081741333</v>
       </c>
       <c r="H1855" t="n">
         <v>47407</v>
@@ -54222,7 +54222,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1857" t="n">
-        <v>24.5273933410645</v>
+        <v>24.5273914337158</v>
       </c>
       <c r="H1857" t="n">
         <v>35774</v>
@@ -54280,7 +54280,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1859" t="n">
-        <v>24.1880836486816</v>
+        <v>24.188081741333</v>
       </c>
       <c r="H1859" t="n">
         <v>28286</v>
@@ -54338,7 +54338,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G1861" t="n">
-        <v>23.8002948760986</v>
+        <v>23.8002967834473</v>
       </c>
       <c r="H1861" t="n">
         <v>13239</v>
@@ -54541,7 +54541,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1868" t="n">
-        <v>22.4915237426758</v>
+        <v>22.4915218353271</v>
       </c>
       <c r="H1868" t="n">
         <v>23547</v>
@@ -54686,7 +54686,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1873" t="n">
-        <v>22.6854133605957</v>
+        <v>22.6854152679443</v>
       </c>
       <c r="H1873" t="n">
         <v>9579</v>
@@ -54715,7 +54715,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1874" t="n">
-        <v>22.4915237426758</v>
+        <v>22.4915218353271</v>
       </c>
       <c r="H1874" t="n">
         <v>11979</v>
@@ -55034,7 +55034,7 @@
         <v>22.5</v>
       </c>
       <c r="G1885" t="n">
-        <v>21.8128986358643</v>
+        <v>21.8129005432129</v>
       </c>
       <c r="H1885" t="n">
         <v>17082</v>
@@ -55092,7 +55092,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1887" t="n">
-        <v>21.7644271850586</v>
+        <v>21.76442527771</v>
       </c>
       <c r="H1887" t="n">
         <v>25843</v>
@@ -55150,7 +55150,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1889" t="n">
-        <v>22.3945770263672</v>
+        <v>22.3945751190186</v>
       </c>
       <c r="H1889" t="n">
         <v>12031</v>
@@ -55208,7 +55208,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1891" t="n">
-        <v>22.3945770263672</v>
+        <v>22.3945751190186</v>
       </c>
       <c r="H1891" t="n">
         <v>6396</v>
@@ -55353,7 +55353,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G1896" t="n">
-        <v>22.3461017608643</v>
+        <v>22.3461036682129</v>
       </c>
       <c r="H1896" t="n">
         <v>13155</v>
@@ -55411,7 +55411,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1898" t="n">
-        <v>22.3945770263672</v>
+        <v>22.3945751190186</v>
       </c>
       <c r="H1898" t="n">
         <v>25414</v>
@@ -55643,7 +55643,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1906" t="n">
-        <v>21.4251155853271</v>
+        <v>21.4251136779785</v>
       </c>
       <c r="H1906" t="n">
         <v>22499</v>
@@ -55701,7 +55701,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1908" t="n">
-        <v>21.2796936035156</v>
+        <v>21.2796955108643</v>
       </c>
       <c r="H1908" t="n">
         <v>6796</v>
@@ -55730,7 +55730,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1909" t="n">
-        <v>21.2796936035156</v>
+        <v>21.2796955108643</v>
       </c>
       <c r="H1909" t="n">
         <v>11741</v>
@@ -55788,7 +55788,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1911" t="n">
-        <v>20.9888572692871</v>
+        <v>20.9888553619385</v>
       </c>
       <c r="H1911" t="n">
         <v>11927</v>
@@ -55875,7 +55875,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G1914" t="n">
-        <v>20.69801902771</v>
+        <v>20.6980171203613</v>
       </c>
       <c r="H1914" t="n">
         <v>11670</v>
@@ -55904,7 +55904,7 @@
         <v>21.5</v>
       </c>
       <c r="G1915" t="n">
-        <v>20.8434352874756</v>
+        <v>20.8434371948242</v>
       </c>
       <c r="H1915" t="n">
         <v>14268</v>
@@ -56281,7 +56281,7 @@
         <v>22.5</v>
       </c>
       <c r="G1928" t="n">
-        <v>21.8128986358643</v>
+        <v>21.8129005432129</v>
       </c>
       <c r="H1928" t="n">
         <v>36177</v>
@@ -56310,7 +56310,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1929" t="n">
-        <v>21.6190032958984</v>
+        <v>21.6190052032471</v>
       </c>
       <c r="H1929" t="n">
         <v>31980</v>
@@ -56339,7 +56339,7 @@
         <v>22.5</v>
       </c>
       <c r="G1930" t="n">
-        <v>21.8128986358643</v>
+        <v>21.8129005432129</v>
       </c>
       <c r="H1930" t="n">
         <v>23759</v>
@@ -56455,7 +56455,7 @@
         <v>21.75</v>
       </c>
       <c r="G1934" t="n">
-        <v>21.0858020782471</v>
+        <v>21.0858039855957</v>
       </c>
       <c r="H1934" t="n">
         <v>14236</v>
@@ -56571,7 +56571,7 @@
         <v>21.5</v>
       </c>
       <c r="G1938" t="n">
-        <v>20.8434352874756</v>
+        <v>20.8434371948242</v>
       </c>
       <c r="H1938" t="n">
         <v>8511</v>
@@ -56600,7 +56600,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G1939" t="n">
-        <v>20.69801902771</v>
+        <v>20.6980171203613</v>
       </c>
       <c r="H1939" t="n">
         <v>11355</v>
@@ -56919,7 +56919,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G1950" t="n">
-        <v>21.7644271850586</v>
+        <v>21.76442527771</v>
       </c>
       <c r="H1950" t="n">
         <v>35629</v>
@@ -56948,7 +56948,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1951" t="n">
-        <v>21.6190032958984</v>
+        <v>21.6190052032471</v>
       </c>
       <c r="H1951" t="n">
         <v>26315</v>
@@ -57006,7 +57006,7 @@
         <v>22.5</v>
       </c>
       <c r="G1953" t="n">
-        <v>21.8128986358643</v>
+        <v>21.8129005432129</v>
       </c>
       <c r="H1953" t="n">
         <v>20390</v>
@@ -57122,7 +57122,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1957" t="n">
-        <v>21.66748046875</v>
+        <v>21.6674785614014</v>
       </c>
       <c r="H1957" t="n">
         <v>11997</v>
@@ -57209,7 +57209,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1960" t="n">
-        <v>22.4915237426758</v>
+        <v>22.4915218353271</v>
       </c>
       <c r="H1960" t="n">
         <v>35140</v>
@@ -57238,7 +57238,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1961" t="n">
-        <v>22.4915237426758</v>
+        <v>22.4915218353271</v>
       </c>
       <c r="H1961" t="n">
         <v>16448</v>
@@ -57267,7 +57267,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G1962" t="n">
-        <v>22.7338905334473</v>
+        <v>22.7338886260986</v>
       </c>
       <c r="H1962" t="n">
         <v>16216</v>
@@ -57325,7 +57325,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1964" t="n">
-        <v>22.4915237426758</v>
+        <v>22.4915218353271</v>
       </c>
       <c r="H1964" t="n">
         <v>21239</v>
@@ -57470,7 +57470,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1969" t="n">
-        <v>24.0426597595215</v>
+        <v>24.0426616668701</v>
       </c>
       <c r="H1969" t="n">
         <v>118094</v>
@@ -57528,7 +57528,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1971" t="n">
-        <v>24.1880836486816</v>
+        <v>24.188081741333</v>
       </c>
       <c r="H1971" t="n">
         <v>277200</v>
@@ -57644,7 +57644,7 @@
         <v>26.5</v>
       </c>
       <c r="G1975" t="n">
-        <v>25.6907482147217</v>
+        <v>25.690746307373</v>
       </c>
       <c r="H1975" t="n">
         <v>54071</v>
@@ -57702,7 +57702,7 @@
         <v>26.5</v>
       </c>
       <c r="G1977" t="n">
-        <v>25.6907482147217</v>
+        <v>25.690746307373</v>
       </c>
       <c r="H1977" t="n">
         <v>48608</v>
@@ -57760,7 +57760,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1979" t="n">
-        <v>25.7876949310303</v>
+        <v>25.7876930236816</v>
       </c>
       <c r="H1979" t="n">
         <v>56735</v>
@@ -57789,7 +57789,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1980" t="n">
-        <v>25.8846397399902</v>
+        <v>25.8846416473389</v>
       </c>
       <c r="H1980" t="n">
         <v>35508</v>
@@ -57992,7 +57992,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1987" t="n">
-        <v>24.818229675293</v>
+        <v>24.8182315826416</v>
       </c>
       <c r="H1987" t="n">
         <v>99091</v>
@@ -58021,7 +58021,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G1988" t="n">
-        <v>24.3819713592529</v>
+        <v>24.3819732666016</v>
       </c>
       <c r="H1988" t="n">
         <v>91502</v>
@@ -58050,7 +58050,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1989" t="n">
-        <v>24.5273933410645</v>
+        <v>24.5273914337158</v>
       </c>
       <c r="H1989" t="n">
         <v>77201</v>
@@ -58079,7 +58079,7 @@
         <v>25.5</v>
       </c>
       <c r="G1990" t="n">
-        <v>24.7212867736816</v>
+        <v>24.721284866333</v>
       </c>
       <c r="H1990" t="n">
         <v>35815</v>
@@ -58108,7 +58108,7 @@
         <v>24.75</v>
       </c>
       <c r="G1991" t="n">
-        <v>23.9941883087158</v>
+        <v>23.9941864013672</v>
       </c>
       <c r="H1991" t="n">
         <v>36401</v>
@@ -58166,7 +58166,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G1993" t="n">
-        <v>23.8002948760986</v>
+        <v>23.8002967834473</v>
       </c>
       <c r="H1993" t="n">
         <v>48945</v>
@@ -58195,7 +58195,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1994" t="n">
-        <v>24.1880836486816</v>
+        <v>24.188081741333</v>
       </c>
       <c r="H1994" t="n">
         <v>27506</v>
@@ -58224,7 +58224,7 @@
         <v>25</v>
       </c>
       <c r="G1995" t="n">
-        <v>24.2365550994873</v>
+        <v>24.2365531921387</v>
       </c>
       <c r="H1995" t="n">
         <v>30807</v>
@@ -58369,7 +58369,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G2000" t="n">
-        <v>24.5273933410645</v>
+        <v>24.5273914337158</v>
       </c>
       <c r="H2000" t="n">
         <v>79601</v>
@@ -58427,7 +58427,7 @@
         <v>26.5</v>
       </c>
       <c r="G2002" t="n">
-        <v>25.6907482147217</v>
+        <v>25.690746307373</v>
       </c>
       <c r="H2002" t="n">
         <v>71828</v>
@@ -58514,7 +58514,7 @@
         <v>26.5</v>
       </c>
       <c r="G2005" t="n">
-        <v>25.6907482147217</v>
+        <v>25.690746307373</v>
       </c>
       <c r="H2005" t="n">
         <v>34142</v>
@@ -58601,7 +58601,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G2008" t="n">
-        <v>25.5453281402588</v>
+        <v>25.5453300476074</v>
       </c>
       <c r="H2008" t="n">
         <v>22936</v>
@@ -79977,9 +79977,38 @@
         <v>51.0499992370605</v>
       </c>
       <c r="H2745" t="n">
-        <v>63649</v>
+        <v>63834</v>
       </c>
       <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>50.7999992370605</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>50.9000015258789</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>49.7999992370605</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>50.6500015258789</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>50.6500015258789</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>62597</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -427,7 +427,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>15.5902509689331</v>
+        <v>15.5902500152588</v>
       </c>
       <c r="H2" t="n">
         <v>57824</v>
@@ -456,7 +456,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7186403274536</v>
+        <v>15.7186422348022</v>
       </c>
       <c r="H3" t="n">
         <v>35642</v>
@@ -485,7 +485,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2234239578247</v>
+        <v>15.2234210968018</v>
       </c>
       <c r="H4" t="n">
         <v>65319</v>
@@ -514,7 +514,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>14.5356178283691</v>
+        <v>14.5356168746948</v>
       </c>
       <c r="H5" t="n">
         <v>96087</v>
@@ -572,7 +572,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>13.9395189285278</v>
+        <v>13.9395179748535</v>
       </c>
       <c r="H7" t="n">
         <v>42515</v>
@@ -630,7 +630,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="G9" t="n">
-        <v>14.040397644043</v>
+        <v>14.0403985977173</v>
       </c>
       <c r="H9" t="n">
         <v>90915</v>
@@ -659,7 +659,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G10" t="n">
-        <v>13.866153717041</v>
+        <v>13.8661527633667</v>
       </c>
       <c r="H10" t="n">
         <v>49474</v>
@@ -688,7 +688,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G11" t="n">
-        <v>13.1049823760986</v>
+        <v>13.1049833297729</v>
       </c>
       <c r="H11" t="n">
         <v>101980</v>
@@ -717,7 +717,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G12" t="n">
-        <v>12.793176651001</v>
+        <v>12.7931756973267</v>
       </c>
       <c r="H12" t="n">
         <v>70420</v>
@@ -746,7 +746,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G13" t="n">
-        <v>12.8848848342896</v>
+        <v>12.8848838806152</v>
       </c>
       <c r="H13" t="n">
         <v>51845</v>
@@ -775,7 +775,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G14" t="n">
-        <v>12.2887878417969</v>
+        <v>12.2887868881226</v>
       </c>
       <c r="H14" t="n">
         <v>71385</v>
@@ -833,7 +833,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>13.132493019104</v>
+        <v>13.1324939727783</v>
       </c>
       <c r="H16" t="n">
         <v>85369</v>
@@ -862,7 +862,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G17" t="n">
-        <v>15.8928861618042</v>
+        <v>15.8928852081299</v>
       </c>
       <c r="H17" t="n">
         <v>376769</v>
@@ -891,7 +891,7 @@
         <v>17.5</v>
       </c>
       <c r="G18" t="n">
-        <v>16.0487880706787</v>
+        <v>16.048791885376</v>
       </c>
       <c r="H18" t="n">
         <v>615324</v>
@@ -949,7 +949,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G20" t="n">
-        <v>16.0854721069336</v>
+        <v>16.085470199585</v>
       </c>
       <c r="H20" t="n">
         <v>156267</v>
@@ -978,7 +978,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G21" t="n">
-        <v>16.360595703125</v>
+        <v>16.3605937957764</v>
       </c>
       <c r="H21" t="n">
         <v>116126</v>
@@ -1036,7 +1036,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>16.5990295410156</v>
+        <v>16.5990314483643</v>
       </c>
       <c r="H23" t="n">
         <v>490894</v>
@@ -1065,7 +1065,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G24" t="n">
-        <v>15.4710330963135</v>
+        <v>15.4710340499878</v>
       </c>
       <c r="H24" t="n">
         <v>293009</v>
@@ -1094,7 +1094,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G25" t="n">
-        <v>16.1038131713867</v>
+        <v>16.1038150787354</v>
       </c>
       <c r="H25" t="n">
         <v>137203</v>
@@ -1123,7 +1123,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G26" t="n">
-        <v>15.3059587478638</v>
+        <v>15.3059577941895</v>
       </c>
       <c r="H26" t="n">
         <v>118150</v>
@@ -1181,7 +1181,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G28" t="n">
-        <v>14.948299407959</v>
+        <v>14.9482984542847</v>
       </c>
       <c r="H28" t="n">
         <v>97617</v>
@@ -1210,7 +1210,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G29" t="n">
-        <v>15.3518123626709</v>
+        <v>15.3518104553223</v>
       </c>
       <c r="H29" t="n">
         <v>133443</v>
@@ -1239,7 +1239,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G30" t="n">
-        <v>15.1042032241821</v>
+        <v>15.1042013168335</v>
       </c>
       <c r="H30" t="n">
         <v>42426</v>
@@ -1268,7 +1268,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G31" t="n">
-        <v>15.0033264160156</v>
+        <v>15.003324508667</v>
       </c>
       <c r="H31" t="n">
         <v>50728</v>
@@ -1297,7 +1297,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>15.911226272583</v>
+        <v>15.9112272262573</v>
       </c>
       <c r="H32" t="n">
         <v>139615</v>
@@ -1326,7 +1326,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G33" t="n">
-        <v>16.2322025299072</v>
+        <v>16.2322044372559</v>
       </c>
       <c r="H33" t="n">
         <v>61554</v>
@@ -1355,7 +1355,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G34" t="n">
-        <v>16.7641086578369</v>
+        <v>16.7641067504883</v>
       </c>
       <c r="H34" t="n">
         <v>132571</v>
@@ -1384,7 +1384,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G35" t="n">
-        <v>16.9200096130371</v>
+        <v>16.9200077056885</v>
       </c>
       <c r="H35" t="n">
         <v>113760</v>
@@ -1413,7 +1413,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>17.0575675964355</v>
+        <v>17.0575714111328</v>
       </c>
       <c r="H36" t="n">
         <v>229585</v>
@@ -1442,7 +1442,7 @@
         <v>18.5</v>
       </c>
       <c r="G37" t="n">
-        <v>16.9658603668213</v>
+        <v>16.9658641815186</v>
       </c>
       <c r="H37" t="n">
         <v>111528</v>
@@ -1471,7 +1471,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G38" t="n">
-        <v>16.709077835083</v>
+        <v>16.7090816497803</v>
       </c>
       <c r="H38" t="n">
         <v>28331</v>
@@ -1500,7 +1500,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G39" t="n">
-        <v>16.360595703125</v>
+        <v>16.3605937957764</v>
       </c>
       <c r="H39" t="n">
         <v>65595</v>
@@ -1529,7 +1529,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>16.3514194488525</v>
+        <v>16.3514251708984</v>
       </c>
       <c r="H40" t="n">
         <v>40812</v>
@@ -1558,7 +1558,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G41" t="n">
-        <v>16.1038131713867</v>
+        <v>16.1038150787354</v>
       </c>
       <c r="H41" t="n">
         <v>103694</v>
@@ -1587,7 +1587,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G42" t="n">
-        <v>16.3422546386719</v>
+        <v>16.3422527313232</v>
       </c>
       <c r="H42" t="n">
         <v>43527</v>
@@ -1645,7 +1645,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>16.6357135772705</v>
+        <v>16.6357154846191</v>
       </c>
       <c r="H44" t="n">
         <v>131715</v>
@@ -1674,7 +1674,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G45" t="n">
-        <v>17.1767864227295</v>
+        <v>17.1767902374268</v>
       </c>
       <c r="H45" t="n">
         <v>95127</v>
@@ -1761,7 +1761,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G48" t="n">
-        <v>17.4335670471191</v>
+        <v>17.433572769165</v>
       </c>
       <c r="H48" t="n">
         <v>322204</v>
@@ -1790,7 +1790,7 @@
         <v>18.5</v>
       </c>
       <c r="G49" t="n">
-        <v>16.9658603668213</v>
+        <v>16.9658641815186</v>
       </c>
       <c r="H49" t="n">
         <v>55559</v>
@@ -1848,7 +1848,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G51" t="n">
-        <v>17.2226428985596</v>
+        <v>17.2226409912109</v>
       </c>
       <c r="H51" t="n">
         <v>34164</v>
@@ -1877,7 +1877,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>17.5161094665527</v>
+        <v>17.5161056518555</v>
       </c>
       <c r="H52" t="n">
         <v>55267</v>
@@ -1906,7 +1906,7 @@
         <v>18.5</v>
       </c>
       <c r="G53" t="n">
-        <v>16.9658603668213</v>
+        <v>16.9658641815186</v>
       </c>
       <c r="H53" t="n">
         <v>23006</v>
@@ -1935,7 +1935,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>16.874153137207</v>
+        <v>16.8741550445557</v>
       </c>
       <c r="H54" t="n">
         <v>28778</v>
@@ -1964,7 +1964,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G55" t="n">
-        <v>17.2593250274658</v>
+        <v>17.2593269348145</v>
       </c>
       <c r="H55" t="n">
         <v>37241</v>
@@ -1993,7 +1993,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G56" t="n">
-        <v>17.4610805511475</v>
+        <v>17.4610824584961</v>
       </c>
       <c r="H56" t="n">
         <v>30163</v>
@@ -2022,7 +2022,7 @@
         <v>18.5</v>
       </c>
       <c r="G57" t="n">
-        <v>16.9658603668213</v>
+        <v>16.9658641815186</v>
       </c>
       <c r="H57" t="n">
         <v>40462</v>
@@ -2051,7 +2051,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>17.0575675964355</v>
+        <v>17.0575714111328</v>
       </c>
       <c r="H58" t="n">
         <v>51915</v>
@@ -2109,7 +2109,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G60" t="n">
-        <v>16.2138595581055</v>
+        <v>16.2138614654541</v>
       </c>
       <c r="H60" t="n">
         <v>98478</v>
@@ -2138,7 +2138,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G61" t="n">
-        <v>16.5531787872314</v>
+        <v>16.5531768798828</v>
       </c>
       <c r="H61" t="n">
         <v>50561</v>
@@ -2167,7 +2167,7 @@
         <v>18.5</v>
       </c>
       <c r="G62" t="n">
-        <v>16.9658603668213</v>
+        <v>16.9658641815186</v>
       </c>
       <c r="H62" t="n">
         <v>31403</v>
@@ -2196,7 +2196,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G63" t="n">
-        <v>16.9383506774902</v>
+        <v>16.9383487701416</v>
       </c>
       <c r="H63" t="n">
         <v>19939</v>
@@ -2225,7 +2225,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G64" t="n">
-        <v>16.709077835083</v>
+        <v>16.7090816497803</v>
       </c>
       <c r="H64" t="n">
         <v>25326</v>
@@ -2254,7 +2254,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>17.2868385314941</v>
+        <v>17.2868366241455</v>
       </c>
       <c r="H65" t="n">
         <v>68353</v>
@@ -2283,7 +2283,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G66" t="n">
-        <v>16.5715179443359</v>
+        <v>16.5715217590332</v>
       </c>
       <c r="H66" t="n">
         <v>32129</v>
@@ -2399,7 +2399,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>17.6353225708008</v>
+        <v>17.6353244781494</v>
       </c>
       <c r="H70" t="n">
         <v>42644</v>
@@ -2428,7 +2428,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G71" t="n">
-        <v>17.4060554504395</v>
+        <v>17.4060573577881</v>
       </c>
       <c r="H71" t="n">
         <v>20298</v>
@@ -2457,7 +2457,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G72" t="n">
-        <v>17.8645915985107</v>
+        <v>17.8645935058594</v>
       </c>
       <c r="H72" t="n">
         <v>69176</v>
@@ -2515,7 +2515,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>18.0204944610596</v>
+        <v>18.0204982757568</v>
       </c>
       <c r="H74" t="n">
         <v>17233</v>
@@ -2573,7 +2573,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G76" t="n">
-        <v>17.5986442565918</v>
+        <v>17.5986423492432</v>
       </c>
       <c r="H76" t="n">
         <v>117794</v>
@@ -2602,7 +2602,7 @@
         <v>20</v>
       </c>
       <c r="G77" t="n">
-        <v>18.3414726257324</v>
+        <v>18.3414688110352</v>
       </c>
       <c r="H77" t="n">
         <v>97186</v>
@@ -2631,7 +2631,7 @@
         <v>20.0699996948242</v>
       </c>
       <c r="G78" t="n">
-        <v>18.405668258667</v>
+        <v>18.4056701660156</v>
       </c>
       <c r="H78" t="n">
         <v>99094</v>
@@ -2689,7 +2689,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G80" t="n">
-        <v>18.0938606262207</v>
+        <v>18.0938625335693</v>
       </c>
       <c r="H80" t="n">
         <v>19099</v>
@@ -2718,7 +2718,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G81" t="n">
-        <v>18.3231315612793</v>
+        <v>18.3231296539307</v>
       </c>
       <c r="H81" t="n">
         <v>26322</v>
@@ -2863,7 +2863,7 @@
         <v>18.5</v>
       </c>
       <c r="G86" t="n">
-        <v>16.9658603668213</v>
+        <v>16.9658641815186</v>
       </c>
       <c r="H86" t="n">
         <v>48847</v>
@@ -2892,7 +2892,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G87" t="n">
-        <v>17.1492786407471</v>
+        <v>17.1492748260498</v>
       </c>
       <c r="H87" t="n">
         <v>16818</v>
@@ -3037,7 +3037,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G92" t="n">
-        <v>16.8374729156494</v>
+        <v>16.837474822998</v>
       </c>
       <c r="H92" t="n">
         <v>18052</v>
@@ -3095,7 +3095,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G94" t="n">
-        <v>16.3147411346436</v>
+        <v>16.3147449493408</v>
       </c>
       <c r="H94" t="n">
         <v>55875</v>
@@ -3124,7 +3124,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G95" t="n">
-        <v>16.1496658325195</v>
+        <v>16.1496677398682</v>
       </c>
       <c r="H95" t="n">
         <v>14197</v>
@@ -3153,7 +3153,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G96" t="n">
-        <v>16.2505435943604</v>
+        <v>16.2505416870117</v>
       </c>
       <c r="H96" t="n">
         <v>36784</v>
@@ -3182,7 +3182,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G97" t="n">
-        <v>16.7457656860352</v>
+        <v>16.7457637786865</v>
       </c>
       <c r="H97" t="n">
         <v>37611</v>
@@ -3240,7 +3240,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G99" t="n">
-        <v>16.4156188964844</v>
+        <v>16.4156169891357</v>
       </c>
       <c r="H99" t="n">
         <v>11742</v>
@@ -3269,7 +3269,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G100" t="n">
-        <v>16.168004989624</v>
+        <v>16.1680068969727</v>
       </c>
       <c r="H100" t="n">
         <v>37522</v>
@@ -3298,7 +3298,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G101" t="n">
-        <v>16.3514194488525</v>
+        <v>16.3514251708984</v>
       </c>
       <c r="H101" t="n">
         <v>40913</v>
@@ -3327,7 +3327,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G102" t="n">
-        <v>16.7457656860352</v>
+        <v>16.7457637786865</v>
       </c>
       <c r="H102" t="n">
         <v>88393</v>
@@ -3356,7 +3356,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G103" t="n">
-        <v>17.3602046966553</v>
+        <v>17.3602066040039</v>
       </c>
       <c r="H103" t="n">
         <v>81800</v>
@@ -3414,7 +3414,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G105" t="n">
-        <v>17.1492786407471</v>
+        <v>17.1492748260498</v>
       </c>
       <c r="H105" t="n">
         <v>9668</v>
@@ -3443,7 +3443,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G106" t="n">
-        <v>16.5164966583252</v>
+        <v>16.5164985656738</v>
       </c>
       <c r="H106" t="n">
         <v>55198</v>
@@ -3559,7 +3559,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G110" t="n">
-        <v>16.9933776855469</v>
+        <v>16.993371963501</v>
       </c>
       <c r="H110" t="n">
         <v>12079</v>
@@ -3588,7 +3588,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G111" t="n">
-        <v>17.0392265319824</v>
+        <v>17.0392284393311</v>
       </c>
       <c r="H111" t="n">
         <v>4487</v>
@@ -3617,7 +3617,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G112" t="n">
-        <v>16.9933776855469</v>
+        <v>16.993371963501</v>
       </c>
       <c r="H112" t="n">
         <v>25750</v>
@@ -3675,7 +3675,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>16.4156188964844</v>
+        <v>16.4156169891357</v>
       </c>
       <c r="H114" t="n">
         <v>28373</v>
@@ -3704,7 +3704,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G115" t="n">
-        <v>15.8103494644165</v>
+        <v>15.8103466033936</v>
       </c>
       <c r="H115" t="n">
         <v>104335</v>
@@ -3733,7 +3733,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G116" t="n">
-        <v>15.84703540802</v>
+        <v>15.8470325469971</v>
       </c>
       <c r="H116" t="n">
         <v>50453</v>
@@ -3762,7 +3762,7 @@
         <v>17</v>
       </c>
       <c r="G117" t="n">
-        <v>15.5902509689331</v>
+        <v>15.5902500152588</v>
       </c>
       <c r="H117" t="n">
         <v>74690</v>
@@ -3820,7 +3820,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G119" t="n">
-        <v>14.7648868560791</v>
+        <v>14.7648859024048</v>
       </c>
       <c r="H119" t="n">
         <v>97119</v>
@@ -3849,7 +3849,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G120" t="n">
-        <v>15.0675191879272</v>
+        <v>15.0675201416016</v>
       </c>
       <c r="H120" t="n">
         <v>58276</v>
@@ -3878,7 +3878,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G121" t="n">
-        <v>15.3334684371948</v>
+        <v>15.3334703445435</v>
       </c>
       <c r="H121" t="n">
         <v>77133</v>
@@ -3907,7 +3907,7 @@
         <v>17</v>
       </c>
       <c r="G122" t="n">
-        <v>15.5902509689331</v>
+        <v>15.5902500152588</v>
       </c>
       <c r="H122" t="n">
         <v>45027</v>
@@ -3936,7 +3936,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G123" t="n">
-        <v>15.9570827484131</v>
+        <v>15.9570808410645</v>
       </c>
       <c r="H123" t="n">
         <v>25684</v>
@@ -3965,7 +3965,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G124" t="n">
-        <v>14.9849843978882</v>
+        <v>14.9849834442139</v>
       </c>
       <c r="H124" t="n">
         <v>97441</v>
@@ -3994,7 +3994,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G125" t="n">
-        <v>14.4530801773071</v>
+        <v>14.4530811309814</v>
       </c>
       <c r="H125" t="n">
         <v>58086</v>
@@ -4023,7 +4023,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G126" t="n">
-        <v>14.8841047286987</v>
+        <v>14.8841037750244</v>
       </c>
       <c r="H126" t="n">
         <v>70918</v>
@@ -4052,7 +4052,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G127" t="n">
-        <v>14.5264453887939</v>
+        <v>14.5264463424683</v>
       </c>
       <c r="H127" t="n">
         <v>39264</v>
@@ -4081,7 +4081,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G128" t="n">
-        <v>14.6823472976685</v>
+        <v>14.6823482513428</v>
       </c>
       <c r="H128" t="n">
         <v>26403</v>
@@ -4110,7 +4110,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G129" t="n">
-        <v>15.4068365097046</v>
+        <v>15.4068355560303</v>
       </c>
       <c r="H129" t="n">
         <v>31770</v>
@@ -4139,7 +4139,7 @@
         <v>16.3899993896484</v>
       </c>
       <c r="G130" t="n">
-        <v>15.030837059021</v>
+        <v>15.0308361053467</v>
       </c>
       <c r="H130" t="n">
         <v>43988</v>
@@ -4197,7 +4197,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G132" t="n">
-        <v>14.0037136077881</v>
+        <v>14.0037145614624</v>
       </c>
       <c r="H132" t="n">
         <v>106495</v>
@@ -4284,7 +4284,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G135" t="n">
-        <v>15.3976678848267</v>
+        <v>15.397668838501</v>
       </c>
       <c r="H135" t="n">
         <v>37687</v>
@@ -4313,7 +4313,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>15.315128326416</v>
+        <v>15.315131187439</v>
       </c>
       <c r="H136" t="n">
         <v>66703</v>
@@ -4342,7 +4342,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>15.2234239578247</v>
+        <v>15.2234210968018</v>
       </c>
       <c r="H137" t="n">
         <v>26494</v>
@@ -4371,7 +4371,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>15.4985456466675</v>
+        <v>15.4985437393188</v>
       </c>
       <c r="H138" t="n">
         <v>25530</v>
@@ -4400,7 +4400,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G139" t="n">
-        <v>15.3518123626709</v>
+        <v>15.3518104553223</v>
       </c>
       <c r="H139" t="n">
         <v>35750</v>
@@ -4429,7 +4429,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G140" t="n">
-        <v>15.315128326416</v>
+        <v>15.315131187439</v>
       </c>
       <c r="H140" t="n">
         <v>16474</v>
@@ -4458,7 +4458,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G141" t="n">
-        <v>15.2509317398071</v>
+        <v>15.2509346008301</v>
       </c>
       <c r="H141" t="n">
         <v>13555</v>
@@ -4487,7 +4487,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G142" t="n">
-        <v>15.3242998123169</v>
+        <v>15.3243007659912</v>
       </c>
       <c r="H142" t="n">
         <v>24507</v>
@@ -4516,7 +4516,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G143" t="n">
-        <v>15.2967891693115</v>
+        <v>15.2967882156372</v>
       </c>
       <c r="H143" t="n">
         <v>24347</v>
@@ -4545,7 +4545,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G144" t="n">
-        <v>15.3793239593506</v>
+        <v>15.3793258666992</v>
       </c>
       <c r="H144" t="n">
         <v>13919</v>
@@ -4574,7 +4574,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>15.4985456466675</v>
+        <v>15.4985437393188</v>
       </c>
       <c r="H145" t="n">
         <v>30704</v>
@@ -4603,7 +4603,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>15.4985456466675</v>
+        <v>15.4985437393188</v>
       </c>
       <c r="H146" t="n">
         <v>31317</v>
@@ -4632,7 +4632,7 @@
         <v>17.5</v>
       </c>
       <c r="G147" t="n">
-        <v>16.0487880706787</v>
+        <v>16.048791885376</v>
       </c>
       <c r="H147" t="n">
         <v>68976</v>
@@ -4661,7 +4661,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G148" t="n">
-        <v>16.2138595581055</v>
+        <v>16.2138614654541</v>
       </c>
       <c r="H148" t="n">
         <v>47178</v>
@@ -4690,7 +4690,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G149" t="n">
-        <v>16.168004989624</v>
+        <v>16.1680068969727</v>
       </c>
       <c r="H149" t="n">
         <v>30727</v>
@@ -4748,7 +4748,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G151" t="n">
-        <v>15.6177654266357</v>
+        <v>15.6177625656128</v>
       </c>
       <c r="H151" t="n">
         <v>37397</v>
@@ -4806,7 +4806,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>15.2234239578247</v>
+        <v>15.2234210968018</v>
       </c>
       <c r="H153" t="n">
         <v>23169</v>
@@ -4835,7 +4835,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G154" t="n">
-        <v>16.1221542358398</v>
+        <v>16.1221561431885</v>
       </c>
       <c r="H154" t="n">
         <v>34140</v>
@@ -4864,7 +4864,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G155" t="n">
-        <v>15.8286914825439</v>
+        <v>15.8286933898926</v>
       </c>
       <c r="H155" t="n">
         <v>9705</v>
@@ -4893,7 +4893,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G156" t="n">
-        <v>16.076301574707</v>
+        <v>16.0762996673584</v>
       </c>
       <c r="H156" t="n">
         <v>10800</v>
@@ -4922,7 +4922,7 @@
         <v>17.5</v>
       </c>
       <c r="G157" t="n">
-        <v>16.0487880706787</v>
+        <v>16.048791885376</v>
       </c>
       <c r="H157" t="n">
         <v>8450</v>
@@ -4980,7 +4980,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G159" t="n">
-        <v>16.1038131713867</v>
+        <v>16.1038150787354</v>
       </c>
       <c r="H159" t="n">
         <v>40283</v>
@@ -5009,7 +5009,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G160" t="n">
-        <v>15.84703540802</v>
+        <v>15.8470325469971</v>
       </c>
       <c r="H160" t="n">
         <v>34139</v>
@@ -5038,7 +5038,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G161" t="n">
-        <v>16.0671291351318</v>
+        <v>16.0671272277832</v>
       </c>
       <c r="H161" t="n">
         <v>32087</v>
@@ -5067,7 +5067,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G162" t="n">
-        <v>15.9845914840698</v>
+        <v>15.9845924377441</v>
       </c>
       <c r="H162" t="n">
         <v>27116</v>
@@ -5096,7 +5096,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>16.4156188964844</v>
+        <v>16.4156169891357</v>
       </c>
       <c r="H163" t="n">
         <v>33297</v>
@@ -5154,7 +5154,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G165" t="n">
-        <v>16.8099613189697</v>
+        <v>16.8099594116211</v>
       </c>
       <c r="H165" t="n">
         <v>28597</v>
@@ -5183,7 +5183,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G166" t="n">
-        <v>16.8099613189697</v>
+        <v>16.8099594116211</v>
       </c>
       <c r="H166" t="n">
         <v>21263</v>
@@ -5241,7 +5241,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G168" t="n">
-        <v>16.874153137207</v>
+        <v>16.8741550445557</v>
       </c>
       <c r="H168" t="n">
         <v>23271</v>
@@ -5270,7 +5270,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G169" t="n">
-        <v>16.6448841094971</v>
+        <v>16.6448822021484</v>
       </c>
       <c r="H169" t="n">
         <v>11997</v>
@@ -5299,7 +5299,7 @@
         <v>18.5</v>
       </c>
       <c r="G170" t="n">
-        <v>16.9658603668213</v>
+        <v>16.9658641815186</v>
       </c>
       <c r="H170" t="n">
         <v>28535</v>
@@ -5328,7 +5328,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G171" t="n">
-        <v>17.6078128814697</v>
+        <v>17.6078109741211</v>
       </c>
       <c r="H171" t="n">
         <v>76322</v>
@@ -5357,7 +5357,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>17.1492786407471</v>
+        <v>17.1492748260498</v>
       </c>
       <c r="H172" t="n">
         <v>36526</v>
@@ -5415,7 +5415,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G174" t="n">
-        <v>17.1584415435791</v>
+        <v>17.158447265625</v>
       </c>
       <c r="H174" t="n">
         <v>31232</v>
@@ -5444,7 +5444,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>17.2868385314941</v>
+        <v>17.2868366241455</v>
       </c>
       <c r="H175" t="n">
         <v>29071</v>
@@ -5473,7 +5473,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.2868385314941</v>
+        <v>17.2868366241455</v>
       </c>
       <c r="H176" t="n">
         <v>30183</v>
@@ -5502,7 +5502,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>17.2868385314941</v>
+        <v>17.2868366241455</v>
       </c>
       <c r="H177" t="n">
         <v>17333</v>
@@ -5531,7 +5531,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G178" t="n">
-        <v>17.4060554504395</v>
+        <v>17.4060573577881</v>
       </c>
       <c r="H178" t="n">
         <v>13916</v>
@@ -5589,7 +5589,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G180" t="n">
-        <v>17.0300579071045</v>
+        <v>17.0300540924072</v>
       </c>
       <c r="H180" t="n">
         <v>9227</v>
@@ -5618,7 +5618,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G181" t="n">
-        <v>17.2226428985596</v>
+        <v>17.2226409912109</v>
       </c>
       <c r="H181" t="n">
         <v>23636</v>
@@ -5647,7 +5647,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G182" t="n">
-        <v>17.4610805511475</v>
+        <v>17.4610824584961</v>
       </c>
       <c r="H182" t="n">
         <v>15383</v>
@@ -5705,7 +5705,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>17.332691192627</v>
+        <v>17.3326892852783</v>
       </c>
       <c r="H184" t="n">
         <v>5983</v>
@@ -5734,7 +5734,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>17.0575675964355</v>
+        <v>17.0575714111328</v>
       </c>
       <c r="H185" t="n">
         <v>9398</v>
@@ -5763,7 +5763,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G186" t="n">
-        <v>16.7457656860352</v>
+        <v>16.7457637786865</v>
       </c>
       <c r="H186" t="n">
         <v>11319</v>
@@ -5792,7 +5792,7 @@
         <v>18.5</v>
       </c>
       <c r="G187" t="n">
-        <v>16.9658603668213</v>
+        <v>16.9658641815186</v>
       </c>
       <c r="H187" t="n">
         <v>39369</v>
@@ -5821,7 +5821,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G188" t="n">
-        <v>17.0300579071045</v>
+        <v>17.0300540924072</v>
       </c>
       <c r="H188" t="n">
         <v>3253</v>
@@ -5850,7 +5850,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G189" t="n">
-        <v>16.7457656860352</v>
+        <v>16.7457637786865</v>
       </c>
       <c r="H189" t="n">
         <v>7874</v>
@@ -5879,7 +5879,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G190" t="n">
-        <v>16.0946407318115</v>
+        <v>16.0946426391602</v>
       </c>
       <c r="H190" t="n">
         <v>57476</v>
@@ -6024,7 +6024,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G195" t="n">
-        <v>15.8286914825439</v>
+        <v>15.8286933898926</v>
       </c>
       <c r="H195" t="n">
         <v>23145</v>
@@ -6053,7 +6053,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G196" t="n">
-        <v>15.9479074478149</v>
+        <v>15.9479093551636</v>
       </c>
       <c r="H196" t="n">
         <v>26230</v>
@@ -6082,7 +6082,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G197" t="n">
-        <v>15.84703540802</v>
+        <v>15.8470325469971</v>
       </c>
       <c r="H197" t="n">
         <v>27826</v>
@@ -6111,7 +6111,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>15.6361055374146</v>
+        <v>15.6361045837402</v>
       </c>
       <c r="H198" t="n">
         <v>38344</v>
@@ -6140,7 +6140,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G199" t="n">
-        <v>15.6636171340942</v>
+        <v>15.6636190414429</v>
       </c>
       <c r="H199" t="n">
         <v>15286</v>
@@ -6169,7 +6169,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>15.4985456466675</v>
+        <v>15.4985437393188</v>
       </c>
       <c r="H200" t="n">
         <v>26596</v>
@@ -6198,7 +6198,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G201" t="n">
-        <v>15.5627365112305</v>
+        <v>15.5627393722534</v>
       </c>
       <c r="H201" t="n">
         <v>28742</v>
@@ -6227,7 +6227,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G202" t="n">
-        <v>15.489372253418</v>
+        <v>15.4893732070923</v>
       </c>
       <c r="H202" t="n">
         <v>13901</v>
@@ -6256,7 +6256,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G203" t="n">
-        <v>15.6085948944092</v>
+        <v>15.6085929870605</v>
       </c>
       <c r="H203" t="n">
         <v>14432</v>
@@ -6285,7 +6285,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>15.6361055374146</v>
+        <v>15.6361045837402</v>
       </c>
       <c r="H204" t="n">
         <v>11898</v>
@@ -6401,7 +6401,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G208" t="n">
-        <v>16.1221542358398</v>
+        <v>16.1221561431885</v>
       </c>
       <c r="H208" t="n">
         <v>32129</v>
@@ -6430,7 +6430,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G209" t="n">
-        <v>16.6999111175537</v>
+        <v>16.6999092102051</v>
       </c>
       <c r="H209" t="n">
         <v>33802</v>
@@ -6517,7 +6517,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G212" t="n">
-        <v>15.5443964004517</v>
+        <v>15.5443983078003</v>
       </c>
       <c r="H212" t="n">
         <v>15697</v>
@@ -6546,7 +6546,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G213" t="n">
-        <v>15.7003011703491</v>
+        <v>15.7003030776978</v>
       </c>
       <c r="H213" t="n">
         <v>29571</v>
@@ -6575,7 +6575,7 @@
         <v>17</v>
       </c>
       <c r="G214" t="n">
-        <v>15.5902509689331</v>
+        <v>15.5902500152588</v>
       </c>
       <c r="H214" t="n">
         <v>9819</v>
@@ -6604,7 +6604,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>15.5443964004517</v>
+        <v>15.5443983078003</v>
       </c>
       <c r="H215" t="n">
         <v>10667</v>
@@ -6633,7 +6633,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>15.4068365097046</v>
+        <v>15.4068355560303</v>
       </c>
       <c r="H216" t="n">
         <v>23788</v>
@@ -6691,7 +6691,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G218" t="n">
-        <v>15.1592264175415</v>
+        <v>15.1592283248901</v>
       </c>
       <c r="H218" t="n">
         <v>13732</v>
@@ -6720,7 +6720,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G219" t="n">
-        <v>15.2330417633057</v>
+        <v>15.2330408096313</v>
       </c>
       <c r="H219" t="n">
         <v>15710</v>
@@ -6749,7 +6749,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G220" t="n">
-        <v>15.3068532943726</v>
+        <v>15.3068513870239</v>
       </c>
       <c r="H220" t="n">
         <v>5766</v>
@@ -6778,7 +6778,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>15.5467414855957</v>
+        <v>15.54674243927</v>
       </c>
       <c r="H221" t="n">
         <v>22485</v>
@@ -6807,7 +6807,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G222" t="n">
-        <v>15.6297826766968</v>
+        <v>15.6297817230225</v>
       </c>
       <c r="H222" t="n">
         <v>22396</v>
@@ -6865,7 +6865,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G224" t="n">
-        <v>15.5190649032593</v>
+        <v>15.5190629959106</v>
       </c>
       <c r="H224" t="n">
         <v>12930</v>
@@ -6894,7 +6894,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G225" t="n">
-        <v>14.9746961593628</v>
+        <v>14.9746952056885</v>
       </c>
       <c r="H225" t="n">
         <v>22272</v>
@@ -6981,7 +6981,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G228" t="n">
-        <v>15.4083433151245</v>
+        <v>15.4083452224731</v>
       </c>
       <c r="H228" t="n">
         <v>7063</v>
@@ -7010,7 +7010,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G229" t="n">
-        <v>15.0577363967896</v>
+        <v>15.0577354431152</v>
       </c>
       <c r="H229" t="n">
         <v>21791</v>
@@ -7039,7 +7039,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G230" t="n">
-        <v>15.7589530944824</v>
+        <v>15.7589550018311</v>
       </c>
       <c r="H230" t="n">
         <v>26262</v>
@@ -7068,7 +7068,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G231" t="n">
-        <v>16.2202777862549</v>
+        <v>16.2202816009521</v>
       </c>
       <c r="H231" t="n">
         <v>47333</v>
@@ -7097,7 +7097,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G232" t="n">
-        <v>15.8235387802124</v>
+        <v>15.823540687561</v>
       </c>
       <c r="H232" t="n">
         <v>10075</v>
@@ -7126,7 +7126,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>15.3898944854736</v>
+        <v>15.3898935317993</v>
       </c>
       <c r="H233" t="n">
         <v>13313</v>
@@ -7184,7 +7184,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G235" t="n">
-        <v>15.2145862579346</v>
+        <v>15.2145872116089</v>
       </c>
       <c r="H235" t="n">
         <v>15151</v>
@@ -7213,7 +7213,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G236" t="n">
-        <v>15.7774066925049</v>
+        <v>15.7774057388306</v>
       </c>
       <c r="H236" t="n">
         <v>26797</v>
@@ -7242,7 +7242,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G237" t="n">
-        <v>15.9434852600098</v>
+        <v>15.9434833526611</v>
       </c>
       <c r="H237" t="n">
         <v>20608</v>
@@ -7271,7 +7271,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G238" t="n">
-        <v>15.8235387802124</v>
+        <v>15.823540687561</v>
       </c>
       <c r="H238" t="n">
         <v>32816</v>
@@ -7329,7 +7329,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G240" t="n">
-        <v>16.2202777862549</v>
+        <v>16.2202816009521</v>
       </c>
       <c r="H240" t="n">
         <v>17938</v>
@@ -7358,7 +7358,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G241" t="n">
-        <v>16.4693965911865</v>
+        <v>16.4693984985352</v>
       </c>
       <c r="H241" t="n">
         <v>43580</v>
@@ -7387,7 +7387,7 @@
         <v>18.5</v>
       </c>
       <c r="G242" t="n">
-        <v>17.0691223144531</v>
+        <v>17.0691242218018</v>
       </c>
       <c r="H242" t="n">
         <v>48602</v>
@@ -7416,7 +7416,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G243" t="n">
-        <v>17.1429347991943</v>
+        <v>17.1429386138916</v>
       </c>
       <c r="H243" t="n">
         <v>41612</v>
@@ -7474,7 +7474,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G245" t="n">
-        <v>17.106029510498</v>
+        <v>17.1060352325439</v>
       </c>
       <c r="H245" t="n">
         <v>36816</v>
@@ -7590,7 +7590,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>16.9768562316895</v>
+        <v>16.9768600463867</v>
       </c>
       <c r="H249" t="n">
         <v>27486</v>
@@ -7619,7 +7619,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>16.792329788208</v>
+        <v>16.7923278808594</v>
       </c>
       <c r="H250" t="n">
         <v>17496</v>
@@ -7648,7 +7648,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G251" t="n">
-        <v>17.0506706237793</v>
+        <v>17.0506687164307</v>
       </c>
       <c r="H251" t="n">
         <v>30246</v>
@@ -7677,7 +7677,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>17.6227207183838</v>
+        <v>17.6227188110352</v>
       </c>
       <c r="H252" t="n">
         <v>152617</v>
@@ -7735,7 +7735,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>17.6227207183838</v>
+        <v>17.6227188110352</v>
       </c>
       <c r="H254" t="n">
         <v>33338</v>
@@ -7764,7 +7764,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G255" t="n">
-        <v>17.8164730072021</v>
+        <v>17.8164749145508</v>
       </c>
       <c r="H255" t="n">
         <v>30009</v>
@@ -7793,7 +7793,7 @@
         <v>19.25</v>
       </c>
       <c r="G256" t="n">
-        <v>17.7611141204834</v>
+        <v>17.761116027832</v>
       </c>
       <c r="H256" t="n">
         <v>19342</v>
@@ -7822,7 +7822,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G257" t="n">
-        <v>17.8164730072021</v>
+        <v>17.8164749145508</v>
       </c>
       <c r="H257" t="n">
         <v>21070</v>
@@ -7851,7 +7851,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G258" t="n">
-        <v>18.3054809570312</v>
+        <v>18.3054828643799</v>
       </c>
       <c r="H258" t="n">
         <v>77282</v>
@@ -7880,7 +7880,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>18.7760391235352</v>
+        <v>18.7760353088379</v>
       </c>
       <c r="H259" t="n">
         <v>73997</v>
@@ -8025,7 +8025,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G264" t="n">
-        <v>18.7852630615234</v>
+        <v>18.7852649688721</v>
       </c>
       <c r="H264" t="n">
         <v>61276</v>
@@ -8054,7 +8054,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>19.3296279907227</v>
+        <v>19.3296298980713</v>
       </c>
       <c r="H265" t="n">
         <v>75197</v>
@@ -8083,7 +8083,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G266" t="n">
-        <v>19.2004566192627</v>
+        <v>19.2004585266113</v>
       </c>
       <c r="H266" t="n">
         <v>44437</v>
@@ -8170,7 +8170,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>18.7299022674561</v>
+        <v>18.7299041748047</v>
       </c>
       <c r="H269" t="n">
         <v>28479</v>
@@ -8199,7 +8199,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G270" t="n">
-        <v>18.8867492675781</v>
+        <v>18.886754989624</v>
       </c>
       <c r="H270" t="n">
         <v>22743</v>
@@ -8228,7 +8228,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G271" t="n">
-        <v>18.8129386901855</v>
+        <v>18.8129405975342</v>
       </c>
       <c r="H271" t="n">
         <v>18271</v>
@@ -8257,7 +8257,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G272" t="n">
-        <v>18.8037128448486</v>
+        <v>18.8037147521973</v>
       </c>
       <c r="H272" t="n">
         <v>21264</v>
@@ -8286,7 +8286,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G273" t="n">
-        <v>18.6284103393555</v>
+        <v>18.6284122467041</v>
       </c>
       <c r="H273" t="n">
         <v>23196</v>
@@ -8315,7 +8315,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>18.7299022674561</v>
+        <v>18.7299041748047</v>
       </c>
       <c r="H274" t="n">
         <v>12986</v>
@@ -8344,7 +8344,7 @@
         <v>20</v>
       </c>
       <c r="G275" t="n">
-        <v>18.4531059265137</v>
+        <v>18.453104019165</v>
       </c>
       <c r="H275" t="n">
         <v>31211</v>
@@ -8373,7 +8373,7 @@
         <v>20</v>
       </c>
       <c r="G276" t="n">
-        <v>18.4531059265137</v>
+        <v>18.453104019165</v>
       </c>
       <c r="H276" t="n">
         <v>13518</v>
@@ -8402,7 +8402,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G277" t="n">
-        <v>18.2778015136719</v>
+        <v>18.2777996063232</v>
       </c>
       <c r="H277" t="n">
         <v>19746</v>
@@ -8431,7 +8431,7 @@
         <v>19.5</v>
       </c>
       <c r="G278" t="n">
-        <v>17.9917755126953</v>
+        <v>17.9917793273926</v>
       </c>
       <c r="H278" t="n">
         <v>16008</v>
@@ -8460,7 +8460,7 @@
         <v>19.8700008392334</v>
       </c>
       <c r="G279" t="n">
-        <v>18.3331642150879</v>
+        <v>18.3331623077393</v>
       </c>
       <c r="H279" t="n">
         <v>20550</v>
@@ -8489,7 +8489,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G280" t="n">
-        <v>18.4069728851318</v>
+        <v>18.4069747924805</v>
       </c>
       <c r="H280" t="n">
         <v>20999</v>
@@ -8518,7 +8518,7 @@
         <v>20</v>
       </c>
       <c r="G281" t="n">
-        <v>18.4531059265137</v>
+        <v>18.453104019165</v>
       </c>
       <c r="H281" t="n">
         <v>8343</v>
@@ -8576,7 +8576,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G283" t="n">
-        <v>18.2501239776611</v>
+        <v>18.2501220703125</v>
       </c>
       <c r="H283" t="n">
         <v>9926</v>
@@ -8634,7 +8634,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G285" t="n">
-        <v>18.1578578948975</v>
+        <v>18.1578598022461</v>
       </c>
       <c r="H285" t="n">
         <v>31091</v>
@@ -8663,7 +8663,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G286" t="n">
-        <v>18.2039890289307</v>
+        <v>18.2039909362793</v>
       </c>
       <c r="H286" t="n">
         <v>18360</v>
@@ -8721,7 +8721,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G288" t="n">
-        <v>18.388521194458</v>
+        <v>18.3885231018066</v>
       </c>
       <c r="H288" t="n">
         <v>13551</v>
@@ -8750,7 +8750,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G289" t="n">
-        <v>18.49001121521</v>
+        <v>18.4900150299072</v>
       </c>
       <c r="H289" t="n">
         <v>58575</v>
@@ -8779,7 +8779,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G290" t="n">
-        <v>18.4992389678955</v>
+        <v>18.4992408752441</v>
       </c>
       <c r="H290" t="n">
         <v>19035</v>
@@ -8837,7 +8837,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G292" t="n">
-        <v>18.6007328033447</v>
+        <v>18.6007308959961</v>
       </c>
       <c r="H292" t="n">
         <v>13563</v>
@@ -8866,7 +8866,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G293" t="n">
-        <v>18.7299022674561</v>
+        <v>18.7299041748047</v>
       </c>
       <c r="H293" t="n">
         <v>11363</v>
@@ -8895,7 +8895,7 @@
         <v>20</v>
       </c>
       <c r="G294" t="n">
-        <v>18.4531059265137</v>
+        <v>18.453104019165</v>
       </c>
       <c r="H294" t="n">
         <v>41413</v>
@@ -8924,7 +8924,7 @@
         <v>20.5</v>
       </c>
       <c r="G295" t="n">
-        <v>18.9144344329834</v>
+        <v>18.9144325256348</v>
       </c>
       <c r="H295" t="n">
         <v>52583</v>
@@ -8953,7 +8953,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>19.2834949493408</v>
+        <v>19.2834968566895</v>
       </c>
       <c r="H296" t="n">
         <v>49075</v>
@@ -9011,7 +9011,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>18.9974746704102</v>
+        <v>18.9974765777588</v>
       </c>
       <c r="H298" t="n">
         <v>7716</v>
@@ -9127,7 +9127,7 @@
         <v>20.4099998474121</v>
       </c>
       <c r="G302" t="n">
-        <v>18.8313961029053</v>
+        <v>18.8313941955566</v>
       </c>
       <c r="H302" t="n">
         <v>18297</v>
@@ -9156,7 +9156,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G303" t="n">
-        <v>19.1174163818359</v>
+        <v>19.1174182891846</v>
       </c>
       <c r="H303" t="n">
         <v>14235</v>
@@ -9185,7 +9185,7 @@
         <v>21</v>
       </c>
       <c r="G304" t="n">
-        <v>19.3757629394531</v>
+        <v>19.3757610321045</v>
       </c>
       <c r="H304" t="n">
         <v>41845</v>
@@ -9214,7 +9214,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G305" t="n">
-        <v>18.9697933197021</v>
+        <v>18.9697952270508</v>
       </c>
       <c r="H305" t="n">
         <v>78089</v>
@@ -9272,7 +9272,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G307" t="n">
-        <v>19.1174163818359</v>
+        <v>19.1174182891846</v>
       </c>
       <c r="H307" t="n">
         <v>19679</v>
@@ -9301,7 +9301,7 @@
         <v>20.8299999237061</v>
       </c>
       <c r="G308" t="n">
-        <v>19.2189083099365</v>
+        <v>19.2189102172852</v>
       </c>
       <c r="H308" t="n">
         <v>37137</v>
@@ -9388,7 +9388,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G311" t="n">
-        <v>19.2558212280273</v>
+        <v>19.2558174133301</v>
       </c>
       <c r="H311" t="n">
         <v>45882</v>
@@ -9417,7 +9417,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G312" t="n">
-        <v>19.1543254852295</v>
+        <v>19.1543273925781</v>
       </c>
       <c r="H312" t="n">
         <v>56794</v>
@@ -9446,7 +9446,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G313" t="n">
-        <v>19.7817325592041</v>
+        <v>19.7817287445068</v>
       </c>
       <c r="H313" t="n">
         <v>66148</v>
@@ -9533,7 +9533,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>20.4829502105713</v>
+        <v>20.482946395874</v>
       </c>
       <c r="H316" t="n">
         <v>56950</v>
@@ -9562,7 +9562,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>20.7136116027832</v>
+        <v>20.7136135101318</v>
       </c>
       <c r="H317" t="n">
         <v>83576</v>
@@ -9591,7 +9591,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G318" t="n">
-        <v>20.8243312835693</v>
+        <v>20.8243293762207</v>
       </c>
       <c r="H318" t="n">
         <v>64884</v>
@@ -9678,7 +9678,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G321" t="n">
-        <v>20.4737205505371</v>
+        <v>20.4737224578857</v>
       </c>
       <c r="H321" t="n">
         <v>30324</v>
@@ -9823,7 +9823,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G326" t="n">
-        <v>20.4644947052002</v>
+        <v>20.4644966125488</v>
       </c>
       <c r="H326" t="n">
         <v>39266</v>
@@ -9852,7 +9852,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G327" t="n">
-        <v>20.4829502105713</v>
+        <v>20.482946395874</v>
       </c>
       <c r="H327" t="n">
         <v>49295</v>
@@ -9881,7 +9881,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G328" t="n">
-        <v>20.3630027770996</v>
+        <v>20.3630046844482</v>
       </c>
       <c r="H328" t="n">
         <v>14357</v>
@@ -9910,7 +9910,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>20.3906841278076</v>
+        <v>20.390682220459</v>
       </c>
       <c r="H329" t="n">
         <v>45217</v>
@@ -9997,7 +9997,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>20.3906841278076</v>
+        <v>20.390682220459</v>
       </c>
       <c r="H332" t="n">
         <v>92155</v>
@@ -10084,7 +10084,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G335" t="n">
-        <v>20.316873550415</v>
+        <v>20.3168754577637</v>
       </c>
       <c r="H335" t="n">
         <v>75417</v>
@@ -10113,7 +10113,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G336" t="n">
-        <v>20.6398029327393</v>
+        <v>20.6398010253906</v>
       </c>
       <c r="H336" t="n">
         <v>121977</v>
@@ -10171,7 +10171,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G338" t="n">
-        <v>21.3502426147461</v>
+        <v>21.3502407073975</v>
       </c>
       <c r="H338" t="n">
         <v>136741</v>
@@ -10200,7 +10200,7 @@
         <v>23</v>
       </c>
       <c r="G339" t="n">
-        <v>21.2210731506348</v>
+        <v>21.2210693359375</v>
       </c>
       <c r="H339" t="n">
         <v>48402</v>
@@ -10258,7 +10258,7 @@
         <v>23</v>
       </c>
       <c r="G341" t="n">
-        <v>21.2210731506348</v>
+        <v>21.2210693359375</v>
       </c>
       <c r="H341" t="n">
         <v>97968</v>
@@ -10287,7 +10287,7 @@
         <v>22.75</v>
       </c>
       <c r="G342" t="n">
-        <v>20.9904098510742</v>
+        <v>20.9904079437256</v>
       </c>
       <c r="H342" t="n">
         <v>60557</v>
@@ -10374,7 +10374,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G345" t="n">
-        <v>20.787425994873</v>
+        <v>20.7874240875244</v>
       </c>
       <c r="H345" t="n">
         <v>61532</v>
@@ -10548,7 +10548,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G351" t="n">
-        <v>21.0826740264893</v>
+        <v>21.0826759338379</v>
       </c>
       <c r="H351" t="n">
         <v>85673</v>
@@ -10577,7 +10577,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G352" t="n">
-        <v>20.5013999938965</v>
+        <v>20.5014038085938</v>
       </c>
       <c r="H352" t="n">
         <v>36212</v>
@@ -10606,7 +10606,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G353" t="n">
-        <v>20.4829502105713</v>
+        <v>20.482946395874</v>
       </c>
       <c r="H353" t="n">
         <v>64595</v>
@@ -10635,7 +10635,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G354" t="n">
-        <v>21.0273189544678</v>
+        <v>21.0273170471191</v>
       </c>
       <c r="H354" t="n">
         <v>34712</v>
@@ -10751,7 +10751,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G358" t="n">
-        <v>21.1011257171631</v>
+        <v>21.1011276245117</v>
       </c>
       <c r="H358" t="n">
         <v>30676</v>
@@ -10780,7 +10780,7 @@
         <v>22.9699993133545</v>
       </c>
       <c r="G359" t="n">
-        <v>21.1933917999268</v>
+        <v>21.1933937072754</v>
       </c>
       <c r="H359" t="n">
         <v>26057</v>
@@ -10867,7 +10867,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G362" t="n">
-        <v>20.7136116027832</v>
+        <v>20.7136135101318</v>
       </c>
       <c r="H362" t="n">
         <v>38496</v>
@@ -10925,7 +10925,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>21.0365409851074</v>
+        <v>21.0365428924561</v>
       </c>
       <c r="H364" t="n">
         <v>12994</v>
@@ -10954,7 +10954,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G365" t="n">
-        <v>20.5936660766602</v>
+        <v>20.5936679840088</v>
       </c>
       <c r="H365" t="n">
         <v>10995</v>
@@ -10983,7 +10983,7 @@
         <v>21.8700008392334</v>
       </c>
       <c r="G366" t="n">
-        <v>20.1784725189209</v>
+        <v>20.1784706115723</v>
       </c>
       <c r="H366" t="n">
         <v>35698</v>
@@ -11070,7 +11070,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G369" t="n">
-        <v>20.5013999938965</v>
+        <v>20.5014038085938</v>
       </c>
       <c r="H369" t="n">
         <v>57155</v>
@@ -11099,7 +11099,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G370" t="n">
-        <v>20.1876983642578</v>
+        <v>20.1876964569092</v>
       </c>
       <c r="H370" t="n">
         <v>20027</v>
@@ -11157,7 +11157,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G372" t="n">
-        <v>20.5936660766602</v>
+        <v>20.5936679840088</v>
       </c>
       <c r="H372" t="n">
         <v>16168</v>
@@ -11244,7 +11244,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G375" t="n">
-        <v>20.0769786834717</v>
+        <v>20.0769805908203</v>
       </c>
       <c r="H375" t="n">
         <v>8785</v>
@@ -11273,7 +11273,7 @@
         <v>21.3099994659424</v>
       </c>
       <c r="G376" t="n">
-        <v>19.6617832183838</v>
+        <v>19.6617851257324</v>
       </c>
       <c r="H376" t="n">
         <v>17186</v>
@@ -11331,7 +11331,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G378" t="n">
-        <v>20.1323394775391</v>
+        <v>20.1323375701904</v>
       </c>
       <c r="H378" t="n">
         <v>16830</v>
@@ -11418,7 +11418,7 @@
         <v>21.8700008392334</v>
       </c>
       <c r="G381" t="n">
-        <v>20.1784725189209</v>
+        <v>20.1784706115723</v>
       </c>
       <c r="H381" t="n">
         <v>33656</v>
@@ -11447,7 +11447,7 @@
         <v>22</v>
       </c>
       <c r="G382" t="n">
-        <v>20.2984180450439</v>
+        <v>20.2984161376953</v>
       </c>
       <c r="H382" t="n">
         <v>12653</v>
@@ -11476,7 +11476,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>19.8186359405518</v>
+        <v>19.8186340332031</v>
       </c>
       <c r="H383" t="n">
         <v>20249</v>
@@ -11505,7 +11505,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>19.6986923217773</v>
+        <v>19.6986904144287</v>
       </c>
       <c r="H384" t="n">
         <v>15447</v>
@@ -11563,7 +11563,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G386" t="n">
-        <v>19.5879726409912</v>
+        <v>19.5879764556885</v>
       </c>
       <c r="H386" t="n">
         <v>50642</v>
@@ -11592,7 +11592,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>19.790958404541</v>
+        <v>19.7909603118896</v>
       </c>
       <c r="H387" t="n">
         <v>13573</v>
@@ -11650,7 +11650,7 @@
         <v>21.5300006866455</v>
       </c>
       <c r="G389" t="n">
-        <v>19.8647708892822</v>
+        <v>19.8647689819336</v>
       </c>
       <c r="H389" t="n">
         <v>13024</v>
@@ -11679,7 +11679,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>19.9754848480225</v>
+        <v>19.9754886627197</v>
       </c>
       <c r="H390" t="n">
         <v>31020</v>
@@ -11708,7 +11708,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G391" t="n">
-        <v>19.5418395996094</v>
+        <v>19.541841506958</v>
       </c>
       <c r="H391" t="n">
         <v>12916</v>
@@ -11737,7 +11737,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>19.9754848480225</v>
+        <v>19.9754886627197</v>
       </c>
       <c r="H392" t="n">
         <v>34425</v>
@@ -11795,7 +11795,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G394" t="n">
-        <v>20.4737205505371</v>
+        <v>20.4737224578857</v>
       </c>
       <c r="H394" t="n">
         <v>6844</v>
@@ -11824,7 +11824,7 @@
         <v>22.25</v>
       </c>
       <c r="G395" t="n">
-        <v>20.5290851593018</v>
+        <v>20.5290794372559</v>
       </c>
       <c r="H395" t="n">
         <v>32303</v>
@@ -11853,7 +11853,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G396" t="n">
-        <v>20.0769786834717</v>
+        <v>20.0769805908203</v>
       </c>
       <c r="H396" t="n">
         <v>38946</v>
@@ -11911,7 +11911,7 @@
         <v>21.7900009155273</v>
       </c>
       <c r="G398" t="n">
-        <v>20.1046600341797</v>
+        <v>20.1046581268311</v>
       </c>
       <c r="H398" t="n">
         <v>30566</v>
@@ -11969,7 +11969,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G400" t="n">
-        <v>19.790958404541</v>
+        <v>19.7909603118896</v>
       </c>
       <c r="H400" t="n">
         <v>14656</v>
@@ -12027,7 +12027,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G402" t="n">
-        <v>19.6986923217773</v>
+        <v>19.6986904144287</v>
       </c>
       <c r="H402" t="n">
         <v>18860</v>
@@ -12056,7 +12056,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>19.6986923217773</v>
+        <v>19.6986904144287</v>
       </c>
       <c r="H403" t="n">
         <v>21085</v>
@@ -12114,7 +12114,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G405" t="n">
-        <v>20.0769786834717</v>
+        <v>20.0769805908203</v>
       </c>
       <c r="H405" t="n">
         <v>39480</v>
@@ -12201,7 +12201,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>20.2799682617188</v>
+        <v>20.2799644470215</v>
       </c>
       <c r="H408" t="n">
         <v>18657</v>
@@ -12230,7 +12230,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G409" t="n">
-        <v>19.9939403533936</v>
+        <v>19.9939422607422</v>
       </c>
       <c r="H409" t="n">
         <v>12488</v>
@@ -12317,7 +12317,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G412" t="n">
-        <v>20.6398029327393</v>
+        <v>20.6398010253906</v>
       </c>
       <c r="H412" t="n">
         <v>33356</v>
@@ -12346,7 +12346,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G413" t="n">
-        <v>20.7043876647949</v>
+        <v>20.7043857574463</v>
       </c>
       <c r="H413" t="n">
         <v>28346</v>
@@ -12375,7 +12375,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G414" t="n">
-        <v>20.2061538696289</v>
+        <v>20.2061500549316</v>
       </c>
       <c r="H414" t="n">
         <v>22878</v>
@@ -12404,7 +12404,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G415" t="n">
-        <v>20.7043876647949</v>
+        <v>20.7043857574463</v>
       </c>
       <c r="H415" t="n">
         <v>7332</v>
@@ -12433,7 +12433,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G416" t="n">
-        <v>20.4275875091553</v>
+        <v>20.4275894165039</v>
       </c>
       <c r="H416" t="n">
         <v>26649</v>
@@ -12462,7 +12462,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G417" t="n">
-        <v>20.7505168914795</v>
+        <v>20.7505187988281</v>
       </c>
       <c r="H417" t="n">
         <v>77812</v>
@@ -12491,7 +12491,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G418" t="n">
-        <v>20.8243312835693</v>
+        <v>20.8243293762207</v>
       </c>
       <c r="H418" t="n">
         <v>45486</v>
@@ -12520,7 +12520,7 @@
         <v>22.75</v>
       </c>
       <c r="G419" t="n">
-        <v>20.9904098510742</v>
+        <v>20.9904079437256</v>
       </c>
       <c r="H419" t="n">
         <v>29090</v>
@@ -12549,7 +12549,7 @@
         <v>22.75</v>
       </c>
       <c r="G420" t="n">
-        <v>20.9904098510742</v>
+        <v>20.9904079437256</v>
       </c>
       <c r="H420" t="n">
         <v>18248</v>
@@ -12578,7 +12578,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G421" t="n">
-        <v>21.0549964904785</v>
+        <v>21.0549945831299</v>
       </c>
       <c r="H421" t="n">
         <v>29792</v>
@@ -12607,7 +12607,7 @@
         <v>22.75</v>
       </c>
       <c r="G422" t="n">
-        <v>20.9904098510742</v>
+        <v>20.9904079437256</v>
       </c>
       <c r="H422" t="n">
         <v>42047</v>
@@ -12636,7 +12636,7 @@
         <v>22.3099994659424</v>
       </c>
       <c r="G423" t="n">
-        <v>20.5844383239746</v>
+        <v>20.5844402313232</v>
       </c>
       <c r="H423" t="n">
         <v>22154</v>
@@ -12723,7 +12723,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>20.3906841278076</v>
+        <v>20.390682220459</v>
       </c>
       <c r="H426" t="n">
         <v>20664</v>
@@ -12897,7 +12897,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G432" t="n">
-        <v>20.2338314056396</v>
+        <v>20.2338352203369</v>
       </c>
       <c r="H432" t="n">
         <v>15469</v>
@@ -12955,7 +12955,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>19.7448215484619</v>
+        <v>19.7448234558105</v>
       </c>
       <c r="H434" t="n">
         <v>11290</v>
@@ -12984,7 +12984,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>19.790958404541</v>
+        <v>19.7909603118896</v>
       </c>
       <c r="H435" t="n">
         <v>27283</v>
@@ -13042,7 +13042,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G437" t="n">
-        <v>19.6341075897217</v>
+        <v>19.634105682373</v>
       </c>
       <c r="H437" t="n">
         <v>26660</v>
@@ -13071,7 +13071,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>19.3296279907227</v>
+        <v>19.3296298980713</v>
       </c>
       <c r="H438" t="n">
         <v>40010</v>
@@ -13100,7 +13100,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G439" t="n">
-        <v>19.7817325592041</v>
+        <v>19.7817287445068</v>
       </c>
       <c r="H439" t="n">
         <v>24594</v>
@@ -13129,7 +13129,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G440" t="n">
-        <v>19.8463191986084</v>
+        <v>19.8463172912598</v>
       </c>
       <c r="H440" t="n">
         <v>25567</v>
@@ -13158,7 +13158,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G441" t="n">
-        <v>19.9570369720459</v>
+        <v>19.9570331573486</v>
       </c>
       <c r="H441" t="n">
         <v>33947</v>
@@ -13187,7 +13187,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G442" t="n">
-        <v>20.2061538696289</v>
+        <v>20.2061500549316</v>
       </c>
       <c r="H442" t="n">
         <v>26218</v>
@@ -13245,7 +13245,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G444" t="n">
-        <v>20.4644947052002</v>
+        <v>20.4644966125488</v>
       </c>
       <c r="H444" t="n">
         <v>13574</v>
@@ -13274,7 +13274,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G445" t="n">
-        <v>20.316873550415</v>
+        <v>20.3168754577637</v>
       </c>
       <c r="H445" t="n">
         <v>15949</v>
@@ -13332,7 +13332,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G447" t="n">
-        <v>20.2799682617188</v>
+        <v>20.2799644470215</v>
       </c>
       <c r="H447" t="n">
         <v>25474</v>
@@ -13361,7 +13361,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>20.3906841278076</v>
+        <v>20.390682220459</v>
       </c>
       <c r="H448" t="n">
         <v>28763</v>
@@ -13390,7 +13390,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>20.3906841278076</v>
+        <v>20.390682220459</v>
       </c>
       <c r="H449" t="n">
         <v>29103</v>
@@ -13419,7 +13419,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G450" t="n">
-        <v>20.3814582824707</v>
+        <v>20.3814544677734</v>
       </c>
       <c r="H450" t="n">
         <v>7845</v>
@@ -13448,7 +13448,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G451" t="n">
-        <v>19.8555431365967</v>
+        <v>19.8555450439453</v>
       </c>
       <c r="H451" t="n">
         <v>36507</v>
@@ -13506,7 +13506,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G453" t="n">
-        <v>19.4034404754639</v>
+        <v>19.4034442901611</v>
       </c>
       <c r="H453" t="n">
         <v>67115</v>
@@ -13622,7 +13622,7 @@
         <v>20.5</v>
       </c>
       <c r="G457" t="n">
-        <v>18.9144344329834</v>
+        <v>18.9144325256348</v>
       </c>
       <c r="H457" t="n">
         <v>9845</v>
@@ -13651,7 +13651,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G458" t="n">
-        <v>18.9974746704102</v>
+        <v>18.9974765777588</v>
       </c>
       <c r="H458" t="n">
         <v>17708</v>
@@ -13680,7 +13680,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G459" t="n">
-        <v>18.6560916900635</v>
+        <v>18.6560878753662</v>
       </c>
       <c r="H459" t="n">
         <v>29725</v>
@@ -13709,7 +13709,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G460" t="n">
-        <v>18.8129386901855</v>
+        <v>18.8129405975342</v>
       </c>
       <c r="H460" t="n">
         <v>29832</v>
@@ -13738,7 +13738,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G461" t="n">
-        <v>18.7114524841309</v>
+        <v>18.7114505767822</v>
       </c>
       <c r="H461" t="n">
         <v>16803</v>
@@ -13796,7 +13796,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G463" t="n">
-        <v>18.8037128448486</v>
+        <v>18.8037147521973</v>
       </c>
       <c r="H463" t="n">
         <v>15728</v>
@@ -13854,7 +13854,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G465" t="n">
-        <v>18.5545978546143</v>
+        <v>18.5545997619629</v>
       </c>
       <c r="H465" t="n">
         <v>13390</v>
@@ -13912,7 +13912,7 @@
         <v>20.0900001525879</v>
       </c>
       <c r="G467" t="n">
-        <v>18.5361480712891</v>
+        <v>18.5361461639404</v>
       </c>
       <c r="H467" t="n">
         <v>19752</v>
@@ -13970,7 +13970,7 @@
         <v>20.25</v>
       </c>
       <c r="G469" t="n">
-        <v>18.6837692260742</v>
+        <v>18.6837711334229</v>
       </c>
       <c r="H469" t="n">
         <v>15211</v>
@@ -14028,7 +14028,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G471" t="n">
-        <v>19.0067024230957</v>
+        <v>19.0066986083984</v>
       </c>
       <c r="H471" t="n">
         <v>26811</v>
@@ -14057,7 +14057,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G472" t="n">
-        <v>18.8037128448486</v>
+        <v>18.8037147521973</v>
       </c>
       <c r="H472" t="n">
         <v>20881</v>
@@ -14144,7 +14144,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G475" t="n">
-        <v>18.8219413757324</v>
+        <v>18.8219432830811</v>
       </c>
       <c r="H475" t="n">
         <v>22915</v>
@@ -14202,7 +14202,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G477" t="n">
-        <v>18.1821823120117</v>
+        <v>18.1821804046631</v>
       </c>
       <c r="H477" t="n">
         <v>27017</v>
@@ -14231,7 +14231,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G478" t="n">
-        <v>17.7834911346436</v>
+        <v>17.7834892272949</v>
       </c>
       <c r="H478" t="n">
         <v>44382</v>
@@ -14260,7 +14260,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G479" t="n">
-        <v>17.7278594970703</v>
+        <v>17.7278575897217</v>
       </c>
       <c r="H479" t="n">
         <v>19845</v>
@@ -14289,7 +14289,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G480" t="n">
-        <v>17.5238780975342</v>
+        <v>17.5238742828369</v>
       </c>
       <c r="H480" t="n">
         <v>28888</v>
@@ -14318,7 +14318,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G481" t="n">
-        <v>17.5516948699951</v>
+        <v>17.5516929626465</v>
       </c>
       <c r="H481" t="n">
         <v>20865</v>
@@ -14405,7 +14405,7 @@
         <v>19.25</v>
       </c>
       <c r="G484" t="n">
-        <v>17.8483924865723</v>
+        <v>17.8483943939209</v>
       </c>
       <c r="H484" t="n">
         <v>13648</v>
@@ -14434,7 +14434,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G485" t="n">
-        <v>18.1450939178467</v>
+        <v>18.1450958251953</v>
       </c>
       <c r="H485" t="n">
         <v>22132</v>
@@ -14463,7 +14463,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G486" t="n">
-        <v>18.3398017883301</v>
+        <v>18.3398036956787</v>
       </c>
       <c r="H486" t="n">
         <v>15740</v>
@@ -14492,7 +14492,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G487" t="n">
-        <v>18.4603385925293</v>
+        <v>18.4603366851807</v>
       </c>
       <c r="H487" t="n">
         <v>25717</v>
@@ -14521,7 +14521,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G488" t="n">
-        <v>18.2841720581055</v>
+        <v>18.2841701507568</v>
       </c>
       <c r="H488" t="n">
         <v>16673</v>
@@ -14550,7 +14550,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G489" t="n">
-        <v>18.2841720581055</v>
+        <v>18.2841701507568</v>
       </c>
       <c r="H489" t="n">
         <v>17087</v>
@@ -14579,7 +14579,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G490" t="n">
-        <v>18.0431022644043</v>
+        <v>18.0431041717529</v>
       </c>
       <c r="H490" t="n">
         <v>16630</v>
@@ -14608,7 +14608,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G491" t="n">
-        <v>18.1821823120117</v>
+        <v>18.1821804046631</v>
       </c>
       <c r="H491" t="n">
         <v>44994</v>
@@ -14637,7 +14637,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G492" t="n">
-        <v>18.367618560791</v>
+        <v>18.3676166534424</v>
       </c>
       <c r="H492" t="n">
         <v>26139</v>
@@ -14695,7 +14695,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G494" t="n">
-        <v>18.0987377166748</v>
+        <v>18.0987339019775</v>
       </c>
       <c r="H494" t="n">
         <v>9160</v>
@@ -14724,7 +14724,7 @@
         <v>20</v>
       </c>
       <c r="G495" t="n">
-        <v>18.5437850952148</v>
+        <v>18.5437831878662</v>
       </c>
       <c r="H495" t="n">
         <v>21814</v>
@@ -14753,7 +14753,7 @@
         <v>20</v>
       </c>
       <c r="G496" t="n">
-        <v>18.5437850952148</v>
+        <v>18.5437831878662</v>
       </c>
       <c r="H496" t="n">
         <v>15923</v>
@@ -14811,7 +14811,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G498" t="n">
-        <v>18.5716018676758</v>
+        <v>18.5715999603271</v>
       </c>
       <c r="H498" t="n">
         <v>4733</v>
@@ -14869,7 +14869,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G500" t="n">
-        <v>18.488151550293</v>
+        <v>18.4881534576416</v>
       </c>
       <c r="H500" t="n">
         <v>22877</v>
@@ -14898,7 +14898,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G501" t="n">
-        <v>18.2285423278809</v>
+        <v>18.2285385131836</v>
       </c>
       <c r="H501" t="n">
         <v>22558</v>
@@ -14927,7 +14927,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G502" t="n">
-        <v>18.2563591003418</v>
+        <v>18.2563552856445</v>
       </c>
       <c r="H502" t="n">
         <v>30706</v>
@@ -14956,7 +14956,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G503" t="n">
-        <v>18.3212604522705</v>
+        <v>18.3212623596191</v>
       </c>
       <c r="H503" t="n">
         <v>35093</v>
@@ -14985,7 +14985,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>18.3583450317383</v>
+        <v>18.3583469390869</v>
       </c>
       <c r="H504" t="n">
         <v>32349</v>
@@ -15072,7 +15072,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G507" t="n">
-        <v>18.5808734893799</v>
+        <v>18.5808753967285</v>
       </c>
       <c r="H507" t="n">
         <v>24263</v>
@@ -15101,7 +15101,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G508" t="n">
-        <v>18.4696083068848</v>
+        <v>18.469612121582</v>
       </c>
       <c r="H508" t="n">
         <v>19500</v>
@@ -15130,7 +15130,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G509" t="n">
-        <v>18.4696083068848</v>
+        <v>18.469612121582</v>
       </c>
       <c r="H509" t="n">
         <v>9688</v>
@@ -15159,7 +15159,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>18.2656288146973</v>
+        <v>18.2656269073486</v>
       </c>
       <c r="H510" t="n">
         <v>16027</v>
@@ -15188,7 +15188,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G511" t="n">
-        <v>18.367618560791</v>
+        <v>18.3676166534424</v>
       </c>
       <c r="H511" t="n">
         <v>20759</v>
@@ -15246,7 +15246,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G513" t="n">
-        <v>18.3768901824951</v>
+        <v>18.3768920898438</v>
       </c>
       <c r="H513" t="n">
         <v>7196</v>
@@ -15275,7 +15275,7 @@
         <v>20.25</v>
       </c>
       <c r="G514" t="n">
-        <v>18.7755813598633</v>
+        <v>18.7755832672119</v>
       </c>
       <c r="H514" t="n">
         <v>40173</v>
@@ -15362,7 +15362,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>19.6100540161133</v>
+        <v>19.610050201416</v>
       </c>
       <c r="H517" t="n">
         <v>46653</v>
@@ -15420,7 +15420,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G519" t="n">
-        <v>21.13991355896</v>
+        <v>21.1399154663086</v>
       </c>
       <c r="H519" t="n">
         <v>163517</v>
@@ -15478,7 +15478,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>21.13991355896</v>
+        <v>21.1399154663086</v>
       </c>
       <c r="H521" t="n">
         <v>76402</v>
@@ -15536,7 +15536,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>21.2326335906982</v>
+        <v>21.2326354980469</v>
       </c>
       <c r="H523" t="n">
         <v>49536</v>
@@ -15565,7 +15565,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>21.4644298553467</v>
+        <v>21.4644336700439</v>
       </c>
       <c r="H524" t="n">
         <v>47137</v>
@@ -15594,7 +15594,7 @@
         <v>23</v>
       </c>
       <c r="G525" t="n">
-        <v>21.3253517150879</v>
+        <v>21.3253498077393</v>
       </c>
       <c r="H525" t="n">
         <v>53312</v>
@@ -15652,7 +15652,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>21.6035079956055</v>
+        <v>21.6035099029541</v>
       </c>
       <c r="H527" t="n">
         <v>69528</v>
@@ -15681,7 +15681,7 @@
         <v>23</v>
       </c>
       <c r="G528" t="n">
-        <v>21.3253517150879</v>
+        <v>21.3253498077393</v>
       </c>
       <c r="H528" t="n">
         <v>55836</v>
@@ -15768,7 +15768,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G531" t="n">
-        <v>21.6498680114746</v>
+        <v>21.6498699188232</v>
       </c>
       <c r="H531" t="n">
         <v>48363</v>
@@ -15797,7 +15797,7 @@
         <v>23</v>
       </c>
       <c r="G532" t="n">
-        <v>21.3253517150879</v>
+        <v>21.3253498077393</v>
       </c>
       <c r="H532" t="n">
         <v>51291</v>
@@ -15855,7 +15855,7 @@
         <v>23</v>
       </c>
       <c r="G534" t="n">
-        <v>21.3253517150879</v>
+        <v>21.3253498077393</v>
       </c>
       <c r="H534" t="n">
         <v>46645</v>
@@ -15884,7 +15884,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G535" t="n">
-        <v>21.2326335906982</v>
+        <v>21.2326354980469</v>
       </c>
       <c r="H535" t="n">
         <v>38209</v>
@@ -15913,7 +15913,7 @@
         <v>22.5</v>
       </c>
       <c r="G536" t="n">
-        <v>20.8617572784424</v>
+        <v>20.861759185791</v>
       </c>
       <c r="H536" t="n">
         <v>45405</v>
@@ -15942,7 +15942,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>20.3054466247559</v>
+        <v>20.3054428100586</v>
       </c>
       <c r="H537" t="n">
         <v>54524</v>
@@ -15971,7 +15971,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>20.9081153869629</v>
+        <v>20.9081192016602</v>
       </c>
       <c r="H538" t="n">
         <v>23371</v>
@@ -16000,7 +16000,7 @@
         <v>22.5</v>
       </c>
       <c r="G539" t="n">
-        <v>20.8617572784424</v>
+        <v>20.861759185791</v>
       </c>
       <c r="H539" t="n">
         <v>66307</v>
@@ -16029,7 +16029,7 @@
         <v>22.5</v>
       </c>
       <c r="G540" t="n">
-        <v>20.8617572784424</v>
+        <v>20.861759185791</v>
       </c>
       <c r="H540" t="n">
         <v>32010</v>
@@ -16058,7 +16058,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G541" t="n">
-        <v>20.3054466247559</v>
+        <v>20.3054428100586</v>
       </c>
       <c r="H541" t="n">
         <v>42378</v>
@@ -16087,7 +16087,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G542" t="n">
-        <v>20.4908847808838</v>
+        <v>20.4908828735352</v>
       </c>
       <c r="H542" t="n">
         <v>23321</v>
@@ -16116,7 +16116,7 @@
         <v>22.25</v>
       </c>
       <c r="G543" t="n">
-        <v>20.6299629211426</v>
+        <v>20.6299591064453</v>
       </c>
       <c r="H543" t="n">
         <v>20428</v>
@@ -16145,7 +16145,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>20.5836029052734</v>
+        <v>20.5835990905762</v>
       </c>
       <c r="H544" t="n">
         <v>12889</v>
@@ -16174,7 +16174,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G545" t="n">
-        <v>20.9544773101807</v>
+        <v>20.9544792175293</v>
       </c>
       <c r="H545" t="n">
         <v>16417</v>
@@ -16203,7 +16203,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G546" t="n">
-        <v>20.9081153869629</v>
+        <v>20.9081192016602</v>
       </c>
       <c r="H546" t="n">
         <v>11923</v>
@@ -16232,7 +16232,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>21.0471935272217</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H547" t="n">
         <v>8341</v>
@@ -16261,7 +16261,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>21.0008335113525</v>
+        <v>21.0008373260498</v>
       </c>
       <c r="H548" t="n">
         <v>10821</v>
@@ -16290,7 +16290,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G549" t="n">
-        <v>20.722677230835</v>
+        <v>20.7226829528809</v>
       </c>
       <c r="H549" t="n">
         <v>9616</v>
@@ -16406,7 +16406,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G553" t="n">
-        <v>21.6035079956055</v>
+        <v>21.6035099029541</v>
       </c>
       <c r="H553" t="n">
         <v>106785</v>
@@ -16435,7 +16435,7 @@
         <v>23.25</v>
       </c>
       <c r="G554" t="n">
-        <v>21.5571479797363</v>
+        <v>21.557149887085</v>
       </c>
       <c r="H554" t="n">
         <v>156886</v>
@@ -16464,7 +16464,7 @@
         <v>23.25</v>
       </c>
       <c r="G555" t="n">
-        <v>21.5571479797363</v>
+        <v>21.557149887085</v>
       </c>
       <c r="H555" t="n">
         <v>237507</v>
@@ -16493,7 +16493,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>21.4644298553467</v>
+        <v>21.4644336700439</v>
       </c>
       <c r="H556" t="n">
         <v>33185</v>
@@ -16522,7 +16522,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G557" t="n">
-        <v>22.0671043395996</v>
+        <v>22.067102432251</v>
       </c>
       <c r="H557" t="n">
         <v>49099</v>
@@ -16551,7 +16551,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G558" t="n">
-        <v>21.7425880432129</v>
+        <v>21.7425899505615</v>
       </c>
       <c r="H558" t="n">
         <v>63622</v>
@@ -16580,7 +16580,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G559" t="n">
-        <v>21.9280281066895</v>
+        <v>21.9280261993408</v>
       </c>
       <c r="H559" t="n">
         <v>54096</v>
@@ -16667,7 +16667,7 @@
         <v>23</v>
       </c>
       <c r="G562" t="n">
-        <v>21.3253517150879</v>
+        <v>21.3253498077393</v>
       </c>
       <c r="H562" t="n">
         <v>50146</v>
@@ -16696,7 +16696,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>21.0471935272217</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H563" t="n">
         <v>43117</v>
@@ -16725,7 +16725,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>21.0471935272217</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H564" t="n">
         <v>21687</v>
@@ -16783,7 +16783,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>20.5836029052734</v>
+        <v>20.5835990905762</v>
       </c>
       <c r="H566" t="n">
         <v>23402</v>
@@ -16812,7 +16812,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>20.9544773101807</v>
+        <v>20.9544792175293</v>
       </c>
       <c r="H567" t="n">
         <v>15271</v>
@@ -16841,7 +16841,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>20.722677230835</v>
+        <v>20.7226829528809</v>
       </c>
       <c r="H568" t="n">
         <v>27519</v>
@@ -16870,7 +16870,7 @@
         <v>22.75</v>
       </c>
       <c r="G569" t="n">
-        <v>21.0935535430908</v>
+        <v>21.0935554504395</v>
       </c>
       <c r="H569" t="n">
         <v>41089</v>
@@ -16899,7 +16899,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>20.722677230835</v>
+        <v>20.7226829528809</v>
       </c>
       <c r="H570" t="n">
         <v>21232</v>
@@ -16928,7 +16928,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>20.722677230835</v>
+        <v>20.7226829528809</v>
       </c>
       <c r="H571" t="n">
         <v>12000</v>
@@ -16986,7 +16986,7 @@
         <v>21.75</v>
       </c>
       <c r="G573" t="n">
-        <v>20.1663684844971</v>
+        <v>20.1663665771484</v>
       </c>
       <c r="H573" t="n">
         <v>19943</v>
@@ -17044,7 +17044,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G575" t="n">
-        <v>20.4908847808838</v>
+        <v>20.4908828735352</v>
       </c>
       <c r="H575" t="n">
         <v>13120</v>
@@ -17073,7 +17073,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.0736465454102</v>
+        <v>20.0736484527588</v>
       </c>
       <c r="H576" t="n">
         <v>20744</v>
@@ -17102,7 +17102,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>20.0736465454102</v>
+        <v>20.0736484527588</v>
       </c>
       <c r="H577" t="n">
         <v>76572</v>
@@ -17131,7 +17131,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>20.7690372467041</v>
+        <v>20.7690410614014</v>
       </c>
       <c r="H578" t="n">
         <v>29293</v>
@@ -17160,7 +17160,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>21.0471935272217</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H579" t="n">
         <v>36379</v>
@@ -17189,7 +17189,7 @@
         <v>22.5</v>
       </c>
       <c r="G580" t="n">
-        <v>20.8617572784424</v>
+        <v>20.861759185791</v>
       </c>
       <c r="H580" t="n">
         <v>11780</v>
@@ -17218,7 +17218,7 @@
         <v>22.5</v>
       </c>
       <c r="G581" t="n">
-        <v>20.8617572784424</v>
+        <v>20.861759185791</v>
       </c>
       <c r="H581" t="n">
         <v>32422</v>
@@ -17247,7 +17247,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>21.0471935272217</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H582" t="n">
         <v>19364</v>
@@ -17276,7 +17276,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>20.7690372467041</v>
+        <v>20.7690410614014</v>
       </c>
       <c r="H583" t="n">
         <v>12663</v>
@@ -17334,7 +17334,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G585" t="n">
-        <v>20.8153972625732</v>
+        <v>20.8153991699219</v>
       </c>
       <c r="H585" t="n">
         <v>34337</v>
@@ -17363,7 +17363,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G586" t="n">
-        <v>21.0471935272217</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H586" t="n">
         <v>31766</v>
@@ -17421,7 +17421,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G588" t="n">
-        <v>20.5836029052734</v>
+        <v>20.5835990905762</v>
       </c>
       <c r="H588" t="n">
         <v>42376</v>
@@ -17450,7 +17450,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>20.9544773101807</v>
+        <v>20.9544792175293</v>
       </c>
       <c r="H589" t="n">
         <v>42855</v>
@@ -17479,7 +17479,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>20.9081153869629</v>
+        <v>20.9081192016602</v>
       </c>
       <c r="H590" t="n">
         <v>5669</v>
@@ -17508,7 +17508,7 @@
         <v>22.5</v>
       </c>
       <c r="G591" t="n">
-        <v>20.8617572784424</v>
+        <v>20.861759185791</v>
       </c>
       <c r="H591" t="n">
         <v>44050</v>
@@ -17537,7 +17537,7 @@
         <v>22.25</v>
       </c>
       <c r="G592" t="n">
-        <v>20.6299629211426</v>
+        <v>20.6299591064453</v>
       </c>
       <c r="H592" t="n">
         <v>27279</v>
@@ -17566,7 +17566,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>20.5836029052734</v>
+        <v>20.5835990905762</v>
       </c>
       <c r="H593" t="n">
         <v>4466</v>
@@ -17624,7 +17624,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G595" t="n">
-        <v>21.2326335906982</v>
+        <v>21.2326354980469</v>
       </c>
       <c r="H595" t="n">
         <v>33837</v>
@@ -17653,7 +17653,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>21.0008335113525</v>
+        <v>21.0008373260498</v>
       </c>
       <c r="H596" t="n">
         <v>7652</v>
@@ -17682,7 +17682,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>20.8153972625732</v>
+        <v>20.8153991699219</v>
       </c>
       <c r="H597" t="n">
         <v>13297</v>
@@ -17711,7 +17711,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>21.0471935272217</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H598" t="n">
         <v>23626</v>
@@ -17740,7 +17740,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G599" t="n">
-        <v>20.4908847808838</v>
+        <v>20.4908828735352</v>
       </c>
       <c r="H599" t="n">
         <v>39405</v>
@@ -17769,7 +17769,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>20.722677230835</v>
+        <v>20.7226829528809</v>
       </c>
       <c r="H600" t="n">
         <v>48289</v>
@@ -17827,7 +17827,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>20.7690372467041</v>
+        <v>20.7690410614014</v>
       </c>
       <c r="H602" t="n">
         <v>22732</v>
@@ -17943,7 +17943,7 @@
         <v>22.25</v>
       </c>
       <c r="G606" t="n">
-        <v>20.6299629211426</v>
+        <v>20.6299591064453</v>
       </c>
       <c r="H606" t="n">
         <v>88362</v>
@@ -18001,7 +18001,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>20.7690372467041</v>
+        <v>20.7690410614014</v>
       </c>
       <c r="H608" t="n">
         <v>17837</v>
@@ -18030,7 +18030,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G609" t="n">
-        <v>20.5836029052734</v>
+        <v>20.5835990905762</v>
       </c>
       <c r="H609" t="n">
         <v>16331</v>
@@ -18088,7 +18088,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G611" t="n">
-        <v>20.722677230835</v>
+        <v>20.7226829528809</v>
       </c>
       <c r="H611" t="n">
         <v>20399</v>
@@ -18117,7 +18117,7 @@
         <v>22.25</v>
       </c>
       <c r="G612" t="n">
-        <v>20.6299629211426</v>
+        <v>20.6299591064453</v>
       </c>
       <c r="H612" t="n">
         <v>25403</v>
@@ -18204,7 +18204,7 @@
         <v>20</v>
       </c>
       <c r="G615" t="n">
-        <v>18.5437850952148</v>
+        <v>18.5437831878662</v>
       </c>
       <c r="H615" t="n">
         <v>83861</v>
@@ -18233,7 +18233,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G616" t="n">
-        <v>18.488151550293</v>
+        <v>18.4881534576416</v>
       </c>
       <c r="H616" t="n">
         <v>41726</v>
@@ -18291,7 +18291,7 @@
         <v>20.5</v>
       </c>
       <c r="G618" t="n">
-        <v>19.0073795318604</v>
+        <v>19.0073776245117</v>
       </c>
       <c r="H618" t="n">
         <v>34244</v>
@@ -18320,7 +18320,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>19.1928176879883</v>
+        <v>19.1928215026855</v>
       </c>
       <c r="H619" t="n">
         <v>18404</v>
@@ -18349,7 +18349,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G620" t="n">
-        <v>19.6564159393311</v>
+        <v>19.6564140319824</v>
       </c>
       <c r="H620" t="n">
         <v>35604</v>
@@ -18378,7 +18378,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G621" t="n">
-        <v>19.6564159393311</v>
+        <v>19.6564140319824</v>
       </c>
       <c r="H621" t="n">
         <v>30321</v>
@@ -18407,7 +18407,7 @@
         <v>21</v>
       </c>
       <c r="G622" t="n">
-        <v>19.4709777832031</v>
+        <v>19.4709739685059</v>
       </c>
       <c r="H622" t="n">
         <v>12684</v>
@@ -18436,7 +18436,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>20.5836029052734</v>
+        <v>20.5835990905762</v>
       </c>
       <c r="H623" t="n">
         <v>20521</v>
@@ -18465,7 +18465,7 @@
         <v>21.75</v>
       </c>
       <c r="G624" t="n">
-        <v>20.1663684844971</v>
+        <v>20.1663665771484</v>
       </c>
       <c r="H624" t="n">
         <v>26565</v>
@@ -18523,7 +18523,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G626" t="n">
-        <v>20.3054466247559</v>
+        <v>20.3054428100586</v>
       </c>
       <c r="H626" t="n">
         <v>13030</v>
@@ -18610,7 +18610,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>19.8418521881104</v>
+        <v>19.8418502807617</v>
       </c>
       <c r="H629" t="n">
         <v>14368</v>
@@ -18639,7 +18639,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G630" t="n">
-        <v>19.8418521881104</v>
+        <v>19.8418502807617</v>
       </c>
       <c r="H630" t="n">
         <v>7158</v>
@@ -18668,7 +18668,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G631" t="n">
-        <v>20.0736465454102</v>
+        <v>20.0736484527588</v>
       </c>
       <c r="H631" t="n">
         <v>17303</v>
@@ -18697,7 +18697,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G632" t="n">
-        <v>20.0272884368896</v>
+        <v>20.0272903442383</v>
       </c>
       <c r="H632" t="n">
         <v>11595</v>
@@ -18755,7 +18755,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G634" t="n">
-        <v>19.8418521881104</v>
+        <v>19.8418502807617</v>
       </c>
       <c r="H634" t="n">
         <v>15839</v>
@@ -18784,7 +18784,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>19.6100540161133</v>
+        <v>19.610050201416</v>
       </c>
       <c r="H635" t="n">
         <v>17303</v>
@@ -18813,7 +18813,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G636" t="n">
-        <v>19.6564159393311</v>
+        <v>19.6564140319824</v>
       </c>
       <c r="H636" t="n">
         <v>16915</v>
@@ -18842,7 +18842,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G637" t="n">
-        <v>19.7491302490234</v>
+        <v>19.7491321563721</v>
       </c>
       <c r="H637" t="n">
         <v>101033</v>
@@ -18871,7 +18871,7 @@
         <v>21</v>
       </c>
       <c r="G638" t="n">
-        <v>19.4709777832031</v>
+        <v>19.4709739685059</v>
       </c>
       <c r="H638" t="n">
         <v>31002</v>
@@ -18900,7 +18900,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G639" t="n">
-        <v>19.7954940795898</v>
+        <v>19.7954902648926</v>
       </c>
       <c r="H639" t="n">
         <v>51440</v>
@@ -18929,7 +18929,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>19.6100540161133</v>
+        <v>19.610050201416</v>
       </c>
       <c r="H640" t="n">
         <v>27459</v>
@@ -18958,7 +18958,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>19.7954940795898</v>
+        <v>19.7954902648926</v>
       </c>
       <c r="H641" t="n">
         <v>20014</v>
@@ -18987,7 +18987,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>19.7954940795898</v>
+        <v>19.7954902648926</v>
       </c>
       <c r="H642" t="n">
         <v>19845</v>
@@ -19016,7 +19016,7 @@
         <v>21.75</v>
       </c>
       <c r="G643" t="n">
-        <v>20.1663684844971</v>
+        <v>20.1663665771484</v>
       </c>
       <c r="H643" t="n">
         <v>20181</v>
@@ -19132,7 +19132,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>20.3054466247559</v>
+        <v>20.3054428100586</v>
       </c>
       <c r="H647" t="n">
         <v>17969</v>
@@ -19248,7 +19248,7 @@
         <v>21.75</v>
       </c>
       <c r="G651" t="n">
-        <v>20.1663684844971</v>
+        <v>20.1663665771484</v>
       </c>
       <c r="H651" t="n">
         <v>14885</v>
@@ -19277,7 +19277,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G652" t="n">
-        <v>19.8418521881104</v>
+        <v>19.8418502807617</v>
       </c>
       <c r="H652" t="n">
         <v>14698</v>
@@ -19422,7 +19422,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G657" t="n">
-        <v>19.6100540161133</v>
+        <v>19.610050201416</v>
       </c>
       <c r="H657" t="n">
         <v>13842</v>
@@ -19451,7 +19451,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>19.5173320770264</v>
+        <v>19.517333984375</v>
       </c>
       <c r="H658" t="n">
         <v>16450</v>
@@ -19480,7 +19480,7 @@
         <v>21</v>
       </c>
       <c r="G659" t="n">
-        <v>19.4709777832031</v>
+        <v>19.4709739685059</v>
       </c>
       <c r="H659" t="n">
         <v>10511</v>
@@ -19509,7 +19509,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>19.6100540161133</v>
+        <v>19.610050201416</v>
       </c>
       <c r="H660" t="n">
         <v>8173</v>
@@ -19538,7 +19538,7 @@
         <v>21</v>
       </c>
       <c r="G661" t="n">
-        <v>19.4709777832031</v>
+        <v>19.4709739685059</v>
       </c>
       <c r="H661" t="n">
         <v>26576</v>
@@ -19567,7 +19567,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G662" t="n">
-        <v>19.5173320770264</v>
+        <v>19.517333984375</v>
       </c>
       <c r="H662" t="n">
         <v>24200</v>
@@ -19596,7 +19596,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G663" t="n">
-        <v>19.5173320770264</v>
+        <v>19.517333984375</v>
       </c>
       <c r="H663" t="n">
         <v>9201</v>
@@ -19625,7 +19625,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G664" t="n">
-        <v>19.6100540161133</v>
+        <v>19.610050201416</v>
       </c>
       <c r="H664" t="n">
         <v>6935</v>
@@ -19683,7 +19683,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G666" t="n">
-        <v>19.6100540161133</v>
+        <v>19.610050201416</v>
       </c>
       <c r="H666" t="n">
         <v>20401</v>
@@ -19712,7 +19712,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G667" t="n">
-        <v>19.6100540161133</v>
+        <v>19.610050201416</v>
       </c>
       <c r="H667" t="n">
         <v>10533</v>
@@ -19799,7 +19799,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G670" t="n">
-        <v>19.5173320770264</v>
+        <v>19.517333984375</v>
       </c>
       <c r="H670" t="n">
         <v>23931</v>
@@ -19857,7 +19857,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G672" t="n">
-        <v>19.1464595794678</v>
+        <v>19.1464576721191</v>
       </c>
       <c r="H672" t="n">
         <v>4451</v>
@@ -19886,7 +19886,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>19.1000995635986</v>
+        <v>19.10009765625</v>
       </c>
       <c r="H673" t="n">
         <v>33687</v>
@@ -19915,7 +19915,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G674" t="n">
-        <v>19.1000995635986</v>
+        <v>19.10009765625</v>
       </c>
       <c r="H674" t="n">
         <v>17054</v>
@@ -19944,7 +19944,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>19.1000995635986</v>
+        <v>19.10009765625</v>
       </c>
       <c r="H675" t="n">
         <v>13909</v>
@@ -19973,7 +19973,7 @@
         <v>20.75</v>
       </c>
       <c r="G676" t="n">
-        <v>19.2391777038574</v>
+        <v>19.2391738891602</v>
       </c>
       <c r="H676" t="n">
         <v>7292</v>
@@ -20060,7 +20060,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>20.0272884368896</v>
+        <v>20.0272903442383</v>
       </c>
       <c r="H679" t="n">
         <v>11621</v>
@@ -20089,7 +20089,7 @@
         <v>21.25</v>
       </c>
       <c r="G680" t="n">
-        <v>19.7027740478516</v>
+        <v>19.7027702331543</v>
       </c>
       <c r="H680" t="n">
         <v>7952</v>
@@ -20147,7 +20147,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>19.7491302490234</v>
+        <v>19.7491321563721</v>
       </c>
       <c r="H682" t="n">
         <v>16185</v>
@@ -20176,7 +20176,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>20.0272884368896</v>
+        <v>20.0272903442383</v>
       </c>
       <c r="H683" t="n">
         <v>13405</v>
@@ -20205,7 +20205,7 @@
         <v>22.25</v>
       </c>
       <c r="G684" t="n">
-        <v>20.6299629211426</v>
+        <v>20.6299591064453</v>
       </c>
       <c r="H684" t="n">
         <v>27903</v>
@@ -20263,7 +20263,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>20.3054466247559</v>
+        <v>20.3054428100586</v>
       </c>
       <c r="H686" t="n">
         <v>23241</v>
@@ -20350,7 +20350,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G689" t="n">
-        <v>20.722677230835</v>
+        <v>20.7226829528809</v>
       </c>
       <c r="H689" t="n">
         <v>13795</v>
@@ -20379,7 +20379,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G690" t="n">
-        <v>21.0008335113525</v>
+        <v>21.0008373260498</v>
       </c>
       <c r="H690" t="n">
         <v>14529</v>
@@ -20408,7 +20408,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>20.9544773101807</v>
+        <v>20.9544792175293</v>
       </c>
       <c r="H691" t="n">
         <v>21175</v>
@@ -20437,7 +20437,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>20.9544773101807</v>
+        <v>20.9544792175293</v>
       </c>
       <c r="H692" t="n">
         <v>4369</v>
@@ -20466,7 +20466,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>20.9081153869629</v>
+        <v>20.9081192016602</v>
       </c>
       <c r="H693" t="n">
         <v>7284</v>
@@ -20495,7 +20495,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>21.2326335906982</v>
+        <v>21.2326354980469</v>
       </c>
       <c r="H694" t="n">
         <v>44066</v>
@@ -20524,7 +20524,7 @@
         <v>23</v>
       </c>
       <c r="G695" t="n">
-        <v>21.3253517150879</v>
+        <v>21.3253498077393</v>
       </c>
       <c r="H695" t="n">
         <v>12234</v>
@@ -20582,7 +20582,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G697" t="n">
-        <v>21.13991355896</v>
+        <v>21.1399154663086</v>
       </c>
       <c r="H697" t="n">
         <v>14041</v>
@@ -20611,7 +20611,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>21.0471935272217</v>
+        <v>21.0471954345703</v>
       </c>
       <c r="H698" t="n">
         <v>23800</v>
@@ -20640,7 +20640,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>21.2326335906982</v>
+        <v>21.2326354980469</v>
       </c>
       <c r="H699" t="n">
         <v>45041</v>
@@ -20727,7 +20727,7 @@
         <v>22.75</v>
       </c>
       <c r="G702" t="n">
-        <v>21.0935535430908</v>
+        <v>21.0935554504395</v>
       </c>
       <c r="H702" t="n">
         <v>9042</v>
@@ -20785,7 +20785,7 @@
         <v>23.25</v>
       </c>
       <c r="G704" t="n">
-        <v>21.5571479797363</v>
+        <v>21.557149887085</v>
       </c>
       <c r="H704" t="n">
         <v>12269</v>
@@ -20814,7 +20814,7 @@
         <v>23.25</v>
       </c>
       <c r="G705" t="n">
-        <v>21.5571479797363</v>
+        <v>21.557149887085</v>
       </c>
       <c r="H705" t="n">
         <v>12214</v>
@@ -20843,7 +20843,7 @@
         <v>22.5</v>
       </c>
       <c r="G706" t="n">
-        <v>20.8617572784424</v>
+        <v>20.861759185791</v>
       </c>
       <c r="H706" t="n">
         <v>6837</v>
@@ -20988,7 +20988,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>19.7954940795898</v>
+        <v>19.7954902648926</v>
       </c>
       <c r="H711" t="n">
         <v>11915</v>
@@ -21017,7 +21017,7 @@
         <v>21</v>
       </c>
       <c r="G712" t="n">
-        <v>19.4709777832031</v>
+        <v>19.4709739685059</v>
       </c>
       <c r="H712" t="n">
         <v>14023</v>
@@ -21104,7 +21104,7 @@
         <v>21</v>
       </c>
       <c r="G715" t="n">
-        <v>19.4709777832031</v>
+        <v>19.4709739685059</v>
       </c>
       <c r="H715" t="n">
         <v>31944</v>
@@ -21162,7 +21162,7 @@
         <v>20.75</v>
       </c>
       <c r="G717" t="n">
-        <v>19.2391777038574</v>
+        <v>19.2391738891602</v>
       </c>
       <c r="H717" t="n">
         <v>8400</v>
@@ -21191,7 +21191,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G718" t="n">
-        <v>17.598051071167</v>
+        <v>17.5980529785156</v>
       </c>
       <c r="H718" t="n">
         <v>65740</v>
@@ -21307,7 +21307,7 @@
         <v>15.5</v>
       </c>
       <c r="G722" t="n">
-        <v>14.3714332580566</v>
+        <v>14.371434211731</v>
       </c>
       <c r="H722" t="n">
         <v>192645</v>
@@ -21394,7 +21394,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G725" t="n">
-        <v>15.5211505889893</v>
+        <v>15.5211458206177</v>
       </c>
       <c r="H725" t="n">
         <v>84445</v>
@@ -21423,7 +21423,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G726" t="n">
-        <v>15.8920221328735</v>
+        <v>15.8920230865479</v>
       </c>
       <c r="H726" t="n">
         <v>89330</v>
@@ -21452,7 +21452,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G727" t="n">
-        <v>15.4284296035767</v>
+        <v>15.4284267425537</v>
       </c>
       <c r="H727" t="n">
         <v>105540</v>
@@ -21481,7 +21481,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G728" t="n">
-        <v>15.2244472503662</v>
+        <v>15.2244462966919</v>
       </c>
       <c r="H728" t="n">
         <v>58119</v>
@@ -21539,7 +21539,7 @@
         <v>17</v>
       </c>
       <c r="G730" t="n">
-        <v>15.7622175216675</v>
+        <v>15.7622156143188</v>
       </c>
       <c r="H730" t="n">
         <v>54217</v>
@@ -21655,7 +21655,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>15.4840593338013</v>
+        <v>15.4840621948242</v>
       </c>
       <c r="H734" t="n">
         <v>42010</v>
@@ -21713,7 +21713,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G736" t="n">
-        <v>14.9092044830322</v>
+        <v>14.9092035293579</v>
       </c>
       <c r="H736" t="n">
         <v>35483</v>
@@ -21771,7 +21771,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G738" t="n">
-        <v>14.4800271987915</v>
+        <v>14.4800281524658</v>
       </c>
       <c r="H738" t="n">
         <v>35416</v>
@@ -21800,7 +21800,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G739" t="n">
-        <v>14.3120889663696</v>
+        <v>14.3120880126953</v>
       </c>
       <c r="H739" t="n">
         <v>29995</v>
@@ -21829,7 +21829,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G740" t="n">
-        <v>14.3494091033936</v>
+        <v>14.3494100570679</v>
       </c>
       <c r="H740" t="n">
         <v>19875</v>
@@ -21858,7 +21858,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G741" t="n">
-        <v>14.3120889663696</v>
+        <v>14.3120880126953</v>
       </c>
       <c r="H741" t="n">
         <v>99873</v>
@@ -21887,7 +21887,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G742" t="n">
-        <v>14.8159036636353</v>
+        <v>14.8159046173096</v>
       </c>
       <c r="H742" t="n">
         <v>23327</v>
@@ -21916,7 +21916,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>14.8345632553101</v>
+        <v>14.8345642089844</v>
       </c>
       <c r="H743" t="n">
         <v>50203</v>
@@ -21945,7 +21945,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G744" t="n">
-        <v>14.5546684265137</v>
+        <v>14.5546674728394</v>
       </c>
       <c r="H744" t="n">
         <v>33338</v>
@@ -22032,7 +22032,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G747" t="n">
-        <v>15.3383798599243</v>
+        <v>15.3383817672729</v>
       </c>
       <c r="H747" t="n">
         <v>22659</v>
@@ -22061,7 +22061,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G748" t="n">
-        <v>15.1704406738281</v>
+        <v>15.1704416275024</v>
       </c>
       <c r="H748" t="n">
         <v>29386</v>
@@ -22119,7 +22119,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G750" t="n">
-        <v>13.9762125015259</v>
+        <v>13.9762115478516</v>
       </c>
       <c r="H750" t="n">
         <v>59346</v>
@@ -22206,7 +22206,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G753" t="n">
-        <v>13.6403341293335</v>
+        <v>13.6403350830078</v>
       </c>
       <c r="H753" t="n">
         <v>38754</v>
@@ -22235,7 +22235,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G754" t="n">
-        <v>14.2374505996704</v>
+        <v>14.2374496459961</v>
       </c>
       <c r="H754" t="n">
         <v>47839</v>
@@ -22264,7 +22264,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G755" t="n">
-        <v>14.0695114135742</v>
+        <v>14.0695104598999</v>
       </c>
       <c r="H755" t="n">
         <v>144043</v>
@@ -22322,7 +22322,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G757" t="n">
-        <v>14.1254911422729</v>
+        <v>14.1254920959473</v>
       </c>
       <c r="H757" t="n">
         <v>31051</v>
@@ -22351,7 +22351,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G758" t="n">
-        <v>13.8642520904541</v>
+        <v>13.8642530441284</v>
       </c>
       <c r="H758" t="n">
         <v>16527</v>
@@ -22380,7 +22380,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G759" t="n">
-        <v>13.5470380783081</v>
+        <v>13.5470361709595</v>
       </c>
       <c r="H759" t="n">
         <v>27400</v>
@@ -22438,7 +22438,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G761" t="n">
-        <v>13.6963157653809</v>
+        <v>13.6963148117065</v>
       </c>
       <c r="H761" t="n">
         <v>32342</v>
@@ -22467,7 +22467,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G762" t="n">
-        <v>13.9575519561768</v>
+        <v>13.9575510025024</v>
       </c>
       <c r="H762" t="n">
         <v>22482</v>
@@ -22496,7 +22496,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G763" t="n">
-        <v>14.2374505996704</v>
+        <v>14.2374496459961</v>
       </c>
       <c r="H763" t="n">
         <v>22749</v>
@@ -22525,7 +22525,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G764" t="n">
-        <v>14.1068315505981</v>
+        <v>14.1068305969238</v>
       </c>
       <c r="H764" t="n">
         <v>20809</v>
@@ -22554,7 +22554,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G765" t="n">
-        <v>14.4240474700928</v>
+        <v>14.4240484237671</v>
       </c>
       <c r="H765" t="n">
         <v>27254</v>
@@ -22583,7 +22583,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>14.5546684265137</v>
+        <v>14.5546674728394</v>
       </c>
       <c r="H766" t="n">
         <v>29260</v>
@@ -22670,7 +22670,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>15.114462852478</v>
+        <v>15.1144609451294</v>
       </c>
       <c r="H769" t="n">
         <v>32371</v>
@@ -22699,7 +22699,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>15.114462852478</v>
+        <v>15.1144609451294</v>
       </c>
       <c r="H770" t="n">
         <v>29082</v>
@@ -22815,7 +22815,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G774" t="n">
-        <v>14.965184211731</v>
+        <v>14.9651832580566</v>
       </c>
       <c r="H774" t="n">
         <v>7959</v>
@@ -22844,7 +22844,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G775" t="n">
-        <v>14.7972431182861</v>
+        <v>14.7972440719604</v>
       </c>
       <c r="H775" t="n">
         <v>22626</v>
@@ -22931,7 +22931,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G778" t="n">
-        <v>15.058482170105</v>
+        <v>15.0584812164307</v>
       </c>
       <c r="H778" t="n">
         <v>11898</v>
@@ -23047,7 +23047,7 @@
         <v>17</v>
       </c>
       <c r="G782" t="n">
-        <v>15.8608541488647</v>
+        <v>15.8608522415161</v>
       </c>
       <c r="H782" t="n">
         <v>60804</v>
@@ -23105,7 +23105,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G784" t="n">
-        <v>16.7751846313477</v>
+        <v>16.7751865386963</v>
       </c>
       <c r="H784" t="n">
         <v>108771</v>
@@ -23134,7 +23134,7 @@
         <v>18</v>
       </c>
       <c r="G785" t="n">
-        <v>16.7938480377197</v>
+        <v>16.7938461303711</v>
       </c>
       <c r="H785" t="n">
         <v>36242</v>
@@ -23163,7 +23163,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G786" t="n">
-        <v>16.3833312988281</v>
+        <v>16.3833293914795</v>
       </c>
       <c r="H786" t="n">
         <v>21191</v>
@@ -23221,7 +23221,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G788" t="n">
-        <v>16.1594085693359</v>
+        <v>16.1594123840332</v>
       </c>
       <c r="H788" t="n">
         <v>18002</v>
@@ -23250,7 +23250,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G789" t="n">
-        <v>16.2527141571045</v>
+        <v>16.2527122497559</v>
       </c>
       <c r="H789" t="n">
         <v>20511</v>
@@ -23279,7 +23279,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G790" t="n">
-        <v>15.8795166015625</v>
+        <v>15.8795156478882</v>
       </c>
       <c r="H790" t="n">
         <v>17031</v>
@@ -23308,7 +23308,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>15.7675552368164</v>
+        <v>15.7675561904907</v>
       </c>
       <c r="H791" t="n">
         <v>21984</v>
@@ -23337,7 +23337,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G792" t="n">
-        <v>15.7115774154663</v>
+        <v>15.711576461792</v>
       </c>
       <c r="H792" t="n">
         <v>9190</v>
@@ -23366,7 +23366,7 @@
         <v>17</v>
       </c>
       <c r="G793" t="n">
-        <v>15.8608541488647</v>
+        <v>15.8608522415161</v>
       </c>
       <c r="H793" t="n">
         <v>19710</v>
@@ -23424,7 +23424,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G795" t="n">
-        <v>16.047456741333</v>
+        <v>16.0474548339844</v>
       </c>
       <c r="H795" t="n">
         <v>9742</v>
@@ -23540,7 +23540,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G799" t="n">
-        <v>16.1780738830566</v>
+        <v>16.178071975708</v>
       </c>
       <c r="H799" t="n">
         <v>35647</v>
@@ -23656,7 +23656,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G803" t="n">
-        <v>16.1220932006836</v>
+        <v>16.1220893859863</v>
       </c>
       <c r="H803" t="n">
         <v>16875</v>
@@ -23685,7 +23685,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G804" t="n">
-        <v>16.1220932006836</v>
+        <v>16.1220893859863</v>
       </c>
       <c r="H804" t="n">
         <v>14233</v>
@@ -23743,7 +23743,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G806" t="n">
-        <v>16.495288848877</v>
+        <v>16.4952926635742</v>
       </c>
       <c r="H806" t="n">
         <v>8339</v>
@@ -23801,7 +23801,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>16.6072444915771</v>
+        <v>16.6072463989258</v>
       </c>
       <c r="H808" t="n">
         <v>7788</v>
@@ -23830,7 +23830,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G809" t="n">
-        <v>16.3646697998047</v>
+        <v>16.3646717071533</v>
       </c>
       <c r="H809" t="n">
         <v>46188</v>
@@ -23859,7 +23859,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G810" t="n">
-        <v>16.2153911590576</v>
+        <v>16.215389251709</v>
       </c>
       <c r="H810" t="n">
         <v>35824</v>
@@ -23888,7 +23888,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>15.7675552368164</v>
+        <v>15.7675561904907</v>
       </c>
       <c r="H811" t="n">
         <v>26100</v>
@@ -23917,7 +23917,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G812" t="n">
-        <v>15.7488956451416</v>
+        <v>15.7488965988159</v>
       </c>
       <c r="H812" t="n">
         <v>18087</v>
@@ -23946,7 +23946,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>15.7675552368164</v>
+        <v>15.7675561904907</v>
       </c>
       <c r="H813" t="n">
         <v>17451</v>
@@ -24004,7 +24004,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G815" t="n">
-        <v>15.7488956451416</v>
+        <v>15.7488965988159</v>
       </c>
       <c r="H815" t="n">
         <v>8805</v>
@@ -24033,7 +24033,7 @@
         <v>17</v>
       </c>
       <c r="G816" t="n">
-        <v>15.8608541488647</v>
+        <v>15.8608522415161</v>
       </c>
       <c r="H816" t="n">
         <v>43526</v>
@@ -24062,7 +24062,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G817" t="n">
-        <v>15.8235349655151</v>
+        <v>15.8235340118408</v>
       </c>
       <c r="H817" t="n">
         <v>19265</v>
@@ -24120,7 +24120,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G819" t="n">
-        <v>15.8795166015625</v>
+        <v>15.8795156478882</v>
       </c>
       <c r="H819" t="n">
         <v>10457</v>
@@ -24149,7 +24149,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G820" t="n">
-        <v>15.8981742858887</v>
+        <v>15.8981733322144</v>
       </c>
       <c r="H820" t="n">
         <v>9126</v>
@@ -24236,7 +24236,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G823" t="n">
-        <v>16.2900314331055</v>
+        <v>16.2900295257568</v>
       </c>
       <c r="H823" t="n">
         <v>15799</v>
@@ -24265,7 +24265,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>16.4206504821777</v>
+        <v>16.4206523895264</v>
       </c>
       <c r="H824" t="n">
         <v>21788</v>
@@ -24294,7 +24294,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G825" t="n">
-        <v>16.2153911590576</v>
+        <v>16.215389251709</v>
       </c>
       <c r="H825" t="n">
         <v>37134</v>
@@ -24352,7 +24352,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G827" t="n">
-        <v>16.8311672210693</v>
+        <v>16.8311653137207</v>
       </c>
       <c r="H827" t="n">
         <v>34581</v>
@@ -24410,7 +24410,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G829" t="n">
-        <v>18.1560153961182</v>
+        <v>18.1560134887695</v>
       </c>
       <c r="H829" t="n">
         <v>112376</v>
@@ -24526,7 +24526,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G833" t="n">
-        <v>17.4096202850342</v>
+        <v>17.4096221923828</v>
       </c>
       <c r="H833" t="n">
         <v>47242</v>
@@ -24555,7 +24555,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G834" t="n">
-        <v>17.0177631378174</v>
+        <v>17.0177612304688</v>
       </c>
       <c r="H834" t="n">
         <v>30697</v>
@@ -24642,7 +24642,7 @@
         <v>18</v>
       </c>
       <c r="G837" t="n">
-        <v>16.7938480377197</v>
+        <v>16.7938461303711</v>
       </c>
       <c r="H837" t="n">
         <v>33449</v>
@@ -24671,7 +24671,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G838" t="n">
-        <v>16.6259059906006</v>
+        <v>16.6259078979492</v>
       </c>
       <c r="H838" t="n">
         <v>17443</v>
@@ -24700,7 +24700,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>16.6072444915771</v>
+        <v>16.6072463989258</v>
       </c>
       <c r="H839" t="n">
         <v>21116</v>
@@ -24729,7 +24729,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>16.6072444915771</v>
+        <v>16.6072463989258</v>
       </c>
       <c r="H840" t="n">
         <v>26446</v>
@@ -24816,7 +24816,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G843" t="n">
-        <v>16.8498268127441</v>
+        <v>16.8498249053955</v>
       </c>
       <c r="H843" t="n">
         <v>30729</v>
@@ -24845,7 +24845,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G844" t="n">
-        <v>16.8498268127441</v>
+        <v>16.8498249053955</v>
       </c>
       <c r="H844" t="n">
         <v>8387</v>
@@ -24932,7 +24932,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G847" t="n">
-        <v>17.0364246368408</v>
+        <v>17.0364227294922</v>
       </c>
       <c r="H847" t="n">
         <v>11139</v>
@@ -25019,7 +25019,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G850" t="n">
-        <v>16.2153911590576</v>
+        <v>16.215389251709</v>
       </c>
       <c r="H850" t="n">
         <v>45906</v>
@@ -25106,7 +25106,7 @@
         <v>17</v>
       </c>
       <c r="G853" t="n">
-        <v>15.8608541488647</v>
+        <v>15.8608522415161</v>
       </c>
       <c r="H853" t="n">
         <v>47412</v>
@@ -25135,7 +25135,7 @@
         <v>16.5</v>
       </c>
       <c r="G854" t="n">
-        <v>15.3943605422974</v>
+        <v>15.394359588623</v>
       </c>
       <c r="H854" t="n">
         <v>40064</v>
@@ -25164,7 +25164,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G855" t="n">
-        <v>15.4130182266235</v>
+        <v>15.4130191802979</v>
       </c>
       <c r="H855" t="n">
         <v>101404</v>
@@ -25193,7 +25193,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G856" t="n">
-        <v>15.3570404052734</v>
+        <v>15.3570384979248</v>
       </c>
       <c r="H856" t="n">
         <v>76066</v>
@@ -25251,7 +25251,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G858" t="n">
-        <v>15.0771417617798</v>
+        <v>15.0771427154541</v>
       </c>
       <c r="H858" t="n">
         <v>25946</v>
@@ -25280,7 +25280,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G859" t="n">
-        <v>14.5919857025146</v>
+        <v>14.591986656189</v>
       </c>
       <c r="H859" t="n">
         <v>22488</v>
@@ -25309,7 +25309,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G860" t="n">
-        <v>14.7039461135864</v>
+        <v>14.7039470672607</v>
       </c>
       <c r="H860" t="n">
         <v>23693</v>
@@ -25338,7 +25338,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G861" t="n">
-        <v>14.9838428497314</v>
+        <v>14.9838418960571</v>
       </c>
       <c r="H861" t="n">
         <v>15878</v>
@@ -25367,7 +25367,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G862" t="n">
-        <v>14.6666259765625</v>
+        <v>14.6666269302368</v>
       </c>
       <c r="H862" t="n">
         <v>15236</v>
@@ -25396,7 +25396,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G863" t="n">
-        <v>14.871883392334</v>
+        <v>14.8718824386597</v>
       </c>
       <c r="H863" t="n">
         <v>11696</v>
@@ -25425,7 +25425,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G864" t="n">
-        <v>14.8345632553101</v>
+        <v>14.8345642089844</v>
       </c>
       <c r="H864" t="n">
         <v>25043</v>
@@ -25483,7 +25483,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G866" t="n">
-        <v>14.4053869247437</v>
+        <v>14.405387878418</v>
       </c>
       <c r="H866" t="n">
         <v>28040</v>
@@ -25512,7 +25512,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G867" t="n">
-        <v>14.5733270645142</v>
+        <v>14.5733261108398</v>
       </c>
       <c r="H867" t="n">
         <v>19352</v>
@@ -25570,7 +25570,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G869" t="n">
-        <v>14.3494091033936</v>
+        <v>14.3494100570679</v>
       </c>
       <c r="H869" t="n">
         <v>17632</v>
@@ -25628,7 +25628,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G871" t="n">
-        <v>14.7972431182861</v>
+        <v>14.7972440719604</v>
       </c>
       <c r="H871" t="n">
         <v>49735</v>
@@ -25657,7 +25657,7 @@
         <v>15.5</v>
       </c>
       <c r="G872" t="n">
-        <v>14.4613676071167</v>
+        <v>14.461368560791</v>
       </c>
       <c r="H872" t="n">
         <v>27300</v>
@@ -25773,7 +25773,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G876" t="n">
-        <v>14.6666259765625</v>
+        <v>14.6666269302368</v>
       </c>
       <c r="H876" t="n">
         <v>9573</v>
@@ -25831,7 +25831,7 @@
         <v>16.5</v>
       </c>
       <c r="G878" t="n">
-        <v>15.3943605422974</v>
+        <v>15.394359588623</v>
       </c>
       <c r="H878" t="n">
         <v>37103</v>
@@ -25889,7 +25889,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G880" t="n">
-        <v>15.3570404052734</v>
+        <v>15.3570384979248</v>
       </c>
       <c r="H880" t="n">
         <v>39729</v>
@@ -25947,7 +25947,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G882" t="n">
-        <v>15.2823991775513</v>
+        <v>15.2824001312256</v>
       </c>
       <c r="H882" t="n">
         <v>22629</v>
@@ -25976,7 +25976,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G883" t="n">
-        <v>15.5622987747192</v>
+        <v>15.5622978210449</v>
       </c>
       <c r="H883" t="n">
         <v>38097</v>
@@ -26034,7 +26034,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G885" t="n">
-        <v>15.1331205368042</v>
+        <v>15.1331214904785</v>
       </c>
       <c r="H885" t="n">
         <v>9715</v>
@@ -26063,7 +26063,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G886" t="n">
-        <v>14.965184211731</v>
+        <v>14.9651832580566</v>
       </c>
       <c r="H886" t="n">
         <v>6520</v>
@@ -26092,7 +26092,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G887" t="n">
-        <v>14.9092044830322</v>
+        <v>14.9092035293579</v>
       </c>
       <c r="H887" t="n">
         <v>21487</v>
@@ -26208,7 +26208,7 @@
         <v>16.5</v>
       </c>
       <c r="G891" t="n">
-        <v>15.3943605422974</v>
+        <v>15.394359588623</v>
       </c>
       <c r="H891" t="n">
         <v>18797</v>
@@ -26440,7 +26440,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G899" t="n">
-        <v>14.871883392334</v>
+        <v>14.8718824386597</v>
       </c>
       <c r="H899" t="n">
         <v>42950</v>
@@ -26469,7 +26469,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G900" t="n">
-        <v>14.9465236663818</v>
+        <v>14.9465227127075</v>
       </c>
       <c r="H900" t="n">
         <v>23925</v>
@@ -26527,7 +26527,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G902" t="n">
-        <v>14.5733270645142</v>
+        <v>14.5733261108398</v>
       </c>
       <c r="H902" t="n">
         <v>42288</v>
@@ -26556,7 +26556,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G903" t="n">
-        <v>14.4427070617676</v>
+        <v>14.4427080154419</v>
       </c>
       <c r="H903" t="n">
         <v>41043</v>
@@ -26585,7 +26585,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G904" t="n">
-        <v>14.5919857025146</v>
+        <v>14.591986656189</v>
       </c>
       <c r="H904" t="n">
         <v>41338</v>
@@ -26643,7 +26643,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G906" t="n">
-        <v>14.9092044830322</v>
+        <v>14.9092035293579</v>
       </c>
       <c r="H906" t="n">
         <v>35494</v>
@@ -26672,7 +26672,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G907" t="n">
-        <v>14.9092044830322</v>
+        <v>14.9092035293579</v>
       </c>
       <c r="H907" t="n">
         <v>21951</v>
@@ -26759,7 +26759,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G910" t="n">
-        <v>14.8159036636353</v>
+        <v>14.8159046173096</v>
       </c>
       <c r="H910" t="n">
         <v>17570</v>
@@ -26817,7 +26817,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G912" t="n">
-        <v>14.685284614563</v>
+        <v>14.6852855682373</v>
       </c>
       <c r="H912" t="n">
         <v>12131</v>
@@ -26846,7 +26846,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G913" t="n">
-        <v>14.6666259765625</v>
+        <v>14.6666269302368</v>
       </c>
       <c r="H913" t="n">
         <v>17280</v>
@@ -26904,7 +26904,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G915" t="n">
-        <v>14.5173482894897</v>
+        <v>14.5173473358154</v>
       </c>
       <c r="H915" t="n">
         <v>13161</v>
@@ -26933,7 +26933,7 @@
         <v>15.5</v>
       </c>
       <c r="G916" t="n">
-        <v>14.4613676071167</v>
+        <v>14.461368560791</v>
       </c>
       <c r="H916" t="n">
         <v>30625</v>
@@ -26962,7 +26962,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G917" t="n">
-        <v>14.5546684265137</v>
+        <v>14.5546674728394</v>
       </c>
       <c r="H917" t="n">
         <v>9480</v>
@@ -26991,7 +26991,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G918" t="n">
-        <v>14.2001304626465</v>
+        <v>14.2001295089722</v>
       </c>
       <c r="H918" t="n">
         <v>9942</v>
@@ -27165,7 +27165,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G924" t="n">
-        <v>14.1628112792969</v>
+        <v>14.1628093719482</v>
       </c>
       <c r="H924" t="n">
         <v>23143</v>
@@ -27252,7 +27252,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G927" t="n">
-        <v>14.0695114135742</v>
+        <v>14.0695104598999</v>
       </c>
       <c r="H927" t="n">
         <v>14937</v>
@@ -27310,7 +27310,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G929" t="n">
-        <v>13.9762125015259</v>
+        <v>13.9762115478516</v>
       </c>
       <c r="H929" t="n">
         <v>36481</v>
@@ -27339,7 +27339,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G930" t="n">
-        <v>13.7522945404053</v>
+        <v>13.752293586731</v>
       </c>
       <c r="H930" t="n">
         <v>33728</v>
@@ -27397,7 +27397,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G932" t="n">
-        <v>13.8455944061279</v>
+        <v>13.8455934524536</v>
       </c>
       <c r="H932" t="n">
         <v>20851</v>
@@ -27426,7 +27426,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G933" t="n">
-        <v>14.1441507339478</v>
+        <v>14.1441497802734</v>
       </c>
       <c r="H933" t="n">
         <v>19429</v>
@@ -27484,7 +27484,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G935" t="n">
-        <v>13.9202327728271</v>
+        <v>13.9202337265015</v>
       </c>
       <c r="H935" t="n">
         <v>14235</v>
@@ -27513,7 +27513,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G936" t="n">
-        <v>14.1068315505981</v>
+        <v>14.1068305969238</v>
       </c>
       <c r="H936" t="n">
         <v>19769</v>
@@ -27542,7 +27542,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G937" t="n">
-        <v>14.4240474700928</v>
+        <v>14.4240484237671</v>
       </c>
       <c r="H937" t="n">
         <v>33693</v>
@@ -27571,7 +27571,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G938" t="n">
-        <v>14.4240474700928</v>
+        <v>14.4240484237671</v>
       </c>
       <c r="H938" t="n">
         <v>24536</v>
@@ -27687,7 +27687,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>14.8345632553101</v>
+        <v>14.8345642089844</v>
       </c>
       <c r="H942" t="n">
         <v>26935</v>
@@ -27803,7 +27803,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G946" t="n">
-        <v>14.7039461135864</v>
+        <v>14.7039470672607</v>
       </c>
       <c r="H946" t="n">
         <v>16079</v>
@@ -27919,7 +27919,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G950" t="n">
-        <v>13.9015731811523</v>
+        <v>13.901572227478</v>
       </c>
       <c r="H950" t="n">
         <v>31947</v>
@@ -27977,7 +27977,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G952" t="n">
-        <v>14.9465236663818</v>
+        <v>14.9465227127075</v>
       </c>
       <c r="H952" t="n">
         <v>82129</v>
@@ -28006,7 +28006,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G953" t="n">
-        <v>15.1331205368042</v>
+        <v>15.1331214904785</v>
       </c>
       <c r="H953" t="n">
         <v>42848</v>
@@ -28122,7 +28122,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G957" t="n">
-        <v>14.1628112792969</v>
+        <v>14.1628093719482</v>
       </c>
       <c r="H957" t="n">
         <v>23706</v>
@@ -28151,7 +28151,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G958" t="n">
-        <v>14.0695114135742</v>
+        <v>14.0695104598999</v>
       </c>
       <c r="H958" t="n">
         <v>28101</v>
@@ -28180,7 +28180,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G959" t="n">
-        <v>14.0135316848755</v>
+        <v>14.0135326385498</v>
       </c>
       <c r="H959" t="n">
         <v>32572</v>
@@ -28296,7 +28296,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G963" t="n">
-        <v>14.4053869247437</v>
+        <v>14.405387878418</v>
       </c>
       <c r="H963" t="n">
         <v>39229</v>
@@ -28412,7 +28412,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G967" t="n">
-        <v>14.3867273330688</v>
+        <v>14.3867292404175</v>
       </c>
       <c r="H967" t="n">
         <v>52484</v>
@@ -28470,7 +28470,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G969" t="n">
-        <v>14.5733270645142</v>
+        <v>14.5733261108398</v>
       </c>
       <c r="H969" t="n">
         <v>27864</v>
@@ -28528,7 +28528,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G971" t="n">
-        <v>14.7972431182861</v>
+        <v>14.7972440719604</v>
       </c>
       <c r="H971" t="n">
         <v>56451</v>
@@ -28615,7 +28615,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G974" t="n">
-        <v>14.3867273330688</v>
+        <v>14.3867292404175</v>
       </c>
       <c r="H974" t="n">
         <v>140755</v>
@@ -28673,7 +28673,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G976" t="n">
-        <v>14.4427070617676</v>
+        <v>14.4427080154419</v>
       </c>
       <c r="H976" t="n">
         <v>46413</v>
@@ -28731,7 +28731,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G978" t="n">
-        <v>14.8345632553101</v>
+        <v>14.8345642089844</v>
       </c>
       <c r="H978" t="n">
         <v>49423</v>
@@ -28760,7 +28760,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G979" t="n">
-        <v>14.8905439376831</v>
+        <v>14.8905429840088</v>
       </c>
       <c r="H979" t="n">
         <v>34422</v>
@@ -28789,7 +28789,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G980" t="n">
-        <v>14.8905439376831</v>
+        <v>14.8905429840088</v>
       </c>
       <c r="H980" t="n">
         <v>30884</v>
@@ -28876,7 +28876,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G983" t="n">
-        <v>15.114462852478</v>
+        <v>15.1144609451294</v>
       </c>
       <c r="H983" t="n">
         <v>20830</v>
@@ -28905,7 +28905,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G984" t="n">
-        <v>15.1891012191772</v>
+        <v>15.1891021728516</v>
       </c>
       <c r="H984" t="n">
         <v>65074</v>
@@ -28934,7 +28934,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G985" t="n">
-        <v>15.058482170105</v>
+        <v>15.0584812164307</v>
       </c>
       <c r="H985" t="n">
         <v>22328</v>
@@ -28963,7 +28963,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G986" t="n">
-        <v>15.058482170105</v>
+        <v>15.0584812164307</v>
       </c>
       <c r="H986" t="n">
         <v>14789</v>
@@ -29021,7 +29021,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G988" t="n">
-        <v>14.9740724563599</v>
+        <v>14.9740743637085</v>
       </c>
       <c r="H988" t="n">
         <v>19772</v>
@@ -29079,7 +29079,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G990" t="n">
-        <v>14.8045558929443</v>
+        <v>14.8045568466187</v>
       </c>
       <c r="H990" t="n">
         <v>25723</v>
@@ -29108,7 +29108,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G991" t="n">
-        <v>14.7103796005249</v>
+        <v>14.7103786468506</v>
       </c>
       <c r="H991" t="n">
         <v>21853</v>
@@ -29166,7 +29166,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G993" t="n">
-        <v>14.7103796005249</v>
+        <v>14.7103786468506</v>
       </c>
       <c r="H993" t="n">
         <v>63330</v>
@@ -29224,7 +29224,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G995" t="n">
-        <v>15.5768070220947</v>
+        <v>15.5768060684204</v>
       </c>
       <c r="H995" t="n">
         <v>234762</v>
@@ -29311,7 +29311,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G998" t="n">
-        <v>15.5768070220947</v>
+        <v>15.5768060684204</v>
       </c>
       <c r="H998" t="n">
         <v>155080</v>
@@ -29340,7 +29340,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G999" t="n">
-        <v>15.5956382751465</v>
+        <v>15.5956373214722</v>
       </c>
       <c r="H999" t="n">
         <v>133198</v>
@@ -29369,7 +29369,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1000" t="n">
-        <v>15.5956382751465</v>
+        <v>15.5956373214722</v>
       </c>
       <c r="H1000" t="n">
         <v>38462</v>
@@ -29398,7 +29398,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1001" t="n">
-        <v>15.5579681396484</v>
+        <v>15.5579690933228</v>
       </c>
       <c r="H1001" t="n">
         <v>29662</v>
@@ -29456,7 +29456,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1003" t="n">
-        <v>15.4449586868286</v>
+        <v>15.4449577331543</v>
       </c>
       <c r="H1003" t="n">
         <v>28443</v>
@@ -29514,7 +29514,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1005" t="n">
-        <v>15.4449586868286</v>
+        <v>15.4449577331543</v>
       </c>
       <c r="H1005" t="n">
         <v>27302</v>
@@ -29543,7 +29543,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1006" t="n">
-        <v>15.6521453857422</v>
+        <v>15.6521463394165</v>
       </c>
       <c r="H1006" t="n">
         <v>38542</v>
@@ -29572,7 +29572,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1007" t="n">
-        <v>15.6521453857422</v>
+        <v>15.6521463394165</v>
       </c>
       <c r="H1007" t="n">
         <v>33587</v>
@@ -29601,7 +29601,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1008" t="n">
-        <v>15.6898164749146</v>
+        <v>15.6898155212402</v>
       </c>
       <c r="H1008" t="n">
         <v>70765</v>
@@ -29659,7 +29659,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1010" t="n">
-        <v>15.6144742965698</v>
+        <v>15.6144752502441</v>
       </c>
       <c r="H1010" t="n">
         <v>63772</v>
@@ -29688,7 +29688,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1011" t="n">
-        <v>15.5014629364014</v>
+        <v>15.5014610290527</v>
       </c>
       <c r="H1011" t="n">
         <v>56247</v>
@@ -29746,7 +29746,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1013" t="n">
-        <v>15.5579681396484</v>
+        <v>15.5579690933228</v>
       </c>
       <c r="H1013" t="n">
         <v>19229</v>
@@ -29775,7 +29775,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1014" t="n">
-        <v>15.5768070220947</v>
+        <v>15.5768060684204</v>
       </c>
       <c r="H1014" t="n">
         <v>15642</v>
@@ -29833,7 +29833,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1016" t="n">
-        <v>15.9346723556519</v>
+        <v>15.9346733093262</v>
       </c>
       <c r="H1016" t="n">
         <v>53402</v>
@@ -29862,7 +29862,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1017" t="n">
-        <v>15.8781700134277</v>
+        <v>15.8781671524048</v>
       </c>
       <c r="H1017" t="n">
         <v>42179</v>
@@ -29891,7 +29891,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1018" t="n">
-        <v>15.6144742965698</v>
+        <v>15.6144752502441</v>
       </c>
       <c r="H1018" t="n">
         <v>34506</v>
@@ -29920,7 +29920,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1019" t="n">
-        <v>15.5014629364014</v>
+        <v>15.5014610290527</v>
       </c>
       <c r="H1019" t="n">
         <v>22812</v>
@@ -30007,7 +30007,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1022" t="n">
-        <v>15.5956382751465</v>
+        <v>15.5956373214722</v>
       </c>
       <c r="H1022" t="n">
         <v>32083</v>
@@ -30123,7 +30123,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.5956382751465</v>
+        <v>15.5956373214722</v>
       </c>
       <c r="H1026" t="n">
         <v>30480</v>
@@ -30152,7 +30152,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.482626914978</v>
+        <v>15.4826288223267</v>
       </c>
       <c r="H1027" t="n">
         <v>19815</v>
@@ -30239,7 +30239,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1030" t="n">
-        <v>15.0117444992065</v>
+        <v>15.0117435455322</v>
       </c>
       <c r="H1030" t="n">
         <v>64174</v>
@@ -30268,7 +30268,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1031" t="n">
-        <v>14.8798971176147</v>
+        <v>14.8798961639404</v>
       </c>
       <c r="H1031" t="n">
         <v>30529</v>
@@ -30355,7 +30355,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1034" t="n">
-        <v>14.8045558929443</v>
+        <v>14.8045568466187</v>
       </c>
       <c r="H1034" t="n">
         <v>22902</v>
@@ -30384,7 +30384,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.8422269821167</v>
+        <v>14.842227935791</v>
       </c>
       <c r="H1035" t="n">
         <v>19012</v>
@@ -30413,7 +30413,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1036" t="n">
-        <v>14.4090137481689</v>
+        <v>14.4090147018433</v>
       </c>
       <c r="H1036" t="n">
         <v>46547</v>
@@ -30471,7 +30471,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1038" t="n">
-        <v>13.8439559936523</v>
+        <v>13.843955039978</v>
       </c>
       <c r="H1038" t="n">
         <v>55688</v>
@@ -30500,7 +30500,7 @@
         <v>15</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.1264848709106</v>
+        <v>14.1264839172363</v>
       </c>
       <c r="H1039" t="n">
         <v>28204</v>
@@ -30558,7 +30558,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1041" t="n">
-        <v>14.6915454864502</v>
+        <v>14.6915445327759</v>
       </c>
       <c r="H1041" t="n">
         <v>30895</v>
@@ -30587,7 +30587,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.4843559265137</v>
+        <v>14.484356880188</v>
       </c>
       <c r="H1042" t="n">
         <v>44262</v>
@@ -30616,7 +30616,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.2960033416748</v>
+        <v>14.2960014343262</v>
       </c>
       <c r="H1043" t="n">
         <v>74475</v>
@@ -30674,7 +30674,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1045" t="n">
-        <v>14.2960033416748</v>
+        <v>14.2960014343262</v>
       </c>
       <c r="H1045" t="n">
         <v>45324</v>
@@ -30703,7 +30703,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.2960033416748</v>
+        <v>14.2960014343262</v>
       </c>
       <c r="H1046" t="n">
         <v>43642</v>
@@ -30732,7 +30732,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1047" t="n">
-        <v>14.3336725234985</v>
+        <v>14.3336734771729</v>
       </c>
       <c r="H1047" t="n">
         <v>22716</v>
@@ -30848,7 +30848,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1051" t="n">
-        <v>13.9569654464722</v>
+        <v>13.9569664001465</v>
       </c>
       <c r="H1051" t="n">
         <v>46619</v>
@@ -30935,7 +30935,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G1054" t="n">
-        <v>12.9210252761841</v>
+        <v>12.9210243225098</v>
       </c>
       <c r="H1054" t="n">
         <v>57592</v>
@@ -30964,7 +30964,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1055" t="n">
-        <v>13.2788972854614</v>
+        <v>13.2788963317871</v>
       </c>
       <c r="H1055" t="n">
         <v>59904</v>
@@ -31080,7 +31080,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1059" t="n">
-        <v>12.0922718048096</v>
+        <v>12.0922708511353</v>
       </c>
       <c r="H1059" t="n">
         <v>63913</v>
@@ -31138,7 +31138,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1061" t="n">
-        <v>11.3953657150269</v>
+        <v>11.3953638076782</v>
       </c>
       <c r="H1061" t="n">
         <v>61208</v>
@@ -31167,7 +31167,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G1062" t="n">
-        <v>10.9621534347534</v>
+        <v>10.9621515274048</v>
       </c>
       <c r="H1062" t="n">
         <v>119472</v>
@@ -31196,7 +31196,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1063" t="n">
-        <v>10.0580587387085</v>
+        <v>10.0580577850342</v>
       </c>
       <c r="H1063" t="n">
         <v>141497</v>
@@ -31312,7 +31312,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G1067" t="n">
-        <v>9.35173320770264</v>
+        <v>9.35173225402832</v>
       </c>
       <c r="H1067" t="n">
         <v>190760</v>
@@ -31370,7 +31370,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.49472713470459</v>
+        <v>8.49472618103027</v>
       </c>
       <c r="H1069" t="n">
         <v>114788</v>
@@ -31399,7 +31399,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1070" t="n">
-        <v>9.04095077514648</v>
+        <v>9.04094886779785</v>
       </c>
       <c r="H1070" t="n">
         <v>49982</v>
@@ -31428,7 +31428,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1071" t="n">
-        <v>10.0957279205322</v>
+        <v>10.0957269668579</v>
       </c>
       <c r="H1071" t="n">
         <v>85106</v>
@@ -31457,7 +31457,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1072" t="n">
-        <v>10.6796236038208</v>
+        <v>10.6796226501465</v>
       </c>
       <c r="H1072" t="n">
         <v>179318</v>
@@ -31515,7 +31515,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1074" t="n">
-        <v>12.8080129623413</v>
+        <v>12.8080139160156</v>
       </c>
       <c r="H1074" t="n">
         <v>113035</v>
@@ -31544,7 +31544,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1075" t="n">
-        <v>11.5272121429443</v>
+        <v>11.52721118927</v>
       </c>
       <c r="H1075" t="n">
         <v>81745</v>
@@ -31602,7 +31602,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1077" t="n">
-        <v>10.8491401672363</v>
+        <v>10.849142074585</v>
       </c>
       <c r="H1077" t="n">
         <v>24643</v>
@@ -31631,7 +31631,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1078" t="n">
-        <v>10.6796236038208</v>
+        <v>10.6796226501465</v>
       </c>
       <c r="H1078" t="n">
         <v>14651</v>
@@ -31689,7 +31689,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1080" t="n">
-        <v>10.0015506744385</v>
+        <v>10.0015497207642</v>
       </c>
       <c r="H1080" t="n">
         <v>31361</v>
@@ -31747,7 +31747,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1082" t="n">
-        <v>10.2652444839478</v>
+        <v>10.2652454376221</v>
       </c>
       <c r="H1082" t="n">
         <v>6546</v>
@@ -31776,7 +31776,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1083" t="n">
-        <v>10.5477743148804</v>
+        <v>10.5477752685547</v>
       </c>
       <c r="H1083" t="n">
         <v>11260</v>
@@ -31863,7 +31863,7 @@
         <v>11.5</v>
       </c>
       <c r="G1086" t="n">
-        <v>10.830304145813</v>
+        <v>10.8303050994873</v>
       </c>
       <c r="H1086" t="n">
         <v>29924</v>
@@ -31892,7 +31892,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1087" t="n">
-        <v>10.5101051330566</v>
+        <v>10.5101041793823</v>
       </c>
       <c r="H1087" t="n">
         <v>44963</v>
@@ -32008,7 +32008,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1091" t="n">
-        <v>10.4347629547119</v>
+        <v>10.4347639083862</v>
       </c>
       <c r="H1091" t="n">
         <v>16860</v>
@@ -32066,7 +32066,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1093" t="n">
-        <v>10.4347629547119</v>
+        <v>10.4347639083862</v>
       </c>
       <c r="H1093" t="n">
         <v>11561</v>
@@ -32617,7 +32617,7 @@
         <v>11.5</v>
       </c>
       <c r="G1112" t="n">
-        <v>10.830304145813</v>
+        <v>10.8303050994873</v>
       </c>
       <c r="H1112" t="n">
         <v>25770</v>
@@ -32733,7 +32733,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1116" t="n">
-        <v>11.4895401000977</v>
+        <v>11.489541053772</v>
       </c>
       <c r="H1116" t="n">
         <v>90141</v>
@@ -32762,7 +32762,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1117" t="n">
-        <v>11.4895401000977</v>
+        <v>11.489541053772</v>
       </c>
       <c r="H1117" t="n">
         <v>82381</v>
@@ -32791,7 +32791,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1118" t="n">
-        <v>11.4895401000977</v>
+        <v>11.489541053772</v>
       </c>
       <c r="H1118" t="n">
         <v>60368</v>
@@ -32849,7 +32849,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1120" t="n">
-        <v>11.3388586044312</v>
+        <v>11.3388595581055</v>
       </c>
       <c r="H1120" t="n">
         <v>57918</v>
@@ -32878,7 +32878,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1121" t="n">
-        <v>11.4330348968506</v>
+        <v>11.4330358505249</v>
       </c>
       <c r="H1121" t="n">
         <v>47351</v>
@@ -33023,7 +33023,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1126" t="n">
-        <v>12.0169305801392</v>
+        <v>12.0169296264648</v>
       </c>
       <c r="H1126" t="n">
         <v>70083</v>
@@ -33052,7 +33052,7 @@
         <v>12.5</v>
       </c>
       <c r="G1127" t="n">
-        <v>11.7720718383789</v>
+        <v>11.7720708847046</v>
       </c>
       <c r="H1127" t="n">
         <v>39780</v>
@@ -33081,7 +33081,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1128" t="n">
-        <v>11.150505065918</v>
+        <v>11.1505041122437</v>
       </c>
       <c r="H1128" t="n">
         <v>44853</v>
@@ -33110,7 +33110,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1129" t="n">
-        <v>10.9433174133301</v>
+        <v>10.9433164596558</v>
       </c>
       <c r="H1129" t="n">
         <v>38358</v>
@@ -33139,7 +33139,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1130" t="n">
-        <v>11.1128358840942</v>
+        <v>11.1128349304199</v>
       </c>
       <c r="H1130" t="n">
         <v>59521</v>
@@ -33168,7 +33168,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1131" t="n">
-        <v>11.1128358840942</v>
+        <v>11.1128349304199</v>
       </c>
       <c r="H1131" t="n">
         <v>135229</v>
@@ -33197,7 +33197,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1132" t="n">
-        <v>10.9433174133301</v>
+        <v>10.9433164596558</v>
       </c>
       <c r="H1132" t="n">
         <v>114207</v>
@@ -33284,7 +33284,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1135" t="n">
-        <v>10.9433174133301</v>
+        <v>10.9433164596558</v>
       </c>
       <c r="H1135" t="n">
         <v>57098</v>
@@ -33371,7 +33371,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>10.8114709854126</v>
+        <v>10.8114700317383</v>
       </c>
       <c r="H1138" t="n">
         <v>27528</v>
@@ -33429,7 +33429,7 @@
         <v>11.5</v>
       </c>
       <c r="G1140" t="n">
-        <v>10.830304145813</v>
+        <v>10.8303050994873</v>
       </c>
       <c r="H1140" t="n">
         <v>16197</v>
@@ -33603,7 +33603,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.5477743148804</v>
+        <v>10.5477752685547</v>
       </c>
       <c r="H1146" t="n">
         <v>20019</v>
@@ -33690,7 +33690,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.3782587051392</v>
+        <v>10.3782577514648</v>
       </c>
       <c r="H1149" t="n">
         <v>23719</v>
@@ -33806,7 +33806,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1153" t="n">
-        <v>11.1128358840942</v>
+        <v>11.1128349304199</v>
       </c>
       <c r="H1153" t="n">
         <v>22649</v>
@@ -33893,7 +33893,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1156" t="n">
-        <v>11.2070121765137</v>
+        <v>11.207010269165</v>
       </c>
       <c r="H1156" t="n">
         <v>26448</v>
@@ -33922,7 +33922,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1157" t="n">
-        <v>10.9998226165771</v>
+        <v>10.9998235702515</v>
       </c>
       <c r="H1157" t="n">
         <v>13154</v>
@@ -33951,7 +33951,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1158" t="n">
-        <v>11.150505065918</v>
+        <v>11.1505041122437</v>
       </c>
       <c r="H1158" t="n">
         <v>20877</v>
@@ -34009,7 +34009,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G1160" t="n">
-        <v>10.8491401672363</v>
+        <v>10.849142074585</v>
       </c>
       <c r="H1160" t="n">
         <v>5037</v>
@@ -34067,7 +34067,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1162" t="n">
-        <v>10.5289402008057</v>
+        <v>10.52894115448</v>
       </c>
       <c r="H1162" t="n">
         <v>22805</v>
@@ -34125,7 +34125,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1164" t="n">
-        <v>10.3970918655396</v>
+        <v>10.3970937728882</v>
       </c>
       <c r="H1164" t="n">
         <v>28392</v>
@@ -34154,7 +34154,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>10.5477743148804</v>
+        <v>10.5477752685547</v>
       </c>
       <c r="H1165" t="n">
         <v>20206</v>
@@ -34241,7 +34241,7 @@
         <v>11.5</v>
       </c>
       <c r="G1168" t="n">
-        <v>10.830304145813</v>
+        <v>10.8303050994873</v>
       </c>
       <c r="H1168" t="n">
         <v>22483</v>
@@ -34270,7 +34270,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1169" t="n">
-        <v>10.6796236038208</v>
+        <v>10.6796226501465</v>
       </c>
       <c r="H1169" t="n">
         <v>11931</v>
@@ -34299,7 +34299,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1170" t="n">
-        <v>10.9998226165771</v>
+        <v>10.9998235702515</v>
       </c>
       <c r="H1170" t="n">
         <v>27415</v>
@@ -34386,7 +34386,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>11.3953657150269</v>
+        <v>11.3953638076782</v>
       </c>
       <c r="H1173" t="n">
         <v>20817</v>
@@ -34415,7 +34415,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1174" t="n">
-        <v>11.3388586044312</v>
+        <v>11.3388595581055</v>
       </c>
       <c r="H1174" t="n">
         <v>7401</v>
@@ -34444,7 +34444,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1175" t="n">
-        <v>11.5272121429443</v>
+        <v>11.52721118927</v>
       </c>
       <c r="H1175" t="n">
         <v>28816</v>
@@ -34502,7 +34502,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1177" t="n">
-        <v>11.6025524139404</v>
+        <v>11.6025533676147</v>
       </c>
       <c r="H1177" t="n">
         <v>12148</v>
@@ -34531,7 +34531,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1178" t="n">
-        <v>11.4518690109253</v>
+        <v>11.4518699645996</v>
       </c>
       <c r="H1178" t="n">
         <v>14878</v>
@@ -34560,7 +34560,7 @@
         <v>12.5</v>
       </c>
       <c r="G1179" t="n">
-        <v>11.7720718383789</v>
+        <v>11.7720708847046</v>
       </c>
       <c r="H1179" t="n">
         <v>25777</v>
@@ -34589,7 +34589,7 @@
         <v>12.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>11.7720718383789</v>
+        <v>11.7720708847046</v>
       </c>
       <c r="H1180" t="n">
         <v>36341</v>
@@ -34618,7 +34618,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1181" t="n">
-        <v>11.546046257019</v>
+        <v>11.5460472106934</v>
       </c>
       <c r="H1181" t="n">
         <v>33161</v>
@@ -34647,7 +34647,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1182" t="n">
-        <v>11.4707069396973</v>
+        <v>11.4707059860229</v>
       </c>
       <c r="H1182" t="n">
         <v>10686</v>
@@ -34676,7 +34676,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1183" t="n">
-        <v>11.4707069396973</v>
+        <v>11.4707059860229</v>
       </c>
       <c r="H1183" t="n">
         <v>11553</v>
@@ -34705,7 +34705,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1184" t="n">
-        <v>11.5272121429443</v>
+        <v>11.52721118927</v>
       </c>
       <c r="H1184" t="n">
         <v>18255</v>
@@ -34734,7 +34734,7 @@
         <v>12.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>11.7720718383789</v>
+        <v>11.7720708847046</v>
       </c>
       <c r="H1185" t="n">
         <v>17102</v>
@@ -34763,7 +34763,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1186" t="n">
-        <v>11.5837173461914</v>
+        <v>11.5837182998657</v>
       </c>
       <c r="H1186" t="n">
         <v>59441</v>
@@ -34821,7 +34821,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1188" t="n">
-        <v>11.6590595245361</v>
+        <v>11.6590585708618</v>
       </c>
       <c r="H1188" t="n">
         <v>18788</v>
@@ -34850,7 +34850,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1189" t="n">
-        <v>11.5272121429443</v>
+        <v>11.52721118927</v>
       </c>
       <c r="H1189" t="n">
         <v>7469</v>
@@ -34908,7 +34908,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1191" t="n">
-        <v>12.1487760543823</v>
+        <v>12.1487770080566</v>
       </c>
       <c r="H1191" t="n">
         <v>66738</v>
@@ -34937,7 +34937,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1192" t="n">
-        <v>12.0545997619629</v>
+        <v>12.0546016693115</v>
       </c>
       <c r="H1192" t="n">
         <v>37163</v>
@@ -34995,7 +34995,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1194" t="n">
-        <v>11.885082244873</v>
+        <v>11.8850831985474</v>
       </c>
       <c r="H1194" t="n">
         <v>20939</v>
@@ -35082,7 +35082,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1197" t="n">
-        <v>11.6590595245361</v>
+        <v>11.6590585708618</v>
       </c>
       <c r="H1197" t="n">
         <v>21232</v>
@@ -35140,7 +35140,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1199" t="n">
-        <v>11.4518690109253</v>
+        <v>11.4518699645996</v>
       </c>
       <c r="H1199" t="n">
         <v>24331</v>
@@ -35227,7 +35227,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1202" t="n">
-        <v>11.546046257019</v>
+        <v>11.5460472106934</v>
       </c>
       <c r="H1202" t="n">
         <v>19283</v>
@@ -35256,7 +35256,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1203" t="n">
-        <v>11.4518690109253</v>
+        <v>11.4518699645996</v>
       </c>
       <c r="H1203" t="n">
         <v>17612</v>
@@ -35285,7 +35285,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1204" t="n">
-        <v>12.5631542205811</v>
+        <v>12.5631551742554</v>
       </c>
       <c r="H1204" t="n">
         <v>679077</v>
@@ -35343,7 +35343,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1206" t="n">
-        <v>13.2977304458618</v>
+        <v>13.2977313995361</v>
       </c>
       <c r="H1206" t="n">
         <v>229443</v>
@@ -35372,7 +35372,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G1207" t="n">
-        <v>13.7686128616333</v>
+        <v>13.7686138153076</v>
       </c>
       <c r="H1207" t="n">
         <v>124694</v>
@@ -35430,7 +35430,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1209" t="n">
-        <v>13.1470489501953</v>
+        <v>13.147047996521</v>
       </c>
       <c r="H1209" t="n">
         <v>158525</v>
@@ -35488,7 +35488,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1211" t="n">
-        <v>13.3730726242065</v>
+        <v>13.3730716705322</v>
       </c>
       <c r="H1211" t="n">
         <v>103432</v>
@@ -35546,7 +35546,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1213" t="n">
-        <v>13.2412261962891</v>
+        <v>13.2412242889404</v>
       </c>
       <c r="H1213" t="n">
         <v>127327</v>
@@ -35575,7 +35575,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1214" t="n">
-        <v>13.2412261962891</v>
+        <v>13.2412242889404</v>
       </c>
       <c r="H1214" t="n">
         <v>120947</v>
@@ -35662,7 +35662,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1217" t="n">
-        <v>13.3165655136108</v>
+        <v>13.3165664672852</v>
       </c>
       <c r="H1217" t="n">
         <v>212459</v>
@@ -35691,7 +35691,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1218" t="n">
-        <v>13.1470489501953</v>
+        <v>13.147047996521</v>
       </c>
       <c r="H1218" t="n">
         <v>203717</v>
@@ -35720,7 +35720,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G1219" t="n">
-        <v>12.9210252761841</v>
+        <v>12.9210243225098</v>
       </c>
       <c r="H1219" t="n">
         <v>126017</v>
@@ -35778,7 +35778,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1221" t="n">
-        <v>13.1470489501953</v>
+        <v>13.147047996521</v>
       </c>
       <c r="H1221" t="n">
         <v>113818</v>
@@ -35807,7 +35807,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1222" t="n">
-        <v>13.2788972854614</v>
+        <v>13.2788963317871</v>
       </c>
       <c r="H1222" t="n">
         <v>94561</v>
@@ -35923,7 +35923,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1226" t="n">
-        <v>13.2788972854614</v>
+        <v>13.2788963317871</v>
       </c>
       <c r="H1226" t="n">
         <v>74093</v>
@@ -36010,7 +36010,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1229" t="n">
-        <v>11.5837173461914</v>
+        <v>11.5837182998657</v>
       </c>
       <c r="H1229" t="n">
         <v>57369</v>
@@ -36068,7 +36068,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1231" t="n">
-        <v>11.9792604446411</v>
+        <v>11.9792594909668</v>
       </c>
       <c r="H1231" t="n">
         <v>93930</v>
@@ -36155,7 +36155,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1234" t="n">
-        <v>12.0545997619629</v>
+        <v>12.0546016693115</v>
       </c>
       <c r="H1234" t="n">
         <v>51769</v>
@@ -36184,7 +36184,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1235" t="n">
-        <v>12.3559656143188</v>
+        <v>12.3559646606445</v>
       </c>
       <c r="H1235" t="n">
         <v>78204</v>
@@ -36242,7 +36242,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1237" t="n">
-        <v>12.8080129623413</v>
+        <v>12.8080139160156</v>
       </c>
       <c r="H1237" t="n">
         <v>58147</v>
@@ -36271,7 +36271,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1238" t="n">
-        <v>12.7326717376709</v>
+        <v>12.7326726913452</v>
       </c>
       <c r="H1238" t="n">
         <v>59041</v>
@@ -36329,7 +36329,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1240" t="n">
-        <v>13.22239112854</v>
+        <v>13.2223901748657</v>
       </c>
       <c r="H1240" t="n">
         <v>81081</v>
@@ -36358,7 +36358,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1241" t="n">
-        <v>13.3542366027832</v>
+        <v>13.3542385101318</v>
       </c>
       <c r="H1241" t="n">
         <v>62691</v>
@@ -36387,7 +36387,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1242" t="n">
-        <v>13.467248916626</v>
+        <v>13.4672498703003</v>
       </c>
       <c r="H1242" t="n">
         <v>41536</v>
@@ -36445,7 +36445,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1244" t="n">
-        <v>13.2977304458618</v>
+        <v>13.2977313995361</v>
       </c>
       <c r="H1244" t="n">
         <v>77644</v>
@@ -36561,7 +36561,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1248" t="n">
-        <v>13.3548040390015</v>
+        <v>13.3548030853271</v>
       </c>
       <c r="H1248" t="n">
         <v>54674</v>
@@ -36648,7 +36648,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>13.4118757247925</v>
+        <v>13.4118747711182</v>
       </c>
       <c r="H1251" t="n">
         <v>48291</v>
@@ -36677,7 +36677,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1252" t="n">
-        <v>13.7543039321899</v>
+        <v>13.7543048858643</v>
       </c>
       <c r="H1252" t="n">
         <v>70314</v>
@@ -36764,7 +36764,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1255" t="n">
-        <v>14.077712059021</v>
+        <v>14.0777130126953</v>
       </c>
       <c r="H1255" t="n">
         <v>52106</v>
@@ -36793,7 +36793,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1256" t="n">
-        <v>14.0586862564087</v>
+        <v>14.0586881637573</v>
       </c>
       <c r="H1256" t="n">
         <v>46069</v>
@@ -36822,7 +36822,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1257" t="n">
-        <v>14.1157608032227</v>
+        <v>14.1157598495483</v>
       </c>
       <c r="H1257" t="n">
         <v>49558</v>
@@ -36851,7 +36851,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1258" t="n">
-        <v>13.88747215271</v>
+        <v>13.8874731063843</v>
       </c>
       <c r="H1258" t="n">
         <v>40359</v>
@@ -36909,7 +36909,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1260" t="n">
-        <v>13.3738269805908</v>
+        <v>13.3738260269165</v>
       </c>
       <c r="H1260" t="n">
         <v>24526</v>
@@ -36967,7 +36967,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1262" t="n">
-        <v>13.6782093048096</v>
+        <v>13.6782102584839</v>
       </c>
       <c r="H1262" t="n">
         <v>60708</v>
@@ -36996,7 +36996,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>13.5069942474365</v>
+        <v>13.5069932937622</v>
       </c>
       <c r="H1263" t="n">
         <v>33237</v>
@@ -37083,7 +37083,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1266" t="n">
-        <v>13.3738269805908</v>
+        <v>13.3738260269165</v>
       </c>
       <c r="H1266" t="n">
         <v>37045</v>
@@ -37141,7 +37141,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1268" t="n">
-        <v>13.6972322463989</v>
+        <v>13.6972332000732</v>
       </c>
       <c r="H1268" t="n">
         <v>31000</v>
@@ -37170,7 +37170,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G1269" t="n">
-        <v>13.6211376190186</v>
+        <v>13.6211366653442</v>
       </c>
       <c r="H1269" t="n">
         <v>34160</v>
@@ -37199,7 +37199,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1270" t="n">
-        <v>13.6782093048096</v>
+        <v>13.6782102584839</v>
       </c>
       <c r="H1270" t="n">
         <v>16047</v>
@@ -37228,7 +37228,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1271" t="n">
-        <v>13.7733297348022</v>
+        <v>13.7733287811279</v>
       </c>
       <c r="H1271" t="n">
         <v>69076</v>
@@ -37257,7 +37257,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1272" t="n">
-        <v>14.039665222168</v>
+        <v>14.0396642684937</v>
       </c>
       <c r="H1272" t="n">
         <v>37089</v>
@@ -37286,7 +37286,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1273" t="n">
-        <v>14.2489280700684</v>
+        <v>14.248927116394</v>
       </c>
       <c r="H1273" t="n">
         <v>56336</v>
@@ -37315,7 +37315,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G1274" t="n">
-        <v>14.6103830337524</v>
+        <v>14.6103820800781</v>
       </c>
       <c r="H1274" t="n">
         <v>54321</v>
@@ -37373,7 +37373,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1276" t="n">
-        <v>14.8957405090332</v>
+        <v>14.8957414627075</v>
       </c>
       <c r="H1276" t="n">
         <v>85533</v>
@@ -37402,7 +37402,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1277" t="n">
-        <v>14.9337892532349</v>
+        <v>14.9337882995605</v>
       </c>
       <c r="H1277" t="n">
         <v>79265</v>
@@ -37547,7 +37547,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1282" t="n">
-        <v>15.7137699127197</v>
+        <v>15.713770866394</v>
       </c>
       <c r="H1282" t="n">
         <v>43067</v>
@@ -37576,7 +37576,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1283" t="n">
-        <v>15.8469390869141</v>
+        <v>15.8469381332397</v>
       </c>
       <c r="H1283" t="n">
         <v>31129</v>
@@ -37663,7 +37663,7 @@
         <v>16</v>
       </c>
       <c r="G1286" t="n">
-        <v>15.2191476821899</v>
+        <v>15.2191486358643</v>
       </c>
       <c r="H1286" t="n">
         <v>39761</v>
@@ -37692,7 +37692,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1287" t="n">
-        <v>15.6376752853394</v>
+        <v>15.6376762390137</v>
       </c>
       <c r="H1287" t="n">
         <v>42862</v>
@@ -37750,7 +37750,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1289" t="n">
-        <v>15.3332920074463</v>
+        <v>15.3332929611206</v>
       </c>
       <c r="H1289" t="n">
         <v>27155</v>
@@ -37895,7 +37895,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1294" t="n">
-        <v>16.4937534332275</v>
+        <v>16.4937515258789</v>
       </c>
       <c r="H1294" t="n">
         <v>84980</v>
@@ -37982,7 +37982,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1297" t="n">
-        <v>16.5317993164062</v>
+        <v>16.5317974090576</v>
       </c>
       <c r="H1297" t="n">
         <v>35213</v>
@@ -38098,7 +38098,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1301" t="n">
-        <v>17.0264225006104</v>
+        <v>17.0264205932617</v>
       </c>
       <c r="H1301" t="n">
         <v>48425</v>
@@ -38214,7 +38214,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1305" t="n">
-        <v>16.3225364685059</v>
+        <v>16.3225383758545</v>
       </c>
       <c r="H1305" t="n">
         <v>83647</v>
@@ -38243,7 +38243,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1306" t="n">
-        <v>16.4937534332275</v>
+        <v>16.4937515258789</v>
       </c>
       <c r="H1306" t="n">
         <v>47420</v>
@@ -38272,7 +38272,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1307" t="n">
-        <v>16.4937534332275</v>
+        <v>16.4937515258789</v>
       </c>
       <c r="H1307" t="n">
         <v>55219</v>
@@ -38301,7 +38301,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1308" t="n">
-        <v>16.798131942749</v>
+        <v>16.7981338500977</v>
       </c>
       <c r="H1308" t="n">
         <v>75807</v>
@@ -38330,7 +38330,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1309" t="n">
-        <v>16.5508232116699</v>
+        <v>16.5508251190186</v>
       </c>
       <c r="H1309" t="n">
         <v>49669</v>
@@ -38446,7 +38446,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1313" t="n">
-        <v>16.81715965271</v>
+        <v>16.8171615600586</v>
       </c>
       <c r="H1313" t="n">
         <v>49919</v>
@@ -38475,7 +38475,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1314" t="n">
-        <v>16.5317993164062</v>
+        <v>16.5317974090576</v>
       </c>
       <c r="H1314" t="n">
         <v>57569</v>
@@ -38562,7 +38562,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1317" t="n">
-        <v>17.9585952758789</v>
+        <v>17.9585971832275</v>
       </c>
       <c r="H1317" t="n">
         <v>159566</v>
@@ -38678,7 +38678,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1321" t="n">
-        <v>19.78489112854</v>
+        <v>19.7848930358887</v>
       </c>
       <c r="H1321" t="n">
         <v>111249</v>
@@ -38707,7 +38707,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>20.1653728485107</v>
+        <v>20.1653709411621</v>
       </c>
       <c r="H1322" t="n">
         <v>187102</v>
@@ -38794,7 +38794,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1325" t="n">
-        <v>20.3556098937988</v>
+        <v>20.3556118011475</v>
       </c>
       <c r="H1325" t="n">
         <v>77087</v>
@@ -38997,7 +38997,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1332" t="n">
-        <v>20.2604885101318</v>
+        <v>20.2604904174805</v>
       </c>
       <c r="H1332" t="n">
         <v>45869</v>
@@ -39026,7 +39026,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1333" t="n">
-        <v>20.403169631958</v>
+        <v>20.4031715393066</v>
       </c>
       <c r="H1333" t="n">
         <v>119933</v>
@@ -39055,7 +39055,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>20.4982891082764</v>
+        <v>20.498291015625</v>
       </c>
       <c r="H1334" t="n">
         <v>39914</v>
@@ -39084,7 +39084,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1335" t="n">
-        <v>20.8312072753906</v>
+        <v>20.8312091827393</v>
       </c>
       <c r="H1335" t="n">
         <v>75131</v>
@@ -39142,7 +39142,7 @@
         <v>21.25</v>
       </c>
       <c r="G1337" t="n">
-        <v>20.2129325866699</v>
+        <v>20.2129306793213</v>
       </c>
       <c r="H1337" t="n">
         <v>32526</v>
@@ -39171,7 +39171,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>19.9275722503662</v>
+        <v>19.9275741577148</v>
       </c>
       <c r="H1338" t="n">
         <v>25422</v>
@@ -39345,7 +39345,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1344" t="n">
-        <v>20.3556098937988</v>
+        <v>20.3556118011475</v>
       </c>
       <c r="H1344" t="n">
         <v>43324</v>
@@ -39461,7 +39461,7 @@
         <v>21.25</v>
       </c>
       <c r="G1348" t="n">
-        <v>20.2129325866699</v>
+        <v>20.2129306793213</v>
       </c>
       <c r="H1348" t="n">
         <v>43561</v>
@@ -39548,7 +39548,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1351" t="n">
-        <v>19.2141761779785</v>
+        <v>19.2141742706299</v>
       </c>
       <c r="H1351" t="n">
         <v>82450</v>
@@ -39664,7 +39664,7 @@
         <v>20</v>
       </c>
       <c r="G1355" t="n">
-        <v>19.0239334106445</v>
+        <v>19.0239353179932</v>
       </c>
       <c r="H1355" t="n">
         <v>78898</v>
@@ -39809,7 +39809,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1360" t="n">
-        <v>20.3556098937988</v>
+        <v>20.3556118011475</v>
       </c>
       <c r="H1360" t="n">
         <v>60933</v>
@@ -39896,7 +39896,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1363" t="n">
-        <v>20.0702495574951</v>
+        <v>20.0702514648438</v>
       </c>
       <c r="H1363" t="n">
         <v>17815</v>
@@ -40128,7 +40128,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1371" t="n">
-        <v>20.3556098937988</v>
+        <v>20.3556118011475</v>
       </c>
       <c r="H1371" t="n">
         <v>30198</v>
@@ -40186,7 +40186,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1373" t="n">
-        <v>20.4982891082764</v>
+        <v>20.498291015625</v>
       </c>
       <c r="H1373" t="n">
         <v>44775</v>
@@ -40215,7 +40215,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1374" t="n">
-        <v>20.9738903045654</v>
+        <v>20.9738883972168</v>
       </c>
       <c r="H1374" t="n">
         <v>46334</v>
@@ -40244,7 +40244,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1375" t="n">
-        <v>21.5446033477783</v>
+        <v>21.544605255127</v>
       </c>
       <c r="H1375" t="n">
         <v>68470</v>
@@ -40273,7 +40273,7 @@
         <v>22.25</v>
       </c>
       <c r="G1376" t="n">
-        <v>21.1641292572021</v>
+        <v>21.1641273498535</v>
       </c>
       <c r="H1376" t="n">
         <v>44222</v>
@@ -40302,7 +40302,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1377" t="n">
-        <v>21.5446033477783</v>
+        <v>21.544605255127</v>
       </c>
       <c r="H1377" t="n">
         <v>80182</v>
@@ -40331,7 +40331,7 @@
         <v>22.75</v>
       </c>
       <c r="G1378" t="n">
-        <v>21.6397266387939</v>
+        <v>21.6397247314453</v>
       </c>
       <c r="H1378" t="n">
         <v>32323</v>
@@ -40389,7 +40389,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1380" t="n">
-        <v>21.6872863769531</v>
+        <v>21.6872844696045</v>
       </c>
       <c r="H1380" t="n">
         <v>51826</v>
@@ -40418,7 +40418,7 @@
         <v>22.5</v>
       </c>
       <c r="G1381" t="n">
-        <v>21.4019260406494</v>
+        <v>21.401927947998</v>
       </c>
       <c r="H1381" t="n">
         <v>80513</v>
@@ -40447,7 +40447,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1382" t="n">
-        <v>21.5446033477783</v>
+        <v>21.544605255127</v>
       </c>
       <c r="H1382" t="n">
         <v>74252</v>
@@ -40563,7 +40563,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>21.5446033477783</v>
+        <v>21.544605255127</v>
       </c>
       <c r="H1386" t="n">
         <v>37330</v>
@@ -40592,7 +40592,7 @@
         <v>22.5</v>
       </c>
       <c r="G1387" t="n">
-        <v>21.4019260406494</v>
+        <v>21.401927947998</v>
       </c>
       <c r="H1387" t="n">
         <v>149276</v>
@@ -40708,7 +40708,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1391" t="n">
-        <v>20.9738903045654</v>
+        <v>20.9738883972168</v>
       </c>
       <c r="H1391" t="n">
         <v>41158</v>
@@ -40737,7 +40737,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1392" t="n">
-        <v>21.2116889953613</v>
+        <v>21.2116870880127</v>
       </c>
       <c r="H1392" t="n">
         <v>40643</v>
@@ -40766,7 +40766,7 @@
         <v>22.75</v>
       </c>
       <c r="G1393" t="n">
-        <v>21.6397266387939</v>
+        <v>21.6397247314453</v>
       </c>
       <c r="H1393" t="n">
         <v>21232</v>
@@ -40795,7 +40795,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>21.2116889953613</v>
+        <v>21.2116870880127</v>
       </c>
       <c r="H1394" t="n">
         <v>25574</v>
@@ -40853,7 +40853,7 @@
         <v>22.25</v>
       </c>
       <c r="G1396" t="n">
-        <v>21.1641292572021</v>
+        <v>21.1641273498535</v>
       </c>
       <c r="H1396" t="n">
         <v>63716</v>
@@ -40911,7 +40911,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1398" t="n">
-        <v>22.6384830474854</v>
+        <v>22.6384811401367</v>
       </c>
       <c r="H1398" t="n">
         <v>114951</v>
@@ -40940,7 +40940,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>23.1616401672363</v>
+        <v>23.161642074585</v>
       </c>
       <c r="H1399" t="n">
         <v>67731</v>
@@ -41027,7 +41027,7 @@
         <v>22.5</v>
       </c>
       <c r="G1402" t="n">
-        <v>21.4019260406494</v>
+        <v>21.401927947998</v>
       </c>
       <c r="H1402" t="n">
         <v>71563</v>
@@ -41056,7 +41056,7 @@
         <v>23</v>
       </c>
       <c r="G1403" t="n">
-        <v>21.8775234222412</v>
+        <v>21.8775253295898</v>
       </c>
       <c r="H1403" t="n">
         <v>38196</v>
@@ -41201,7 +41201,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1408" t="n">
-        <v>21.2592468261719</v>
+        <v>21.2592506408691</v>
       </c>
       <c r="H1408" t="n">
         <v>31281</v>
@@ -41230,7 +41230,7 @@
         <v>21.75</v>
       </c>
       <c r="G1409" t="n">
-        <v>20.6885299682617</v>
+        <v>20.6885318756104</v>
       </c>
       <c r="H1409" t="n">
         <v>68569</v>
@@ -41259,7 +41259,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1410" t="n">
-        <v>20.6409721374512</v>
+        <v>20.6409702301025</v>
       </c>
       <c r="H1410" t="n">
         <v>41453</v>
@@ -41288,7 +41288,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1411" t="n">
-        <v>21.2592468261719</v>
+        <v>21.2592506408691</v>
       </c>
       <c r="H1411" t="n">
         <v>49262</v>
@@ -41317,7 +41317,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1412" t="n">
-        <v>21.2592468261719</v>
+        <v>21.2592506408691</v>
       </c>
       <c r="H1412" t="n">
         <v>30319</v>
@@ -41346,7 +41346,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G1413" t="n">
-        <v>21.5446033477783</v>
+        <v>21.544605255127</v>
       </c>
       <c r="H1413" t="n">
         <v>28728</v>
@@ -41375,7 +41375,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1414" t="n">
-        <v>21.7824058532715</v>
+        <v>21.7824039459229</v>
       </c>
       <c r="H1414" t="n">
         <v>31750</v>
@@ -41404,7 +41404,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1415" t="n">
-        <v>21.7824058532715</v>
+        <v>21.7824039459229</v>
       </c>
       <c r="H1415" t="n">
         <v>15907</v>
@@ -41433,7 +41433,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1416" t="n">
-        <v>22.6384830474854</v>
+        <v>22.6384811401367</v>
       </c>
       <c r="H1416" t="n">
         <v>84686</v>
@@ -41462,7 +41462,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1417" t="n">
-        <v>24.3506374359131</v>
+        <v>24.3506393432617</v>
       </c>
       <c r="H1417" t="n">
         <v>114064</v>
@@ -41491,7 +41491,7 @@
         <v>25</v>
       </c>
       <c r="G1418" t="n">
-        <v>23.7799205780029</v>
+        <v>23.7799186706543</v>
       </c>
       <c r="H1418" t="n">
         <v>94597</v>
@@ -41520,7 +41520,7 @@
         <v>24.5</v>
       </c>
       <c r="G1419" t="n">
-        <v>23.3043212890625</v>
+        <v>23.3043231964111</v>
       </c>
       <c r="H1419" t="n">
         <v>45529</v>
@@ -41549,7 +41549,7 @@
         <v>24.5</v>
       </c>
       <c r="G1420" t="n">
-        <v>23.3043212890625</v>
+        <v>23.3043231964111</v>
       </c>
       <c r="H1420" t="n">
         <v>34914</v>
@@ -41578,7 +41578,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>23.2567596435547</v>
+        <v>23.256763458252</v>
       </c>
       <c r="H1421" t="n">
         <v>49055</v>
@@ -41607,7 +41607,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G1422" t="n">
-        <v>23.1616401672363</v>
+        <v>23.161642074585</v>
       </c>
       <c r="H1422" t="n">
         <v>22597</v>
@@ -41636,7 +41636,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1423" t="n">
-        <v>23.0189628601074</v>
+        <v>23.0189609527588</v>
       </c>
       <c r="H1423" t="n">
         <v>27136</v>
@@ -41665,7 +41665,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>23.0189628601074</v>
+        <v>23.0189609527588</v>
       </c>
       <c r="H1424" t="n">
         <v>16295</v>
@@ -41781,7 +41781,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1428" t="n">
-        <v>23.5896778106689</v>
+        <v>23.5896797180176</v>
       </c>
       <c r="H1428" t="n">
         <v>48691</v>
@@ -41839,7 +41839,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1430" t="n">
-        <v>23.2567596435547</v>
+        <v>23.256763458252</v>
       </c>
       <c r="H1430" t="n">
         <v>24482</v>
@@ -41868,7 +41868,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1431" t="n">
-        <v>23.5896778106689</v>
+        <v>23.5896797180176</v>
       </c>
       <c r="H1431" t="n">
         <v>38396</v>
@@ -41955,7 +41955,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>23.1616401672363</v>
+        <v>23.161642074585</v>
       </c>
       <c r="H1434" t="n">
         <v>22385</v>
@@ -42013,7 +42013,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G1436" t="n">
-        <v>23.1616401672363</v>
+        <v>23.161642074585</v>
       </c>
       <c r="H1436" t="n">
         <v>6854</v>
@@ -42071,7 +42071,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>23.5896778106689</v>
+        <v>23.5896797180176</v>
       </c>
       <c r="H1438" t="n">
         <v>11644</v>
@@ -42100,7 +42100,7 @@
         <v>24.75</v>
       </c>
       <c r="G1439" t="n">
-        <v>23.5421199798584</v>
+        <v>23.542121887207</v>
       </c>
       <c r="H1439" t="n">
         <v>15683</v>
@@ -42129,7 +42129,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>23.4945621490479</v>
+        <v>23.4945602416992</v>
       </c>
       <c r="H1440" t="n">
         <v>14918</v>
@@ -42187,7 +42187,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1442" t="n">
-        <v>23.4945621490479</v>
+        <v>23.4945602416992</v>
       </c>
       <c r="H1442" t="n">
         <v>10407</v>
@@ -42216,7 +42216,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1443" t="n">
-        <v>23.2567596435547</v>
+        <v>23.256763458252</v>
       </c>
       <c r="H1443" t="n">
         <v>12029</v>
@@ -42245,7 +42245,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1444" t="n">
-        <v>23.2567596435547</v>
+        <v>23.256763458252</v>
       </c>
       <c r="H1444" t="n">
         <v>13098</v>
@@ -42274,7 +42274,7 @@
         <v>24.4500007629395</v>
       </c>
       <c r="G1445" t="n">
-        <v>23.2567596435547</v>
+        <v>23.256763458252</v>
       </c>
       <c r="H1445" t="n">
         <v>16636</v>
@@ -42303,7 +42303,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1446" t="n">
-        <v>22.6384830474854</v>
+        <v>22.6384811401367</v>
       </c>
       <c r="H1446" t="n">
         <v>39831</v>
@@ -42390,7 +42390,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1449" t="n">
-        <v>23.3994407653809</v>
+        <v>23.3994426727295</v>
       </c>
       <c r="H1449" t="n">
         <v>45794</v>
@@ -42419,7 +42419,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1450" t="n">
-        <v>23.0189628601074</v>
+        <v>23.0189609527588</v>
       </c>
       <c r="H1450" t="n">
         <v>57630</v>
@@ -42448,7 +42448,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>22.6860446929932</v>
+        <v>22.6860427856445</v>
       </c>
       <c r="H1451" t="n">
         <v>17980</v>
@@ -42477,7 +42477,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>22.4482460021973</v>
+        <v>22.4482440948486</v>
       </c>
       <c r="H1452" t="n">
         <v>36859</v>
@@ -42506,7 +42506,7 @@
         <v>23.25</v>
       </c>
       <c r="G1453" t="n">
-        <v>22.1153259277344</v>
+        <v>22.1153240203857</v>
       </c>
       <c r="H1453" t="n">
         <v>30904</v>
@@ -42622,7 +42622,7 @@
         <v>23.25</v>
       </c>
       <c r="G1457" t="n">
-        <v>22.1153259277344</v>
+        <v>22.1153240203857</v>
       </c>
       <c r="H1457" t="n">
         <v>23780</v>
@@ -42651,7 +42651,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1458" t="n">
-        <v>22.020206451416</v>
+        <v>22.0202045440674</v>
       </c>
       <c r="H1458" t="n">
         <v>20644</v>
@@ -42709,7 +42709,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1460" t="n">
-        <v>24.065279006958</v>
+        <v>24.0652770996094</v>
       </c>
       <c r="H1460" t="n">
         <v>328290</v>
@@ -42738,7 +42738,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>24.3506374359131</v>
+        <v>24.3506393432617</v>
       </c>
       <c r="H1461" t="n">
         <v>76766</v>
@@ -42796,7 +42796,7 @@
         <v>25.5499992370605</v>
       </c>
       <c r="G1463" t="n">
-        <v>24.3030757904053</v>
+        <v>24.3030796051025</v>
       </c>
       <c r="H1463" t="n">
         <v>46885</v>
@@ -42854,7 +42854,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1465" t="n">
-        <v>24.3506374359131</v>
+        <v>24.3506393432617</v>
       </c>
       <c r="H1465" t="n">
         <v>27274</v>
@@ -42941,7 +42941,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1468" t="n">
-        <v>25.3018360137939</v>
+        <v>25.3018341064453</v>
       </c>
       <c r="H1468" t="n">
         <v>174579</v>
@@ -42970,7 +42970,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1469" t="n">
-        <v>25.5871925354004</v>
+        <v>25.587194442749</v>
       </c>
       <c r="H1469" t="n">
         <v>59036</v>
@@ -42999,7 +42999,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1470" t="n">
-        <v>25.5871925354004</v>
+        <v>25.587194442749</v>
       </c>
       <c r="H1470" t="n">
         <v>32590</v>
@@ -43028,7 +43028,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>25.9676704406738</v>
+        <v>25.9676685333252</v>
       </c>
       <c r="H1471" t="n">
         <v>64417</v>
@@ -43057,7 +43057,7 @@
         <v>27</v>
       </c>
       <c r="G1472" t="n">
-        <v>25.6823101043701</v>
+        <v>25.6823120117188</v>
       </c>
       <c r="H1472" t="n">
         <v>71179</v>
@@ -43086,7 +43086,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1473" t="n">
-        <v>25.5871925354004</v>
+        <v>25.587194442749</v>
       </c>
       <c r="H1473" t="n">
         <v>69207</v>
@@ -43115,7 +43115,7 @@
         <v>27</v>
       </c>
       <c r="G1474" t="n">
-        <v>25.6823101043701</v>
+        <v>25.6823120117188</v>
       </c>
       <c r="H1474" t="n">
         <v>52662</v>
@@ -43231,7 +43231,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>26.3005905151367</v>
+        <v>26.3005886077881</v>
       </c>
       <c r="H1478" t="n">
         <v>120375</v>
@@ -43347,7 +43347,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>27.156665802002</v>
+        <v>27.1566677093506</v>
       </c>
       <c r="H1482" t="n">
         <v>48644</v>
@@ -43405,7 +43405,7 @@
         <v>29.75</v>
       </c>
       <c r="G1484" t="n">
-        <v>28.2981052398682</v>
+        <v>28.2981033325195</v>
       </c>
       <c r="H1484" t="n">
         <v>36314</v>
@@ -43434,7 +43434,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1485" t="n">
-        <v>27.7749443054199</v>
+        <v>27.7749462127686</v>
       </c>
       <c r="H1485" t="n">
         <v>107361</v>
@@ -43608,7 +43608,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1491" t="n">
-        <v>27.5371475219727</v>
+        <v>27.537145614624</v>
       </c>
       <c r="H1491" t="n">
         <v>43894</v>
@@ -43637,7 +43637,7 @@
         <v>28.75</v>
       </c>
       <c r="G1492" t="n">
-        <v>27.3469066619873</v>
+        <v>27.3469085693359</v>
       </c>
       <c r="H1492" t="n">
         <v>58069</v>
@@ -43695,7 +43695,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>26.7761878967285</v>
+        <v>26.7761898040771</v>
       </c>
       <c r="H1494" t="n">
         <v>34445</v>
@@ -43724,7 +43724,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1495" t="n">
-        <v>26.9664287567139</v>
+        <v>26.9664268493652</v>
       </c>
       <c r="H1495" t="n">
         <v>32902</v>
@@ -43753,7 +43753,7 @@
         <v>28.25</v>
       </c>
       <c r="G1496" t="n">
-        <v>26.8713092803955</v>
+        <v>26.8713073730469</v>
       </c>
       <c r="H1496" t="n">
         <v>60459</v>
@@ -43782,7 +43782,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1497" t="n">
-        <v>26.5383892059326</v>
+        <v>26.538387298584</v>
       </c>
       <c r="H1497" t="n">
         <v>48672</v>
@@ -43811,7 +43811,7 @@
         <v>28.25</v>
       </c>
       <c r="G1498" t="n">
-        <v>26.8713092803955</v>
+        <v>26.8713073730469</v>
       </c>
       <c r="H1498" t="n">
         <v>65385</v>
@@ -80009,6 +80009,35 @@
         <v>62597</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>51.4000015258789</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>50.2000007629395</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>41177</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAN.MI.xlsx
+++ b/data/DAN.MI.xlsx
@@ -427,7 +427,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>15.5902528762817</v>
+        <v>15.5902509689331</v>
       </c>
       <c r="H2" t="n">
         <v>57824</v>
@@ -485,7 +485,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2234230041504</v>
+        <v>15.2234239578247</v>
       </c>
       <c r="H4" t="n">
         <v>65319</v>
@@ -514,7 +514,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G5" t="n">
-        <v>14.5356159210205</v>
+        <v>14.5356168746948</v>
       </c>
       <c r="H5" t="n">
         <v>96087</v>
@@ -543,7 +543,7 @@
         <v>15.5</v>
       </c>
       <c r="G6" t="n">
-        <v>14.2146415710449</v>
+        <v>14.2146406173706</v>
       </c>
       <c r="H6" t="n">
         <v>81338</v>
@@ -601,7 +601,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G8" t="n">
-        <v>14.2880067825317</v>
+        <v>14.2880077362061</v>
       </c>
       <c r="H8" t="n">
         <v>64629</v>
@@ -659,7 +659,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G10" t="n">
-        <v>13.8661527633667</v>
+        <v>13.866153717041</v>
       </c>
       <c r="H10" t="n">
         <v>49474</v>
@@ -688,7 +688,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G11" t="n">
-        <v>13.1049823760986</v>
+        <v>13.1049833297729</v>
       </c>
       <c r="H11" t="n">
         <v>101980</v>
@@ -717,7 +717,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G12" t="n">
-        <v>12.7931756973267</v>
+        <v>12.7931776046753</v>
       </c>
       <c r="H12" t="n">
         <v>70420</v>
@@ -775,7 +775,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G14" t="n">
-        <v>12.2887868881226</v>
+        <v>12.2887887954712</v>
       </c>
       <c r="H14" t="n">
         <v>71385</v>
@@ -804,7 +804,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G15" t="n">
-        <v>12.9490804672241</v>
+        <v>12.9490795135498</v>
       </c>
       <c r="H15" t="n">
         <v>79009</v>
@@ -833,7 +833,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G16" t="n">
-        <v>13.132493019104</v>
+        <v>13.1324939727783</v>
       </c>
       <c r="H16" t="n">
         <v>85369</v>
@@ -862,7 +862,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G17" t="n">
-        <v>15.8928861618042</v>
+        <v>15.8928871154785</v>
       </c>
       <c r="H17" t="n">
         <v>376769</v>
@@ -891,7 +891,7 @@
         <v>17.5</v>
       </c>
       <c r="G18" t="n">
-        <v>16.0487880706787</v>
+        <v>16.0487899780273</v>
       </c>
       <c r="H18" t="n">
         <v>615324</v>
@@ -920,7 +920,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G19" t="n">
-        <v>16.3239097595215</v>
+        <v>16.3239078521729</v>
       </c>
       <c r="H19" t="n">
         <v>253918</v>
@@ -949,7 +949,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G20" t="n">
-        <v>16.0854721069336</v>
+        <v>16.0854740142822</v>
       </c>
       <c r="H20" t="n">
         <v>156267</v>
@@ -978,7 +978,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G21" t="n">
-        <v>16.3605937957764</v>
+        <v>16.360595703125</v>
       </c>
       <c r="H21" t="n">
         <v>116126</v>
@@ -1007,7 +1007,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G22" t="n">
-        <v>17.1125946044922</v>
+        <v>17.1125926971436</v>
       </c>
       <c r="H22" t="n">
         <v>392788</v>
@@ -1036,7 +1036,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>16.5990352630615</v>
+        <v>16.5990333557129</v>
       </c>
       <c r="H23" t="n">
         <v>490894</v>
@@ -1065,7 +1065,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G24" t="n">
-        <v>15.4710330963135</v>
+        <v>15.4710321426392</v>
       </c>
       <c r="H24" t="n">
         <v>293009</v>
@@ -1094,7 +1094,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G25" t="n">
-        <v>16.1038093566895</v>
+        <v>16.1038150787354</v>
       </c>
       <c r="H25" t="n">
         <v>137203</v>
@@ -1123,7 +1123,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G26" t="n">
-        <v>15.3059577941895</v>
+        <v>15.3059587478638</v>
       </c>
       <c r="H26" t="n">
         <v>118150</v>
@@ -1152,7 +1152,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G27" t="n">
-        <v>14.9391307830811</v>
+        <v>14.9391298294067</v>
       </c>
       <c r="H27" t="n">
         <v>147822</v>
@@ -1210,7 +1210,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G29" t="n">
-        <v>15.3518142700195</v>
+        <v>15.3518104553223</v>
       </c>
       <c r="H29" t="n">
         <v>133443</v>
@@ -1239,7 +1239,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G30" t="n">
-        <v>15.1042032241821</v>
+        <v>15.1042022705078</v>
       </c>
       <c r="H30" t="n">
         <v>42426</v>
@@ -1268,7 +1268,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G31" t="n">
-        <v>15.0033254623413</v>
+        <v>15.003324508667</v>
       </c>
       <c r="H31" t="n">
         <v>50728</v>
@@ -1326,7 +1326,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G33" t="n">
-        <v>16.2322025299072</v>
+        <v>16.2322063446045</v>
       </c>
       <c r="H33" t="n">
         <v>61554</v>
@@ -1413,7 +1413,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>17.0575675964355</v>
+        <v>17.0575695037842</v>
       </c>
       <c r="H36" t="n">
         <v>229585</v>
@@ -1442,7 +1442,7 @@
         <v>18.5</v>
       </c>
       <c r="G37" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H37" t="n">
         <v>111528</v>
@@ -1500,7 +1500,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G39" t="n">
-        <v>16.3605937957764</v>
+        <v>16.360595703125</v>
       </c>
       <c r="H39" t="n">
         <v>65595</v>
@@ -1558,7 +1558,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G41" t="n">
-        <v>16.1038093566895</v>
+        <v>16.1038150787354</v>
       </c>
       <c r="H41" t="n">
         <v>103694</v>
@@ -1587,7 +1587,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G42" t="n">
-        <v>16.3422508239746</v>
+        <v>16.3422546386719</v>
       </c>
       <c r="H42" t="n">
         <v>43527</v>
@@ -1616,7 +1616,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>16.8283004760742</v>
+        <v>16.8282985687256</v>
       </c>
       <c r="H43" t="n">
         <v>95437</v>
@@ -1645,7 +1645,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G44" t="n">
-        <v>16.6357135772705</v>
+        <v>16.6357154846191</v>
       </c>
       <c r="H44" t="n">
         <v>131715</v>
@@ -1703,7 +1703,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G46" t="n">
-        <v>17.3051815032959</v>
+        <v>17.3051776885986</v>
       </c>
       <c r="H46" t="n">
         <v>69241</v>
@@ -1732,7 +1732,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G47" t="n">
-        <v>17.3693714141846</v>
+        <v>17.3693771362305</v>
       </c>
       <c r="H47" t="n">
         <v>111422</v>
@@ -1761,7 +1761,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G48" t="n">
-        <v>17.4335708618164</v>
+        <v>17.4335689544678</v>
       </c>
       <c r="H48" t="n">
         <v>322204</v>
@@ -1790,7 +1790,7 @@
         <v>18.5</v>
       </c>
       <c r="G49" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H49" t="n">
         <v>55559</v>
@@ -1819,7 +1819,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G50" t="n">
-        <v>16.534839630127</v>
+        <v>16.5348415374756</v>
       </c>
       <c r="H50" t="n">
         <v>79172</v>
@@ -1848,7 +1848,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G51" t="n">
-        <v>17.2226448059082</v>
+        <v>17.2226409912109</v>
       </c>
       <c r="H51" t="n">
         <v>34164</v>
@@ -1877,7 +1877,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>17.5161094665527</v>
+        <v>17.5161037445068</v>
       </c>
       <c r="H52" t="n">
         <v>55267</v>
@@ -1906,7 +1906,7 @@
         <v>18.5</v>
       </c>
       <c r="G53" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H53" t="n">
         <v>23006</v>
@@ -1964,7 +1964,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G55" t="n">
-        <v>17.2593250274658</v>
+        <v>17.2593231201172</v>
       </c>
       <c r="H55" t="n">
         <v>37241</v>
@@ -1993,7 +1993,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G56" t="n">
-        <v>17.4610805511475</v>
+        <v>17.4610824584961</v>
       </c>
       <c r="H56" t="n">
         <v>30163</v>
@@ -2022,7 +2022,7 @@
         <v>18.5</v>
       </c>
       <c r="G57" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H57" t="n">
         <v>40462</v>
@@ -2051,7 +2051,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>17.0575675964355</v>
+        <v>17.0575695037842</v>
       </c>
       <c r="H58" t="n">
         <v>51915</v>
@@ -2080,7 +2080,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G59" t="n">
-        <v>17.0117149353027</v>
+        <v>17.0117130279541</v>
       </c>
       <c r="H59" t="n">
         <v>17205</v>
@@ -2138,7 +2138,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G61" t="n">
-        <v>16.5531806945801</v>
+        <v>16.5531787872314</v>
       </c>
       <c r="H61" t="n">
         <v>50561</v>
@@ -2167,7 +2167,7 @@
         <v>18.5</v>
       </c>
       <c r="G62" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H62" t="n">
         <v>31403</v>
@@ -2196,7 +2196,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G63" t="n">
-        <v>16.938346862793</v>
+        <v>16.9383525848389</v>
       </c>
       <c r="H63" t="n">
         <v>19939</v>
@@ -2254,7 +2254,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G65" t="n">
-        <v>17.2868404388428</v>
+        <v>17.2868385314941</v>
       </c>
       <c r="H65" t="n">
         <v>68353</v>
@@ -2283,7 +2283,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G66" t="n">
-        <v>16.5715198516846</v>
+        <v>16.5715236663818</v>
       </c>
       <c r="H66" t="n">
         <v>32129</v>
@@ -2341,7 +2341,7 @@
         <v>18.6700000762939</v>
       </c>
       <c r="G68" t="n">
-        <v>17.1217651367188</v>
+        <v>17.1217594146729</v>
       </c>
       <c r="H68" t="n">
         <v>54494</v>
@@ -2370,7 +2370,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>17.5619583129883</v>
+        <v>17.5619564056396</v>
       </c>
       <c r="H69" t="n">
         <v>83128</v>
@@ -2399,7 +2399,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>17.6353244781494</v>
+        <v>17.635326385498</v>
       </c>
       <c r="H70" t="n">
         <v>42644</v>
@@ -2428,7 +2428,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G71" t="n">
-        <v>17.4060573577881</v>
+        <v>17.4060592651367</v>
       </c>
       <c r="H71" t="n">
         <v>20298</v>
@@ -2457,7 +2457,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G72" t="n">
-        <v>17.8645935058594</v>
+        <v>17.864595413208</v>
       </c>
       <c r="H72" t="n">
         <v>69176</v>
@@ -2486,7 +2486,7 @@
         <v>19.75</v>
       </c>
       <c r="G73" t="n">
-        <v>18.1122055053711</v>
+        <v>18.1122035980225</v>
       </c>
       <c r="H73" t="n">
         <v>66473</v>
@@ -2515,7 +2515,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G74" t="n">
-        <v>18.0204982757568</v>
+        <v>18.0204963684082</v>
       </c>
       <c r="H74" t="n">
         <v>17233</v>
@@ -2544,7 +2544,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>17.7912273406982</v>
+        <v>17.7912292480469</v>
       </c>
       <c r="H75" t="n">
         <v>25659</v>
@@ -2573,7 +2573,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G76" t="n">
-        <v>17.5986442565918</v>
+        <v>17.5986404418945</v>
       </c>
       <c r="H76" t="n">
         <v>117794</v>
@@ -2602,7 +2602,7 @@
         <v>20</v>
       </c>
       <c r="G77" t="n">
-        <v>18.3414745330811</v>
+        <v>18.3414726257324</v>
       </c>
       <c r="H77" t="n">
         <v>97186</v>
@@ -2631,7 +2631,7 @@
         <v>20.0699996948242</v>
       </c>
       <c r="G78" t="n">
-        <v>18.4056644439697</v>
+        <v>18.4056663513184</v>
       </c>
       <c r="H78" t="n">
         <v>99094</v>
@@ -2689,7 +2689,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G80" t="n">
-        <v>18.0938625335693</v>
+        <v>18.0938606262207</v>
       </c>
       <c r="H80" t="n">
         <v>19099</v>
@@ -2718,7 +2718,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G81" t="n">
-        <v>18.3231334686279</v>
+        <v>18.3231315612793</v>
       </c>
       <c r="H81" t="n">
         <v>26322</v>
@@ -2747,7 +2747,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G82" t="n">
-        <v>18.029670715332</v>
+        <v>18.0296688079834</v>
       </c>
       <c r="H82" t="n">
         <v>13198</v>
@@ -2776,7 +2776,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>17.8921051025391</v>
+        <v>17.8921089172363</v>
       </c>
       <c r="H83" t="n">
         <v>58839</v>
@@ -2805,7 +2805,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>17.5619583129883</v>
+        <v>17.5619564056396</v>
       </c>
       <c r="H84" t="n">
         <v>37467</v>
@@ -2834,7 +2834,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G85" t="n">
-        <v>17.470251083374</v>
+        <v>17.4702491760254</v>
       </c>
       <c r="H85" t="n">
         <v>50865</v>
@@ -2863,7 +2863,7 @@
         <v>18.5</v>
       </c>
       <c r="G86" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H86" t="n">
         <v>48847</v>
@@ -2892,7 +2892,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G87" t="n">
-        <v>17.1492767333984</v>
+        <v>17.1492786407471</v>
       </c>
       <c r="H87" t="n">
         <v>16818</v>
@@ -3008,7 +3008,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G91" t="n">
-        <v>16.7732791900635</v>
+        <v>16.7732772827148</v>
       </c>
       <c r="H91" t="n">
         <v>20209</v>
@@ -3037,7 +3037,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G92" t="n">
-        <v>16.837474822998</v>
+        <v>16.8374691009521</v>
       </c>
       <c r="H92" t="n">
         <v>18052</v>
@@ -3095,7 +3095,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G94" t="n">
-        <v>16.3147430419922</v>
+        <v>16.3147411346436</v>
       </c>
       <c r="H94" t="n">
         <v>55875</v>
@@ -3124,7 +3124,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G95" t="n">
-        <v>16.1496658325195</v>
+        <v>16.1496677398682</v>
       </c>
       <c r="H95" t="n">
         <v>14197</v>
@@ -3153,7 +3153,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G96" t="n">
-        <v>16.250545501709</v>
+        <v>16.2505435943604</v>
       </c>
       <c r="H96" t="n">
         <v>36784</v>
@@ -3211,7 +3211,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G98" t="n">
-        <v>16.452299118042</v>
+        <v>16.4523029327393</v>
       </c>
       <c r="H98" t="n">
         <v>15133</v>
@@ -3240,7 +3240,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G99" t="n">
-        <v>16.415620803833</v>
+        <v>16.4156188964844</v>
       </c>
       <c r="H99" t="n">
         <v>11742</v>
@@ -3269,7 +3269,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G100" t="n">
-        <v>16.1680068969727</v>
+        <v>16.168004989624</v>
       </c>
       <c r="H100" t="n">
         <v>37522</v>
@@ -3356,7 +3356,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G103" t="n">
-        <v>17.360200881958</v>
+        <v>17.3602046966553</v>
       </c>
       <c r="H103" t="n">
         <v>81800</v>
@@ -3385,7 +3385,7 @@
         <v>18.8700008392334</v>
       </c>
       <c r="G104" t="n">
-        <v>17.3051815032959</v>
+        <v>17.3051776885986</v>
       </c>
       <c r="H104" t="n">
         <v>65612</v>
@@ -3414,7 +3414,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G105" t="n">
-        <v>17.1492767333984</v>
+        <v>17.1492786407471</v>
       </c>
       <c r="H105" t="n">
         <v>9668</v>
@@ -3443,7 +3443,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G106" t="n">
-        <v>16.5164966583252</v>
+        <v>16.5164985656738</v>
       </c>
       <c r="H106" t="n">
         <v>55198</v>
@@ -3530,7 +3530,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G109" t="n">
-        <v>17.0117149353027</v>
+        <v>17.0117130279541</v>
       </c>
       <c r="H109" t="n">
         <v>13742</v>
@@ -3588,7 +3588,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G111" t="n">
-        <v>17.0392265319824</v>
+        <v>17.0392284393311</v>
       </c>
       <c r="H111" t="n">
         <v>4487</v>
@@ -3646,7 +3646,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G113" t="n">
-        <v>16.7732791900635</v>
+        <v>16.7732772827148</v>
       </c>
       <c r="H113" t="n">
         <v>25389</v>
@@ -3675,7 +3675,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>16.415620803833</v>
+        <v>16.4156188964844</v>
       </c>
       <c r="H114" t="n">
         <v>28373</v>
@@ -3704,7 +3704,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G115" t="n">
-        <v>15.8103513717651</v>
+        <v>15.8103485107422</v>
       </c>
       <c r="H115" t="n">
         <v>104335</v>
@@ -3733,7 +3733,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G116" t="n">
-        <v>15.8470344543457</v>
+        <v>15.8470363616943</v>
       </c>
       <c r="H116" t="n">
         <v>50453</v>
@@ -3762,7 +3762,7 @@
         <v>17</v>
       </c>
       <c r="G117" t="n">
-        <v>15.5902528762817</v>
+        <v>15.5902509689331</v>
       </c>
       <c r="H117" t="n">
         <v>74690</v>
@@ -3791,7 +3791,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G118" t="n">
-        <v>14.9574689865112</v>
+        <v>14.9574708938599</v>
       </c>
       <c r="H118" t="n">
         <v>117400</v>
@@ -3820,7 +3820,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G119" t="n">
-        <v>14.7648859024048</v>
+        <v>14.7648868560791</v>
       </c>
       <c r="H119" t="n">
         <v>97119</v>
@@ -3849,7 +3849,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G120" t="n">
-        <v>15.0675191879272</v>
+        <v>15.0675210952759</v>
       </c>
       <c r="H120" t="n">
         <v>58276</v>
@@ -3878,7 +3878,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G121" t="n">
-        <v>15.3334712982178</v>
+        <v>15.3334684371948</v>
       </c>
       <c r="H121" t="n">
         <v>77133</v>
@@ -3907,7 +3907,7 @@
         <v>17</v>
       </c>
       <c r="G122" t="n">
-        <v>15.5902528762817</v>
+        <v>15.5902509689331</v>
       </c>
       <c r="H122" t="n">
         <v>45027</v>
@@ -3936,7 +3936,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G123" t="n">
-        <v>15.9570817947388</v>
+        <v>15.9570789337158</v>
       </c>
       <c r="H123" t="n">
         <v>25684</v>
@@ -3965,7 +3965,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G124" t="n">
-        <v>14.9849843978882</v>
+        <v>14.9849834442139</v>
       </c>
       <c r="H124" t="n">
         <v>97441</v>
@@ -4023,7 +4023,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G126" t="n">
-        <v>14.8841037750244</v>
+        <v>14.8841047286987</v>
       </c>
       <c r="H126" t="n">
         <v>70918</v>
@@ -4052,7 +4052,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G127" t="n">
-        <v>14.5264463424683</v>
+        <v>14.5264453887939</v>
       </c>
       <c r="H127" t="n">
         <v>39264</v>
@@ -4110,7 +4110,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G129" t="n">
-        <v>15.4068355560303</v>
+        <v>15.4068365097046</v>
       </c>
       <c r="H129" t="n">
         <v>31770</v>
@@ -4226,7 +4226,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>14.2604951858521</v>
+        <v>14.2604961395264</v>
       </c>
       <c r="H133" t="n">
         <v>11274</v>
@@ -4255,7 +4255,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G134" t="n">
-        <v>14.6548366546631</v>
+        <v>14.6548337936401</v>
       </c>
       <c r="H134" t="n">
         <v>19776</v>
@@ -4284,7 +4284,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G135" t="n">
-        <v>15.397668838501</v>
+        <v>15.3976669311523</v>
       </c>
       <c r="H135" t="n">
         <v>37687</v>
@@ -4342,7 +4342,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>15.2234230041504</v>
+        <v>15.2234239578247</v>
       </c>
       <c r="H137" t="n">
         <v>26494</v>
@@ -4371,7 +4371,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>15.4985418319702</v>
+        <v>15.4985446929932</v>
       </c>
       <c r="H138" t="n">
         <v>25530</v>
@@ -4400,7 +4400,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G139" t="n">
-        <v>15.3518142700195</v>
+        <v>15.3518104553223</v>
       </c>
       <c r="H139" t="n">
         <v>35750</v>
@@ -4458,7 +4458,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G141" t="n">
-        <v>15.2509326934814</v>
+        <v>15.2509346008301</v>
       </c>
       <c r="H141" t="n">
         <v>13555</v>
@@ -4487,7 +4487,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G142" t="n">
-        <v>15.3242979049683</v>
+        <v>15.3242998123169</v>
       </c>
       <c r="H142" t="n">
         <v>24507</v>
@@ -4516,7 +4516,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G143" t="n">
-        <v>15.2967872619629</v>
+        <v>15.2967891693115</v>
       </c>
       <c r="H143" t="n">
         <v>24347</v>
@@ -4545,7 +4545,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G144" t="n">
-        <v>15.3793258666992</v>
+        <v>15.3793239593506</v>
       </c>
       <c r="H144" t="n">
         <v>13919</v>
@@ -4574,7 +4574,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>15.4985418319702</v>
+        <v>15.4985446929932</v>
       </c>
       <c r="H145" t="n">
         <v>30704</v>
@@ -4603,7 +4603,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>15.4985418319702</v>
+        <v>15.4985446929932</v>
       </c>
       <c r="H146" t="n">
         <v>31317</v>
@@ -4632,7 +4632,7 @@
         <v>17.5</v>
       </c>
       <c r="G147" t="n">
-        <v>16.0487880706787</v>
+        <v>16.0487899780273</v>
       </c>
       <c r="H147" t="n">
         <v>68976</v>
@@ -4690,7 +4690,7 @@
         <v>17.6299991607666</v>
       </c>
       <c r="G149" t="n">
-        <v>16.1680068969727</v>
+        <v>16.168004989624</v>
       </c>
       <c r="H149" t="n">
         <v>30727</v>
@@ -4719,7 +4719,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>16.1404933929443</v>
+        <v>16.1404972076416</v>
       </c>
       <c r="H150" t="n">
         <v>41609</v>
@@ -4748,7 +4748,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G151" t="n">
-        <v>15.6177635192871</v>
+        <v>15.6177625656128</v>
       </c>
       <c r="H151" t="n">
         <v>37397</v>
@@ -4806,7 +4806,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>15.2234230041504</v>
+        <v>15.2234239578247</v>
       </c>
       <c r="H153" t="n">
         <v>23169</v>
@@ -4922,7 +4922,7 @@
         <v>17.5</v>
       </c>
       <c r="G157" t="n">
-        <v>16.0487880706787</v>
+        <v>16.0487899780273</v>
       </c>
       <c r="H157" t="n">
         <v>8450</v>
@@ -4980,7 +4980,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G159" t="n">
-        <v>16.1038093566895</v>
+        <v>16.1038150787354</v>
       </c>
       <c r="H159" t="n">
         <v>40283</v>
@@ -5009,7 +5009,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G160" t="n">
-        <v>15.8470344543457</v>
+        <v>15.8470363616943</v>
       </c>
       <c r="H160" t="n">
         <v>34139</v>
@@ -5038,7 +5038,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G161" t="n">
-        <v>16.0671329498291</v>
+        <v>16.0671310424805</v>
       </c>
       <c r="H161" t="n">
         <v>32087</v>
@@ -5067,7 +5067,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G162" t="n">
-        <v>15.9845905303955</v>
+        <v>15.9845924377441</v>
       </c>
       <c r="H162" t="n">
         <v>27116</v>
@@ -5096,7 +5096,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>16.415620803833</v>
+        <v>16.4156188964844</v>
       </c>
       <c r="H163" t="n">
         <v>33297</v>
@@ -5125,7 +5125,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G164" t="n">
-        <v>17.1401062011719</v>
+        <v>17.1401042938232</v>
       </c>
       <c r="H164" t="n">
         <v>61398</v>
@@ -5154,7 +5154,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G165" t="n">
-        <v>16.8099594116211</v>
+        <v>16.8099575042725</v>
       </c>
       <c r="H165" t="n">
         <v>28597</v>
@@ -5183,7 +5183,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G166" t="n">
-        <v>16.8099594116211</v>
+        <v>16.8099575042725</v>
       </c>
       <c r="H166" t="n">
         <v>21263</v>
@@ -5212,7 +5212,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G167" t="n">
-        <v>16.6082057952881</v>
+        <v>16.6082038879395</v>
       </c>
       <c r="H167" t="n">
         <v>4393</v>
@@ -5270,7 +5270,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G169" t="n">
-        <v>16.6448841094971</v>
+        <v>16.644889831543</v>
       </c>
       <c r="H169" t="n">
         <v>11997</v>
@@ -5299,7 +5299,7 @@
         <v>18.5</v>
       </c>
       <c r="G170" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H170" t="n">
         <v>28535</v>
@@ -5328,7 +5328,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G171" t="n">
-        <v>17.6078147888184</v>
+        <v>17.6078128814697</v>
       </c>
       <c r="H171" t="n">
         <v>76322</v>
@@ -5357,7 +5357,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>17.1492767333984</v>
+        <v>17.1492786407471</v>
       </c>
       <c r="H172" t="n">
         <v>36526</v>
@@ -5415,7 +5415,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G174" t="n">
-        <v>17.158447265625</v>
+        <v>17.1584434509277</v>
       </c>
       <c r="H174" t="n">
         <v>31232</v>
@@ -5444,7 +5444,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G175" t="n">
-        <v>17.2868404388428</v>
+        <v>17.2868385314941</v>
       </c>
       <c r="H175" t="n">
         <v>29071</v>
@@ -5473,7 +5473,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>17.2868404388428</v>
+        <v>17.2868385314941</v>
       </c>
       <c r="H176" t="n">
         <v>30183</v>
@@ -5502,7 +5502,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>17.2868404388428</v>
+        <v>17.2868385314941</v>
       </c>
       <c r="H177" t="n">
         <v>17333</v>
@@ -5531,7 +5531,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G178" t="n">
-        <v>17.4060573577881</v>
+        <v>17.4060592651367</v>
       </c>
       <c r="H178" t="n">
         <v>13916</v>
@@ -5589,7 +5589,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G180" t="n">
-        <v>17.0300559997559</v>
+        <v>17.0300579071045</v>
       </c>
       <c r="H180" t="n">
         <v>9227</v>
@@ -5618,7 +5618,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G181" t="n">
-        <v>17.2226448059082</v>
+        <v>17.2226409912109</v>
       </c>
       <c r="H181" t="n">
         <v>23636</v>
@@ -5647,7 +5647,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G182" t="n">
-        <v>17.4610805511475</v>
+        <v>17.4610824584961</v>
       </c>
       <c r="H182" t="n">
         <v>15383</v>
@@ -5676,7 +5676,7 @@
         <v>18.75</v>
       </c>
       <c r="G183" t="n">
-        <v>17.1951313018799</v>
+        <v>17.1951293945312</v>
       </c>
       <c r="H183" t="n">
         <v>26910</v>
@@ -5734,7 +5734,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G185" t="n">
-        <v>17.0575675964355</v>
+        <v>17.0575695037842</v>
       </c>
       <c r="H185" t="n">
         <v>9398</v>
@@ -5792,7 +5792,7 @@
         <v>18.5</v>
       </c>
       <c r="G187" t="n">
-        <v>16.9658622741699</v>
+        <v>16.9658603668213</v>
       </c>
       <c r="H187" t="n">
         <v>39369</v>
@@ -5821,7 +5821,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G188" t="n">
-        <v>17.0300559997559</v>
+        <v>17.0300579071045</v>
       </c>
       <c r="H188" t="n">
         <v>3253</v>
@@ -5908,7 +5908,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G191" t="n">
-        <v>15.7828369140625</v>
+        <v>15.7828388214111</v>
       </c>
       <c r="H191" t="n">
         <v>119969</v>
@@ -5937,7 +5937,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G192" t="n">
-        <v>15.7828369140625</v>
+        <v>15.7828388214111</v>
       </c>
       <c r="H192" t="n">
         <v>32497</v>
@@ -5966,7 +5966,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G193" t="n">
-        <v>15.7553253173828</v>
+        <v>15.7553262710571</v>
       </c>
       <c r="H193" t="n">
         <v>20971</v>
@@ -5995,7 +5995,7 @@
         <v>17.25</v>
       </c>
       <c r="G194" t="n">
-        <v>15.8195199966431</v>
+        <v>15.8195209503174</v>
       </c>
       <c r="H194" t="n">
         <v>39194</v>
@@ -6053,7 +6053,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G196" t="n">
-        <v>15.9479093551636</v>
+        <v>15.9479103088379</v>
       </c>
       <c r="H196" t="n">
         <v>26230</v>
@@ -6082,7 +6082,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G197" t="n">
-        <v>15.8470344543457</v>
+        <v>15.8470363616943</v>
       </c>
       <c r="H197" t="n">
         <v>27826</v>
@@ -6111,7 +6111,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>15.6361026763916</v>
+        <v>15.6361045837402</v>
       </c>
       <c r="H198" t="n">
         <v>38344</v>
@@ -6140,7 +6140,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G199" t="n">
-        <v>15.6636152267456</v>
+        <v>15.6636180877686</v>
       </c>
       <c r="H199" t="n">
         <v>15286</v>
@@ -6169,7 +6169,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>15.4985418319702</v>
+        <v>15.4985446929932</v>
       </c>
       <c r="H200" t="n">
         <v>26596</v>
@@ -6198,7 +6198,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G201" t="n">
-        <v>15.5627384185791</v>
+        <v>15.5627403259277</v>
       </c>
       <c r="H201" t="n">
         <v>28742</v>
@@ -6227,7 +6227,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G202" t="n">
-        <v>15.4893732070923</v>
+        <v>15.4893703460693</v>
       </c>
       <c r="H202" t="n">
         <v>13901</v>
@@ -6256,7 +6256,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G203" t="n">
-        <v>15.6085948944092</v>
+        <v>15.6085920333862</v>
       </c>
       <c r="H203" t="n">
         <v>14432</v>
@@ -6285,7 +6285,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>15.6361026763916</v>
+        <v>15.6361045837402</v>
       </c>
       <c r="H204" t="n">
         <v>11898</v>
@@ -6314,7 +6314,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G205" t="n">
-        <v>15.7553253173828</v>
+        <v>15.7553262710571</v>
       </c>
       <c r="H205" t="n">
         <v>20290</v>
@@ -6343,7 +6343,7 @@
         <v>17.25</v>
       </c>
       <c r="G206" t="n">
-        <v>15.8195199966431</v>
+        <v>15.8195209503174</v>
       </c>
       <c r="H206" t="n">
         <v>15108</v>
@@ -6459,7 +6459,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G210" t="n">
-        <v>16.0579624176025</v>
+        <v>16.0579643249512</v>
       </c>
       <c r="H210" t="n">
         <v>31814</v>
@@ -6488,7 +6488,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G211" t="n">
-        <v>15.5352258682251</v>
+        <v>15.5352268218994</v>
       </c>
       <c r="H211" t="n">
         <v>104198</v>
@@ -6517,7 +6517,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G212" t="n">
-        <v>15.5443983078003</v>
+        <v>15.5443992614746</v>
       </c>
       <c r="H212" t="n">
         <v>15697</v>
@@ -6546,7 +6546,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G213" t="n">
-        <v>15.7003030776978</v>
+        <v>15.7003002166748</v>
       </c>
       <c r="H213" t="n">
         <v>29571</v>
@@ -6575,7 +6575,7 @@
         <v>17</v>
       </c>
       <c r="G214" t="n">
-        <v>15.5902528762817</v>
+        <v>15.5902509689331</v>
       </c>
       <c r="H214" t="n">
         <v>9819</v>
@@ -6604,7 +6604,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>15.5443983078003</v>
+        <v>15.5443992614746</v>
       </c>
       <c r="H215" t="n">
         <v>10667</v>
@@ -6633,7 +6633,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>15.4068355560303</v>
+        <v>15.4068365097046</v>
       </c>
       <c r="H216" t="n">
         <v>23788</v>
@@ -6662,7 +6662,7 @@
         <v>16.75</v>
       </c>
       <c r="G217" t="n">
-        <v>15.3609848022461</v>
+        <v>15.3609838485718</v>
       </c>
       <c r="H217" t="n">
         <v>17451</v>
@@ -6691,7 +6691,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G218" t="n">
-        <v>15.1592292785645</v>
+        <v>15.1592264175415</v>
       </c>
       <c r="H218" t="n">
         <v>13732</v>
@@ -6749,7 +6749,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G220" t="n">
-        <v>15.3068542480469</v>
+        <v>15.3068513870239</v>
       </c>
       <c r="H220" t="n">
         <v>5766</v>
@@ -6778,7 +6778,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>15.546745300293</v>
+        <v>15.5467443466187</v>
       </c>
       <c r="H221" t="n">
         <v>22485</v>
@@ -6807,7 +6807,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G222" t="n">
-        <v>15.6297798156738</v>
+        <v>15.6297817230225</v>
       </c>
       <c r="H222" t="n">
         <v>22396</v>
@@ -6836,7 +6836,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G223" t="n">
-        <v>15.7866353988647</v>
+        <v>15.7866344451904</v>
       </c>
       <c r="H223" t="n">
         <v>18529</v>
@@ -6865,7 +6865,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G224" t="n">
-        <v>15.5190601348877</v>
+        <v>15.5190649032593</v>
       </c>
       <c r="H224" t="n">
         <v>12930</v>
@@ -6923,7 +6923,7 @@
         <v>16.6100006103516</v>
       </c>
       <c r="G226" t="n">
-        <v>15.325306892395</v>
+        <v>15.3253049850464</v>
       </c>
       <c r="H226" t="n">
         <v>16757</v>
@@ -6952,7 +6952,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G227" t="n">
-        <v>15.4175682067871</v>
+        <v>15.4175710678101</v>
       </c>
       <c r="H227" t="n">
         <v>23714</v>
@@ -6981,7 +6981,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G228" t="n">
-        <v>15.4083452224731</v>
+        <v>15.4083461761475</v>
       </c>
       <c r="H228" t="n">
         <v>7063</v>
@@ -7010,7 +7010,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G229" t="n">
-        <v>15.0577344894409</v>
+        <v>15.0577373504639</v>
       </c>
       <c r="H229" t="n">
         <v>21791</v>
@@ -7039,7 +7039,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G230" t="n">
-        <v>15.7589511871338</v>
+        <v>15.7589550018311</v>
       </c>
       <c r="H230" t="n">
         <v>26262</v>
@@ -7097,7 +7097,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G232" t="n">
-        <v>15.8235378265381</v>
+        <v>15.8235387802124</v>
       </c>
       <c r="H232" t="n">
         <v>10075</v>
@@ -7126,7 +7126,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G233" t="n">
-        <v>15.3898916244507</v>
+        <v>15.389892578125</v>
       </c>
       <c r="H233" t="n">
         <v>13313</v>
@@ -7155,7 +7155,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>15.5006074905396</v>
+        <v>15.5006103515625</v>
       </c>
       <c r="H234" t="n">
         <v>38423</v>
@@ -7242,7 +7242,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G237" t="n">
-        <v>15.9434852600098</v>
+        <v>15.9434871673584</v>
       </c>
       <c r="H237" t="n">
         <v>20608</v>
@@ -7271,7 +7271,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G238" t="n">
-        <v>15.8235378265381</v>
+        <v>15.8235387802124</v>
       </c>
       <c r="H238" t="n">
         <v>32816</v>
@@ -7300,7 +7300,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>15.7312717437744</v>
+        <v>15.731273651123</v>
       </c>
       <c r="H239" t="n">
         <v>13860</v>
@@ -7358,7 +7358,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G241" t="n">
-        <v>16.4693984985352</v>
+        <v>16.4693965911865</v>
       </c>
       <c r="H241" t="n">
         <v>43580</v>
@@ -7387,7 +7387,7 @@
         <v>18.5</v>
       </c>
       <c r="G242" t="n">
-        <v>17.0691261291504</v>
+        <v>17.0691242218018</v>
       </c>
       <c r="H242" t="n">
         <v>48602</v>
@@ -7416,7 +7416,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G243" t="n">
-        <v>17.1429309844971</v>
+        <v>17.142936706543</v>
       </c>
       <c r="H243" t="n">
         <v>41612</v>
@@ -7445,7 +7445,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G244" t="n">
-        <v>17.0229911804199</v>
+        <v>17.0229949951172</v>
       </c>
       <c r="H244" t="n">
         <v>26797</v>
@@ -7474,7 +7474,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G245" t="n">
-        <v>17.1060333251953</v>
+        <v>17.1060314178467</v>
       </c>
       <c r="H245" t="n">
         <v>36816</v>
@@ -7532,7 +7532,7 @@
         <v>18.25</v>
       </c>
       <c r="G247" t="n">
-        <v>16.8384609222412</v>
+        <v>16.8384590148926</v>
       </c>
       <c r="H247" t="n">
         <v>14036</v>
@@ -7619,7 +7619,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>16.7923240661621</v>
+        <v>16.7923278808594</v>
       </c>
       <c r="H250" t="n">
         <v>17496</v>
@@ -7677,7 +7677,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>17.6227188110352</v>
+        <v>17.6227169036865</v>
       </c>
       <c r="H252" t="n">
         <v>152617</v>
@@ -7706,7 +7706,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G253" t="n">
-        <v>17.7795696258545</v>
+        <v>17.7795677185059</v>
       </c>
       <c r="H253" t="n">
         <v>63110</v>
@@ -7735,7 +7735,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>17.6227188110352</v>
+        <v>17.6227169036865</v>
       </c>
       <c r="H254" t="n">
         <v>33338</v>
@@ -7764,7 +7764,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G255" t="n">
-        <v>17.8164749145508</v>
+        <v>17.8164768218994</v>
       </c>
       <c r="H255" t="n">
         <v>30009</v>
@@ -7822,7 +7822,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G257" t="n">
-        <v>17.8164749145508</v>
+        <v>17.8164768218994</v>
       </c>
       <c r="H257" t="n">
         <v>21070</v>
@@ -7851,7 +7851,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G258" t="n">
-        <v>18.3054809570312</v>
+        <v>18.3054828643799</v>
       </c>
       <c r="H258" t="n">
         <v>77282</v>
@@ -7880,7 +7880,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G259" t="n">
-        <v>18.7760353088379</v>
+        <v>18.7760372161865</v>
       </c>
       <c r="H259" t="n">
         <v>73997</v>
@@ -7909,7 +7909,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>18.8221683502197</v>
+        <v>18.8221664428711</v>
       </c>
       <c r="H260" t="n">
         <v>29111</v>
@@ -7938,7 +7938,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G261" t="n">
-        <v>19.4218940734863</v>
+        <v>19.4218902587891</v>
       </c>
       <c r="H261" t="n">
         <v>109705</v>
@@ -7967,7 +7967,7 @@
         <v>21.1299991607666</v>
       </c>
       <c r="G262" t="n">
-        <v>19.4957065582275</v>
+        <v>19.4957046508789</v>
       </c>
       <c r="H262" t="n">
         <v>36901</v>
@@ -7996,7 +7996,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G263" t="n">
-        <v>18.9882507324219</v>
+        <v>18.9882469177246</v>
       </c>
       <c r="H263" t="n">
         <v>64025</v>
@@ -8025,7 +8025,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G264" t="n">
-        <v>18.7852611541748</v>
+        <v>18.7852630615234</v>
       </c>
       <c r="H264" t="n">
         <v>61276</v>
@@ -8054,7 +8054,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>19.3296298980713</v>
+        <v>19.3296318054199</v>
       </c>
       <c r="H265" t="n">
         <v>75197</v>
@@ -8083,7 +8083,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G266" t="n">
-        <v>19.2004566192627</v>
+        <v>19.2004585266113</v>
       </c>
       <c r="H266" t="n">
         <v>44437</v>
@@ -8112,7 +8112,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G267" t="n">
-        <v>19.0528335571289</v>
+        <v>19.0528354644775</v>
       </c>
       <c r="H267" t="n">
         <v>21370</v>
@@ -8141,7 +8141,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G268" t="n">
-        <v>18.9513416290283</v>
+        <v>18.9513397216797</v>
       </c>
       <c r="H268" t="n">
         <v>24551</v>
@@ -8170,7 +8170,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>18.7299041748047</v>
+        <v>18.7299022674561</v>
       </c>
       <c r="H269" t="n">
         <v>28479</v>
@@ -8199,7 +8199,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G270" t="n">
-        <v>18.886754989624</v>
+        <v>18.8867568969727</v>
       </c>
       <c r="H270" t="n">
         <v>22743</v>
@@ -8228,7 +8228,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G271" t="n">
-        <v>18.8129405975342</v>
+        <v>18.8129425048828</v>
       </c>
       <c r="H271" t="n">
         <v>18271</v>
@@ -8257,7 +8257,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G272" t="n">
-        <v>18.8037166595459</v>
+        <v>18.8037109375</v>
       </c>
       <c r="H272" t="n">
         <v>21264</v>
@@ -8286,7 +8286,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G273" t="n">
-        <v>18.6284160614014</v>
+        <v>18.6284141540527</v>
       </c>
       <c r="H273" t="n">
         <v>23196</v>
@@ -8315,7 +8315,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>18.7299041748047</v>
+        <v>18.7299022674561</v>
       </c>
       <c r="H274" t="n">
         <v>12986</v>
@@ -8344,7 +8344,7 @@
         <v>20</v>
       </c>
       <c r="G275" t="n">
-        <v>18.4531078338623</v>
+        <v>18.4531059265137</v>
       </c>
       <c r="H275" t="n">
         <v>31211</v>
@@ -8373,7 +8373,7 @@
         <v>20</v>
       </c>
       <c r="G276" t="n">
-        <v>18.4531078338623</v>
+        <v>18.4531059265137</v>
       </c>
       <c r="H276" t="n">
         <v>13518</v>
@@ -8402,7 +8402,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G277" t="n">
-        <v>18.2778053283691</v>
+        <v>18.2777996063232</v>
       </c>
       <c r="H277" t="n">
         <v>19746</v>
@@ -8489,7 +8489,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G280" t="n">
-        <v>18.4069747924805</v>
+        <v>18.4069728851318</v>
       </c>
       <c r="H280" t="n">
         <v>20999</v>
@@ -8518,7 +8518,7 @@
         <v>20</v>
       </c>
       <c r="G281" t="n">
-        <v>18.4531078338623</v>
+        <v>18.4531059265137</v>
       </c>
       <c r="H281" t="n">
         <v>8343</v>
@@ -8547,7 +8547,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G282" t="n">
-        <v>18.3423900604248</v>
+        <v>18.3423862457275</v>
       </c>
       <c r="H282" t="n">
         <v>18898</v>
@@ -8576,7 +8576,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G283" t="n">
-        <v>18.2501201629639</v>
+        <v>18.2501239776611</v>
       </c>
       <c r="H283" t="n">
         <v>9926</v>
@@ -8634,7 +8634,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G285" t="n">
-        <v>18.1578578948975</v>
+        <v>18.1578559875488</v>
       </c>
       <c r="H285" t="n">
         <v>31091</v>
@@ -8663,7 +8663,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G286" t="n">
-        <v>18.2039890289307</v>
+        <v>18.203987121582</v>
       </c>
       <c r="H286" t="n">
         <v>18360</v>
@@ -8721,7 +8721,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G288" t="n">
-        <v>18.3885231018066</v>
+        <v>18.388521194458</v>
       </c>
       <c r="H288" t="n">
         <v>13551</v>
@@ -8750,7 +8750,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G289" t="n">
-        <v>18.4900131225586</v>
+        <v>18.4900169372559</v>
       </c>
       <c r="H289" t="n">
         <v>58575</v>
@@ -8779,7 +8779,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G290" t="n">
-        <v>18.4992408752441</v>
+        <v>18.4992370605469</v>
       </c>
       <c r="H290" t="n">
         <v>19035</v>
@@ -8837,7 +8837,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G292" t="n">
-        <v>18.6007308959961</v>
+        <v>18.6007328033447</v>
       </c>
       <c r="H292" t="n">
         <v>13563</v>
@@ -8866,7 +8866,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G293" t="n">
-        <v>18.7299041748047</v>
+        <v>18.7299022674561</v>
       </c>
       <c r="H293" t="n">
         <v>11363</v>
@@ -8895,7 +8895,7 @@
         <v>20</v>
       </c>
       <c r="G294" t="n">
-        <v>18.4531078338623</v>
+        <v>18.4531059265137</v>
       </c>
       <c r="H294" t="n">
         <v>41413</v>
@@ -8924,7 +8924,7 @@
         <v>20.5</v>
       </c>
       <c r="G295" t="n">
-        <v>18.9144344329834</v>
+        <v>18.914436340332</v>
       </c>
       <c r="H295" t="n">
         <v>52583</v>
@@ -8953,7 +8953,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>19.2834987640381</v>
+        <v>19.2834949493408</v>
       </c>
       <c r="H296" t="n">
         <v>49075</v>
@@ -8982,7 +8982,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>18.9605674743652</v>
+        <v>18.9605655670166</v>
       </c>
       <c r="H297" t="n">
         <v>135669</v>
@@ -9011,7 +9011,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>18.9974708557129</v>
+        <v>18.9974746704102</v>
       </c>
       <c r="H298" t="n">
         <v>7716</v>
@@ -9069,7 +9069,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G300" t="n">
-        <v>19.3204040527344</v>
+        <v>19.3204021453857</v>
       </c>
       <c r="H300" t="n">
         <v>18717</v>
@@ -9098,7 +9098,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G301" t="n">
-        <v>18.9882507324219</v>
+        <v>18.9882469177246</v>
       </c>
       <c r="H301" t="n">
         <v>16302</v>
@@ -9185,7 +9185,7 @@
         <v>21</v>
       </c>
       <c r="G304" t="n">
-        <v>19.3757610321045</v>
+        <v>19.3757629394531</v>
       </c>
       <c r="H304" t="n">
         <v>41845</v>
@@ -9214,7 +9214,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G305" t="n">
-        <v>18.9697952270508</v>
+        <v>18.9697933197021</v>
       </c>
       <c r="H305" t="n">
         <v>78089</v>
@@ -9243,7 +9243,7 @@
         <v>20.6900005340576</v>
       </c>
       <c r="G306" t="n">
-        <v>19.0897407531738</v>
+        <v>19.0897426605225</v>
       </c>
       <c r="H306" t="n">
         <v>14734</v>
@@ -9330,7 +9330,7 @@
         <v>20.4899997711182</v>
       </c>
       <c r="G309" t="n">
-        <v>18.9052085876465</v>
+        <v>18.9052047729492</v>
       </c>
       <c r="H309" t="n">
         <v>22820</v>
@@ -9359,7 +9359,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.0989665985107</v>
+        <v>19.0989685058594</v>
       </c>
       <c r="H310" t="n">
         <v>29568</v>
@@ -9417,7 +9417,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G312" t="n">
-        <v>19.1543292999268</v>
+        <v>19.1543254852295</v>
       </c>
       <c r="H312" t="n">
         <v>56794</v>
@@ -9446,7 +9446,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G313" t="n">
-        <v>19.7817325592041</v>
+        <v>19.7817268371582</v>
       </c>
       <c r="H313" t="n">
         <v>66148</v>
@@ -9504,7 +9504,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G315" t="n">
-        <v>20.2430572509766</v>
+        <v>20.2430629730225</v>
       </c>
       <c r="H315" t="n">
         <v>83043</v>
@@ -9533,7 +9533,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>20.4829502105713</v>
+        <v>20.4829521179199</v>
       </c>
       <c r="H316" t="n">
         <v>56950</v>
@@ -9591,7 +9591,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G318" t="n">
-        <v>20.8243312835693</v>
+        <v>20.8243293762207</v>
       </c>
       <c r="H318" t="n">
         <v>64884</v>
@@ -9620,7 +9620,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>20.8058757781982</v>
+        <v>20.8058776855469</v>
       </c>
       <c r="H319" t="n">
         <v>82957</v>
@@ -9678,7 +9678,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G321" t="n">
-        <v>20.4737205505371</v>
+        <v>20.4737224578857</v>
       </c>
       <c r="H321" t="n">
         <v>30324</v>
@@ -9707,7 +9707,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>20.2522888183594</v>
+        <v>20.2522869110107</v>
       </c>
       <c r="H322" t="n">
         <v>33960</v>
@@ -9765,7 +9765,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>20.4368171691895</v>
+        <v>20.4368133544922</v>
       </c>
       <c r="H324" t="n">
         <v>22191</v>
@@ -9852,7 +9852,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G327" t="n">
-        <v>20.4829502105713</v>
+        <v>20.4829521179199</v>
       </c>
       <c r="H327" t="n">
         <v>49295</v>
@@ -9881,7 +9881,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G328" t="n">
-        <v>20.3630046844482</v>
+        <v>20.3630027770996</v>
       </c>
       <c r="H328" t="n">
         <v>14357</v>
@@ -9910,7 +9910,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>20.390682220459</v>
+        <v>20.3906841278076</v>
       </c>
       <c r="H329" t="n">
         <v>45217</v>
@@ -9939,7 +9939,7 @@
         <v>22.2399997711182</v>
       </c>
       <c r="G330" t="n">
-        <v>20.5198554992676</v>
+        <v>20.5198535919189</v>
       </c>
       <c r="H330" t="n">
         <v>42645</v>
@@ -9997,7 +9997,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>20.390682220459</v>
+        <v>20.3906841278076</v>
       </c>
       <c r="H332" t="n">
         <v>92155</v>
@@ -10026,7 +10026,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G333" t="n">
-        <v>20.6767063140869</v>
+        <v>20.6767044067383</v>
       </c>
       <c r="H333" t="n">
         <v>71142</v>
@@ -10055,7 +10055,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G334" t="n">
-        <v>20.7228355407715</v>
+        <v>20.7228374481201</v>
       </c>
       <c r="H334" t="n">
         <v>28824</v>
@@ -10113,7 +10113,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G336" t="n">
-        <v>20.639799118042</v>
+        <v>20.6398029327393</v>
       </c>
       <c r="H336" t="n">
         <v>121977</v>
@@ -10142,7 +10142,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G337" t="n">
-        <v>21.4978675842285</v>
+        <v>21.4978694915771</v>
       </c>
       <c r="H337" t="n">
         <v>203523</v>
@@ -10171,7 +10171,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G338" t="n">
-        <v>21.3502445220947</v>
+        <v>21.3502426147461</v>
       </c>
       <c r="H338" t="n">
         <v>136741</v>
@@ -10229,7 +10229,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G340" t="n">
-        <v>21.1749401092529</v>
+        <v>21.1749420166016</v>
       </c>
       <c r="H340" t="n">
         <v>31821</v>
@@ -10287,7 +10287,7 @@
         <v>22.75</v>
       </c>
       <c r="G342" t="n">
-        <v>20.9904079437256</v>
+        <v>20.9904098510742</v>
       </c>
       <c r="H342" t="n">
         <v>60557</v>
@@ -10316,7 +10316,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>21.1749401092529</v>
+        <v>21.1749420166016</v>
       </c>
       <c r="H343" t="n">
         <v>64135</v>
@@ -10374,7 +10374,7 @@
         <v>22.5300006866455</v>
       </c>
       <c r="G345" t="n">
-        <v>20.7874240875244</v>
+        <v>20.7874279022217</v>
       </c>
       <c r="H345" t="n">
         <v>61532</v>
@@ -10432,7 +10432,7 @@
         <v>22.7199993133545</v>
       </c>
       <c r="G347" t="n">
-        <v>20.9627304077148</v>
+        <v>20.9627265930176</v>
       </c>
       <c r="H347" t="n">
         <v>92377</v>
@@ -10519,7 +10519,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G350" t="n">
-        <v>21.2026195526123</v>
+        <v>21.2026214599609</v>
       </c>
       <c r="H350" t="n">
         <v>45857</v>
@@ -10548,7 +10548,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G351" t="n">
-        <v>21.0826740264893</v>
+        <v>21.0826797485352</v>
       </c>
       <c r="H351" t="n">
         <v>85673</v>
@@ -10577,7 +10577,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G352" t="n">
-        <v>20.5013999938965</v>
+        <v>20.5014019012451</v>
       </c>
       <c r="H352" t="n">
         <v>36212</v>
@@ -10606,7 +10606,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G353" t="n">
-        <v>20.4829502105713</v>
+        <v>20.4829521179199</v>
       </c>
       <c r="H353" t="n">
         <v>64595</v>
@@ -10635,7 +10635,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G354" t="n">
-        <v>21.0273189544678</v>
+        <v>21.0273151397705</v>
       </c>
       <c r="H354" t="n">
         <v>34712</v>
@@ -10896,7 +10896,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G363" t="n">
-        <v>20.7966537475586</v>
+        <v>20.7966499328613</v>
       </c>
       <c r="H363" t="n">
         <v>57934</v>
@@ -10954,7 +10954,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G365" t="n">
-        <v>20.5936679840088</v>
+        <v>20.5936660766602</v>
       </c>
       <c r="H365" t="n">
         <v>10995</v>
@@ -11012,7 +11012,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G367" t="n">
-        <v>20.2615089416504</v>
+        <v>20.261510848999</v>
       </c>
       <c r="H367" t="n">
         <v>26603</v>
@@ -11041,7 +11041,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G368" t="n">
-        <v>20.2707366943359</v>
+        <v>20.2707386016846</v>
       </c>
       <c r="H368" t="n">
         <v>69910</v>
@@ -11070,7 +11070,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G369" t="n">
-        <v>20.5013999938965</v>
+        <v>20.5014019012451</v>
       </c>
       <c r="H369" t="n">
         <v>57155</v>
@@ -11099,7 +11099,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G370" t="n">
-        <v>20.1876983642578</v>
+        <v>20.1876964569092</v>
       </c>
       <c r="H370" t="n">
         <v>20027</v>
@@ -11128,7 +11128,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G371" t="n">
-        <v>20.4921760559082</v>
+        <v>20.4921722412109</v>
       </c>
       <c r="H371" t="n">
         <v>62846</v>
@@ -11157,7 +11157,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G372" t="n">
-        <v>20.5936679840088</v>
+        <v>20.5936660766602</v>
       </c>
       <c r="H372" t="n">
         <v>16168</v>
@@ -11186,7 +11186,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G373" t="n">
-        <v>20.1415672302246</v>
+        <v>20.1415691375732</v>
       </c>
       <c r="H373" t="n">
         <v>13228</v>
@@ -11215,7 +11215,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G374" t="n">
-        <v>19.9109001159668</v>
+        <v>19.9109020233154</v>
       </c>
       <c r="H374" t="n">
         <v>58932</v>
@@ -11244,7 +11244,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G375" t="n">
-        <v>20.0769805908203</v>
+        <v>20.0769786834717</v>
       </c>
       <c r="H375" t="n">
         <v>8785</v>
@@ -11273,7 +11273,7 @@
         <v>21.3099994659424</v>
       </c>
       <c r="G376" t="n">
-        <v>19.6617870330811</v>
+        <v>19.6617851257324</v>
       </c>
       <c r="H376" t="n">
         <v>17186</v>
@@ -11302,7 +11302,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G377" t="n">
-        <v>19.7725067138672</v>
+        <v>19.7725009918213</v>
       </c>
       <c r="H377" t="n">
         <v>24885</v>
@@ -11331,7 +11331,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G378" t="n">
-        <v>20.1323394775391</v>
+        <v>20.1323375701904</v>
       </c>
       <c r="H378" t="n">
         <v>16830</v>
@@ -11360,7 +11360,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>20.1600170135498</v>
+        <v>20.1600189208984</v>
       </c>
       <c r="H379" t="n">
         <v>12751</v>
@@ -11389,7 +11389,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G380" t="n">
-        <v>20.4091358184814</v>
+        <v>20.4091377258301</v>
       </c>
       <c r="H380" t="n">
         <v>23075</v>
@@ -11447,7 +11447,7 @@
         <v>22</v>
       </c>
       <c r="G382" t="n">
-        <v>20.2984199523926</v>
+        <v>20.2984180450439</v>
       </c>
       <c r="H382" t="n">
         <v>12653</v>
@@ -11476,7 +11476,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>19.8186378479004</v>
+        <v>19.8186359405518</v>
       </c>
       <c r="H383" t="n">
         <v>20249</v>
@@ -11505,7 +11505,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G384" t="n">
-        <v>19.6986923217773</v>
+        <v>19.6986904144287</v>
       </c>
       <c r="H384" t="n">
         <v>15447</v>
@@ -11563,7 +11563,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G386" t="n">
-        <v>19.5879726409912</v>
+        <v>19.5879745483398</v>
       </c>
       <c r="H386" t="n">
         <v>50642</v>
@@ -11592,7 +11592,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>19.7909603118896</v>
+        <v>19.790958404541</v>
       </c>
       <c r="H387" t="n">
         <v>13573</v>
@@ -11621,7 +11621,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G388" t="n">
-        <v>19.9385795593262</v>
+        <v>19.9385833740234</v>
       </c>
       <c r="H388" t="n">
         <v>15173</v>
@@ -11650,7 +11650,7 @@
         <v>21.5300006866455</v>
       </c>
       <c r="G389" t="n">
-        <v>19.8647708892822</v>
+        <v>19.8647727966309</v>
       </c>
       <c r="H389" t="n">
         <v>13024</v>
@@ -11679,7 +11679,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G390" t="n">
-        <v>19.9754886627197</v>
+        <v>19.9754867553711</v>
       </c>
       <c r="H390" t="n">
         <v>31020</v>
@@ -11708,7 +11708,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G391" t="n">
-        <v>19.5418395996094</v>
+        <v>19.5418434143066</v>
       </c>
       <c r="H391" t="n">
         <v>12916</v>
@@ -11737,7 +11737,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G392" t="n">
-        <v>19.9754886627197</v>
+        <v>19.9754867553711</v>
       </c>
       <c r="H392" t="n">
         <v>34425</v>
@@ -11766,7 +11766,7 @@
         <v>22.2399997711182</v>
       </c>
       <c r="G393" t="n">
-        <v>20.5198554992676</v>
+        <v>20.5198535919189</v>
       </c>
       <c r="H393" t="n">
         <v>30307</v>
@@ -11795,7 +11795,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G394" t="n">
-        <v>20.4737205505371</v>
+        <v>20.4737224578857</v>
       </c>
       <c r="H394" t="n">
         <v>6844</v>
@@ -11853,7 +11853,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G396" t="n">
-        <v>20.0769805908203</v>
+        <v>20.0769786834717</v>
       </c>
       <c r="H396" t="n">
         <v>38946</v>
@@ -11882,7 +11882,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G397" t="n">
-        <v>20.2522888183594</v>
+        <v>20.2522869110107</v>
       </c>
       <c r="H397" t="n">
         <v>42378</v>
@@ -11911,7 +11911,7 @@
         <v>21.7900009155273</v>
       </c>
       <c r="G398" t="n">
-        <v>20.1046581268311</v>
+        <v>20.1046619415283</v>
       </c>
       <c r="H398" t="n">
         <v>30566</v>
@@ -11940,7 +11940,7 @@
         <v>21.5</v>
       </c>
       <c r="G399" t="n">
-        <v>19.8370914459229</v>
+        <v>19.8370895385742</v>
       </c>
       <c r="H399" t="n">
         <v>36331</v>
@@ -11969,7 +11969,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G400" t="n">
-        <v>19.7909603118896</v>
+        <v>19.790958404541</v>
       </c>
       <c r="H400" t="n">
         <v>14656</v>
@@ -11998,7 +11998,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G401" t="n">
-        <v>19.9109001159668</v>
+        <v>19.9109020233154</v>
       </c>
       <c r="H401" t="n">
         <v>23442</v>
@@ -12027,7 +12027,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G402" t="n">
-        <v>19.6986923217773</v>
+        <v>19.6986904144287</v>
       </c>
       <c r="H402" t="n">
         <v>18860</v>
@@ -12056,7 +12056,7 @@
         <v>21.3500003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>19.6986923217773</v>
+        <v>19.6986904144287</v>
       </c>
       <c r="H403" t="n">
         <v>21085</v>
@@ -12114,7 +12114,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G405" t="n">
-        <v>20.0769805908203</v>
+        <v>20.0769786834717</v>
       </c>
       <c r="H405" t="n">
         <v>39480</v>
@@ -12143,7 +12143,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G406" t="n">
-        <v>20.2707366943359</v>
+        <v>20.2707386016846</v>
       </c>
       <c r="H406" t="n">
         <v>19645</v>
@@ -12172,7 +12172,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G407" t="n">
-        <v>20.2707366943359</v>
+        <v>20.2707386016846</v>
       </c>
       <c r="H407" t="n">
         <v>12205</v>
@@ -12230,7 +12230,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G409" t="n">
-        <v>19.9939403533936</v>
+        <v>19.9939441680908</v>
       </c>
       <c r="H409" t="n">
         <v>12488</v>
@@ -12259,7 +12259,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>20.2522888183594</v>
+        <v>20.2522869110107</v>
       </c>
       <c r="H410" t="n">
         <v>36549</v>
@@ -12317,7 +12317,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G412" t="n">
-        <v>20.639799118042</v>
+        <v>20.6398029327393</v>
       </c>
       <c r="H412" t="n">
         <v>33356</v>
@@ -12375,7 +12375,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G414" t="n">
-        <v>20.2061519622803</v>
+        <v>20.2061500549316</v>
       </c>
       <c r="H414" t="n">
         <v>22878</v>
@@ -12433,7 +12433,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G416" t="n">
-        <v>20.4275894165039</v>
+        <v>20.4275913238525</v>
       </c>
       <c r="H416" t="n">
         <v>26649</v>
@@ -12491,7 +12491,7 @@
         <v>22.5699996948242</v>
       </c>
       <c r="G418" t="n">
-        <v>20.8243312835693</v>
+        <v>20.8243293762207</v>
       </c>
       <c r="H418" t="n">
         <v>45486</v>
@@ -12520,7 +12520,7 @@
         <v>22.75</v>
       </c>
       <c r="G419" t="n">
-        <v>20.9904079437256</v>
+        <v>20.9904098510742</v>
       </c>
       <c r="H419" t="n">
         <v>29090</v>
@@ -12549,7 +12549,7 @@
         <v>22.75</v>
       </c>
       <c r="G420" t="n">
-        <v>20.9904079437256</v>
+        <v>20.9904098510742</v>
       </c>
       <c r="H420" t="n">
         <v>18248</v>
@@ -12607,7 +12607,7 @@
         <v>22.75</v>
       </c>
       <c r="G422" t="n">
-        <v>20.9904079437256</v>
+        <v>20.9904098510742</v>
       </c>
       <c r="H422" t="n">
         <v>42047</v>
@@ -12665,7 +12665,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G424" t="n">
-        <v>20.3353252410889</v>
+        <v>20.3353233337402</v>
       </c>
       <c r="H424" t="n">
         <v>6450</v>
@@ -12694,7 +12694,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G425" t="n">
-        <v>20.2707366943359</v>
+        <v>20.2707386016846</v>
       </c>
       <c r="H425" t="n">
         <v>20559</v>
@@ -12723,7 +12723,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>20.390682220459</v>
+        <v>20.3906841278076</v>
       </c>
       <c r="H426" t="n">
         <v>20664</v>
@@ -12781,7 +12781,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G428" t="n">
-        <v>20.1969261169434</v>
+        <v>20.1969242095947</v>
       </c>
       <c r="H428" t="n">
         <v>15886</v>
@@ -12810,7 +12810,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G429" t="n">
-        <v>20.1969261169434</v>
+        <v>20.1969242095947</v>
       </c>
       <c r="H429" t="n">
         <v>22061</v>
@@ -12839,7 +12839,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G430" t="n">
-        <v>20.2430572509766</v>
+        <v>20.2430629730225</v>
       </c>
       <c r="H430" t="n">
         <v>12930</v>
@@ -12868,7 +12868,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>20.1600170135498</v>
+        <v>20.1600189208984</v>
       </c>
       <c r="H431" t="n">
         <v>11427</v>
@@ -12926,7 +12926,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G433" t="n">
-        <v>19.9109001159668</v>
+        <v>19.9109020233154</v>
       </c>
       <c r="H433" t="n">
         <v>48281</v>
@@ -12955,7 +12955,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G434" t="n">
-        <v>19.7448215484619</v>
+        <v>19.7448234558105</v>
       </c>
       <c r="H434" t="n">
         <v>11290</v>
@@ -12984,7 +12984,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G435" t="n">
-        <v>19.7909603118896</v>
+        <v>19.790958404541</v>
       </c>
       <c r="H435" t="n">
         <v>27283</v>
@@ -13071,7 +13071,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G438" t="n">
-        <v>19.3296298980713</v>
+        <v>19.3296318054199</v>
       </c>
       <c r="H438" t="n">
         <v>40010</v>
@@ -13100,7 +13100,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G439" t="n">
-        <v>19.7817325592041</v>
+        <v>19.7817268371582</v>
       </c>
       <c r="H439" t="n">
         <v>24594</v>
@@ -13129,7 +13129,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G440" t="n">
-        <v>19.8463153839111</v>
+        <v>19.8463172912598</v>
       </c>
       <c r="H440" t="n">
         <v>25567</v>
@@ -13187,7 +13187,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G442" t="n">
-        <v>20.2061519622803</v>
+        <v>20.2061500549316</v>
       </c>
       <c r="H442" t="n">
         <v>26218</v>
@@ -13216,7 +13216,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G443" t="n">
-        <v>20.2707366943359</v>
+        <v>20.2707386016846</v>
       </c>
       <c r="H443" t="n">
         <v>7095</v>
@@ -13361,7 +13361,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>20.390682220459</v>
+        <v>20.3906841278076</v>
       </c>
       <c r="H448" t="n">
         <v>28763</v>
@@ -13390,7 +13390,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G449" t="n">
-        <v>20.390682220459</v>
+        <v>20.3906841278076</v>
       </c>
       <c r="H449" t="n">
         <v>29103</v>
@@ -13419,7 +13419,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G450" t="n">
-        <v>20.3814601898193</v>
+        <v>20.3814582824707</v>
       </c>
       <c r="H450" t="n">
         <v>7845</v>
@@ -13448,7 +13448,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G451" t="n">
-        <v>19.8555431365967</v>
+        <v>19.8555450439453</v>
       </c>
       <c r="H451" t="n">
         <v>36507</v>
@@ -13535,7 +13535,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G454" t="n">
-        <v>19.1266422271729</v>
+        <v>19.1266479492188</v>
       </c>
       <c r="H454" t="n">
         <v>40764</v>
@@ -13564,7 +13564,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>19.0528335571289</v>
+        <v>19.0528354644775</v>
       </c>
       <c r="H455" t="n">
         <v>33727</v>
@@ -13593,7 +13593,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G456" t="n">
-        <v>19.0528335571289</v>
+        <v>19.0528354644775</v>
       </c>
       <c r="H456" t="n">
         <v>35171</v>
@@ -13622,7 +13622,7 @@
         <v>20.5</v>
       </c>
       <c r="G457" t="n">
-        <v>18.9144344329834</v>
+        <v>18.914436340332</v>
       </c>
       <c r="H457" t="n">
         <v>9845</v>
@@ -13651,7 +13651,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G458" t="n">
-        <v>18.9974708557129</v>
+        <v>18.9974746704102</v>
       </c>
       <c r="H458" t="n">
         <v>17708</v>
@@ -13680,7 +13680,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G459" t="n">
-        <v>18.6560897827148</v>
+        <v>18.6560916900635</v>
       </c>
       <c r="H459" t="n">
         <v>29725</v>
@@ -13709,7 +13709,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G460" t="n">
-        <v>18.8129405975342</v>
+        <v>18.8129425048828</v>
       </c>
       <c r="H460" t="n">
         <v>29832</v>
@@ -13738,7 +13738,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G461" t="n">
-        <v>18.7114505767822</v>
+        <v>18.7114524841309</v>
       </c>
       <c r="H461" t="n">
         <v>16803</v>
@@ -13796,7 +13796,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G463" t="n">
-        <v>18.8037166595459</v>
+        <v>18.8037109375</v>
       </c>
       <c r="H463" t="n">
         <v>15728</v>
@@ -13825,7 +13825,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G464" t="n">
-        <v>18.8683013916016</v>
+        <v>18.8683032989502</v>
       </c>
       <c r="H464" t="n">
         <v>23270</v>
@@ -13854,7 +13854,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G465" t="n">
-        <v>18.5546016693115</v>
+        <v>18.5545978546143</v>
       </c>
       <c r="H465" t="n">
         <v>13390</v>
@@ -13941,7 +13941,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G468" t="n">
-        <v>18.3147068023682</v>
+        <v>18.3147106170654</v>
       </c>
       <c r="H468" t="n">
         <v>8584</v>
@@ -13999,7 +13999,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G470" t="n">
-        <v>18.9605674743652</v>
+        <v>18.9605655670166</v>
       </c>
       <c r="H470" t="n">
         <v>21082</v>
@@ -14028,7 +14028,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G471" t="n">
-        <v>19.0066986083984</v>
+        <v>19.0067005157471</v>
       </c>
       <c r="H471" t="n">
         <v>26811</v>
@@ -14057,7 +14057,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G472" t="n">
-        <v>18.8037166595459</v>
+        <v>18.8037109375</v>
       </c>
       <c r="H472" t="n">
         <v>20881</v>
@@ -14086,7 +14086,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G473" t="n">
-        <v>18.8683013916016</v>
+        <v>18.8683032989502</v>
       </c>
       <c r="H473" t="n">
         <v>34569</v>
@@ -14115,7 +14115,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G474" t="n">
-        <v>18.8497562408447</v>
+        <v>18.8497581481934</v>
       </c>
       <c r="H474" t="n">
         <v>18471</v>
@@ -14144,7 +14144,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G475" t="n">
-        <v>18.8219432830811</v>
+        <v>18.8219413757324</v>
       </c>
       <c r="H475" t="n">
         <v>22915</v>
@@ -14173,7 +14173,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G476" t="n">
-        <v>18.4047050476074</v>
+        <v>18.4047069549561</v>
       </c>
       <c r="H476" t="n">
         <v>17548</v>
@@ -14202,7 +14202,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G477" t="n">
-        <v>18.1821823120117</v>
+        <v>18.1821804046631</v>
       </c>
       <c r="H477" t="n">
         <v>27017</v>
@@ -14231,7 +14231,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G478" t="n">
-        <v>17.7834911346436</v>
+        <v>17.7834930419922</v>
       </c>
       <c r="H478" t="n">
         <v>44382</v>
@@ -14260,7 +14260,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G479" t="n">
-        <v>17.7278575897217</v>
+        <v>17.7278594970703</v>
       </c>
       <c r="H479" t="n">
         <v>19845</v>
@@ -14289,7 +14289,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G480" t="n">
-        <v>17.5238761901855</v>
+        <v>17.5238780975342</v>
       </c>
       <c r="H480" t="n">
         <v>28888</v>
@@ -14318,7 +14318,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G481" t="n">
-        <v>17.5516929626465</v>
+        <v>17.5516948699951</v>
       </c>
       <c r="H481" t="n">
         <v>20865</v>
@@ -14376,7 +14376,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G483" t="n">
-        <v>17.7742214202881</v>
+        <v>17.7742195129395</v>
       </c>
       <c r="H483" t="n">
         <v>14059</v>
@@ -14405,7 +14405,7 @@
         <v>19.25</v>
       </c>
       <c r="G484" t="n">
-        <v>17.8483905792236</v>
+        <v>17.8483943939209</v>
       </c>
       <c r="H484" t="n">
         <v>13648</v>
@@ -14434,7 +14434,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G485" t="n">
-        <v>18.1450939178467</v>
+        <v>18.145092010498</v>
       </c>
       <c r="H485" t="n">
         <v>22132</v>
@@ -14463,7 +14463,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G486" t="n">
-        <v>18.3398017883301</v>
+        <v>18.3398056030273</v>
       </c>
       <c r="H486" t="n">
         <v>15740</v>
@@ -14521,7 +14521,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G488" t="n">
-        <v>18.2841701507568</v>
+        <v>18.2841720581055</v>
       </c>
       <c r="H488" t="n">
         <v>16673</v>
@@ -14550,7 +14550,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G489" t="n">
-        <v>18.2841701507568</v>
+        <v>18.2841720581055</v>
       </c>
       <c r="H489" t="n">
         <v>17087</v>
@@ -14579,7 +14579,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G490" t="n">
-        <v>18.0431022644043</v>
+        <v>18.0431041717529</v>
       </c>
       <c r="H490" t="n">
         <v>16630</v>
@@ -14608,7 +14608,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G491" t="n">
-        <v>18.1821823120117</v>
+        <v>18.1821804046631</v>
       </c>
       <c r="H491" t="n">
         <v>44994</v>
@@ -14637,7 +14637,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G492" t="n">
-        <v>18.3676204681396</v>
+        <v>18.367618560791</v>
       </c>
       <c r="H492" t="n">
         <v>26139</v>
@@ -14695,7 +14695,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G494" t="n">
-        <v>18.0987377166748</v>
+        <v>18.0987339019775</v>
       </c>
       <c r="H494" t="n">
         <v>9160</v>
@@ -14724,7 +14724,7 @@
         <v>20</v>
       </c>
       <c r="G495" t="n">
-        <v>18.5437850952148</v>
+        <v>18.5437831878662</v>
       </c>
       <c r="H495" t="n">
         <v>21814</v>
@@ -14753,7 +14753,7 @@
         <v>20</v>
       </c>
       <c r="G496" t="n">
-        <v>18.5437850952148</v>
+        <v>18.5437831878662</v>
       </c>
       <c r="H496" t="n">
         <v>15923</v>
@@ -14782,7 +14782,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G497" t="n">
-        <v>18.6457786560059</v>
+        <v>18.6457767486572</v>
       </c>
       <c r="H497" t="n">
         <v>12181</v>
@@ -14840,7 +14840,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G499" t="n">
-        <v>18.5623321533203</v>
+        <v>18.5623302459717</v>
       </c>
       <c r="H499" t="n">
         <v>11716</v>
@@ -14869,7 +14869,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G500" t="n">
-        <v>18.4881553649902</v>
+        <v>18.4881572723389</v>
       </c>
       <c r="H500" t="n">
         <v>22877</v>
@@ -14898,7 +14898,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G501" t="n">
-        <v>18.2285404205322</v>
+        <v>18.2285423278809</v>
       </c>
       <c r="H501" t="n">
         <v>22558</v>
@@ -14927,7 +14927,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G502" t="n">
-        <v>18.2563571929932</v>
+        <v>18.2563552856445</v>
       </c>
       <c r="H502" t="n">
         <v>30706</v>
@@ -14985,7 +14985,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>18.3583488464355</v>
+        <v>18.3583450317383</v>
       </c>
       <c r="H504" t="n">
         <v>32349</v>
@@ -15014,7 +15014,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G505" t="n">
-        <v>18.3490791320801</v>
+        <v>18.3490772247314</v>
       </c>
       <c r="H505" t="n">
         <v>18477</v>
@@ -15072,7 +15072,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G507" t="n">
-        <v>18.5808715820312</v>
+        <v>18.5808734893799</v>
       </c>
       <c r="H507" t="n">
         <v>24263</v>
@@ -15101,7 +15101,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G508" t="n">
-        <v>18.4696102142334</v>
+        <v>18.4696083068848</v>
       </c>
       <c r="H508" t="n">
         <v>19500</v>
@@ -15130,7 +15130,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G509" t="n">
-        <v>18.4696102142334</v>
+        <v>18.4696083068848</v>
       </c>
       <c r="H509" t="n">
         <v>9688</v>
@@ -15159,7 +15159,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G510" t="n">
-        <v>18.2656288146973</v>
+        <v>18.2656326293945</v>
       </c>
       <c r="H510" t="n">
         <v>16027</v>
@@ -15188,7 +15188,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G511" t="n">
-        <v>18.3676204681396</v>
+        <v>18.367618560791</v>
       </c>
       <c r="H511" t="n">
         <v>20759</v>
@@ -15217,7 +15217,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G512" t="n">
-        <v>18.3490791320801</v>
+        <v>18.3490772247314</v>
       </c>
       <c r="H512" t="n">
         <v>6062</v>
@@ -15246,7 +15246,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G513" t="n">
-        <v>18.3768901824951</v>
+        <v>18.3768920898438</v>
       </c>
       <c r="H513" t="n">
         <v>7196</v>
@@ -15304,7 +15304,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>19.0537395477295</v>
+        <v>19.0537376403809</v>
       </c>
       <c r="H515" t="n">
         <v>24155</v>
@@ -15391,7 +15391,7 @@
         <v>22</v>
       </c>
       <c r="G518" t="n">
-        <v>20.3981647491455</v>
+        <v>20.3981666564941</v>
       </c>
       <c r="H518" t="n">
         <v>70505</v>
@@ -15449,7 +15449,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G520" t="n">
-        <v>21.4180717468262</v>
+        <v>21.4180698394775</v>
       </c>
       <c r="H520" t="n">
         <v>127851</v>
@@ -15536,7 +15536,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>21.2326335906982</v>
+        <v>21.2326354980469</v>
       </c>
       <c r="H523" t="n">
         <v>49536</v>
@@ -15565,7 +15565,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G524" t="n">
-        <v>21.4644317626953</v>
+        <v>21.4644298553467</v>
       </c>
       <c r="H524" t="n">
         <v>47137</v>
@@ -15623,7 +15623,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G526" t="n">
-        <v>21.4180717468262</v>
+        <v>21.4180698394775</v>
       </c>
       <c r="H526" t="n">
         <v>35276</v>
@@ -15739,7 +15739,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>21.4180717468262</v>
+        <v>21.4180698394775</v>
       </c>
       <c r="H530" t="n">
         <v>47121</v>
@@ -15884,7 +15884,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G535" t="n">
-        <v>21.2326335906982</v>
+        <v>21.2326354980469</v>
       </c>
       <c r="H535" t="n">
         <v>38209</v>
@@ -15942,7 +15942,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>20.3054447174072</v>
+        <v>20.3054428100586</v>
       </c>
       <c r="H537" t="n">
         <v>54524</v>
@@ -15971,7 +15971,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>20.9081192016602</v>
+        <v>20.9081172943115</v>
       </c>
       <c r="H538" t="n">
         <v>23371</v>
@@ -16058,7 +16058,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G541" t="n">
-        <v>20.3054447174072</v>
+        <v>20.3054428100586</v>
       </c>
       <c r="H541" t="n">
         <v>42378</v>
@@ -16116,7 +16116,7 @@
         <v>22.25</v>
       </c>
       <c r="G543" t="n">
-        <v>20.6299591064453</v>
+        <v>20.6299629211426</v>
       </c>
       <c r="H543" t="n">
         <v>20428</v>
@@ -16174,7 +16174,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G545" t="n">
-        <v>20.9544773101807</v>
+        <v>20.9544792175293</v>
       </c>
       <c r="H545" t="n">
         <v>16417</v>
@@ -16203,7 +16203,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G546" t="n">
-        <v>20.9081192016602</v>
+        <v>20.9081172943115</v>
       </c>
       <c r="H546" t="n">
         <v>11923</v>
@@ -16232,7 +16232,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471992492676</v>
       </c>
       <c r="H547" t="n">
         <v>8341</v>
@@ -16261,7 +16261,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>21.0008392333984</v>
+        <v>21.0008354187012</v>
       </c>
       <c r="H548" t="n">
         <v>10821</v>
@@ -16290,7 +16290,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G549" t="n">
-        <v>20.7226791381836</v>
+        <v>20.722677230835</v>
       </c>
       <c r="H549" t="n">
         <v>9616</v>
@@ -16319,7 +16319,7 @@
         <v>22</v>
       </c>
       <c r="G550" t="n">
-        <v>20.3981647491455</v>
+        <v>20.3981666564941</v>
       </c>
       <c r="H550" t="n">
         <v>10608</v>
@@ -16348,7 +16348,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G551" t="n">
-        <v>20.5372447967529</v>
+        <v>20.5372409820557</v>
       </c>
       <c r="H551" t="n">
         <v>11868</v>
@@ -16377,7 +16377,7 @@
         <v>22</v>
       </c>
       <c r="G552" t="n">
-        <v>20.3981647491455</v>
+        <v>20.3981666564941</v>
       </c>
       <c r="H552" t="n">
         <v>63901</v>
@@ -16435,7 +16435,7 @@
         <v>23.25</v>
       </c>
       <c r="G554" t="n">
-        <v>21.5571517944336</v>
+        <v>21.557149887085</v>
       </c>
       <c r="H554" t="n">
         <v>156886</v>
@@ -16464,7 +16464,7 @@
         <v>23.25</v>
       </c>
       <c r="G555" t="n">
-        <v>21.5571517944336</v>
+        <v>21.557149887085</v>
       </c>
       <c r="H555" t="n">
         <v>237507</v>
@@ -16493,7 +16493,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G556" t="n">
-        <v>21.4644317626953</v>
+        <v>21.4644298553467</v>
       </c>
       <c r="H556" t="n">
         <v>33185</v>
@@ -16609,7 +16609,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G560" t="n">
-        <v>21.8353080749512</v>
+        <v>21.8353042602539</v>
       </c>
       <c r="H560" t="n">
         <v>38449</v>
@@ -16696,7 +16696,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G563" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471992492676</v>
       </c>
       <c r="H563" t="n">
         <v>43117</v>
@@ -16725,7 +16725,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471992492676</v>
       </c>
       <c r="H564" t="n">
         <v>21687</v>
@@ -16754,7 +16754,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G565" t="n">
-        <v>20.6763210296631</v>
+        <v>20.6763191223145</v>
       </c>
       <c r="H565" t="n">
         <v>63751</v>
@@ -16812,7 +16812,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>20.9544773101807</v>
+        <v>20.9544792175293</v>
       </c>
       <c r="H567" t="n">
         <v>15271</v>
@@ -16841,7 +16841,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>20.7226791381836</v>
+        <v>20.722677230835</v>
       </c>
       <c r="H568" t="n">
         <v>27519</v>
@@ -16870,7 +16870,7 @@
         <v>22.75</v>
       </c>
       <c r="G569" t="n">
-        <v>21.0935535430908</v>
+        <v>21.0935554504395</v>
       </c>
       <c r="H569" t="n">
         <v>41089</v>
@@ -16899,7 +16899,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>20.7226791381836</v>
+        <v>20.722677230835</v>
       </c>
       <c r="H570" t="n">
         <v>21232</v>
@@ -16928,7 +16928,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G571" t="n">
-        <v>20.7226791381836</v>
+        <v>20.722677230835</v>
       </c>
       <c r="H571" t="n">
         <v>12000</v>
@@ -16957,7 +16957,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G572" t="n">
-        <v>20.6763210296631</v>
+        <v>20.6763191223145</v>
       </c>
       <c r="H572" t="n">
         <v>22651</v>
@@ -16986,7 +16986,7 @@
         <v>21.75</v>
       </c>
       <c r="G573" t="n">
-        <v>20.1663665771484</v>
+        <v>20.1663684844971</v>
       </c>
       <c r="H573" t="n">
         <v>19943</v>
@@ -17015,7 +17015,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>20.5372447967529</v>
+        <v>20.5372409820557</v>
       </c>
       <c r="H574" t="n">
         <v>13004</v>
@@ -17073,7 +17073,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G576" t="n">
-        <v>20.0736484527588</v>
+        <v>20.0736465454102</v>
       </c>
       <c r="H576" t="n">
         <v>20744</v>
@@ -17102,7 +17102,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>20.0736484527588</v>
+        <v>20.0736465454102</v>
       </c>
       <c r="H577" t="n">
         <v>76572</v>
@@ -17131,7 +17131,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G578" t="n">
-        <v>20.7690391540527</v>
+        <v>20.7690410614014</v>
       </c>
       <c r="H578" t="n">
         <v>29293</v>
@@ -17160,7 +17160,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471992492676</v>
       </c>
       <c r="H579" t="n">
         <v>36379</v>
@@ -17247,7 +17247,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G582" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471992492676</v>
       </c>
       <c r="H582" t="n">
         <v>19364</v>
@@ -17276,7 +17276,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>20.7690391540527</v>
+        <v>20.7690410614014</v>
       </c>
       <c r="H583" t="n">
         <v>12663</v>
@@ -17334,7 +17334,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G585" t="n">
-        <v>20.8154010772705</v>
+        <v>20.8154029846191</v>
       </c>
       <c r="H585" t="n">
         <v>34337</v>
@@ -17363,7 +17363,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G586" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471992492676</v>
       </c>
       <c r="H586" t="n">
         <v>31766</v>
@@ -17392,7 +17392,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G587" t="n">
-        <v>20.6763210296631</v>
+        <v>20.6763191223145</v>
       </c>
       <c r="H587" t="n">
         <v>36209</v>
@@ -17450,7 +17450,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>20.9544773101807</v>
+        <v>20.9544792175293</v>
       </c>
       <c r="H589" t="n">
         <v>42855</v>
@@ -17479,7 +17479,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>20.9081192016602</v>
+        <v>20.9081172943115</v>
       </c>
       <c r="H590" t="n">
         <v>5669</v>
@@ -17537,7 +17537,7 @@
         <v>22.25</v>
       </c>
       <c r="G592" t="n">
-        <v>20.6299591064453</v>
+        <v>20.6299629211426</v>
       </c>
       <c r="H592" t="n">
         <v>27279</v>
@@ -17595,7 +17595,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>21.1862754821777</v>
+        <v>21.1862773895264</v>
       </c>
       <c r="H594" t="n">
         <v>23518</v>
@@ -17624,7 +17624,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G595" t="n">
-        <v>21.2326335906982</v>
+        <v>21.2326354980469</v>
       </c>
       <c r="H595" t="n">
         <v>33837</v>
@@ -17653,7 +17653,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>21.0008392333984</v>
+        <v>21.0008354187012</v>
       </c>
       <c r="H596" t="n">
         <v>7652</v>
@@ -17682,7 +17682,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G597" t="n">
-        <v>20.8154010772705</v>
+        <v>20.8154029846191</v>
       </c>
       <c r="H597" t="n">
         <v>13297</v>
@@ -17711,7 +17711,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471992492676</v>
       </c>
       <c r="H598" t="n">
         <v>23626</v>
@@ -17769,7 +17769,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G600" t="n">
-        <v>20.7226791381836</v>
+        <v>20.722677230835</v>
       </c>
       <c r="H600" t="n">
         <v>48289</v>
@@ -17798,7 +17798,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G601" t="n">
-        <v>20.6763210296631</v>
+        <v>20.6763191223145</v>
       </c>
       <c r="H601" t="n">
         <v>17464</v>
@@ -17827,7 +17827,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>20.7690391540527</v>
+        <v>20.7690410614014</v>
       </c>
       <c r="H602" t="n">
         <v>22732</v>
@@ -17885,7 +17885,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G604" t="n">
-        <v>20.2590827941895</v>
+        <v>20.2590847015381</v>
       </c>
       <c r="H604" t="n">
         <v>18982</v>
@@ -17943,7 +17943,7 @@
         <v>22.25</v>
       </c>
       <c r="G606" t="n">
-        <v>20.6299591064453</v>
+        <v>20.6299629211426</v>
       </c>
       <c r="H606" t="n">
         <v>88362</v>
@@ -17972,7 +17972,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>20.6763210296631</v>
+        <v>20.6763191223145</v>
       </c>
       <c r="H607" t="n">
         <v>56599</v>
@@ -18001,7 +18001,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>20.7690391540527</v>
+        <v>20.7690410614014</v>
       </c>
       <c r="H608" t="n">
         <v>17837</v>
@@ -18059,7 +18059,7 @@
         <v>22</v>
       </c>
       <c r="G610" t="n">
-        <v>20.3981647491455</v>
+        <v>20.3981666564941</v>
       </c>
       <c r="H610" t="n">
         <v>17228</v>
@@ -18088,7 +18088,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G611" t="n">
-        <v>20.7226791381836</v>
+        <v>20.722677230835</v>
       </c>
       <c r="H611" t="n">
         <v>20399</v>
@@ -18117,7 +18117,7 @@
         <v>22.25</v>
       </c>
       <c r="G612" t="n">
-        <v>20.6299591064453</v>
+        <v>20.6299629211426</v>
       </c>
       <c r="H612" t="n">
         <v>25403</v>
@@ -18175,7 +18175,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G614" t="n">
-        <v>18.8682994842529</v>
+        <v>18.8683032989502</v>
       </c>
       <c r="H614" t="n">
         <v>68212</v>
@@ -18204,7 +18204,7 @@
         <v>20</v>
       </c>
       <c r="G615" t="n">
-        <v>18.5437850952148</v>
+        <v>18.5437831878662</v>
       </c>
       <c r="H615" t="n">
         <v>83861</v>
@@ -18233,7 +18233,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G616" t="n">
-        <v>18.4881553649902</v>
+        <v>18.4881572723389</v>
       </c>
       <c r="H616" t="n">
         <v>41726</v>
@@ -18262,7 +18262,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>18.9146595001221</v>
+        <v>18.9146614074707</v>
       </c>
       <c r="H617" t="n">
         <v>25607</v>
@@ -18291,7 +18291,7 @@
         <v>20.5</v>
       </c>
       <c r="G618" t="n">
-        <v>19.0073795318604</v>
+        <v>19.0073833465576</v>
       </c>
       <c r="H618" t="n">
         <v>34244</v>
@@ -18320,7 +18320,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>19.1928195953369</v>
+        <v>19.1928215026855</v>
       </c>
       <c r="H619" t="n">
         <v>18404</v>
@@ -18465,7 +18465,7 @@
         <v>21.75</v>
       </c>
       <c r="G624" t="n">
-        <v>20.1663665771484</v>
+        <v>20.1663684844971</v>
       </c>
       <c r="H624" t="n">
         <v>26565</v>
@@ -18523,7 +18523,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G626" t="n">
-        <v>20.3054447174072</v>
+        <v>20.3054428100586</v>
       </c>
       <c r="H626" t="n">
         <v>13030</v>
@@ -18552,7 +18552,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G627" t="n">
-        <v>20.1200084686279</v>
+        <v>20.1200065612793</v>
       </c>
       <c r="H627" t="n">
         <v>16136</v>
@@ -18581,7 +18581,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>20.5372447967529</v>
+        <v>20.5372409820557</v>
       </c>
       <c r="H628" t="n">
         <v>9112</v>
@@ -18668,7 +18668,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G631" t="n">
-        <v>20.0736484527588</v>
+        <v>20.0736465454102</v>
       </c>
       <c r="H631" t="n">
         <v>17303</v>
@@ -18697,7 +18697,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G632" t="n">
-        <v>20.027286529541</v>
+        <v>20.0272884368896</v>
       </c>
       <c r="H632" t="n">
         <v>11595</v>
@@ -18726,7 +18726,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G633" t="n">
-        <v>19.8882122039795</v>
+        <v>19.8882102966309</v>
       </c>
       <c r="H633" t="n">
         <v>14444</v>
@@ -18842,7 +18842,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G637" t="n">
-        <v>19.7491321563721</v>
+        <v>19.7491283416748</v>
       </c>
       <c r="H637" t="n">
         <v>101033</v>
@@ -19016,7 +19016,7 @@
         <v>21.75</v>
       </c>
       <c r="G643" t="n">
-        <v>20.1663665771484</v>
+        <v>20.1663684844971</v>
       </c>
       <c r="H643" t="n">
         <v>20181</v>
@@ -19074,7 +19074,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G645" t="n">
-        <v>20.1200084686279</v>
+        <v>20.1200065612793</v>
       </c>
       <c r="H645" t="n">
         <v>34095</v>
@@ -19132,7 +19132,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>20.3054447174072</v>
+        <v>20.3054428100586</v>
       </c>
       <c r="H647" t="n">
         <v>17969</v>
@@ -19219,7 +19219,7 @@
         <v>22</v>
       </c>
       <c r="G650" t="n">
-        <v>20.3981647491455</v>
+        <v>20.3981666564941</v>
       </c>
       <c r="H650" t="n">
         <v>5748</v>
@@ -19248,7 +19248,7 @@
         <v>21.75</v>
       </c>
       <c r="G651" t="n">
-        <v>20.1663665771484</v>
+        <v>20.1663684844971</v>
       </c>
       <c r="H651" t="n">
         <v>14885</v>
@@ -19306,7 +19306,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>19.2855339050293</v>
+        <v>19.2855377197266</v>
       </c>
       <c r="H653" t="n">
         <v>25929</v>
@@ -19335,7 +19335,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G654" t="n">
-        <v>19.4246158599854</v>
+        <v>19.4246196746826</v>
       </c>
       <c r="H654" t="n">
         <v>27208</v>
@@ -19364,7 +19364,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G655" t="n">
-        <v>19.2855339050293</v>
+        <v>19.2855377197266</v>
       </c>
       <c r="H655" t="n">
         <v>22236</v>
@@ -19393,7 +19393,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G656" t="n">
-        <v>19.3782577514648</v>
+        <v>19.3782539367676</v>
       </c>
       <c r="H656" t="n">
         <v>42291</v>
@@ -19654,7 +19654,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>19.5636959075928</v>
+        <v>19.5636920928955</v>
       </c>
       <c r="H665" t="n">
         <v>7572</v>
@@ -19741,7 +19741,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G668" t="n">
-        <v>19.4246158599854</v>
+        <v>19.4246196746826</v>
       </c>
       <c r="H668" t="n">
         <v>9967</v>
@@ -19770,7 +19770,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G669" t="n">
-        <v>19.5636959075928</v>
+        <v>19.5636920928955</v>
       </c>
       <c r="H669" t="n">
         <v>10384</v>
@@ -19886,7 +19886,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>19.10009765625</v>
+        <v>19.1000995635986</v>
       </c>
       <c r="H673" t="n">
         <v>33687</v>
@@ -19915,7 +19915,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G674" t="n">
-        <v>19.10009765625</v>
+        <v>19.1000995635986</v>
       </c>
       <c r="H674" t="n">
         <v>17054</v>
@@ -19944,7 +19944,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>19.10009765625</v>
+        <v>19.1000995635986</v>
       </c>
       <c r="H675" t="n">
         <v>13909</v>
@@ -19973,7 +19973,7 @@
         <v>20.75</v>
       </c>
       <c r="G676" t="n">
-        <v>19.2391777038574</v>
+        <v>19.2391796112061</v>
       </c>
       <c r="H676" t="n">
         <v>7292</v>
@@ -20002,7 +20002,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G677" t="n">
-        <v>19.4246158599854</v>
+        <v>19.4246196746826</v>
       </c>
       <c r="H677" t="n">
         <v>4723</v>
@@ -20031,7 +20031,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>19.4246158599854</v>
+        <v>19.4246196746826</v>
       </c>
       <c r="H678" t="n">
         <v>3805</v>
@@ -20060,7 +20060,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>20.027286529541</v>
+        <v>20.0272884368896</v>
       </c>
       <c r="H679" t="n">
         <v>11621</v>
@@ -20089,7 +20089,7 @@
         <v>21.25</v>
       </c>
       <c r="G680" t="n">
-        <v>19.7027721405029</v>
+        <v>19.7027702331543</v>
       </c>
       <c r="H680" t="n">
         <v>7952</v>
@@ -20118,7 +20118,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>19.5636959075928</v>
+        <v>19.5636920928955</v>
       </c>
       <c r="H681" t="n">
         <v>14113</v>
@@ -20147,7 +20147,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G682" t="n">
-        <v>19.7491321563721</v>
+        <v>19.7491283416748</v>
       </c>
       <c r="H682" t="n">
         <v>16185</v>
@@ -20176,7 +20176,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>20.027286529541</v>
+        <v>20.0272884368896</v>
       </c>
       <c r="H683" t="n">
         <v>13405</v>
@@ -20205,7 +20205,7 @@
         <v>22.25</v>
       </c>
       <c r="G684" t="n">
-        <v>20.6299591064453</v>
+        <v>20.6299629211426</v>
       </c>
       <c r="H684" t="n">
         <v>27903</v>
@@ -20234,7 +20234,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G685" t="n">
-        <v>20.5372447967529</v>
+        <v>20.5372409820557</v>
       </c>
       <c r="H685" t="n">
         <v>17031</v>
@@ -20263,7 +20263,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>20.3054447174072</v>
+        <v>20.3054428100586</v>
       </c>
       <c r="H686" t="n">
         <v>23241</v>
@@ -20292,7 +20292,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>20.5372447967529</v>
+        <v>20.5372409820557</v>
       </c>
       <c r="H687" t="n">
         <v>12731</v>
@@ -20321,7 +20321,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G688" t="n">
-        <v>20.6763210296631</v>
+        <v>20.6763191223145</v>
       </c>
       <c r="H688" t="n">
         <v>14418</v>
@@ -20350,7 +20350,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G689" t="n">
-        <v>20.7226791381836</v>
+        <v>20.722677230835</v>
       </c>
       <c r="H689" t="n">
         <v>13795</v>
@@ -20379,7 +20379,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G690" t="n">
-        <v>21.0008392333984</v>
+        <v>21.0008354187012</v>
       </c>
       <c r="H690" t="n">
         <v>14529</v>
@@ -20408,7 +20408,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>20.9544773101807</v>
+        <v>20.9544792175293</v>
       </c>
       <c r="H691" t="n">
         <v>21175</v>
@@ -20437,7 +20437,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>20.9544773101807</v>
+        <v>20.9544792175293</v>
       </c>
       <c r="H692" t="n">
         <v>4369</v>
@@ -20466,7 +20466,7 @@
         <v>22.5499992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>20.9081192016602</v>
+        <v>20.9081172943115</v>
       </c>
       <c r="H693" t="n">
         <v>7284</v>
@@ -20495,7 +20495,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>21.2326335906982</v>
+        <v>21.2326354980469</v>
       </c>
       <c r="H694" t="n">
         <v>44066</v>
@@ -20553,7 +20553,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G696" t="n">
-        <v>21.1862754821777</v>
+        <v>21.1862773895264</v>
       </c>
       <c r="H696" t="n">
         <v>30291</v>
@@ -20611,7 +20611,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>21.0471954345703</v>
+        <v>21.0471992492676</v>
       </c>
       <c r="H698" t="n">
         <v>23800</v>
@@ -20640,7 +20640,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>21.2326335906982</v>
+        <v>21.2326354980469</v>
       </c>
       <c r="H699" t="n">
         <v>45041</v>
@@ -20669,7 +20669,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G700" t="n">
-        <v>21.4180717468262</v>
+        <v>21.4180698394775</v>
       </c>
       <c r="H700" t="n">
         <v>23699</v>
@@ -20698,7 +20698,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G701" t="n">
-        <v>21.2789936065674</v>
+        <v>21.278995513916</v>
       </c>
       <c r="H701" t="n">
         <v>20186</v>
@@ -20727,7 +20727,7 @@
         <v>22.75</v>
       </c>
       <c r="G702" t="n">
-        <v>21.0935535430908</v>
+        <v>21.0935554504395</v>
       </c>
       <c r="H702" t="n">
         <v>9042</v>
@@ -20756,7 +20756,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G703" t="n">
-        <v>21.1862754821777</v>
+        <v>21.1862773895264</v>
       </c>
       <c r="H703" t="n">
         <v>22966</v>
@@ -20785,7 +20785,7 @@
         <v>23.25</v>
       </c>
       <c r="G704" t="n">
-        <v>21.5571517944336</v>
+        <v>21.557149887085</v>
       </c>
       <c r="H704" t="n">
         <v>12269</v>
@@ -20814,7 +20814,7 @@
         <v>23.25</v>
       </c>
       <c r="G705" t="n">
-        <v>21.5571517944336</v>
+        <v>21.557149887085</v>
       </c>
       <c r="H705" t="n">
         <v>12214</v>
@@ -20872,7 +20872,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>20.1200084686279</v>
+        <v>20.1200065612793</v>
       </c>
       <c r="H707" t="n">
         <v>26134</v>
@@ -20901,7 +20901,7 @@
         <v>21.5</v>
       </c>
       <c r="G708" t="n">
-        <v>19.9345703125</v>
+        <v>19.9345684051514</v>
       </c>
       <c r="H708" t="n">
         <v>33477</v>
@@ -20930,7 +20930,7 @@
         <v>21.5</v>
       </c>
       <c r="G709" t="n">
-        <v>19.9345703125</v>
+        <v>19.9345684051514</v>
       </c>
       <c r="H709" t="n">
         <v>18501</v>
@@ -20959,7 +20959,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G710" t="n">
-        <v>19.8882122039795</v>
+        <v>19.8882102966309</v>
       </c>
       <c r="H710" t="n">
         <v>25401</v>
@@ -21046,7 +21046,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G713" t="n">
-        <v>20.1200084686279</v>
+        <v>20.1200065612793</v>
       </c>
       <c r="H713" t="n">
         <v>20192</v>
@@ -21075,7 +21075,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>19.5636959075928</v>
+        <v>19.5636920928955</v>
       </c>
       <c r="H714" t="n">
         <v>60696</v>
@@ -21133,7 +21133,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>19.2855339050293</v>
+        <v>19.2855377197266</v>
       </c>
       <c r="H716" t="n">
         <v>53397</v>
@@ -21162,7 +21162,7 @@
         <v>20.75</v>
       </c>
       <c r="G717" t="n">
-        <v>19.2391777038574</v>
+        <v>19.2391796112061</v>
       </c>
       <c r="H717" t="n">
         <v>8400</v>
@@ -21191,7 +21191,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G718" t="n">
-        <v>17.598051071167</v>
+        <v>17.5980529785156</v>
       </c>
       <c r="H718" t="n">
         <v>65740</v>
@@ -21220,7 +21220,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G719" t="n">
-        <v>15.2059049606323</v>
+        <v>15.205904006958</v>
       </c>
       <c r="H719" t="n">
         <v>293766</v>
@@ -21249,7 +21249,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G720" t="n">
-        <v>15.5953216552734</v>
+        <v>15.5953245162964</v>
       </c>
       <c r="H720" t="n">
         <v>193084</v>
@@ -21278,7 +21278,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G721" t="n">
-        <v>14.6681356430054</v>
+        <v>14.6681337356567</v>
       </c>
       <c r="H721" t="n">
         <v>187665</v>
@@ -21307,7 +21307,7 @@
         <v>15.5</v>
       </c>
       <c r="G722" t="n">
-        <v>14.371434211731</v>
+        <v>14.3714332580566</v>
       </c>
       <c r="H722" t="n">
         <v>192645</v>
@@ -21336,7 +21336,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G723" t="n">
-        <v>14.7052211761475</v>
+        <v>14.7052221298218</v>
       </c>
       <c r="H723" t="n">
         <v>79691</v>
@@ -21365,7 +21365,7 @@
         <v>16.5</v>
       </c>
       <c r="G724" t="n">
-        <v>15.298623085022</v>
+        <v>15.2986221313477</v>
       </c>
       <c r="H724" t="n">
         <v>86425</v>
@@ -21423,7 +21423,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G726" t="n">
-        <v>15.8920230865479</v>
+        <v>15.8920240402222</v>
       </c>
       <c r="H726" t="n">
         <v>89330</v>
@@ -21481,7 +21481,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G728" t="n">
-        <v>15.2244501113892</v>
+        <v>15.2244482040405</v>
       </c>
       <c r="H728" t="n">
         <v>58119</v>
@@ -21510,7 +21510,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G729" t="n">
-        <v>15.3542518615723</v>
+        <v>15.3542528152466</v>
       </c>
       <c r="H729" t="n">
         <v>20474</v>
@@ -21539,7 +21539,7 @@
         <v>17</v>
       </c>
       <c r="G730" t="n">
-        <v>15.7622175216675</v>
+        <v>15.7622184753418</v>
       </c>
       <c r="H730" t="n">
         <v>54217</v>
@@ -21568,7 +21568,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G731" t="n">
-        <v>15.6880435943604</v>
+        <v>15.6880416870117</v>
       </c>
       <c r="H731" t="n">
         <v>46259</v>
@@ -21597,7 +21597,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G732" t="n">
-        <v>15.6880435943604</v>
+        <v>15.6880416870117</v>
       </c>
       <c r="H732" t="n">
         <v>40182</v>
@@ -21626,7 +21626,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G733" t="n">
-        <v>15.5582361221313</v>
+        <v>15.55823802948</v>
       </c>
       <c r="H733" t="n">
         <v>68590</v>
@@ -21655,7 +21655,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>15.4840612411499</v>
+        <v>15.4840631484985</v>
       </c>
       <c r="H734" t="n">
         <v>42010</v>
@@ -21684,7 +21684,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G735" t="n">
-        <v>15.2800798416138</v>
+        <v>15.2800788879395</v>
       </c>
       <c r="H735" t="n">
         <v>38419</v>
@@ -21742,7 +21742,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G737" t="n">
-        <v>14.7599258422852</v>
+        <v>14.7599248886108</v>
       </c>
       <c r="H737" t="n">
         <v>32514</v>
@@ -21771,7 +21771,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G738" t="n">
-        <v>14.4800281524658</v>
+        <v>14.4800291061401</v>
       </c>
       <c r="H738" t="n">
         <v>35416</v>
@@ -21829,7 +21829,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G740" t="n">
-        <v>14.3494100570679</v>
+        <v>14.3494081497192</v>
       </c>
       <c r="H740" t="n">
         <v>19875</v>
@@ -21887,7 +21887,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G742" t="n">
-        <v>14.8159046173096</v>
+        <v>14.8159036636353</v>
       </c>
       <c r="H742" t="n">
         <v>23327</v>
@@ -21916,7 +21916,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>14.8345632553101</v>
+        <v>14.8345642089844</v>
       </c>
       <c r="H743" t="n">
         <v>50203</v>
@@ -21945,7 +21945,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G744" t="n">
-        <v>14.5546674728394</v>
+        <v>14.5546684265137</v>
       </c>
       <c r="H744" t="n">
         <v>33338</v>
@@ -21974,7 +21974,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G745" t="n">
-        <v>14.7599258422852</v>
+        <v>14.7599248886108</v>
       </c>
       <c r="H745" t="n">
         <v>79480</v>
@@ -22003,7 +22003,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G746" t="n">
-        <v>15.0398235321045</v>
+        <v>15.0398225784302</v>
       </c>
       <c r="H746" t="n">
         <v>39162</v>
@@ -22032,7 +22032,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G747" t="n">
-        <v>15.33837890625</v>
+        <v>15.3383808135986</v>
       </c>
       <c r="H747" t="n">
         <v>22659</v>
@@ -22090,7 +22090,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G749" t="n">
-        <v>14.7599258422852</v>
+        <v>14.7599248886108</v>
       </c>
       <c r="H749" t="n">
         <v>27881</v>
@@ -22148,7 +22148,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G751" t="n">
-        <v>13.8269319534302</v>
+        <v>13.8269329071045</v>
       </c>
       <c r="H751" t="n">
         <v>21193</v>
@@ -22235,7 +22235,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G754" t="n">
-        <v>14.2374486923218</v>
+        <v>14.2374496459961</v>
       </c>
       <c r="H754" t="n">
         <v>47839</v>
@@ -22264,7 +22264,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G755" t="n">
-        <v>14.0695123672485</v>
+        <v>14.0695104598999</v>
       </c>
       <c r="H755" t="n">
         <v>144043</v>
@@ -22293,7 +22293,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G756" t="n">
-        <v>14.0508527755737</v>
+        <v>14.0508508682251</v>
       </c>
       <c r="H756" t="n">
         <v>39824</v>
@@ -22322,7 +22322,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G757" t="n">
-        <v>14.1254911422729</v>
+        <v>14.1254920959473</v>
       </c>
       <c r="H757" t="n">
         <v>31051</v>
@@ -22380,7 +22380,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G759" t="n">
-        <v>13.5470371246338</v>
+        <v>13.5470361709595</v>
       </c>
       <c r="H759" t="n">
         <v>27400</v>
@@ -22438,7 +22438,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G761" t="n">
-        <v>13.6963157653809</v>
+        <v>13.6963148117065</v>
       </c>
       <c r="H761" t="n">
         <v>32342</v>
@@ -22467,7 +22467,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G762" t="n">
-        <v>13.9575519561768</v>
+        <v>13.9575529098511</v>
       </c>
       <c r="H762" t="n">
         <v>22482</v>
@@ -22496,7 +22496,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G763" t="n">
-        <v>14.2374486923218</v>
+        <v>14.2374496459961</v>
       </c>
       <c r="H763" t="n">
         <v>22749</v>
@@ -22583,7 +22583,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G766" t="n">
-        <v>14.5546674728394</v>
+        <v>14.5546684265137</v>
       </c>
       <c r="H766" t="n">
         <v>29260</v>
@@ -22612,7 +22612,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G767" t="n">
-        <v>14.7599258422852</v>
+        <v>14.7599248886108</v>
       </c>
       <c r="H767" t="n">
         <v>15092</v>
@@ -22670,7 +22670,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G769" t="n">
-        <v>15.114462852478</v>
+        <v>15.1144609451294</v>
       </c>
       <c r="H769" t="n">
         <v>32371</v>
@@ -22699,7 +22699,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>15.114462852478</v>
+        <v>15.1144609451294</v>
       </c>
       <c r="H770" t="n">
         <v>29082</v>
@@ -22728,7 +22728,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G771" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211620330811</v>
       </c>
       <c r="H771" t="n">
         <v>18295</v>
@@ -22815,7 +22815,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G774" t="n">
-        <v>14.9651832580566</v>
+        <v>14.965184211731</v>
       </c>
       <c r="H774" t="n">
         <v>7959</v>
@@ -22902,7 +22902,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G777" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211620330811</v>
       </c>
       <c r="H777" t="n">
         <v>12161</v>
@@ -22960,7 +22960,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G779" t="n">
-        <v>15.0398235321045</v>
+        <v>15.0398225784302</v>
       </c>
       <c r="H779" t="n">
         <v>23254</v>
@@ -22989,7 +22989,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G780" t="n">
-        <v>15.0958013534546</v>
+        <v>15.0958032608032</v>
       </c>
       <c r="H780" t="n">
         <v>7450</v>
@@ -23018,7 +23018,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G781" t="n">
-        <v>15.4316806793213</v>
+        <v>15.4316787719727</v>
       </c>
       <c r="H781" t="n">
         <v>75352</v>
@@ -23105,7 +23105,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G784" t="n">
-        <v>16.7751865386963</v>
+        <v>16.7751846313477</v>
       </c>
       <c r="H784" t="n">
         <v>108771</v>
@@ -23134,7 +23134,7 @@
         <v>18</v>
       </c>
       <c r="G785" t="n">
-        <v>16.7938461303711</v>
+        <v>16.7938480377197</v>
       </c>
       <c r="H785" t="n">
         <v>36242</v>
@@ -23163,7 +23163,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G786" t="n">
-        <v>16.3833255767822</v>
+        <v>16.3833293914795</v>
       </c>
       <c r="H786" t="n">
         <v>21191</v>
@@ -23192,7 +23192,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G787" t="n">
-        <v>16.3086891174316</v>
+        <v>16.3086910247803</v>
       </c>
       <c r="H787" t="n">
         <v>15241</v>
@@ -23221,7 +23221,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G788" t="n">
-        <v>16.1594104766846</v>
+        <v>16.1594085693359</v>
       </c>
       <c r="H788" t="n">
         <v>18002</v>
@@ -23308,7 +23308,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G791" t="n">
-        <v>15.7675542831421</v>
+        <v>15.7675561904907</v>
       </c>
       <c r="H791" t="n">
         <v>21984</v>
@@ -23598,7 +23598,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G801" t="n">
-        <v>16.3460121154785</v>
+        <v>16.3460102081299</v>
       </c>
       <c r="H801" t="n">
         <v>15026</v>
@@ -23627,7 +23627,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G802" t="n">
-        <v>16.3086891174316</v>
+        <v>16.3086910247803</v>
       </c>
       <c r="H802" t="n">
         <v>10410</v>
@@ -23743,7 +23743,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G806" t="n">
-        <v>16.495288848877</v>
+        <v>16.4952869415283</v>
       </c>
       <c r="H806" t="n">
         <v>8339</v>
@@ -23801,7 +23801,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>16.607250213623</v>
+        <v>16.6072483062744</v>
       </c>
       <c r="H808" t="n">
         <v>7788</v>
@@ -23830,7 +23830,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G809" t="n">
-        <v>16.3646717071533</v>
+        <v>16.3646697998047</v>
       </c>
       <c r="H809" t="n">
         <v>46188</v>
@@ -23859,7 +23859,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G810" t="n">
-        <v>16.2153911590576</v>
+        <v>16.2153930664062</v>
       </c>
       <c r="H810" t="n">
         <v>35824</v>
@@ -23888,7 +23888,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>15.7675542831421</v>
+        <v>15.7675561904907</v>
       </c>
       <c r="H811" t="n">
         <v>26100</v>
@@ -23917,7 +23917,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G812" t="n">
-        <v>15.7488965988159</v>
+        <v>15.7488946914673</v>
       </c>
       <c r="H812" t="n">
         <v>18087</v>
@@ -23946,7 +23946,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>15.7675542831421</v>
+        <v>15.7675561904907</v>
       </c>
       <c r="H813" t="n">
         <v>17451</v>
@@ -24004,7 +24004,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G815" t="n">
-        <v>15.7488965988159</v>
+        <v>15.7488946914673</v>
       </c>
       <c r="H815" t="n">
         <v>8805</v>
@@ -24091,7 +24091,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G818" t="n">
-        <v>16.0101337432861</v>
+        <v>16.0101318359375</v>
       </c>
       <c r="H818" t="n">
         <v>10130</v>
@@ -24178,7 +24178,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G821" t="n">
-        <v>16.0101337432861</v>
+        <v>16.0101318359375</v>
       </c>
       <c r="H821" t="n">
         <v>16712</v>
@@ -24207,7 +24207,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>16.2340526580811</v>
+        <v>16.2340507507324</v>
       </c>
       <c r="H822" t="n">
         <v>61264</v>
@@ -24236,7 +24236,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G823" t="n">
-        <v>16.2900276184082</v>
+        <v>16.2900295257568</v>
       </c>
       <c r="H823" t="n">
         <v>15799</v>
@@ -24265,7 +24265,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>16.4206504821777</v>
+        <v>16.4206523895264</v>
       </c>
       <c r="H824" t="n">
         <v>21788</v>
@@ -24294,7 +24294,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G825" t="n">
-        <v>16.2153911590576</v>
+        <v>16.2153930664062</v>
       </c>
       <c r="H825" t="n">
         <v>37134</v>
@@ -24323,7 +24323,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G826" t="n">
-        <v>16.6632289886475</v>
+        <v>16.6632270812988</v>
       </c>
       <c r="H826" t="n">
         <v>36590</v>
@@ -24439,7 +24439,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G830" t="n">
-        <v>18.1373558044434</v>
+        <v>18.1373538970947</v>
       </c>
       <c r="H830" t="n">
         <v>50235</v>
@@ -24468,7 +24468,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G831" t="n">
-        <v>18.1186962127686</v>
+        <v>18.1186923980713</v>
       </c>
       <c r="H831" t="n">
         <v>21478</v>
@@ -24526,7 +24526,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G833" t="n">
-        <v>17.4096202850342</v>
+        <v>17.4096221923828</v>
       </c>
       <c r="H833" t="n">
         <v>47242</v>
@@ -24555,7 +24555,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G834" t="n">
-        <v>17.0177631378174</v>
+        <v>17.017765045166</v>
       </c>
       <c r="H834" t="n">
         <v>30697</v>
@@ -24584,7 +24584,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>16.8871459960938</v>
+        <v>16.8871440887451</v>
       </c>
       <c r="H835" t="n">
         <v>22596</v>
@@ -24613,7 +24613,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G836" t="n">
-        <v>16.8684844970703</v>
+        <v>16.8684864044189</v>
       </c>
       <c r="H836" t="n">
         <v>31843</v>
@@ -24642,7 +24642,7 @@
         <v>18</v>
       </c>
       <c r="G837" t="n">
-        <v>16.7938461303711</v>
+        <v>16.7938480377197</v>
       </c>
       <c r="H837" t="n">
         <v>33449</v>
@@ -24671,7 +24671,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G838" t="n">
-        <v>16.625904083252</v>
+        <v>16.6259078979492</v>
       </c>
       <c r="H838" t="n">
         <v>17443</v>
@@ -24700,7 +24700,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>16.607250213623</v>
+        <v>16.6072483062744</v>
       </c>
       <c r="H839" t="n">
         <v>21116</v>
@@ -24729,7 +24729,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>16.607250213623</v>
+        <v>16.6072483062744</v>
       </c>
       <c r="H840" t="n">
         <v>26446</v>
@@ -24758,7 +24758,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G841" t="n">
-        <v>16.6632289886475</v>
+        <v>16.6632270812988</v>
       </c>
       <c r="H841" t="n">
         <v>47781</v>
@@ -24787,7 +24787,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G842" t="n">
-        <v>16.5326080322266</v>
+        <v>16.5326061248779</v>
       </c>
       <c r="H842" t="n">
         <v>6625</v>
@@ -24816,7 +24816,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G843" t="n">
-        <v>16.8498249053955</v>
+        <v>16.8498268127441</v>
       </c>
       <c r="H843" t="n">
         <v>30729</v>
@@ -24845,7 +24845,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G844" t="n">
-        <v>16.8498249053955</v>
+        <v>16.8498268127441</v>
       </c>
       <c r="H844" t="n">
         <v>8387</v>
@@ -24932,7 +24932,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G847" t="n">
-        <v>17.0364227294922</v>
+        <v>17.0364246368408</v>
       </c>
       <c r="H847" t="n">
         <v>11139</v>
@@ -24961,7 +24961,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G848" t="n">
-        <v>17.11106300354</v>
+        <v>17.1110610961914</v>
       </c>
       <c r="H848" t="n">
         <v>14480</v>
@@ -24990,7 +24990,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G849" t="n">
-        <v>16.644567489624</v>
+        <v>16.6445693969727</v>
       </c>
       <c r="H849" t="n">
         <v>27230</v>
@@ -25019,7 +25019,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G850" t="n">
-        <v>16.2153911590576</v>
+        <v>16.2153930664062</v>
       </c>
       <c r="H850" t="n">
         <v>45906</v>
@@ -25048,7 +25048,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G851" t="n">
-        <v>16.1034317016602</v>
+        <v>16.1034336090088</v>
       </c>
       <c r="H851" t="n">
         <v>27584</v>
@@ -25077,7 +25077,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G852" t="n">
-        <v>16.1034317016602</v>
+        <v>16.1034336090088</v>
       </c>
       <c r="H852" t="n">
         <v>40911</v>
@@ -25135,7 +25135,7 @@
         <v>16.5</v>
       </c>
       <c r="G854" t="n">
-        <v>15.394359588623</v>
+        <v>15.3943586349487</v>
       </c>
       <c r="H854" t="n">
         <v>40064</v>
@@ -25164,7 +25164,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G855" t="n">
-        <v>15.4130201339722</v>
+        <v>15.4130182266235</v>
       </c>
       <c r="H855" t="n">
         <v>101404</v>
@@ -25222,7 +25222,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G857" t="n">
-        <v>15.4316806793213</v>
+        <v>15.4316787719727</v>
       </c>
       <c r="H857" t="n">
         <v>42973</v>
@@ -25251,7 +25251,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G858" t="n">
-        <v>15.0771417617798</v>
+        <v>15.0771427154541</v>
       </c>
       <c r="H858" t="n">
         <v>25946</v>
@@ -25280,7 +25280,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G859" t="n">
-        <v>14.591986656189</v>
+        <v>14.5919876098633</v>
       </c>
       <c r="H859" t="n">
         <v>22488</v>
@@ -25367,7 +25367,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G862" t="n">
-        <v>14.6666259765625</v>
+        <v>14.6666269302368</v>
       </c>
       <c r="H862" t="n">
         <v>15236</v>
@@ -25425,7 +25425,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G864" t="n">
-        <v>14.8345632553101</v>
+        <v>14.8345642089844</v>
       </c>
       <c r="H864" t="n">
         <v>25043</v>
@@ -25454,7 +25454,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G865" t="n">
-        <v>14.7412662506104</v>
+        <v>14.7412643432617</v>
       </c>
       <c r="H865" t="n">
         <v>13099</v>
@@ -25483,7 +25483,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G866" t="n">
-        <v>14.4053888320923</v>
+        <v>14.405387878418</v>
       </c>
       <c r="H866" t="n">
         <v>28040</v>
@@ -25541,7 +25541,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G868" t="n">
-        <v>14.27476978302</v>
+        <v>14.2747688293457</v>
       </c>
       <c r="H868" t="n">
         <v>39174</v>
@@ -25570,7 +25570,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G869" t="n">
-        <v>14.3494100570679</v>
+        <v>14.3494081497192</v>
       </c>
       <c r="H869" t="n">
         <v>17632</v>
@@ -25599,7 +25599,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G870" t="n">
-        <v>14.7226047515869</v>
+        <v>14.7226057052612</v>
       </c>
       <c r="H870" t="n">
         <v>35178</v>
@@ -25657,7 +25657,7 @@
         <v>15.5</v>
       </c>
       <c r="G872" t="n">
-        <v>14.461368560791</v>
+        <v>14.4613676071167</v>
       </c>
       <c r="H872" t="n">
         <v>27300</v>
@@ -25686,7 +25686,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G873" t="n">
-        <v>14.368067741394</v>
+        <v>14.3680686950684</v>
       </c>
       <c r="H873" t="n">
         <v>30809</v>
@@ -25715,7 +25715,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G874" t="n">
-        <v>14.5360059738159</v>
+        <v>14.5360069274902</v>
       </c>
       <c r="H874" t="n">
         <v>20430</v>
@@ -25773,7 +25773,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G876" t="n">
-        <v>14.6666259765625</v>
+        <v>14.6666269302368</v>
       </c>
       <c r="H876" t="n">
         <v>9573</v>
@@ -25802,7 +25802,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G877" t="n">
-        <v>15.4689970016479</v>
+        <v>15.4689998626709</v>
       </c>
       <c r="H877" t="n">
         <v>48759</v>
@@ -25831,7 +25831,7 @@
         <v>16.5</v>
       </c>
       <c r="G878" t="n">
-        <v>15.394359588623</v>
+        <v>15.3943586349487</v>
       </c>
       <c r="H878" t="n">
         <v>37103</v>
@@ -25860,7 +25860,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G879" t="n">
-        <v>15.4316806793213</v>
+        <v>15.4316787719727</v>
       </c>
       <c r="H879" t="n">
         <v>22992</v>
@@ -25918,7 +25918,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>15.3010606765747</v>
+        <v>15.3010597229004</v>
       </c>
       <c r="H881" t="n">
         <v>18408</v>
@@ -25976,7 +25976,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G883" t="n">
-        <v>15.5622978210449</v>
+        <v>15.5622987747192</v>
       </c>
       <c r="H883" t="n">
         <v>38097</v>
@@ -26005,7 +26005,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G884" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211620330811</v>
       </c>
       <c r="H884" t="n">
         <v>14419</v>
@@ -26034,7 +26034,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G885" t="n">
-        <v>15.1331205368042</v>
+        <v>15.1331214904785</v>
       </c>
       <c r="H885" t="n">
         <v>9715</v>
@@ -26063,7 +26063,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G886" t="n">
-        <v>14.9651832580566</v>
+        <v>14.965184211731</v>
       </c>
       <c r="H886" t="n">
         <v>6520</v>
@@ -26121,7 +26121,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G888" t="n">
-        <v>15.0398235321045</v>
+        <v>15.0398225784302</v>
       </c>
       <c r="H888" t="n">
         <v>11864</v>
@@ -26179,7 +26179,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G890" t="n">
-        <v>15.4316806793213</v>
+        <v>15.4316787719727</v>
       </c>
       <c r="H890" t="n">
         <v>18050</v>
@@ -26208,7 +26208,7 @@
         <v>16.5</v>
       </c>
       <c r="G891" t="n">
-        <v>15.394359588623</v>
+        <v>15.3943586349487</v>
       </c>
       <c r="H891" t="n">
         <v>18797</v>
@@ -26237,7 +26237,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G892" t="n">
-        <v>15.4689970016479</v>
+        <v>15.4689998626709</v>
       </c>
       <c r="H892" t="n">
         <v>22331</v>
@@ -26266,7 +26266,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G893" t="n">
-        <v>15.3197221755981</v>
+        <v>15.3197193145752</v>
       </c>
       <c r="H893" t="n">
         <v>22421</v>
@@ -26295,7 +26295,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G894" t="n">
-        <v>15.2264184951782</v>
+        <v>15.2264213562012</v>
       </c>
       <c r="H894" t="n">
         <v>6135</v>
@@ -26324,7 +26324,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G895" t="n">
-        <v>15.2264184951782</v>
+        <v>15.2264213562012</v>
       </c>
       <c r="H895" t="n">
         <v>5603</v>
@@ -26353,7 +26353,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G896" t="n">
-        <v>15.0958013534546</v>
+        <v>15.0958032608032</v>
       </c>
       <c r="H896" t="n">
         <v>8149</v>
@@ -26411,7 +26411,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G898" t="n">
-        <v>14.7599258422852</v>
+        <v>14.7599248886108</v>
       </c>
       <c r="H898" t="n">
         <v>42893</v>
@@ -26469,7 +26469,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G900" t="n">
-        <v>14.9465217590332</v>
+        <v>14.9465227127075</v>
       </c>
       <c r="H900" t="n">
         <v>23925</v>
@@ -26498,7 +26498,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G901" t="n">
-        <v>14.7785844802856</v>
+        <v>14.77858543396</v>
       </c>
       <c r="H901" t="n">
         <v>22369</v>
@@ -26556,7 +26556,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G903" t="n">
-        <v>14.4427070617676</v>
+        <v>14.4427061080933</v>
       </c>
       <c r="H903" t="n">
         <v>41043</v>
@@ -26585,7 +26585,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G904" t="n">
-        <v>14.591986656189</v>
+        <v>14.5919876098633</v>
       </c>
       <c r="H904" t="n">
         <v>41338</v>
@@ -26614,7 +26614,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211620330811</v>
       </c>
       <c r="H905" t="n">
         <v>56292</v>
@@ -26701,7 +26701,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211620330811</v>
       </c>
       <c r="H908" t="n">
         <v>12911</v>
@@ -26730,7 +26730,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G909" t="n">
-        <v>14.7785844802856</v>
+        <v>14.77858543396</v>
       </c>
       <c r="H909" t="n">
         <v>13798</v>
@@ -26759,7 +26759,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G910" t="n">
-        <v>14.8159046173096</v>
+        <v>14.8159036636353</v>
       </c>
       <c r="H910" t="n">
         <v>17570</v>
@@ -26788,7 +26788,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G911" t="n">
-        <v>14.7226047515869</v>
+        <v>14.7226057052612</v>
       </c>
       <c r="H911" t="n">
         <v>15210</v>
@@ -26817,7 +26817,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G912" t="n">
-        <v>14.685284614563</v>
+        <v>14.6852855682373</v>
       </c>
       <c r="H912" t="n">
         <v>12131</v>
@@ -26846,7 +26846,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G913" t="n">
-        <v>14.6666259765625</v>
+        <v>14.6666269302368</v>
       </c>
       <c r="H913" t="n">
         <v>17280</v>
@@ -26875,7 +26875,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G914" t="n">
-        <v>14.7599258422852</v>
+        <v>14.7599248886108</v>
       </c>
       <c r="H914" t="n">
         <v>16508</v>
@@ -26933,7 +26933,7 @@
         <v>15.5</v>
       </c>
       <c r="G916" t="n">
-        <v>14.461368560791</v>
+        <v>14.4613676071167</v>
       </c>
       <c r="H916" t="n">
         <v>30625</v>
@@ -26962,7 +26962,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G917" t="n">
-        <v>14.5546674728394</v>
+        <v>14.5546684265137</v>
       </c>
       <c r="H917" t="n">
         <v>9480</v>
@@ -26991,7 +26991,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G918" t="n">
-        <v>14.2001304626465</v>
+        <v>14.2001295089722</v>
       </c>
       <c r="H918" t="n">
         <v>9942</v>
@@ -27020,7 +27020,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G919" t="n">
-        <v>14.181468963623</v>
+        <v>14.1814708709717</v>
       </c>
       <c r="H919" t="n">
         <v>10661</v>
@@ -27049,7 +27049,7 @@
         <v>15</v>
       </c>
       <c r="G920" t="n">
-        <v>13.9948711395264</v>
+        <v>13.994873046875</v>
       </c>
       <c r="H920" t="n">
         <v>33025</v>
@@ -27078,7 +27078,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G921" t="n">
-        <v>13.8082752227783</v>
+        <v>13.808274269104</v>
       </c>
       <c r="H921" t="n">
         <v>16368</v>
@@ -27107,7 +27107,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G922" t="n">
-        <v>13.6776552200317</v>
+        <v>13.6776542663574</v>
       </c>
       <c r="H922" t="n">
         <v>25261</v>
@@ -27136,7 +27136,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G923" t="n">
-        <v>14.3307495117188</v>
+        <v>14.3307485580444</v>
       </c>
       <c r="H923" t="n">
         <v>13369</v>
@@ -27194,7 +27194,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G925" t="n">
-        <v>14.27476978302</v>
+        <v>14.2747688293457</v>
       </c>
       <c r="H925" t="n">
         <v>36761</v>
@@ -27223,7 +27223,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G926" t="n">
-        <v>14.3307495117188</v>
+        <v>14.3307485580444</v>
       </c>
       <c r="H926" t="n">
         <v>13857</v>
@@ -27252,7 +27252,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G927" t="n">
-        <v>14.0695123672485</v>
+        <v>14.0695104598999</v>
       </c>
       <c r="H927" t="n">
         <v>14937</v>
@@ -27281,7 +27281,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>13.7149744033813</v>
+        <v>13.714973449707</v>
       </c>
       <c r="H928" t="n">
         <v>50442</v>
@@ -27368,7 +27368,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G931" t="n">
-        <v>13.9388914108276</v>
+        <v>13.938892364502</v>
       </c>
       <c r="H931" t="n">
         <v>39887</v>
@@ -27455,7 +27455,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G934" t="n">
-        <v>13.8082752227783</v>
+        <v>13.808274269104</v>
       </c>
       <c r="H934" t="n">
         <v>10751</v>
@@ -27484,7 +27484,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G935" t="n">
-        <v>13.9202327728271</v>
+        <v>13.9202318191528</v>
       </c>
       <c r="H935" t="n">
         <v>14235</v>
@@ -27600,7 +27600,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>14.368067741394</v>
+        <v>14.3680686950684</v>
       </c>
       <c r="H939" t="n">
         <v>13296</v>
@@ -27629,7 +27629,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G940" t="n">
-        <v>14.7226047515869</v>
+        <v>14.7226057052612</v>
       </c>
       <c r="H940" t="n">
         <v>35960</v>
@@ -27658,7 +27658,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G941" t="n">
-        <v>14.7226047515869</v>
+        <v>14.7226057052612</v>
       </c>
       <c r="H941" t="n">
         <v>12188</v>
@@ -27687,7 +27687,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G942" t="n">
-        <v>14.8345632553101</v>
+        <v>14.8345642089844</v>
       </c>
       <c r="H942" t="n">
         <v>26935</v>
@@ -27716,7 +27716,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G943" t="n">
-        <v>14.7599258422852</v>
+        <v>14.7599248886108</v>
       </c>
       <c r="H943" t="n">
         <v>29056</v>
@@ -27774,7 +27774,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G945" t="n">
-        <v>14.4986886978149</v>
+        <v>14.4986877441406</v>
       </c>
       <c r="H945" t="n">
         <v>7627</v>
@@ -27832,7 +27832,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G947" t="n">
-        <v>14.7412662506104</v>
+        <v>14.7412643432617</v>
       </c>
       <c r="H947" t="n">
         <v>32039</v>
@@ -27861,7 +27861,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>14.368067741394</v>
+        <v>14.3680686950684</v>
       </c>
       <c r="H948" t="n">
         <v>32512</v>
@@ -27890,7 +27890,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G949" t="n">
-        <v>14.27476978302</v>
+        <v>14.2747688293457</v>
       </c>
       <c r="H949" t="n">
         <v>31043</v>
@@ -27919,7 +27919,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G950" t="n">
-        <v>13.901572227478</v>
+        <v>13.9015712738037</v>
       </c>
       <c r="H950" t="n">
         <v>31947</v>
@@ -27977,7 +27977,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G952" t="n">
-        <v>14.9465217590332</v>
+        <v>14.9465227127075</v>
       </c>
       <c r="H952" t="n">
         <v>82129</v>
@@ -28006,7 +28006,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G953" t="n">
-        <v>15.1331205368042</v>
+        <v>15.1331214904785</v>
       </c>
       <c r="H953" t="n">
         <v>42848</v>
@@ -28064,7 +28064,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G955" t="n">
-        <v>14.088171005249</v>
+        <v>14.0881719589233</v>
       </c>
       <c r="H955" t="n">
         <v>53160</v>
@@ -28093,7 +28093,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G956" t="n">
-        <v>13.9388914108276</v>
+        <v>13.938892364502</v>
       </c>
       <c r="H956" t="n">
         <v>38593</v>
@@ -28151,7 +28151,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G958" t="n">
-        <v>14.0695123672485</v>
+        <v>14.0695104598999</v>
       </c>
       <c r="H958" t="n">
         <v>28101</v>
@@ -28180,7 +28180,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G959" t="n">
-        <v>14.0135326385498</v>
+        <v>14.0135307312012</v>
       </c>
       <c r="H959" t="n">
         <v>32572</v>
@@ -28209,7 +28209,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>14.088171005249</v>
+        <v>14.0881719589233</v>
       </c>
       <c r="H960" t="n">
         <v>26160</v>
@@ -28238,7 +28238,7 @@
         <v>15</v>
       </c>
       <c r="G961" t="n">
-        <v>13.9948711395264</v>
+        <v>13.994873046875</v>
       </c>
       <c r="H961" t="n">
         <v>44078</v>
@@ -28267,7 +28267,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G962" t="n">
-        <v>14.3307495117188</v>
+        <v>14.3307485580444</v>
       </c>
       <c r="H962" t="n">
         <v>62002</v>
@@ -28296,7 +28296,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G963" t="n">
-        <v>14.4053888320923</v>
+        <v>14.405387878418</v>
       </c>
       <c r="H963" t="n">
         <v>39229</v>
@@ -28325,7 +28325,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G964" t="n">
-        <v>14.3307495117188</v>
+        <v>14.3307485580444</v>
       </c>
       <c r="H964" t="n">
         <v>33011</v>
@@ -28354,7 +28354,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G965" t="n">
-        <v>14.3307495117188</v>
+        <v>14.3307485580444</v>
       </c>
       <c r="H965" t="n">
         <v>63095</v>
@@ -28383,7 +28383,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G966" t="n">
-        <v>14.27476978302</v>
+        <v>14.2747688293457</v>
       </c>
       <c r="H966" t="n">
         <v>54032</v>
@@ -28499,7 +28499,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G970" t="n">
-        <v>14.7412662506104</v>
+        <v>14.7412643432617</v>
       </c>
       <c r="H970" t="n">
         <v>93949</v>
@@ -28557,7 +28557,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G972" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211620330811</v>
       </c>
       <c r="H972" t="n">
         <v>45023</v>
@@ -28644,7 +28644,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G975" t="n">
-        <v>14.4986886978149</v>
+        <v>14.4986877441406</v>
       </c>
       <c r="H975" t="n">
         <v>68150</v>
@@ -28673,7 +28673,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G976" t="n">
-        <v>14.4427070617676</v>
+        <v>14.4427061080933</v>
       </c>
       <c r="H976" t="n">
         <v>46413</v>
@@ -28731,7 +28731,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G978" t="n">
-        <v>14.8345632553101</v>
+        <v>14.8345642089844</v>
       </c>
       <c r="H978" t="n">
         <v>49423</v>
@@ -28760,7 +28760,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G979" t="n">
-        <v>14.8905429840088</v>
+        <v>14.8905439376831</v>
       </c>
       <c r="H979" t="n">
         <v>34422</v>
@@ -28789,7 +28789,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G980" t="n">
-        <v>14.8905429840088</v>
+        <v>14.8905439376831</v>
       </c>
       <c r="H980" t="n">
         <v>30884</v>
@@ -28818,7 +28818,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G981" t="n">
-        <v>15.0958013534546</v>
+        <v>15.0958032608032</v>
       </c>
       <c r="H981" t="n">
         <v>45959</v>
@@ -28847,7 +28847,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211620330811</v>
       </c>
       <c r="H982" t="n">
         <v>43914</v>
@@ -28876,7 +28876,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G983" t="n">
-        <v>15.114462852478</v>
+        <v>15.1144609451294</v>
       </c>
       <c r="H983" t="n">
         <v>20830</v>
@@ -28992,7 +28992,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>15.0211639404297</v>
+        <v>15.0211620330811</v>
       </c>
       <c r="H987" t="n">
         <v>38085</v>
@@ -29021,7 +29021,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G988" t="n">
-        <v>14.9740724563599</v>
+        <v>14.9740743637085</v>
       </c>
       <c r="H988" t="n">
         <v>19772</v>
@@ -29050,7 +29050,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G989" t="n">
-        <v>14.9552392959595</v>
+        <v>14.9552383422852</v>
       </c>
       <c r="H989" t="n">
         <v>18527</v>
@@ -29137,7 +29137,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>14.7857217788696</v>
+        <v>14.785719871521</v>
       </c>
       <c r="H992" t="n">
         <v>41280</v>
@@ -29195,7 +29195,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G994" t="n">
-        <v>15.2754383087158</v>
+        <v>15.2754392623901</v>
       </c>
       <c r="H994" t="n">
         <v>96495</v>
@@ -29224,7 +29224,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G995" t="n">
-        <v>15.5768051147461</v>
+        <v>15.5768041610718</v>
       </c>
       <c r="H995" t="n">
         <v>234762</v>
@@ -29282,7 +29282,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G997" t="n">
-        <v>16.2172050476074</v>
+        <v>16.2172031402588</v>
       </c>
       <c r="H997" t="n">
         <v>252404</v>
@@ -29311,7 +29311,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G998" t="n">
-        <v>15.5768051147461</v>
+        <v>15.5768041610718</v>
       </c>
       <c r="H998" t="n">
         <v>155080</v>
@@ -29340,7 +29340,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G999" t="n">
-        <v>15.5956382751465</v>
+        <v>15.5956373214722</v>
       </c>
       <c r="H999" t="n">
         <v>133198</v>
@@ -29369,7 +29369,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1000" t="n">
-        <v>15.5956382751465</v>
+        <v>15.5956373214722</v>
       </c>
       <c r="H1000" t="n">
         <v>38462</v>
@@ -29398,7 +29398,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1001" t="n">
-        <v>15.5579710006714</v>
+        <v>15.5579681396484</v>
       </c>
       <c r="H1001" t="n">
         <v>29662</v>
@@ -29427,7 +29427,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1002" t="n">
-        <v>15.426118850708</v>
+        <v>15.4261198043823</v>
       </c>
       <c r="H1002" t="n">
         <v>56187</v>
@@ -29456,7 +29456,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1003" t="n">
-        <v>15.4449586868286</v>
+        <v>15.44495677948</v>
       </c>
       <c r="H1003" t="n">
         <v>28443</v>
@@ -29485,7 +29485,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1004" t="n">
-        <v>15.3507795333862</v>
+        <v>15.3507804870605</v>
       </c>
       <c r="H1004" t="n">
         <v>50387</v>
@@ -29514,7 +29514,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1005" t="n">
-        <v>15.4449586868286</v>
+        <v>15.44495677948</v>
       </c>
       <c r="H1005" t="n">
         <v>27302</v>
@@ -29601,7 +29601,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1008" t="n">
-        <v>15.6898136138916</v>
+        <v>15.6898174285889</v>
       </c>
       <c r="H1008" t="n">
         <v>70765</v>
@@ -29630,7 +29630,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1009" t="n">
-        <v>16.0665225982666</v>
+        <v>16.066520690918</v>
       </c>
       <c r="H1009" t="n">
         <v>80937</v>
@@ -29659,7 +29659,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1010" t="n">
-        <v>15.6144723892212</v>
+        <v>15.6144752502441</v>
       </c>
       <c r="H1010" t="n">
         <v>63772</v>
@@ -29717,7 +29717,7 @@
         <v>16.5</v>
       </c>
       <c r="G1012" t="n">
-        <v>15.539134979248</v>
+        <v>15.5391321182251</v>
       </c>
       <c r="H1012" t="n">
         <v>48674</v>
@@ -29746,7 +29746,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1013" t="n">
-        <v>15.5579710006714</v>
+        <v>15.5579681396484</v>
       </c>
       <c r="H1013" t="n">
         <v>19229</v>
@@ -29775,7 +29775,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1014" t="n">
-        <v>15.5768051147461</v>
+        <v>15.5768041610718</v>
       </c>
       <c r="H1014" t="n">
         <v>15642</v>
@@ -29804,7 +29804,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1015" t="n">
-        <v>15.426118850708</v>
+        <v>15.4261198043823</v>
       </c>
       <c r="H1015" t="n">
         <v>16496</v>
@@ -29833,7 +29833,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1016" t="n">
-        <v>15.9346733093262</v>
+        <v>15.9346742630005</v>
       </c>
       <c r="H1016" t="n">
         <v>53402</v>
@@ -29862,7 +29862,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1017" t="n">
-        <v>15.8781690597534</v>
+        <v>15.8781681060791</v>
       </c>
       <c r="H1017" t="n">
         <v>42179</v>
@@ -29891,7 +29891,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1018" t="n">
-        <v>15.6144723892212</v>
+        <v>15.6144752502441</v>
       </c>
       <c r="H1018" t="n">
         <v>34506</v>
@@ -29949,7 +29949,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1020" t="n">
-        <v>15.3131084442139</v>
+        <v>15.3131103515625</v>
       </c>
       <c r="H1020" t="n">
         <v>45082</v>
@@ -30007,7 +30007,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1022" t="n">
-        <v>15.5956382751465</v>
+        <v>15.5956373214722</v>
       </c>
       <c r="H1022" t="n">
         <v>32083</v>
@@ -30065,7 +30065,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1024" t="n">
-        <v>15.3319463729858</v>
+        <v>15.3319454193115</v>
       </c>
       <c r="H1024" t="n">
         <v>35910</v>
@@ -30123,7 +30123,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.5956382751465</v>
+        <v>15.5956373214722</v>
       </c>
       <c r="H1026" t="n">
         <v>30480</v>
@@ -30152,7 +30152,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.4826278686523</v>
+        <v>15.4826288223267</v>
       </c>
       <c r="H1027" t="n">
         <v>19815</v>
@@ -30181,7 +30181,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1028" t="n">
-        <v>15.3319463729858</v>
+        <v>15.3319454193115</v>
       </c>
       <c r="H1028" t="n">
         <v>30374</v>
@@ -30413,7 +30413,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1036" t="n">
-        <v>14.4090156555176</v>
+        <v>14.4090137481689</v>
       </c>
       <c r="H1036" t="n">
         <v>46547</v>
@@ -30442,7 +30442,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1037" t="n">
-        <v>13.9381313323975</v>
+        <v>13.9381322860718</v>
       </c>
       <c r="H1037" t="n">
         <v>76112</v>
@@ -30529,7 +30529,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>14.5031900405884</v>
+        <v>14.5031909942627</v>
       </c>
       <c r="H1040" t="n">
         <v>41498</v>
@@ -30558,7 +30558,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1041" t="n">
-        <v>14.6915445327759</v>
+        <v>14.6915454864502</v>
       </c>
       <c r="H1041" t="n">
         <v>30895</v>
@@ -30587,7 +30587,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.484356880188</v>
+        <v>14.4843549728394</v>
       </c>
       <c r="H1042" t="n">
         <v>44262</v>
@@ -30616,7 +30616,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.2960014343262</v>
+        <v>14.2960033416748</v>
       </c>
       <c r="H1043" t="n">
         <v>74475</v>
@@ -30645,7 +30645,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.5031900405884</v>
+        <v>14.5031909942627</v>
       </c>
       <c r="H1044" t="n">
         <v>29673</v>
@@ -30674,7 +30674,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1045" t="n">
-        <v>14.2960014343262</v>
+        <v>14.2960033416748</v>
       </c>
       <c r="H1045" t="n">
         <v>45324</v>
@@ -30703,7 +30703,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.2960014343262</v>
+        <v>14.2960033416748</v>
       </c>
       <c r="H1046" t="n">
         <v>43642</v>
@@ -30732,7 +30732,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1047" t="n">
-        <v>14.3336744308472</v>
+        <v>14.3336725234985</v>
       </c>
       <c r="H1047" t="n">
         <v>22716</v>
@@ -30819,7 +30819,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1050" t="n">
-        <v>14.182991027832</v>
+        <v>14.1829900741577</v>
       </c>
       <c r="H1050" t="n">
         <v>38460</v>
@@ -30906,7 +30906,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1053" t="n">
-        <v>13.0528707504272</v>
+        <v>13.0528717041016</v>
       </c>
       <c r="H1053" t="n">
         <v>93637</v>
@@ -30935,7 +30935,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G1054" t="n">
-        <v>12.9210252761841</v>
+        <v>12.9210243225098</v>
       </c>
       <c r="H1054" t="n">
         <v>57592</v>
@@ -30993,7 +30993,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1056" t="n">
-        <v>12.9963665008545</v>
+        <v>12.9963655471802</v>
       </c>
       <c r="H1056" t="n">
         <v>113856</v>
@@ -31051,7 +31051,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1058" t="n">
-        <v>12.3371295928955</v>
+        <v>12.3371305465698</v>
       </c>
       <c r="H1058" t="n">
         <v>74518</v>
@@ -31138,7 +31138,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1061" t="n">
-        <v>11.3953647613525</v>
+        <v>11.3953657150269</v>
       </c>
       <c r="H1061" t="n">
         <v>61208</v>
@@ -31167,7 +31167,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G1062" t="n">
-        <v>10.9621524810791</v>
+        <v>10.9621534347534</v>
       </c>
       <c r="H1062" t="n">
         <v>119472</v>
@@ -31225,7 +31225,7 @@
         <v>10.5</v>
       </c>
       <c r="G1064" t="n">
-        <v>9.88854026794434</v>
+        <v>9.88853931427002</v>
       </c>
       <c r="H1064" t="n">
         <v>109052</v>
@@ -31312,7 +31312,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G1067" t="n">
-        <v>9.35173320770264</v>
+        <v>9.35173225402832</v>
       </c>
       <c r="H1067" t="n">
         <v>190760</v>
@@ -31341,7 +31341,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.04267883300781</v>
+        <v>8.04267978668213</v>
       </c>
       <c r="H1068" t="n">
         <v>106769</v>
@@ -31399,7 +31399,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1070" t="n">
-        <v>9.04094982147217</v>
+        <v>9.04095077514648</v>
       </c>
       <c r="H1070" t="n">
         <v>49982</v>
@@ -31457,7 +31457,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1072" t="n">
-        <v>10.6796236038208</v>
+        <v>10.6796226501465</v>
       </c>
       <c r="H1072" t="n">
         <v>179318</v>
@@ -31515,7 +31515,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1074" t="n">
-        <v>12.808012008667</v>
+        <v>12.8080139160156</v>
       </c>
       <c r="H1074" t="n">
         <v>113035</v>
@@ -31573,7 +31573,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1076" t="n">
-        <v>10.8868112564087</v>
+        <v>10.8868103027344</v>
       </c>
       <c r="H1076" t="n">
         <v>92029</v>
@@ -31631,7 +31631,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1078" t="n">
-        <v>10.6796236038208</v>
+        <v>10.6796226501465</v>
       </c>
       <c r="H1078" t="n">
         <v>14651</v>
@@ -31660,7 +31660,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1079" t="n">
-        <v>10.5666103363037</v>
+        <v>10.566611289978</v>
       </c>
       <c r="H1079" t="n">
         <v>24736</v>
@@ -31689,7 +31689,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1080" t="n">
-        <v>10.0015506744385</v>
+        <v>10.0015516281128</v>
       </c>
       <c r="H1080" t="n">
         <v>31361</v>
@@ -31718,7 +31718,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1081" t="n">
-        <v>10.5666103363037</v>
+        <v>10.566611289978</v>
       </c>
       <c r="H1081" t="n">
         <v>20239</v>
@@ -31776,7 +31776,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1083" t="n">
-        <v>10.5477752685547</v>
+        <v>10.5477743148804</v>
       </c>
       <c r="H1083" t="n">
         <v>11260</v>
@@ -31805,7 +31805,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1084" t="n">
-        <v>10.6607866287231</v>
+        <v>10.6607885360718</v>
       </c>
       <c r="H1084" t="n">
         <v>39954</v>
@@ -31834,7 +31834,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1085" t="n">
-        <v>11.0374937057495</v>
+        <v>11.0374946594238</v>
       </c>
       <c r="H1085" t="n">
         <v>29423</v>
@@ -31979,7 +31979,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1090" t="n">
-        <v>10.1522331237793</v>
+        <v>10.1522340774536</v>
       </c>
       <c r="H1090" t="n">
         <v>40026</v>
@@ -32095,7 +32095,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1094" t="n">
-        <v>10.6984577178955</v>
+        <v>10.6984567642212</v>
       </c>
       <c r="H1094" t="n">
         <v>30009</v>
@@ -32124,7 +32124,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1095" t="n">
-        <v>10.6419534683228</v>
+        <v>10.6419515609741</v>
       </c>
       <c r="H1095" t="n">
         <v>22763</v>
@@ -32211,7 +32211,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1098" t="n">
-        <v>10.8868112564087</v>
+        <v>10.8868103027344</v>
       </c>
       <c r="H1098" t="n">
         <v>21458</v>
@@ -32240,7 +32240,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1099" t="n">
-        <v>10.8868112564087</v>
+        <v>10.8868103027344</v>
       </c>
       <c r="H1099" t="n">
         <v>13705</v>
@@ -32327,7 +32327,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1102" t="n">
-        <v>10.6607866287231</v>
+        <v>10.6607885360718</v>
       </c>
       <c r="H1102" t="n">
         <v>22423</v>
@@ -32356,7 +32356,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1103" t="n">
-        <v>10.4724349975586</v>
+        <v>10.4724340438843</v>
       </c>
       <c r="H1103" t="n">
         <v>16823</v>
@@ -32385,7 +32385,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1104" t="n">
-        <v>10.6607866287231</v>
+        <v>10.6607885360718</v>
       </c>
       <c r="H1104" t="n">
         <v>2137</v>
@@ -32443,7 +32443,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1106" t="n">
-        <v>10.6984577178955</v>
+        <v>10.6984567642212</v>
       </c>
       <c r="H1106" t="n">
         <v>8760</v>
@@ -32472,7 +32472,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1107" t="n">
-        <v>10.4724349975586</v>
+        <v>10.4724340438843</v>
       </c>
       <c r="H1107" t="n">
         <v>9680</v>
@@ -32501,7 +32501,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1108" t="n">
-        <v>10.1522331237793</v>
+        <v>10.1522340774536</v>
       </c>
       <c r="H1108" t="n">
         <v>24692</v>
@@ -32530,7 +32530,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1109" t="n">
-        <v>10.5666103363037</v>
+        <v>10.566611289978</v>
       </c>
       <c r="H1109" t="n">
         <v>11668</v>
@@ -32559,7 +32559,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1110" t="n">
-        <v>10.8868112564087</v>
+        <v>10.8868103027344</v>
       </c>
       <c r="H1110" t="n">
         <v>59827</v>
@@ -32588,7 +32588,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>10.9244813919067</v>
+        <v>10.9244823455811</v>
       </c>
       <c r="H1111" t="n">
         <v>28876</v>
@@ -32646,7 +32646,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1113" t="n">
-        <v>10.9244813919067</v>
+        <v>10.9244823455811</v>
       </c>
       <c r="H1113" t="n">
         <v>40746</v>
@@ -32675,7 +32675,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1114" t="n">
-        <v>10.867974281311</v>
+        <v>10.8679752349854</v>
       </c>
       <c r="H1114" t="n">
         <v>30468</v>
@@ -32733,7 +32733,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1116" t="n">
-        <v>11.4895401000977</v>
+        <v>11.489541053772</v>
       </c>
       <c r="H1116" t="n">
         <v>90141</v>
@@ -32762,7 +32762,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1117" t="n">
-        <v>11.4895401000977</v>
+        <v>11.489541053772</v>
       </c>
       <c r="H1117" t="n">
         <v>82381</v>
@@ -32791,7 +32791,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1118" t="n">
-        <v>11.4895401000977</v>
+        <v>11.489541053772</v>
       </c>
       <c r="H1118" t="n">
         <v>60368</v>
@@ -32820,7 +32820,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G1119" t="n">
-        <v>10.9809885025024</v>
+        <v>10.9809865951538</v>
       </c>
       <c r="H1119" t="n">
         <v>54432</v>
@@ -32849,7 +32849,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1120" t="n">
-        <v>11.3388576507568</v>
+        <v>11.3388586044312</v>
       </c>
       <c r="H1120" t="n">
         <v>57918</v>
@@ -32878,7 +32878,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1121" t="n">
-        <v>11.4330358505249</v>
+        <v>11.4330348968506</v>
       </c>
       <c r="H1121" t="n">
         <v>47351</v>
@@ -32907,7 +32907,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1122" t="n">
-        <v>11.7155647277832</v>
+        <v>11.7155656814575</v>
       </c>
       <c r="H1122" t="n">
         <v>73584</v>
@@ -32936,7 +32936,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1123" t="n">
-        <v>11.9227523803711</v>
+        <v>11.9227533340454</v>
       </c>
       <c r="H1123" t="n">
         <v>70358</v>
@@ -32965,7 +32965,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1124" t="n">
-        <v>12.205283164978</v>
+        <v>12.2052822113037</v>
       </c>
       <c r="H1124" t="n">
         <v>73154</v>
@@ -32994,7 +32994,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G1125" t="n">
-        <v>12.1299419403076</v>
+        <v>12.1299409866333</v>
       </c>
       <c r="H1125" t="n">
         <v>139785</v>
@@ -33023,7 +33023,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G1126" t="n">
-        <v>12.0169286727905</v>
+        <v>12.0169296264648</v>
       </c>
       <c r="H1126" t="n">
         <v>70083</v>
@@ -33052,7 +33052,7 @@
         <v>12.5</v>
       </c>
       <c r="G1127" t="n">
-        <v>11.7720718383789</v>
+        <v>11.7720708847046</v>
       </c>
       <c r="H1127" t="n">
         <v>39780</v>
@@ -33081,7 +33081,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1128" t="n">
-        <v>11.1505060195923</v>
+        <v>11.150505065918</v>
       </c>
       <c r="H1128" t="n">
         <v>44853</v>
@@ -33110,7 +33110,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1129" t="n">
-        <v>10.9433164596558</v>
+        <v>10.9433174133301</v>
       </c>
       <c r="H1129" t="n">
         <v>38358</v>
@@ -33197,7 +33197,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1132" t="n">
-        <v>10.9433164596558</v>
+        <v>10.9433174133301</v>
       </c>
       <c r="H1132" t="n">
         <v>114207</v>
@@ -33226,7 +33226,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1133" t="n">
-        <v>10.6607866287231</v>
+        <v>10.6607885360718</v>
       </c>
       <c r="H1133" t="n">
         <v>82825</v>
@@ -33284,7 +33284,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1135" t="n">
-        <v>10.9433164596558</v>
+        <v>10.9433174133301</v>
       </c>
       <c r="H1135" t="n">
         <v>57098</v>
@@ -33371,7 +33371,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>10.8114700317383</v>
+        <v>10.811469078064</v>
       </c>
       <c r="H1138" t="n">
         <v>27528</v>
@@ -33458,7 +33458,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1141" t="n">
-        <v>10.7172927856445</v>
+        <v>10.7172918319702</v>
       </c>
       <c r="H1141" t="n">
         <v>30811</v>
@@ -33516,7 +33516,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1143" t="n">
-        <v>10.7172927856445</v>
+        <v>10.7172918319702</v>
       </c>
       <c r="H1143" t="n">
         <v>32003</v>
@@ -33545,7 +33545,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1144" t="n">
-        <v>10.4724349975586</v>
+        <v>10.4724340438843</v>
       </c>
       <c r="H1144" t="n">
         <v>19008</v>
@@ -33603,7 +33603,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.5477752685547</v>
+        <v>10.5477743148804</v>
       </c>
       <c r="H1146" t="n">
         <v>20019</v>
@@ -33632,7 +33632,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1147" t="n">
-        <v>10.4724349975586</v>
+        <v>10.4724340438843</v>
       </c>
       <c r="H1147" t="n">
         <v>14881</v>
@@ -33661,7 +33661,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1148" t="n">
-        <v>10.3405866622925</v>
+        <v>10.3405857086182</v>
       </c>
       <c r="H1148" t="n">
         <v>19361</v>
@@ -33690,7 +33690,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.3782587051392</v>
+        <v>10.3782577514648</v>
       </c>
       <c r="H1149" t="n">
         <v>23719</v>
@@ -33719,7 +33719,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1150" t="n">
-        <v>10.5854444503784</v>
+        <v>10.5854473114014</v>
       </c>
       <c r="H1150" t="n">
         <v>19570</v>
@@ -33777,7 +33777,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1152" t="n">
-        <v>10.8868112564087</v>
+        <v>10.8868103027344</v>
       </c>
       <c r="H1152" t="n">
         <v>30370</v>
@@ -33835,7 +33835,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1154" t="n">
-        <v>11.1316690444946</v>
+        <v>11.1316699981689</v>
       </c>
       <c r="H1154" t="n">
         <v>22117</v>
@@ -33864,7 +33864,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.2635173797607</v>
+        <v>11.2635164260864</v>
       </c>
       <c r="H1155" t="n">
         <v>19863</v>
@@ -33893,7 +33893,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1156" t="n">
-        <v>11.207010269165</v>
+        <v>11.2070112228394</v>
       </c>
       <c r="H1156" t="n">
         <v>26448</v>
@@ -33922,7 +33922,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1157" t="n">
-        <v>10.9998235702515</v>
+        <v>10.9998226165771</v>
       </c>
       <c r="H1157" t="n">
         <v>13154</v>
@@ -33951,7 +33951,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1158" t="n">
-        <v>11.1505060195923</v>
+        <v>11.150505065918</v>
       </c>
       <c r="H1158" t="n">
         <v>20877</v>
@@ -33980,7 +33980,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1159" t="n">
-        <v>10.9056463241577</v>
+        <v>10.9056453704834</v>
       </c>
       <c r="H1159" t="n">
         <v>13158</v>
@@ -34067,7 +34067,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1162" t="n">
-        <v>10.5289392471313</v>
+        <v>10.5289402008057</v>
       </c>
       <c r="H1162" t="n">
         <v>22805</v>
@@ -34096,7 +34096,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1163" t="n">
-        <v>10.3029165267944</v>
+        <v>10.3029174804688</v>
       </c>
       <c r="H1163" t="n">
         <v>22454</v>
@@ -34125,7 +34125,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1164" t="n">
-        <v>10.3970918655396</v>
+        <v>10.3970928192139</v>
       </c>
       <c r="H1164" t="n">
         <v>28392</v>
@@ -34154,7 +34154,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1165" t="n">
-        <v>10.5477752685547</v>
+        <v>10.5477743148804</v>
       </c>
       <c r="H1165" t="n">
         <v>20206</v>
@@ -34183,7 +34183,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1166" t="n">
-        <v>10.7172927856445</v>
+        <v>10.7172918319702</v>
       </c>
       <c r="H1166" t="n">
         <v>14758</v>
@@ -34212,7 +34212,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G1167" t="n">
-        <v>10.8868112564087</v>
+        <v>10.8868103027344</v>
       </c>
       <c r="H1167" t="n">
         <v>15874</v>
@@ -34270,7 +34270,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1169" t="n">
-        <v>10.6796236038208</v>
+        <v>10.6796226501465</v>
       </c>
       <c r="H1169" t="n">
         <v>11931</v>
@@ -34299,7 +34299,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G1170" t="n">
-        <v>10.9998235702515</v>
+        <v>10.9998226165771</v>
       </c>
       <c r="H1170" t="n">
         <v>27415</v>
@@ -34357,7 +34357,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1172" t="n">
-        <v>11.5648822784424</v>
+        <v>11.5648832321167</v>
       </c>
       <c r="H1172" t="n">
         <v>18291</v>
@@ -34386,7 +34386,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>11.3953647613525</v>
+        <v>11.3953657150269</v>
       </c>
       <c r="H1173" t="n">
         <v>20817</v>
@@ -34415,7 +34415,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1174" t="n">
-        <v>11.3388576507568</v>
+        <v>11.3388586044312</v>
       </c>
       <c r="H1174" t="n">
         <v>7401</v>
@@ -34473,7 +34473,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1176" t="n">
-        <v>11.3576955795288</v>
+        <v>11.3576936721802</v>
       </c>
       <c r="H1176" t="n">
         <v>33595</v>
@@ -34560,7 +34560,7 @@
         <v>12.5</v>
       </c>
       <c r="G1179" t="n">
-        <v>11.7720718383789</v>
+        <v>11.7720708847046</v>
       </c>
       <c r="H1179" t="n">
         <v>25777</v>
@@ -34589,7 +34589,7 @@
         <v>12.5</v>
       </c>
       <c r="G1180" t="n">
-        <v>11.7720718383789</v>
+        <v>11.7720708847046</v>
       </c>
       <c r="H1180" t="n">
         <v>36341</v>
@@ -34618,7 +34618,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1181" t="n">
-        <v>11.546046257019</v>
+        <v>11.5460472106934</v>
       </c>
       <c r="H1181" t="n">
         <v>33161</v>
@@ -34734,7 +34734,7 @@
         <v>12.5</v>
       </c>
       <c r="G1185" t="n">
-        <v>11.7720718383789</v>
+        <v>11.7720708847046</v>
       </c>
       <c r="H1185" t="n">
         <v>17102</v>
@@ -34937,7 +34937,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1192" t="n">
-        <v>12.0546007156372</v>
+        <v>12.0545997619629</v>
       </c>
       <c r="H1192" t="n">
         <v>37163</v>
@@ -34995,7 +34995,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1194" t="n">
-        <v>11.8850841522217</v>
+        <v>11.885082244873</v>
       </c>
       <c r="H1194" t="n">
         <v>20939</v>
@@ -35024,7 +35024,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1195" t="n">
-        <v>11.9039182662964</v>
+        <v>11.9039192199707</v>
       </c>
       <c r="H1195" t="n">
         <v>21760</v>
@@ -35053,7 +35053,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1196" t="n">
-        <v>11.7344007492065</v>
+        <v>11.7343997955322</v>
       </c>
       <c r="H1196" t="n">
         <v>6951</v>
@@ -35111,7 +35111,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>11.6778926849365</v>
+        <v>11.6778936386108</v>
       </c>
       <c r="H1198" t="n">
         <v>17452</v>
@@ -35169,7 +35169,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1200" t="n">
-        <v>11.1316690444946</v>
+        <v>11.1316699981689</v>
       </c>
       <c r="H1200" t="n">
         <v>13334</v>
@@ -35198,7 +35198,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1201" t="n">
-        <v>11.1693410873413</v>
+        <v>11.169340133667</v>
       </c>
       <c r="H1201" t="n">
         <v>25594</v>
@@ -35227,7 +35227,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1202" t="n">
-        <v>11.546046257019</v>
+        <v>11.5460472106934</v>
       </c>
       <c r="H1202" t="n">
         <v>19283</v>
@@ -35285,7 +35285,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1204" t="n">
-        <v>12.5631551742554</v>
+        <v>12.5631532669067</v>
       </c>
       <c r="H1204" t="n">
         <v>679077</v>
@@ -35314,7 +35314,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1205" t="n">
-        <v>13.5614242553711</v>
+        <v>13.5614261627197</v>
       </c>
       <c r="H1205" t="n">
         <v>353033</v>
@@ -35372,7 +35372,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G1207" t="n">
-        <v>13.7686128616333</v>
+        <v>13.7686138153076</v>
       </c>
       <c r="H1207" t="n">
         <v>124694</v>
@@ -35459,7 +35459,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1210" t="n">
-        <v>13.3354015350342</v>
+        <v>13.3354005813599</v>
       </c>
       <c r="H1210" t="n">
         <v>72649</v>
@@ -35488,7 +35488,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1211" t="n">
-        <v>13.3730726242065</v>
+        <v>13.3730716705322</v>
       </c>
       <c r="H1211" t="n">
         <v>103432</v>
@@ -35517,7 +35517,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1212" t="n">
-        <v>13.0152006149292</v>
+        <v>13.0152015686035</v>
       </c>
       <c r="H1212" t="n">
         <v>79712</v>
@@ -35546,7 +35546,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1213" t="n">
-        <v>13.2412261962891</v>
+        <v>13.2412242889404</v>
       </c>
       <c r="H1213" t="n">
         <v>127327</v>
@@ -35575,7 +35575,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1214" t="n">
-        <v>13.2412261962891</v>
+        <v>13.2412242889404</v>
       </c>
       <c r="H1214" t="n">
         <v>120947</v>
@@ -35604,7 +35604,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1215" t="n">
-        <v>14.0323066711426</v>
+        <v>14.0323076248169</v>
       </c>
       <c r="H1215" t="n">
         <v>202425</v>
@@ -35720,7 +35720,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G1219" t="n">
-        <v>12.9210252761841</v>
+        <v>12.9210243225098</v>
       </c>
       <c r="H1219" t="n">
         <v>126017</v>
@@ -35749,7 +35749,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>12.9963665008545</v>
+        <v>12.9963655471802</v>
       </c>
       <c r="H1220" t="n">
         <v>316579</v>
@@ -35952,7 +35952,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1227" t="n">
-        <v>11.9415884017944</v>
+        <v>11.9415893554688</v>
       </c>
       <c r="H1227" t="n">
         <v>174326</v>
@@ -35981,7 +35981,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1228" t="n">
-        <v>11.6778926849365</v>
+        <v>11.6778936386108</v>
       </c>
       <c r="H1228" t="n">
         <v>327627</v>
@@ -36155,7 +36155,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1234" t="n">
-        <v>12.0546007156372</v>
+        <v>12.0545997619629</v>
       </c>
       <c r="H1234" t="n">
         <v>51769</v>
@@ -36213,7 +36213,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1236" t="n">
-        <v>12.7703428268433</v>
+        <v>12.7703418731689</v>
       </c>
       <c r="H1236" t="n">
         <v>72300</v>
@@ -36242,7 +36242,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1237" t="n">
-        <v>12.808012008667</v>
+        <v>12.8080139160156</v>
       </c>
       <c r="H1237" t="n">
         <v>58147</v>
@@ -36329,7 +36329,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1240" t="n">
-        <v>13.2223892211914</v>
+        <v>13.2223901748657</v>
       </c>
       <c r="H1240" t="n">
         <v>81081</v>
@@ -36387,7 +36387,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1242" t="n">
-        <v>13.4672479629517</v>
+        <v>13.467248916626</v>
       </c>
       <c r="H1242" t="n">
         <v>41536</v>
@@ -36416,7 +36416,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G1243" t="n">
-        <v>13.3354015350342</v>
+        <v>13.3354005813599</v>
       </c>
       <c r="H1243" t="n">
         <v>72531</v>
@@ -36503,7 +36503,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1246" t="n">
-        <v>13.5450410842896</v>
+        <v>13.5450420379639</v>
       </c>
       <c r="H1246" t="n">
         <v>58153</v>
@@ -36532,7 +36532,7 @@
         <v>14</v>
       </c>
       <c r="G1247" t="n">
-        <v>13.3167552947998</v>
+        <v>13.3167543411255</v>
       </c>
       <c r="H1247" t="n">
         <v>136688</v>
@@ -36561,7 +36561,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G1248" t="n">
-        <v>13.3548021316528</v>
+        <v>13.3548040390015</v>
       </c>
       <c r="H1248" t="n">
         <v>54674</v>
@@ -36590,7 +36590,7 @@
         <v>14</v>
       </c>
       <c r="G1249" t="n">
-        <v>13.3167552947998</v>
+        <v>13.3167543411255</v>
       </c>
       <c r="H1249" t="n">
         <v>29135</v>
@@ -36735,7 +36735,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1254" t="n">
-        <v>13.6591854095459</v>
+        <v>13.6591844558716</v>
       </c>
       <c r="H1254" t="n">
         <v>63791</v>
@@ -36822,7 +36822,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1257" t="n">
-        <v>14.1157608032227</v>
+        <v>14.1157598495483</v>
       </c>
       <c r="H1257" t="n">
         <v>49558</v>
@@ -36851,7 +36851,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1258" t="n">
-        <v>13.8874731063843</v>
+        <v>13.8874740600586</v>
       </c>
       <c r="H1258" t="n">
         <v>40359</v>
@@ -36880,7 +36880,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1259" t="n">
-        <v>13.6021127700806</v>
+        <v>13.6021137237549</v>
       </c>
       <c r="H1259" t="n">
         <v>39144</v>
@@ -36909,7 +36909,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1260" t="n">
-        <v>13.3738279342651</v>
+        <v>13.3738260269165</v>
       </c>
       <c r="H1260" t="n">
         <v>24526</v>
@@ -36967,7 +36967,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1262" t="n">
-        <v>13.6782093048096</v>
+        <v>13.6782083511353</v>
       </c>
       <c r="H1262" t="n">
         <v>60708</v>
@@ -37083,7 +37083,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1266" t="n">
-        <v>13.3738279342651</v>
+        <v>13.3738260269165</v>
       </c>
       <c r="H1266" t="n">
         <v>37045</v>
@@ -37112,7 +37112,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1267" t="n">
-        <v>13.6021127700806</v>
+        <v>13.6021137237549</v>
       </c>
       <c r="H1267" t="n">
         <v>48312</v>
@@ -37141,7 +37141,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1268" t="n">
-        <v>13.6972322463989</v>
+        <v>13.6972332000732</v>
       </c>
       <c r="H1268" t="n">
         <v>31000</v>
@@ -37170,7 +37170,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G1269" t="n">
-        <v>13.6211366653442</v>
+        <v>13.6211376190186</v>
       </c>
       <c r="H1269" t="n">
         <v>34160</v>
@@ -37199,7 +37199,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1270" t="n">
-        <v>13.6782093048096</v>
+        <v>13.6782083511353</v>
       </c>
       <c r="H1270" t="n">
         <v>16047</v>
@@ -37286,7 +37286,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1273" t="n">
-        <v>14.2489280700684</v>
+        <v>14.248927116394</v>
       </c>
       <c r="H1273" t="n">
         <v>56336</v>
@@ -37373,7 +37373,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1276" t="n">
-        <v>14.8957414627075</v>
+        <v>14.8957405090332</v>
       </c>
       <c r="H1276" t="n">
         <v>85533</v>
@@ -37402,7 +37402,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1277" t="n">
-        <v>14.9337902069092</v>
+        <v>14.9337892532349</v>
       </c>
       <c r="H1277" t="n">
         <v>79265</v>
@@ -37431,7 +37431,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1278" t="n">
-        <v>16.3796081542969</v>
+        <v>16.3796062469482</v>
       </c>
       <c r="H1278" t="n">
         <v>384544</v>
@@ -37460,7 +37460,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1279" t="n">
-        <v>16.2274169921875</v>
+        <v>16.2274150848389</v>
       </c>
       <c r="H1279" t="n">
         <v>185202</v>
@@ -37547,7 +37547,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1282" t="n">
-        <v>15.7137727737427</v>
+        <v>15.7137699127197</v>
       </c>
       <c r="H1282" t="n">
         <v>43067</v>
@@ -37576,7 +37576,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1283" t="n">
-        <v>15.8469362258911</v>
+        <v>15.8469400405884</v>
       </c>
       <c r="H1283" t="n">
         <v>31129</v>
@@ -37605,7 +37605,7 @@
         <v>16.5</v>
       </c>
       <c r="G1284" t="n">
-        <v>15.6947479248047</v>
+        <v>15.6947460174561</v>
       </c>
       <c r="H1284" t="n">
         <v>56150</v>
@@ -37692,7 +37692,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1287" t="n">
-        <v>15.6376752853394</v>
+        <v>15.6376762390137</v>
       </c>
       <c r="H1287" t="n">
         <v>42862</v>
@@ -37808,7 +37808,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1291" t="n">
-        <v>15.6186504364014</v>
+        <v>15.6186513900757</v>
       </c>
       <c r="H1291" t="n">
         <v>40152</v>
@@ -37837,7 +37837,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1292" t="n">
-        <v>15.7518177032471</v>
+        <v>15.7518167495728</v>
       </c>
       <c r="H1292" t="n">
         <v>30840</v>
@@ -37866,7 +37866,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1293" t="n">
-        <v>16.1513195037842</v>
+        <v>16.1513214111328</v>
       </c>
       <c r="H1293" t="n">
         <v>58673</v>
@@ -37924,7 +37924,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1295" t="n">
-        <v>16.6649703979492</v>
+        <v>16.664966583252</v>
       </c>
       <c r="H1295" t="n">
         <v>81726</v>
@@ -37953,7 +37953,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1296" t="n">
-        <v>16.5698471069336</v>
+        <v>16.5698490142822</v>
       </c>
       <c r="H1296" t="n">
         <v>52211</v>
@@ -38040,7 +38040,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1299" t="n">
-        <v>16.5888710021973</v>
+        <v>16.5888729095459</v>
       </c>
       <c r="H1299" t="n">
         <v>87784</v>
@@ -38127,7 +38127,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1302" t="n">
-        <v>17.08349609375</v>
+        <v>17.0834922790527</v>
       </c>
       <c r="H1302" t="n">
         <v>51459</v>
@@ -38185,7 +38185,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1304" t="n">
-        <v>16.3415622711182</v>
+        <v>16.3415603637695</v>
       </c>
       <c r="H1304" t="n">
         <v>47971</v>
@@ -38214,7 +38214,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1305" t="n">
-        <v>16.3225383758545</v>
+        <v>16.3225364685059</v>
       </c>
       <c r="H1305" t="n">
         <v>83647</v>
@@ -38330,7 +38330,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1309" t="n">
-        <v>16.5508232116699</v>
+        <v>16.5508213043213</v>
       </c>
       <c r="H1309" t="n">
         <v>49669</v>
@@ -38359,7 +38359,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1310" t="n">
-        <v>16.5698471069336</v>
+        <v>16.5698490142822</v>
       </c>
       <c r="H1310" t="n">
         <v>92845</v>
@@ -38388,7 +38388,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1311" t="n">
-        <v>16.5698471069336</v>
+        <v>16.5698490142822</v>
       </c>
       <c r="H1311" t="n">
         <v>90055</v>
@@ -38417,7 +38417,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1312" t="n">
-        <v>16.836181640625</v>
+        <v>16.8361835479736</v>
       </c>
       <c r="H1312" t="n">
         <v>29348</v>
@@ -38504,7 +38504,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1315" t="n">
-        <v>16.7410621643066</v>
+        <v>16.7410640716553</v>
       </c>
       <c r="H1315" t="n">
         <v>102800</v>
@@ -38707,7 +38707,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>20.1653709411621</v>
+        <v>20.1653728485107</v>
       </c>
       <c r="H1322" t="n">
         <v>187102</v>
@@ -38765,7 +38765,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1324" t="n">
-        <v>20.5934104919434</v>
+        <v>20.5934085845947</v>
       </c>
       <c r="H1324" t="n">
         <v>163874</v>
@@ -38794,7 +38794,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1325" t="n">
-        <v>20.3556118011475</v>
+        <v>20.3556098937988</v>
       </c>
       <c r="H1325" t="n">
         <v>77087</v>
@@ -38852,7 +38852,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1327" t="n">
-        <v>19.8324527740479</v>
+        <v>19.8324508666992</v>
       </c>
       <c r="H1327" t="n">
         <v>67445</v>
@@ -38881,7 +38881,7 @@
         <v>20.75</v>
       </c>
       <c r="G1328" t="n">
-        <v>19.7373332977295</v>
+        <v>19.7373352050781</v>
       </c>
       <c r="H1328" t="n">
         <v>37827</v>
@@ -38910,7 +38910,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1329" t="n">
-        <v>19.8800106048584</v>
+        <v>19.8800144195557</v>
       </c>
       <c r="H1329" t="n">
         <v>37861</v>
@@ -38997,7 +38997,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1332" t="n">
-        <v>20.2604885101318</v>
+        <v>20.2604923248291</v>
       </c>
       <c r="H1332" t="n">
         <v>45869</v>
@@ -39084,7 +39084,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1335" t="n">
-        <v>20.8312072753906</v>
+        <v>20.8312091827393</v>
       </c>
       <c r="H1335" t="n">
         <v>75131</v>
@@ -39171,7 +39171,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1338" t="n">
-        <v>19.9275722503662</v>
+        <v>19.9275741577148</v>
       </c>
       <c r="H1338" t="n">
         <v>25422</v>
@@ -39229,7 +39229,7 @@
         <v>20.75</v>
       </c>
       <c r="G1340" t="n">
-        <v>19.7373332977295</v>
+        <v>19.7373352050781</v>
       </c>
       <c r="H1340" t="n">
         <v>39655</v>
@@ -39258,7 +39258,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1341" t="n">
-        <v>19.8324527740479</v>
+        <v>19.8324508666992</v>
       </c>
       <c r="H1341" t="n">
         <v>38357</v>
@@ -39316,7 +39316,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1343" t="n">
-        <v>20.7836494445801</v>
+        <v>20.7836475372314</v>
       </c>
       <c r="H1343" t="n">
         <v>100221</v>
@@ -39345,7 +39345,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1344" t="n">
-        <v>20.3556118011475</v>
+        <v>20.3556098937988</v>
       </c>
       <c r="H1344" t="n">
         <v>43324</v>
@@ -39403,7 +39403,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1346" t="n">
-        <v>19.8324527740479</v>
+        <v>19.8324508666992</v>
       </c>
       <c r="H1346" t="n">
         <v>47741</v>
@@ -39432,7 +39432,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1347" t="n">
-        <v>19.8800106048584</v>
+        <v>19.8800144195557</v>
       </c>
       <c r="H1347" t="n">
         <v>37284</v>
@@ -39606,7 +39606,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1353" t="n">
-        <v>19.4044151306152</v>
+        <v>19.4044132232666</v>
       </c>
       <c r="H1353" t="n">
         <v>47807</v>
@@ -39635,7 +39635,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1354" t="n">
-        <v>19.6897754669189</v>
+        <v>19.6897735595703</v>
       </c>
       <c r="H1354" t="n">
         <v>62104</v>
@@ -39664,7 +39664,7 @@
         <v>20</v>
       </c>
       <c r="G1355" t="n">
-        <v>19.0239353179932</v>
+        <v>19.0239334106445</v>
       </c>
       <c r="H1355" t="n">
         <v>78898</v>
@@ -39722,7 +39722,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1357" t="n">
-        <v>19.6897754669189</v>
+        <v>19.6897735595703</v>
       </c>
       <c r="H1357" t="n">
         <v>51491</v>
@@ -39751,7 +39751,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1358" t="n">
-        <v>19.6897754669189</v>
+        <v>19.6897735595703</v>
       </c>
       <c r="H1358" t="n">
         <v>32149</v>
@@ -39780,7 +39780,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1359" t="n">
-        <v>20.1178092956543</v>
+        <v>20.1178112030029</v>
       </c>
       <c r="H1359" t="n">
         <v>107381</v>
@@ -39809,7 +39809,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1360" t="n">
-        <v>20.3556118011475</v>
+        <v>20.3556098937988</v>
       </c>
       <c r="H1360" t="n">
         <v>60933</v>
@@ -39925,7 +39925,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1364" t="n">
-        <v>20.1178092956543</v>
+        <v>20.1178112030029</v>
       </c>
       <c r="H1364" t="n">
         <v>24564</v>
@@ -39954,7 +39954,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1365" t="n">
-        <v>20.1178092956543</v>
+        <v>20.1178112030029</v>
       </c>
       <c r="H1365" t="n">
         <v>40916</v>
@@ -40012,7 +40012,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1367" t="n">
-        <v>19.6897754669189</v>
+        <v>19.6897735595703</v>
       </c>
       <c r="H1367" t="n">
         <v>26808</v>
@@ -40128,7 +40128,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1371" t="n">
-        <v>20.3556118011475</v>
+        <v>20.3556098937988</v>
       </c>
       <c r="H1371" t="n">
         <v>30198</v>
@@ -40215,7 +40215,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1374" t="n">
-        <v>20.9738883972168</v>
+        <v>20.9738864898682</v>
       </c>
       <c r="H1374" t="n">
         <v>46334</v>
@@ -40360,7 +40360,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1379" t="n">
-        <v>21.5921669006348</v>
+        <v>21.5921649932861</v>
       </c>
       <c r="H1379" t="n">
         <v>26702</v>
@@ -40418,7 +40418,7 @@
         <v>22.5</v>
       </c>
       <c r="G1381" t="n">
-        <v>21.4019260406494</v>
+        <v>21.4019241333008</v>
       </c>
       <c r="H1381" t="n">
         <v>80513</v>
@@ -40476,7 +40476,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1383" t="n">
-        <v>21.7348480224609</v>
+        <v>21.7348442077637</v>
       </c>
       <c r="H1383" t="n">
         <v>26308</v>
@@ -40505,7 +40505,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1384" t="n">
-        <v>21.7348480224609</v>
+        <v>21.7348442077637</v>
       </c>
       <c r="H1384" t="n">
         <v>20189</v>
@@ -40534,7 +40534,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1385" t="n">
-        <v>21.8299655914307</v>
+        <v>21.8299674987793</v>
       </c>
       <c r="H1385" t="n">
         <v>24532</v>
@@ -40592,7 +40592,7 @@
         <v>22.5</v>
       </c>
       <c r="G1387" t="n">
-        <v>21.4019260406494</v>
+        <v>21.4019241333008</v>
       </c>
       <c r="H1387" t="n">
         <v>149276</v>
@@ -40621,7 +40621,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1388" t="n">
-        <v>20.7836494445801</v>
+        <v>20.7836475372314</v>
       </c>
       <c r="H1388" t="n">
         <v>78380</v>
@@ -40650,7 +40650,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G1389" t="n">
-        <v>20.7836494445801</v>
+        <v>20.7836475372314</v>
       </c>
       <c r="H1389" t="n">
         <v>50208</v>
@@ -40679,7 +40679,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1390" t="n">
-        <v>21.0690059661865</v>
+        <v>21.0690078735352</v>
       </c>
       <c r="H1390" t="n">
         <v>55459</v>
@@ -40708,7 +40708,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G1391" t="n">
-        <v>20.9738883972168</v>
+        <v>20.9738864898682</v>
       </c>
       <c r="H1391" t="n">
         <v>41158</v>
@@ -40737,7 +40737,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1392" t="n">
-        <v>21.2116870880127</v>
+        <v>21.2116889953613</v>
       </c>
       <c r="H1392" t="n">
         <v>40643</v>
@@ -40795,7 +40795,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>21.2116870880127</v>
+        <v>21.2116889953613</v>
       </c>
       <c r="H1394" t="n">
         <v>25574</v>
@@ -40824,7 +40824,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1395" t="n">
-        <v>21.3068065643311</v>
+        <v>21.3068046569824</v>
       </c>
       <c r="H1395" t="n">
         <v>18384</v>
@@ -40911,7 +40911,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1398" t="n">
-        <v>22.6384811401367</v>
+        <v>22.6384830474854</v>
       </c>
       <c r="H1398" t="n">
         <v>114951</v>
@@ -41027,7 +41027,7 @@
         <v>22.5</v>
       </c>
       <c r="G1402" t="n">
-        <v>21.4019260406494</v>
+        <v>21.4019241333008</v>
       </c>
       <c r="H1402" t="n">
         <v>71563</v>
@@ -41056,7 +41056,7 @@
         <v>23</v>
       </c>
       <c r="G1403" t="n">
-        <v>21.8775253295898</v>
+        <v>21.8775272369385</v>
       </c>
       <c r="H1403" t="n">
         <v>38196</v>
@@ -41085,7 +41085,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1404" t="n">
-        <v>21.8299655914307</v>
+        <v>21.8299674987793</v>
       </c>
       <c r="H1404" t="n">
         <v>22381</v>
@@ -41114,7 +41114,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1405" t="n">
-        <v>21.7348480224609</v>
+        <v>21.7348442077637</v>
       </c>
       <c r="H1405" t="n">
         <v>10809</v>
@@ -41143,7 +41143,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1406" t="n">
-        <v>21.497049331665</v>
+        <v>21.4970474243164</v>
       </c>
       <c r="H1406" t="n">
         <v>23953</v>
@@ -41172,7 +41172,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1407" t="n">
-        <v>21.497049331665</v>
+        <v>21.4970474243164</v>
       </c>
       <c r="H1407" t="n">
         <v>36023</v>
@@ -41201,7 +41201,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1408" t="n">
-        <v>21.2592506408691</v>
+        <v>21.2592487335205</v>
       </c>
       <c r="H1408" t="n">
         <v>31281</v>
@@ -41230,7 +41230,7 @@
         <v>21.75</v>
       </c>
       <c r="G1409" t="n">
-        <v>20.6885299682617</v>
+        <v>20.6885318756104</v>
       </c>
       <c r="H1409" t="n">
         <v>68569</v>
@@ -41288,7 +41288,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1411" t="n">
-        <v>21.2592506408691</v>
+        <v>21.2592487335205</v>
       </c>
       <c r="H1411" t="n">
         <v>49262</v>
@@ -41317,7 +41317,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1412" t="n">
-        <v>21.2592506408691</v>
+        <v>21.2592487335205</v>
       </c>
       <c r="H1412" t="n">
         <v>30319</v>
@@ -41375,7 +41375,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1414" t="n">
-        <v>21.7824077606201</v>
+        <v>21.7824039459229</v>
       </c>
       <c r="H1414" t="n">
         <v>31750</v>
@@ -41404,7 +41404,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1415" t="n">
-        <v>21.7824077606201</v>
+        <v>21.7824039459229</v>
       </c>
       <c r="H1415" t="n">
         <v>15907</v>
@@ -41433,7 +41433,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1416" t="n">
-        <v>22.6384811401367</v>
+        <v>22.6384830474854</v>
       </c>
       <c r="H1416" t="n">
         <v>84686</v>
@@ -41462,7 +41462,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1417" t="n">
-        <v>24.3506374359131</v>
+        <v>24.3506355285645</v>
       </c>
       <c r="H1417" t="n">
         <v>114064</v>
@@ -41520,7 +41520,7 @@
         <v>24.5</v>
       </c>
       <c r="G1419" t="n">
-        <v>23.3043231964111</v>
+        <v>23.3043193817139</v>
       </c>
       <c r="H1419" t="n">
         <v>45529</v>
@@ -41549,7 +41549,7 @@
         <v>24.5</v>
       </c>
       <c r="G1420" t="n">
-        <v>23.3043231964111</v>
+        <v>23.3043193817139</v>
       </c>
       <c r="H1420" t="n">
         <v>34914</v>
@@ -41636,7 +41636,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1423" t="n">
-        <v>23.0189628601074</v>
+        <v>23.0189647674561</v>
       </c>
       <c r="H1423" t="n">
         <v>27136</v>
@@ -41665,7 +41665,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>23.0189628601074</v>
+        <v>23.0189647674561</v>
       </c>
       <c r="H1424" t="n">
         <v>16295</v>
@@ -41694,7 +41694,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1425" t="n">
-        <v>23.1140785217285</v>
+        <v>23.1140804290771</v>
       </c>
       <c r="H1425" t="n">
         <v>13483</v>
@@ -42042,7 +42042,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>23.6372413635254</v>
+        <v>23.6372375488281</v>
       </c>
       <c r="H1437" t="n">
         <v>45021</v>
@@ -42100,7 +42100,7 @@
         <v>24.75</v>
       </c>
       <c r="G1439" t="n">
-        <v>23.5421199798584</v>
+        <v>23.542121887207</v>
       </c>
       <c r="H1439" t="n">
         <v>15683</v>
@@ -42303,7 +42303,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1446" t="n">
-        <v>22.6384811401367</v>
+        <v>22.6384830474854</v>
       </c>
       <c r="H1446" t="n">
         <v>39831</v>
@@ -42419,7 +42419,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1450" t="n">
-        <v>23.0189628601074</v>
+        <v>23.0189647674561</v>
       </c>
       <c r="H1450" t="n">
         <v>57630</v>
@@ -42448,7 +42448,7 @@
         <v>23.8500003814697</v>
       </c>
       <c r="G1451" t="n">
-        <v>22.6860446929932</v>
+        <v>22.6860427856445</v>
       </c>
       <c r="H1451" t="n">
         <v>17980</v>
@@ -42535,7 +42535,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>21.5921669006348</v>
+        <v>21.5921649932861</v>
       </c>
       <c r="H1454" t="n">
         <v>22726</v>
@@ -42593,7 +42593,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1456" t="n">
-        <v>22.0677642822266</v>
+        <v>22.0677661895752</v>
       </c>
       <c r="H1456" t="n">
         <v>22236</v>
@@ -42651,7 +42651,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G1458" t="n">
-        <v>22.0202045440674</v>
+        <v>22.020206451416</v>
       </c>
       <c r="H1458" t="n">
         <v>20644</v>
@@ -42738,7 +42738,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>24.3506374359131</v>
+        <v>24.3506355285645</v>
       </c>
       <c r="H1461" t="n">
         <v>76766</v>
@@ -42767,7 +42767,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G1462" t="n">
-        <v>23.7323608398438</v>
+        <v>23.7323589324951</v>
       </c>
       <c r="H1462" t="n">
         <v>57211</v>
@@ -42825,7 +42825,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1464" t="n">
-        <v>23.875036239624</v>
+        <v>23.8750381469727</v>
       </c>
       <c r="H1464" t="n">
         <v>50500</v>
@@ -42854,7 +42854,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1465" t="n">
-        <v>24.3506374359131</v>
+        <v>24.3506355285645</v>
       </c>
       <c r="H1465" t="n">
         <v>27274</v>
@@ -42883,7 +42883,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1466" t="n">
-        <v>23.6848011016846</v>
+        <v>23.6847991943359</v>
       </c>
       <c r="H1466" t="n">
         <v>30449</v>
@@ -42912,7 +42912,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1467" t="n">
-        <v>23.6848011016846</v>
+        <v>23.6847991943359</v>
       </c>
       <c r="H1467" t="n">
         <v>16035</v>
@@ -43028,7 +43028,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>25.9676685333252</v>
+        <v>25.9676704406738</v>
       </c>
       <c r="H1471" t="n">
         <v>64417</v>
@@ -43144,7 +43144,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G1475" t="n">
-        <v>25.6347541809082</v>
+        <v>25.6347522735596</v>
       </c>
       <c r="H1475" t="n">
         <v>37635</v>
@@ -43231,7 +43231,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>26.3005886077881</v>
+        <v>26.3005905151367</v>
       </c>
       <c r="H1478" t="n">
         <v>120375</v>
@@ -43289,7 +43289,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1480" t="n">
-        <v>27.2993488311768</v>
+        <v>27.2993469238281</v>
       </c>
       <c r="H1480" t="n">
         <v>76138</v>
@@ -43318,7 +43318,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1481" t="n">
-        <v>27.2042255401611</v>
+        <v>27.2042274475098</v>
       </c>
       <c r="H1481" t="n">
         <v>60662</v>
@@ -43347,7 +43347,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>27.156665802002</v>
+        <v>27.1566677093506</v>
       </c>
       <c r="H1482" t="n">
         <v>48644</v>
@@ -43376,7 +43376,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1483" t="n">
-        <v>27.6798267364502</v>
+        <v>27.6798248291016</v>
       </c>
       <c r="H1483" t="n">
         <v>47611</v>
@@ -43434,7 +43434,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1485" t="n">
-        <v>27.7749462127686</v>
+        <v>27.7749481201172</v>
       </c>
       <c r="H1485" t="n">
         <v>107361</v>
@@ -43463,7 +43463,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G1486" t="n">
-        <v>28.1078624725342</v>
+        <v>28.1078662872314</v>
       </c>
       <c r="H1486" t="n">
         <v>49683</v>
@@ -43521,7 +43521,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1488" t="n">
-        <v>27.6798267364502</v>
+        <v>27.6798248291016</v>
       </c>
       <c r="H1488" t="n">
         <v>73233</v>
@@ -43608,7 +43608,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G1491" t="n">
-        <v>27.5371494293213</v>
+        <v>27.5371475219727</v>
       </c>
       <c r="H1491" t="n">
         <v>43894</v>
@@ -43637,7 +43637,7 @@
         <v>28.75</v>
       </c>
       <c r="G1492" t="n">
-        <v>27.3469066619873</v>
+        <v>27.3469085693359</v>
       </c>
       <c r="H1492" t="n">
         <v>58069</v>
@@ -43666,7 +43666,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G1493" t="n">
-        <v>27.0615482330322</v>
+        <v>27.0615501403809</v>
       </c>
       <c r="H1493" t="n">
         <v>27966</v>
@@ -43695,7 +43695,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G1494" t="n">
-        <v>26.7761898040771</v>
+        <v>26.7761878967285</v>
       </c>
       <c r="H1494" t="n">
         <v>34445</v>
@@ -43724,7 +43724,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G1495" t="n">
-        <v>26.9664287567139</v>
+        <v>26.9664306640625</v>
       </c>
       <c r="H1495" t="n">
         <v>32902</v>
@@ -43753,7 +43753,7 @@
         <v>28.25</v>
       </c>
       <c r="G1496" t="n">
-        <v>26.8713092803955</v>
+        <v>26.8713073730469</v>
       </c>
       <c r="H1496" t="n">
         <v>60459</v>
@@ -43811,7 +43811,7 @@
         <v>28.25</v>
       </c>
       <c r="G1498" t="n">
-        <v>26.8713092803955</v>
+        <v>26.8713073730469</v>
       </c>
       <c r="H1498" t="n">
         <v>65385</v>
@@ -80125,6 +80125,35 @@
         <v>89667</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>49.0800018310547</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>51.6500015258789</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>49.0800018310547</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>51.7000007629395</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>51.7000007629395</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>80585</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>
